--- a/stat/data.xlsx
+++ b/stat/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr-PC\Documents\Workspace\LLMHalluMiti\test\stat\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr-PC\Documents\Workspace\LLMHalluMiti\stat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB53D1D1-9FBB-450D-84BD-EA7024D1EAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB5BED9-3025-4034-8716-D4AD39290DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="14">
   <si>
     <t>gpt-4o</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -76,6 +76,10 @@
   </si>
   <si>
     <t>overcorrection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pass@6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -401,10 +405,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>2</v>
       </c>
@@ -420,13 +424,31 @@
       <c r="F1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -445,8 +467,23 @@
       <c r="F3">
         <v>1.5811999999999999</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H3">
+        <v>38</v>
+      </c>
+      <c r="I3">
+        <v>26.53</v>
+      </c>
+      <c r="J3">
+        <v>3.92</v>
+      </c>
+      <c r="K3">
+        <v>101.73</v>
+      </c>
+      <c r="L3">
+        <v>1.4113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -466,27 +503,27 @@
         <v>13.4636</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -505,8 +542,23 @@
       <c r="F9">
         <v>17.4329</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H9">
+        <v>43</v>
+      </c>
+      <c r="I9">
+        <v>20.41</v>
+      </c>
+      <c r="J9">
+        <v>7.84</v>
+      </c>
+      <c r="K9">
+        <v>2633.25</v>
+      </c>
+      <c r="L9">
+        <v>30.0015</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -526,12 +578,12 @@
         <v>155.00290000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -550,8 +602,23 @@
       <c r="F12">
         <v>34.570399999999999</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H12">
+        <v>38</v>
+      </c>
+      <c r="I12">
+        <v>30.61</v>
+      </c>
+      <c r="J12">
+        <v>7.84</v>
+      </c>
+      <c r="K12">
+        <v>4222.12</v>
+      </c>
+      <c r="L12">
+        <v>42.000700000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -571,12 +638,12 @@
         <v>78.007099999999994</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -595,8 +662,23 @@
       <c r="F15">
         <v>1.4267000000000001</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H15">
+        <v>16</v>
+      </c>
+      <c r="I15">
+        <v>69.39</v>
+      </c>
+      <c r="J15">
+        <v>1.96</v>
+      </c>
+      <c r="K15">
+        <v>197.15</v>
+      </c>
+      <c r="L15">
+        <v>1.8134999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -616,12 +698,12 @@
         <v>27.958100000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>0</v>
       </c>
@@ -640,8 +722,26 @@
       <c r="F18">
         <v>17.093699999999998</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H18">
+        <v>17</v>
+      </c>
+      <c r="I18">
+        <v>67.349999999999994</v>
+      </c>
+      <c r="J18">
+        <v>1.96</v>
+      </c>
+      <c r="K18">
+        <v>1763.87</v>
+      </c>
+      <c r="L18">
+        <v>11.2498</v>
+      </c>
+      <c r="M18">
+        <v>79.59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>1</v>
       </c>

--- a/stat/data.xlsx
+++ b/stat/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr-PC\Documents\Workspace\LLMHalluMiti\stat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB5BED9-3025-4034-8716-D4AD39290DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5792DB0F-F3E1-4DE2-AA40-E7BB37E5FE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="15">
   <si>
     <t>gpt-4o</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -80,6 +80,10 @@
   </si>
   <si>
     <t>pass@6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oa-vs</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -405,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
@@ -468,19 +472,19 @@
         <v>1.5811999999999999</v>
       </c>
       <c r="H3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I3">
-        <v>26.53</v>
+        <v>31.08</v>
       </c>
       <c r="J3">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="K3">
-        <v>101.73</v>
+        <v>106.37</v>
       </c>
       <c r="L3">
-        <v>1.4113</v>
+        <v>1.4337</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
@@ -663,19 +667,19 @@
         <v>1.4267000000000001</v>
       </c>
       <c r="H15">
-        <v>16</v>
+        <v>21.33</v>
       </c>
       <c r="I15">
-        <v>69.39</v>
+        <v>62.16</v>
       </c>
       <c r="J15">
-        <v>1.96</v>
+        <v>5.26</v>
       </c>
       <c r="K15">
-        <v>197.15</v>
+        <v>199.29</v>
       </c>
       <c r="L15">
-        <v>1.8134999999999999</v>
+        <v>1.7201</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
@@ -723,22 +727,22 @@
         <v>17.093699999999998</v>
       </c>
       <c r="H18">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I18">
-        <v>67.349999999999994</v>
+        <v>62.16</v>
       </c>
       <c r="J18">
-        <v>1.96</v>
+        <v>2.63</v>
       </c>
       <c r="K18">
-        <v>1763.87</v>
+        <v>1805.82</v>
       </c>
       <c r="L18">
-        <v>11.2498</v>
+        <v>11.7181</v>
       </c>
       <c r="M18">
-        <v>79.59</v>
+        <v>72.97</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
@@ -759,6 +763,36 @@
       </c>
       <c r="F19">
         <v>240.96270000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>19.329999999999998</v>
+      </c>
+      <c r="I21">
+        <v>65.33</v>
+      </c>
+      <c r="J21">
+        <v>4</v>
+      </c>
+      <c r="K21">
+        <v>596.13</v>
+      </c>
+      <c r="L21">
+        <v>4.4482999999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/stat/data.xlsx
+++ b/stat/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr-PC\Documents\Workspace\LLMHalluMiti\stat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5792DB0F-F3E1-4DE2-AA40-E7BB37E5FE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC3C6637-286D-433A-9D07-49AEE9F9E2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -547,19 +547,19 @@
         <v>17.4329</v>
       </c>
       <c r="H9">
-        <v>43</v>
+        <v>40.67</v>
       </c>
       <c r="I9">
-        <v>20.41</v>
+        <v>27.03</v>
       </c>
       <c r="J9">
-        <v>7.84</v>
+        <v>9.2100000000000009</v>
       </c>
       <c r="K9">
-        <v>2633.25</v>
+        <v>2293.4899999999998</v>
       </c>
       <c r="L9">
-        <v>30.0015</v>
+        <v>24.464099999999998</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
@@ -610,16 +610,16 @@
         <v>38</v>
       </c>
       <c r="I12">
-        <v>30.61</v>
+        <v>31.08</v>
       </c>
       <c r="J12">
-        <v>7.84</v>
+        <v>7.89</v>
       </c>
       <c r="K12">
-        <v>4222.12</v>
+        <v>3808.19</v>
       </c>
       <c r="L12">
-        <v>42.000700000000002</v>
+        <v>35.700099999999999</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
@@ -701,6 +701,21 @@
       <c r="F16">
         <v>27.958100000000002</v>
       </c>
+      <c r="H16">
+        <v>20</v>
+      </c>
+      <c r="I16">
+        <v>61.33</v>
+      </c>
+      <c r="J16">
+        <v>1.33</v>
+      </c>
+      <c r="K16">
+        <v>188.51</v>
+      </c>
+      <c r="L16">
+        <v>21.434799999999999</v>
+      </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
@@ -793,6 +808,21 @@
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>1</v>
+      </c>
+      <c r="H22">
+        <v>16</v>
+      </c>
+      <c r="I22">
+        <v>68</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>580.04999999999995</v>
+      </c>
+      <c r="L22">
+        <v>36.996099999999998</v>
       </c>
     </row>
   </sheetData>

--- a/stat/data.xlsx
+++ b/stat/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr-PC\Documents\Workspace\LLMHalluMiti\stat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC3C6637-286D-433A-9D07-49AEE9F9E2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CAA8110-920F-4A61-BC42-696760BF931F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -506,6 +506,21 @@
       <c r="F4">
         <v>13.4636</v>
       </c>
+      <c r="H4">
+        <v>39.33</v>
+      </c>
+      <c r="I4">
+        <v>24</v>
+      </c>
+      <c r="J4">
+        <v>2.67</v>
+      </c>
+      <c r="K4">
+        <v>87.03</v>
+      </c>
+      <c r="L4">
+        <v>12.4434</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -778,6 +793,24 @@
       </c>
       <c r="F19">
         <v>240.96270000000001</v>
+      </c>
+      <c r="H19">
+        <v>18</v>
+      </c>
+      <c r="I19">
+        <v>64</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>1775.89</v>
+      </c>
+      <c r="L19">
+        <v>187.8108</v>
+      </c>
+      <c r="M19">
+        <v>74.67</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">

--- a/stat/data.xlsx
+++ b/stat/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr-PC\Documents\Workspace\LLMHalluMiti\stat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CAA8110-920F-4A61-BC42-696760BF931F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03F9188-1F29-484C-8487-87320490562E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -596,6 +596,21 @@
       <c r="F10">
         <v>155.00290000000001</v>
       </c>
+      <c r="H10">
+        <v>32</v>
+      </c>
+      <c r="I10">
+        <v>45.33</v>
+      </c>
+      <c r="J10">
+        <v>9.33</v>
+      </c>
+      <c r="K10">
+        <v>6824.61</v>
+      </c>
+      <c r="L10">
+        <v>202.18029999999999</v>
+      </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">

--- a/stat/data.xlsx
+++ b/stat/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr-PC\Documents\Workspace\LLMHalluMiti\stat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03F9188-1F29-484C-8487-87320490562E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A75F67-67A2-4935-9D06-3E0E6C52E28B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/stat/data.xlsx
+++ b/stat/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr-PC\Documents\Workspace\LLMHalluMiti\stat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A75F67-67A2-4935-9D06-3E0E6C52E28B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4855A375-D10D-46FE-A2E3-DEB4C611DFBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -671,6 +671,21 @@
       <c r="F13">
         <v>78.007099999999994</v>
       </c>
+      <c r="H13">
+        <v>32.67</v>
+      </c>
+      <c r="I13">
+        <v>45.33</v>
+      </c>
+      <c r="J13">
+        <v>10.67</v>
+      </c>
+      <c r="K13">
+        <v>7828.29</v>
+      </c>
+      <c r="L13">
+        <v>142.8083</v>
+      </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">

--- a/stat/data.xlsx
+++ b/stat/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr-PC\Documents\Workspace\LLMHalluMiti\stat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB42173-75C0-4087-B277-881D7284AFC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D9F8DAF-9840-4FFE-9600-10488F037FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -155,17 +155,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -447,12 +443,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD37"/>
+  <dimension ref="A1:X37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
       <c r="C1" s="2" t="s">
         <v>16</v>
       </c>
@@ -483,585 +479,922 @@
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-      <c r="AA1" s="3"/>
-      <c r="AB1" s="3"/>
-      <c r="AC1" s="3"/>
-      <c r="AD1" s="3"/>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4" t="s">
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="R2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="T2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="U2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="V2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="W2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="2">
         <v>39.81</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="1">
         <v>22.95</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="1">
         <v>49.45</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="1">
         <v>4.7300000000000004</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="1">
         <v>100.61</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="1">
         <v>4.9604999999999997</v>
       </c>
-      <c r="I3" s="4"/>
+      <c r="I3" s="1"/>
       <c r="J3" s="2">
         <v>45.78</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="1">
         <v>24.6</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="1">
         <v>56.95</v>
       </c>
-      <c r="M3" s="4">
+      <c r="M3" s="1">
         <v>9.0299999999999994</v>
       </c>
-      <c r="N3" s="4"/>
+      <c r="N3" s="1"/>
       <c r="O3" s="2">
         <v>38.03</v>
       </c>
-      <c r="P3" s="4">
+      <c r="P3" s="1">
         <v>28.52</v>
       </c>
-      <c r="Q3" s="4">
+      <c r="Q3" s="1">
         <v>27.16</v>
       </c>
-      <c r="R3" s="4">
+      <c r="R3" s="1">
         <v>1.32</v>
       </c>
-      <c r="S3" s="4"/>
+      <c r="S3" s="1"/>
       <c r="T3" s="2">
         <v>30.33</v>
       </c>
-      <c r="U3" s="4">
+      <c r="U3" s="1">
         <v>11.28</v>
       </c>
-      <c r="V3" s="4">
+      <c r="V3" s="1">
         <v>68.599999999999994</v>
       </c>
-      <c r="W3" s="4">
+      <c r="W3" s="1">
         <v>2.52</v>
       </c>
-      <c r="X3" s="4"/>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="X3" s="1"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="4">
+      <c r="D4" s="1">
         <v>25.03</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="1">
         <v>55.23</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="1">
         <v>12</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="1">
         <v>2253.6799999999998</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="1">
         <v>22.125900000000001</v>
       </c>
-      <c r="I4" s="4"/>
+      <c r="I4" s="1"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="4">
+      <c r="K4" s="1">
         <v>23.38</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="1">
         <v>67.11</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="1">
         <v>15.35</v>
       </c>
-      <c r="N4" s="4"/>
+      <c r="N4" s="1"/>
       <c r="O4" s="2"/>
-      <c r="P4" s="4">
+      <c r="P4" s="1">
         <v>35.9</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="Q4" s="1">
         <v>25.43</v>
       </c>
-      <c r="R4" s="4">
+      <c r="R4" s="1">
         <v>12.17</v>
       </c>
-      <c r="S4" s="4"/>
+      <c r="S4" s="1"/>
       <c r="T4" s="2"/>
-      <c r="U4" s="4">
+      <c r="U4" s="1">
         <v>11.78</v>
       </c>
-      <c r="V4" s="4">
+      <c r="V4" s="1">
         <v>75.209999999999994</v>
       </c>
-      <c r="W4" s="4">
+      <c r="W4" s="1">
         <v>6.12</v>
       </c>
-      <c r="X4" s="4"/>
-    </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="X4" s="1"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="4">
+      <c r="D5" s="1">
         <v>25.58</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="1">
         <v>53.72</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="1">
         <v>11.91</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="1">
         <v>3623.59</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="1">
         <v>33.609499999999997</v>
       </c>
-      <c r="I5" s="4"/>
+      <c r="I5" s="1"/>
       <c r="J5" s="2"/>
-      <c r="K5" s="4">
+      <c r="K5" s="1">
         <v>22.4</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="1">
         <v>62.3</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="1">
         <v>9.48</v>
       </c>
-      <c r="N5" s="4"/>
+      <c r="N5" s="1"/>
       <c r="O5" s="2"/>
-      <c r="P5" s="4">
+      <c r="P5" s="1">
         <v>38.03</v>
       </c>
-      <c r="Q5" s="4">
+      <c r="Q5" s="1">
         <v>31.47</v>
       </c>
-      <c r="R5" s="4">
+      <c r="R5" s="1">
         <v>19.309999999999999</v>
       </c>
-      <c r="S5" s="4"/>
+      <c r="S5" s="1"/>
       <c r="T5" s="2"/>
-      <c r="U5" s="4">
+      <c r="U5" s="1">
         <v>13.03</v>
       </c>
-      <c r="V5" s="4">
+      <c r="V5" s="1">
         <v>70.25</v>
       </c>
-      <c r="W5" s="4">
+      <c r="W5" s="1">
         <v>5.76</v>
       </c>
-      <c r="X5" s="4"/>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="X5" s="1"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="4">
+      <c r="D6" s="1">
         <v>17.579999999999998</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="1">
         <v>65.150000000000006</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="1">
         <v>6.18</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="1">
         <v>207.21</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="1">
         <v>6.4598000000000004</v>
       </c>
-      <c r="I6" s="4"/>
+      <c r="I6" s="1"/>
       <c r="J6" s="2"/>
-      <c r="K6" s="4">
+      <c r="K6" s="1">
         <v>10.4</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="1">
         <v>85.56</v>
       </c>
-      <c r="M6" s="4">
+      <c r="M6" s="1">
         <v>7</v>
       </c>
-      <c r="N6" s="4"/>
+      <c r="N6" s="1"/>
       <c r="O6" s="2"/>
-      <c r="P6" s="4">
+      <c r="P6" s="1">
         <v>31.97</v>
       </c>
-      <c r="Q6" s="4">
+      <c r="Q6" s="1">
         <v>27.16</v>
       </c>
-      <c r="R6" s="4">
+      <c r="R6" s="1">
         <v>6.88</v>
       </c>
-      <c r="S6" s="4"/>
+      <c r="S6" s="1"/>
       <c r="T6" s="2"/>
-      <c r="U6" s="4">
+      <c r="U6" s="1">
         <v>10.28</v>
       </c>
-      <c r="V6" s="4">
+      <c r="V6" s="1">
         <v>74.38</v>
       </c>
-      <c r="W6" s="4">
+      <c r="W6" s="1">
         <v>3.6</v>
       </c>
-      <c r="X6" s="4"/>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="X6" s="1"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="4">
+      <c r="D7" s="1">
         <v>15.55</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="1">
         <v>66.709999999999994</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="1">
         <v>3.91</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="1">
         <v>3190.56</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="1">
         <v>17.849</v>
       </c>
       <c r="I7" s="2">
         <v>72.760000000000005</v>
       </c>
       <c r="J7" s="2"/>
-      <c r="K7" s="4">
+      <c r="K7" s="1">
         <v>7.34</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="1">
         <v>86.9</v>
       </c>
-      <c r="M7" s="4">
+      <c r="M7" s="1">
         <v>2.48</v>
       </c>
       <c r="N7" s="2">
         <v>90.37</v>
       </c>
       <c r="O7" s="2"/>
-      <c r="P7" s="4">
+      <c r="P7" s="1">
         <v>30.49</v>
       </c>
-      <c r="Q7" s="4">
+      <c r="Q7" s="1">
         <v>28.45</v>
       </c>
-      <c r="R7" s="4">
+      <c r="R7" s="1">
         <v>5.29</v>
       </c>
       <c r="S7" s="2">
         <v>39.22</v>
       </c>
       <c r="T7" s="2"/>
-      <c r="U7" s="4">
+      <c r="U7" s="1">
         <v>9.52</v>
       </c>
-      <c r="V7" s="4">
+      <c r="V7" s="1">
         <v>77.69</v>
       </c>
-      <c r="W7" s="4">
+      <c r="W7" s="1">
         <v>4.32</v>
       </c>
       <c r="X7" s="2">
         <v>82.64</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="4">
+      <c r="D8" s="1">
         <v>19.11</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="1">
         <v>64.239999999999995</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="1">
         <v>8.1</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="1">
         <v>3441.64</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="1">
         <v>20.038900000000002</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="4">
+      <c r="K8" s="1">
         <v>8.69</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8" s="1">
         <v>85.56</v>
       </c>
-      <c r="M8" s="4">
+      <c r="M8" s="1">
         <v>3.84</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="4">
+      <c r="P8" s="1">
         <v>31.8</v>
       </c>
-      <c r="Q8" s="4">
+      <c r="Q8" s="1">
         <v>29.74</v>
       </c>
-      <c r="R8" s="4">
+      <c r="R8" s="1">
         <v>8.1999999999999993</v>
       </c>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
-      <c r="U8" s="4">
+      <c r="U8" s="1">
         <v>21.05</v>
       </c>
-      <c r="V8" s="4">
+      <c r="V8" s="1">
         <v>64.459999999999994</v>
       </c>
-      <c r="W8" s="4">
+      <c r="W8" s="1">
         <v>14.75</v>
       </c>
       <c r="X8" s="2"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="4">
+      <c r="D9" s="1">
         <v>14.07</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="1">
         <v>69.05</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="1">
         <v>2.91</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="1">
         <v>4191.1000000000004</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="1">
         <v>22.114799999999999</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="4">
+      <c r="K9" s="1">
         <v>6.61</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9" s="1">
         <v>87.97</v>
       </c>
-      <c r="M9" s="4">
+      <c r="M9" s="1">
         <v>2.0299999999999998</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="4">
+      <c r="P9" s="1">
         <v>26.39</v>
       </c>
-      <c r="Q9" s="4">
+      <c r="Q9" s="1">
         <v>35.78</v>
       </c>
-      <c r="R9" s="4">
+      <c r="R9" s="1">
         <v>3.17</v>
       </c>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
-      <c r="U9" s="4">
+      <c r="U9" s="1">
         <v>10.53</v>
       </c>
-      <c r="V9" s="4">
+      <c r="V9" s="1">
         <v>74.38</v>
       </c>
-      <c r="W9" s="4">
+      <c r="W9" s="1">
         <v>3.96</v>
       </c>
       <c r="X9" s="2"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="C10" s="2">
+        <v>19.93</v>
+      </c>
+      <c r="D10" s="1">
+        <v>15.44</v>
+      </c>
+      <c r="E10" s="1">
+        <v>29.4</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1.71</v>
+      </c>
+      <c r="G10" s="1">
+        <v>94.58</v>
+      </c>
+      <c r="H10">
+        <v>12.401999999999999</v>
+      </c>
+      <c r="J10" s="2">
+        <v>25.95</v>
+      </c>
+      <c r="K10" s="1">
+        <v>18.12</v>
+      </c>
+      <c r="L10" s="1">
+        <v>38.68</v>
+      </c>
+      <c r="M10" s="1">
+        <v>2.98</v>
+      </c>
+      <c r="O10" s="2">
+        <v>19.18</v>
+      </c>
+      <c r="P10">
+        <v>17.05</v>
+      </c>
+      <c r="Q10">
+        <v>15.38</v>
+      </c>
+      <c r="R10" s="1">
+        <v>1.01</v>
+      </c>
+      <c r="T10" s="2">
+        <v>8.77</v>
+      </c>
+      <c r="U10">
+        <v>7.52</v>
+      </c>
+      <c r="V10" s="1">
+        <v>20</v>
+      </c>
+      <c r="W10">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="C11" s="2"/>
+      <c r="D11">
+        <v>17.03</v>
+      </c>
+      <c r="E11">
+        <v>41.76</v>
+      </c>
+      <c r="F11" s="1">
+        <v>6.77</v>
+      </c>
+      <c r="G11">
+        <v>6743.49</v>
+      </c>
+      <c r="H11">
+        <v>114.9687</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11">
+        <v>16.77</v>
+      </c>
+      <c r="L11" s="1">
+        <v>57.08</v>
+      </c>
+      <c r="M11">
+        <v>7.6</v>
+      </c>
+      <c r="O11" s="2"/>
+      <c r="P11" s="1">
+        <v>22.3</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>17.95</v>
+      </c>
+      <c r="R11" s="1">
+        <v>8.11</v>
+      </c>
+      <c r="T11" s="2"/>
+      <c r="U11" s="1">
+        <v>9.52</v>
+      </c>
+      <c r="V11" s="1">
+        <v>28.57</v>
+      </c>
+      <c r="W11" s="1">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="C12" s="2"/>
+      <c r="D12">
+        <v>15.5</v>
+      </c>
+      <c r="E12">
+        <v>43.68</v>
+      </c>
+      <c r="F12">
+        <v>5.34</v>
+      </c>
+      <c r="G12">
+        <v>7320.52</v>
+      </c>
+      <c r="H12">
+        <v>113.2599</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="1">
+        <v>13.83</v>
+      </c>
+      <c r="L12">
+        <v>57.55</v>
+      </c>
+      <c r="M12">
+        <v>3.8</v>
+      </c>
+      <c r="O12" s="2"/>
+      <c r="P12">
+        <v>22.62</v>
+      </c>
+      <c r="Q12">
+        <v>15.38</v>
+      </c>
+      <c r="R12" s="1">
+        <v>7.91</v>
+      </c>
+      <c r="T12" s="2"/>
+      <c r="U12">
+        <v>8.02</v>
+      </c>
+      <c r="V12">
+        <v>54.29</v>
+      </c>
+      <c r="W12" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="C13" s="2"/>
+      <c r="D13">
+        <v>11.66</v>
+      </c>
+      <c r="E13">
+        <v>49.45</v>
+      </c>
+      <c r="F13">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="G13">
+        <v>194.27</v>
+      </c>
+      <c r="H13">
+        <v>17.3841</v>
+      </c>
+      <c r="J13" s="2"/>
+      <c r="K13">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="L13">
+        <v>72.17</v>
+      </c>
+      <c r="M13">
+        <v>1.49</v>
+      </c>
+      <c r="O13" s="2"/>
+      <c r="P13">
+        <v>20.16</v>
+      </c>
+      <c r="Q13">
+        <v>10.26</v>
+      </c>
+      <c r="R13">
+        <v>3.65</v>
+      </c>
+      <c r="T13" s="2"/>
+      <c r="U13" s="1">
+        <v>5.76</v>
+      </c>
+      <c r="V13" s="1">
+        <v>42.86</v>
+      </c>
+      <c r="W13" s="1">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="C14" s="2"/>
+      <c r="D14">
+        <v>10.08</v>
+      </c>
+      <c r="E14">
+        <v>51.37</v>
+      </c>
+      <c r="F14">
+        <v>0.48</v>
+      </c>
+      <c r="G14">
+        <v>3227.5</v>
+      </c>
+      <c r="H14">
+        <v>147.7028</v>
+      </c>
+      <c r="I14" s="2">
+        <v>65.11</v>
+      </c>
+      <c r="J14" s="2"/>
+      <c r="K14">
+        <v>7.47</v>
+      </c>
+      <c r="L14">
+        <v>71.23</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2">
+        <v>80.66</v>
+      </c>
+      <c r="O14" s="2"/>
+      <c r="P14">
+        <v>17.05</v>
+      </c>
+      <c r="Q14">
+        <v>16.239999999999998</v>
+      </c>
+      <c r="R14" s="1">
+        <v>1.22</v>
+      </c>
+      <c r="S14" s="2">
+        <v>34.19</v>
+      </c>
+      <c r="T14" s="2"/>
+      <c r="U14">
+        <v>4.76</v>
+      </c>
+      <c r="V14" s="1">
+        <v>48.57</v>
+      </c>
+      <c r="W14" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="X14" s="2">
+        <v>74.290000000000006</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="1"/>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="C15" s="2"/>
+      <c r="D15">
+        <v>9.15</v>
+      </c>
+      <c r="E15">
+        <v>56.59</v>
+      </c>
+      <c r="F15">
+        <v>0.62</v>
+      </c>
+      <c r="G15">
+        <v>3337.4</v>
+      </c>
+      <c r="H15">
+        <v>159.09700000000001</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15">
+        <v>5.88</v>
+      </c>
+      <c r="L15">
+        <v>77.36</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15">
+        <v>16.07</v>
+      </c>
+      <c r="Q15">
+        <v>22.22</v>
+      </c>
+      <c r="R15" s="1">
+        <v>1.42</v>
+      </c>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="1">
+        <v>5.26</v>
+      </c>
+      <c r="V15" s="1">
+        <v>45.71</v>
+      </c>
+      <c r="W15" s="1">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="X15" s="2"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="1"/>
+      <c r="C16" s="2"/>
+      <c r="D16">
+        <v>7.89</v>
+      </c>
+      <c r="E16">
+        <v>61.54</v>
+      </c>
+      <c r="F16">
+        <v>0.27</v>
+      </c>
+      <c r="G16">
+        <v>3609.91</v>
+      </c>
+      <c r="H16">
+        <v>168.54599999999999</v>
+      </c>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16">
+        <v>5.14</v>
+      </c>
+      <c r="L16">
+        <v>80.19</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16">
+        <v>14.1</v>
+      </c>
+      <c r="Q16">
+        <v>29.91</v>
+      </c>
+      <c r="R16" s="1">
+        <v>0.81</v>
+      </c>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16">
+        <v>4.01</v>
+      </c>
+      <c r="V16" s="1">
+        <v>54.29</v>
+      </c>
+      <c r="W16" s="1">
+        <v>0</v>
+      </c>
+      <c r="X16" s="2"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1069,43 +1402,43 @@
       <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1115,24 +1448,31 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="24">
+    <mergeCell ref="T10:T16"/>
+    <mergeCell ref="N14:N16"/>
+    <mergeCell ref="S14:S16"/>
+    <mergeCell ref="X14:X16"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="J10:J16"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="T1:X1"/>
+    <mergeCell ref="O3:O9"/>
+    <mergeCell ref="T3:T9"/>
     <mergeCell ref="A10:A16"/>
     <mergeCell ref="C10:C16"/>
     <mergeCell ref="A17:A23"/>
     <mergeCell ref="A24:A30"/>
     <mergeCell ref="S7:S9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="T1:X1"/>
-    <mergeCell ref="O3:O9"/>
-    <mergeCell ref="T3:T9"/>
     <mergeCell ref="A3:A9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J3:J9"/>
-    <mergeCell ref="J1:N1"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="O10:O16"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/stat/data.xlsx
+++ b/stat/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr-PC\Documents\Workspace\LLMHalluMiti\stat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D9F8DAF-9840-4FFE-9600-10488F037FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D826848F-CCEE-41E5-8083-D0B22505C64F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1354,51 +1354,401 @@
       </c>
       <c r="X16" s="2"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C17" s="2">
+        <v>29.96</v>
+      </c>
+      <c r="D17">
+        <v>23.38</v>
+      </c>
+      <c r="E17">
+        <v>24.5</v>
+      </c>
+      <c r="F17">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="G17">
+        <v>95.45</v>
+      </c>
+      <c r="H17">
+        <v>3.6791999999999998</v>
+      </c>
+      <c r="J17" s="2">
+        <v>28.64</v>
+      </c>
+      <c r="K17">
+        <v>17.38</v>
+      </c>
+      <c r="L17">
+        <v>42.31</v>
+      </c>
+      <c r="M17">
+        <v>1.2</v>
+      </c>
+      <c r="O17" s="2">
+        <v>40.82</v>
+      </c>
+      <c r="P17">
+        <v>38.85</v>
+      </c>
+      <c r="Q17">
+        <v>7.23</v>
+      </c>
+      <c r="R17" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="T17" s="2">
+        <v>16.04</v>
+      </c>
+      <c r="U17">
+        <v>12.03</v>
+      </c>
+      <c r="V17" s="1">
+        <v>26.56</v>
+      </c>
+      <c r="W17" s="1">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C18" s="2"/>
+      <c r="D18">
+        <v>36.31</v>
+      </c>
+      <c r="E18">
+        <v>31.08</v>
+      </c>
+      <c r="F18">
+        <v>22.36</v>
+      </c>
+      <c r="G18">
+        <v>3620.41</v>
+      </c>
+      <c r="H18">
+        <v>26.883299999999998</v>
+      </c>
+      <c r="J18" s="2"/>
+      <c r="K18">
+        <v>31.46</v>
+      </c>
+      <c r="L18">
+        <v>47.86</v>
+      </c>
+      <c r="M18">
+        <v>23.16</v>
+      </c>
+      <c r="O18" s="2"/>
+      <c r="P18">
+        <v>48.2</v>
+      </c>
+      <c r="Q18">
+        <v>14.06</v>
+      </c>
+      <c r="R18" s="1">
+        <v>22.16</v>
+      </c>
+      <c r="T18" s="2"/>
+      <c r="U18">
+        <v>28.07</v>
+      </c>
+      <c r="V18" s="1">
+        <v>35.94</v>
+      </c>
+      <c r="W18" s="1">
+        <v>21.19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C19" s="2"/>
+      <c r="D19">
+        <v>55.31</v>
+      </c>
+      <c r="E19">
+        <v>14.08</v>
+      </c>
+      <c r="F19">
+        <v>41.14</v>
+      </c>
+      <c r="G19">
+        <v>3227.44</v>
+      </c>
+      <c r="H19">
+        <v>24.215399999999999</v>
+      </c>
+      <c r="J19" s="2"/>
+      <c r="K19">
+        <v>53.12</v>
+      </c>
+      <c r="L19">
+        <v>16.670000000000002</v>
+      </c>
+      <c r="M19">
+        <v>40.82</v>
+      </c>
+      <c r="O19" s="2"/>
+      <c r="P19">
+        <v>66.89</v>
+      </c>
+      <c r="Q19">
+        <v>9.64</v>
+      </c>
+      <c r="R19" s="1">
+        <v>50.69</v>
+      </c>
+      <c r="T19" s="2"/>
+      <c r="U19">
+        <v>42.11</v>
+      </c>
+      <c r="V19">
+        <v>21.88</v>
+      </c>
+      <c r="W19">
+        <v>35.22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C20" s="2"/>
+      <c r="D20">
+        <v>20.87</v>
+      </c>
+      <c r="E20">
+        <v>35.47</v>
+      </c>
+      <c r="F20">
+        <v>2.19</v>
+      </c>
+      <c r="G20">
+        <v>205.87</v>
+      </c>
+      <c r="H20">
+        <v>2.9369000000000001</v>
+      </c>
+      <c r="J20" s="2"/>
+      <c r="K20">
+        <v>14.93</v>
+      </c>
+      <c r="L20">
+        <v>51.71</v>
+      </c>
+      <c r="M20">
+        <v>1.54</v>
+      </c>
+      <c r="O20" s="2"/>
+      <c r="P20">
+        <v>36.72</v>
+      </c>
+      <c r="Q20">
+        <v>17.670000000000002</v>
+      </c>
+      <c r="R20">
+        <v>5.26</v>
+      </c>
+      <c r="T20" s="2"/>
+      <c r="U20">
+        <v>8.77</v>
+      </c>
+      <c r="V20">
+        <v>45.31</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C21" s="2"/>
+      <c r="D21">
+        <v>18.89</v>
+      </c>
+      <c r="E21">
+        <v>39.31</v>
+      </c>
+      <c r="F21">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="G21">
+        <v>3422.22</v>
+      </c>
+      <c r="H21">
+        <v>22.941400000000002</v>
+      </c>
+      <c r="I21" s="2">
+        <v>48.81</v>
+      </c>
+      <c r="J21" s="2"/>
+      <c r="K21">
+        <v>12.48</v>
+      </c>
+      <c r="L21">
+        <v>58.97</v>
+      </c>
+      <c r="M21">
+        <v>1.03</v>
+      </c>
+      <c r="N21" s="2">
+        <v>67.09</v>
+      </c>
+      <c r="O21" s="2"/>
+      <c r="P21">
+        <v>34.590000000000003</v>
+      </c>
+      <c r="Q21">
+        <v>18.07</v>
+      </c>
+      <c r="R21">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="S21" s="2">
+        <v>30.12</v>
+      </c>
+      <c r="T21" s="2"/>
+      <c r="U21">
+        <v>8.02</v>
+      </c>
+      <c r="V21">
+        <v>50</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21" s="2">
+        <v>54.69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C22" s="2"/>
+      <c r="D22">
+        <v>17.8</v>
+      </c>
+      <c r="E22">
+        <v>43.33</v>
+      </c>
+      <c r="F22">
+        <v>1.17</v>
+      </c>
+      <c r="G22">
+        <v>3532.35</v>
+      </c>
+      <c r="H22">
+        <v>23.260400000000001</v>
+      </c>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22">
+        <v>10.89</v>
+      </c>
+      <c r="L22">
+        <v>64.959999999999994</v>
+      </c>
+      <c r="M22">
+        <v>1.2</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22">
+        <v>33.61</v>
+      </c>
+      <c r="Q22">
+        <v>20.88</v>
+      </c>
+      <c r="R22">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22">
+        <v>7.77</v>
+      </c>
+      <c r="V22">
+        <v>51.56</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22" s="2"/>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C23" s="2"/>
+      <c r="D23">
+        <v>16.43</v>
+      </c>
+      <c r="E23">
+        <v>46.62</v>
+      </c>
+      <c r="F23">
+        <v>0.63</v>
+      </c>
+      <c r="G23">
+        <v>4536.21</v>
+      </c>
+      <c r="H23">
+        <v>52.032899999999998</v>
+      </c>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23">
+        <v>10.039999999999999</v>
+      </c>
+      <c r="L23">
+        <v>66.67</v>
+      </c>
+      <c r="M23">
+        <v>0.69</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23">
+        <v>30.82</v>
+      </c>
+      <c r="Q23">
+        <v>26.1</v>
+      </c>
+      <c r="R23">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23">
+        <v>7.52</v>
+      </c>
+      <c r="V23">
+        <v>53.12</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23" s="2"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
@@ -1406,37 +1756,37 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="1" t="s">
         <v>12</v>
@@ -1448,13 +1798,24 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="T10:T16"/>
-    <mergeCell ref="N14:N16"/>
-    <mergeCell ref="S14:S16"/>
-    <mergeCell ref="X14:X16"/>
-    <mergeCell ref="J1:N1"/>
-    <mergeCell ref="N7:N9"/>
+  <mergeCells count="32">
+    <mergeCell ref="T17:T23"/>
+    <mergeCell ref="X21:X23"/>
+    <mergeCell ref="A10:A16"/>
+    <mergeCell ref="C10:C16"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="A24:A30"/>
+    <mergeCell ref="S7:S9"/>
+    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J3:J9"/>
+    <mergeCell ref="O10:O16"/>
+    <mergeCell ref="C17:C23"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="N21:N23"/>
+    <mergeCell ref="O17:O23"/>
+    <mergeCell ref="S21:S23"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="C3:C9"/>
     <mergeCell ref="I14:I16"/>
@@ -1464,15 +1825,12 @@
     <mergeCell ref="T1:X1"/>
     <mergeCell ref="O3:O9"/>
     <mergeCell ref="T3:T9"/>
-    <mergeCell ref="A10:A16"/>
-    <mergeCell ref="C10:C16"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="A24:A30"/>
-    <mergeCell ref="S7:S9"/>
-    <mergeCell ref="A3:A9"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J3:J9"/>
-    <mergeCell ref="O10:O16"/>
+    <mergeCell ref="T10:T16"/>
+    <mergeCell ref="N14:N16"/>
+    <mergeCell ref="S14:S16"/>
+    <mergeCell ref="X14:X16"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="N7:N9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/stat/data.xlsx
+++ b/stat/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr-PC\Documents\Workspace\LLMHalluMiti\stat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D826848F-CCEE-41E5-8083-D0B22505C64F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2184E5-82C9-4A84-B0CA-7FAE08FEB482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="22">
   <si>
     <t>gpt-4o</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -443,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X37"/>
+  <dimension ref="A1:X30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.2">
@@ -1755,67 +1755,399 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="C24" s="2">
+        <v>44.74</v>
+      </c>
+      <c r="D24">
+        <v>36.14</v>
+      </c>
+      <c r="E24">
+        <v>26.19</v>
+      </c>
+      <c r="F24">
+        <v>5.65</v>
+      </c>
+      <c r="G24">
+        <v>514.66999999999996</v>
+      </c>
+      <c r="H24">
+        <v>15.446099999999999</v>
+      </c>
+      <c r="J24" s="2">
+        <v>38.07</v>
+      </c>
+      <c r="K24">
+        <v>24.24</v>
+      </c>
+      <c r="L24">
+        <v>44.69</v>
+      </c>
+      <c r="M24">
+        <v>5.14</v>
+      </c>
+      <c r="O24" s="2">
+        <v>56.89</v>
+      </c>
+      <c r="P24">
+        <v>53.44</v>
+      </c>
+      <c r="Q24">
+        <v>11.24</v>
+      </c>
+      <c r="R24">
+        <v>6.84</v>
+      </c>
+      <c r="T24" s="2">
+        <v>39.85</v>
+      </c>
+      <c r="U24">
+        <v>34.090000000000003</v>
+      </c>
+      <c r="V24">
+        <v>22.64</v>
+      </c>
+      <c r="W24">
+        <v>5.42</v>
+      </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="C25" s="2"/>
+      <c r="D25">
+        <v>40.53</v>
+      </c>
+      <c r="E25">
+        <v>31.95</v>
+      </c>
+      <c r="F25">
+        <v>18.43</v>
+      </c>
+      <c r="G25">
+        <v>2260.0300000000002</v>
+      </c>
+      <c r="H25">
+        <v>27.349599999999999</v>
+      </c>
+      <c r="J25" s="2"/>
+      <c r="K25">
+        <v>26.44</v>
+      </c>
+      <c r="L25">
+        <v>52.73</v>
+      </c>
+      <c r="M25">
+        <v>14.03</v>
+      </c>
+      <c r="O25" s="2"/>
+      <c r="P25">
+        <v>61.97</v>
+      </c>
+      <c r="Q25">
+        <v>11.24</v>
+      </c>
+      <c r="R25">
+        <v>26.62</v>
+      </c>
+      <c r="T25" s="2"/>
+      <c r="U25">
+        <v>36.590000000000003</v>
+      </c>
+      <c r="V25">
+        <v>36.479999999999997</v>
+      </c>
+      <c r="W25">
+        <v>18.75</v>
+      </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="C26" s="2"/>
+      <c r="D26">
+        <v>45.02</v>
+      </c>
+      <c r="E26">
+        <v>27.54</v>
+      </c>
+      <c r="F26">
+        <v>22.79</v>
+      </c>
+      <c r="G26">
+        <v>3219.47</v>
+      </c>
+      <c r="H26">
+        <v>35.505099999999999</v>
+      </c>
+      <c r="J26" s="2"/>
+      <c r="K26">
+        <v>34.39</v>
+      </c>
+      <c r="L26">
+        <v>42.77</v>
+      </c>
+      <c r="M26">
+        <v>19.96</v>
+      </c>
+      <c r="O26" s="2"/>
+      <c r="P26">
+        <v>63.28</v>
+      </c>
+      <c r="Q26">
+        <v>11.53</v>
+      </c>
+      <c r="R26">
+        <v>30.04</v>
+      </c>
+      <c r="T26" s="2"/>
+      <c r="U26">
+        <v>38.85</v>
+      </c>
+      <c r="V26">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="W26">
+        <v>20</v>
+      </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="C27" s="2"/>
+      <c r="D27">
+        <v>31.16</v>
+      </c>
+      <c r="E27">
+        <v>40.020000000000003</v>
+      </c>
+      <c r="F27">
+        <v>7.83</v>
+      </c>
+      <c r="G27">
+        <v>234.65</v>
+      </c>
+      <c r="H27">
+        <v>1.3381000000000001</v>
+      </c>
+      <c r="J27" s="2"/>
+      <c r="K27">
+        <v>12.97</v>
+      </c>
+      <c r="L27">
+        <v>70.739999999999995</v>
+      </c>
+      <c r="M27">
+        <v>2.96</v>
+      </c>
+      <c r="O27" s="2"/>
+      <c r="P27">
+        <v>53.28</v>
+      </c>
+      <c r="Q27">
+        <v>17</v>
+      </c>
+      <c r="R27">
+        <v>14.07</v>
+      </c>
+      <c r="T27" s="2"/>
+      <c r="U27">
+        <v>34.590000000000003</v>
+      </c>
+      <c r="V27">
+        <v>30.19</v>
+      </c>
+      <c r="W27">
+        <v>11.25</v>
+      </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="C28" s="2"/>
+      <c r="D28">
+        <v>28.31</v>
+      </c>
+      <c r="E28">
+        <v>41.13</v>
+      </c>
+      <c r="F28">
+        <v>3.57</v>
+      </c>
+      <c r="G28">
+        <v>3697.93</v>
+      </c>
+      <c r="H28">
+        <v>13.305</v>
+      </c>
+      <c r="I28" s="2">
+        <v>48.1</v>
+      </c>
+      <c r="J28" s="2"/>
+      <c r="K28">
+        <v>11.75</v>
+      </c>
+      <c r="L28">
+        <v>71.7</v>
+      </c>
+      <c r="M28">
+        <v>1.58</v>
+      </c>
+      <c r="N28" s="2">
+        <v>76.209999999999994</v>
+      </c>
+      <c r="O28" s="2"/>
+      <c r="P28">
+        <v>50.16</v>
+      </c>
+      <c r="Q28">
+        <v>16.43</v>
+      </c>
+      <c r="R28">
+        <v>6.08</v>
+      </c>
+      <c r="S28" s="2">
+        <v>23.05</v>
+      </c>
+      <c r="T28" s="2"/>
+      <c r="U28">
+        <v>28.82</v>
+      </c>
+      <c r="V28">
+        <v>35.22</v>
+      </c>
+      <c r="W28">
+        <v>5</v>
+      </c>
+      <c r="X28" s="2">
+        <v>47.8</v>
+      </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="C29" s="2"/>
+      <c r="D29">
+        <v>27.66</v>
+      </c>
+      <c r="E29">
+        <v>42.72</v>
+      </c>
+      <c r="F29">
+        <v>3.67</v>
+      </c>
+      <c r="G29">
+        <v>3988.17</v>
+      </c>
+      <c r="H29">
+        <v>15.7463</v>
+      </c>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29">
+        <v>11.75</v>
+      </c>
+      <c r="L29">
+        <v>72.03</v>
+      </c>
+      <c r="M29">
+        <v>1.78</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29">
+        <v>49.18</v>
+      </c>
+      <c r="Q29">
+        <v>17.87</v>
+      </c>
+      <c r="R29">
+        <v>5.7</v>
+      </c>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29">
+        <v>27.32</v>
+      </c>
+      <c r="V29">
+        <v>36.92</v>
+      </c>
+      <c r="W29">
+        <v>5.42</v>
+      </c>
+      <c r="X29" s="2"/>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
-        <v>20</v>
-      </c>
+      <c r="C30" s="2"/>
+      <c r="D30">
+        <v>25.96</v>
+      </c>
+      <c r="E30">
+        <v>45.17</v>
+      </c>
+      <c r="F30">
+        <v>2.58</v>
+      </c>
+      <c r="G30">
+        <v>4521.08</v>
+      </c>
+      <c r="H30">
+        <v>21.763400000000001</v>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30">
+        <v>10.28</v>
+      </c>
+      <c r="L30">
+        <v>74.92</v>
+      </c>
+      <c r="M30">
+        <v>1.19</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30">
+        <v>47.54</v>
+      </c>
+      <c r="Q30">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="R30">
+        <v>4.18</v>
+      </c>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30">
+        <v>25.06</v>
+      </c>
+      <c r="V30">
+        <v>42.77</v>
+      </c>
+      <c r="W30">
+        <v>3.75</v>
+      </c>
+      <c r="X30" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="T17:T23"/>
-    <mergeCell ref="X21:X23"/>
-    <mergeCell ref="A10:A16"/>
-    <mergeCell ref="C10:C16"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="A24:A30"/>
-    <mergeCell ref="S7:S9"/>
-    <mergeCell ref="A3:A9"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J3:J9"/>
-    <mergeCell ref="O10:O16"/>
-    <mergeCell ref="C17:C23"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="N21:N23"/>
-    <mergeCell ref="O17:O23"/>
-    <mergeCell ref="S21:S23"/>
+  <mergeCells count="40">
+    <mergeCell ref="T24:T30"/>
+    <mergeCell ref="N28:N30"/>
+    <mergeCell ref="S28:S30"/>
+    <mergeCell ref="X28:X30"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="C3:C9"/>
     <mergeCell ref="I14:I16"/>
@@ -1831,6 +2163,27 @@
     <mergeCell ref="X14:X16"/>
     <mergeCell ref="J1:N1"/>
     <mergeCell ref="N7:N9"/>
+    <mergeCell ref="A24:A30"/>
+    <mergeCell ref="S7:S9"/>
+    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J3:J9"/>
+    <mergeCell ref="O10:O16"/>
+    <mergeCell ref="C17:C23"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="N21:N23"/>
+    <mergeCell ref="O17:O23"/>
+    <mergeCell ref="S21:S23"/>
+    <mergeCell ref="C24:C30"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="J24:J30"/>
+    <mergeCell ref="O24:O30"/>
+    <mergeCell ref="T17:T23"/>
+    <mergeCell ref="X21:X23"/>
+    <mergeCell ref="A10:A16"/>
+    <mergeCell ref="C10:C16"/>
+    <mergeCell ref="A17:A23"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/stat/data.xlsx
+++ b/stat/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr-PC\Documents\Workspace\LLMHalluMiti\stat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2184E5-82C9-4A84-B0CA-7FAE08FEB482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B9F5CD-9E75-4C14-94E4-B88563EDAE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2144,6 +2144,30 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="A10:A16"/>
+    <mergeCell ref="C10:C16"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="J24:J30"/>
+    <mergeCell ref="O24:O30"/>
+    <mergeCell ref="T17:T23"/>
+    <mergeCell ref="X21:X23"/>
+    <mergeCell ref="X14:X16"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="A24:A30"/>
+    <mergeCell ref="S7:S9"/>
+    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J3:J9"/>
+    <mergeCell ref="O10:O16"/>
+    <mergeCell ref="C17:C23"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="N21:N23"/>
+    <mergeCell ref="O17:O23"/>
+    <mergeCell ref="S21:S23"/>
+    <mergeCell ref="C24:C30"/>
     <mergeCell ref="T24:T30"/>
     <mergeCell ref="N28:N30"/>
     <mergeCell ref="S28:S30"/>
@@ -2160,30 +2184,6 @@
     <mergeCell ref="T10:T16"/>
     <mergeCell ref="N14:N16"/>
     <mergeCell ref="S14:S16"/>
-    <mergeCell ref="X14:X16"/>
-    <mergeCell ref="J1:N1"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="A24:A30"/>
-    <mergeCell ref="S7:S9"/>
-    <mergeCell ref="A3:A9"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J3:J9"/>
-    <mergeCell ref="O10:O16"/>
-    <mergeCell ref="C17:C23"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="N21:N23"/>
-    <mergeCell ref="O17:O23"/>
-    <mergeCell ref="S21:S23"/>
-    <mergeCell ref="C24:C30"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="J24:J30"/>
-    <mergeCell ref="O24:O30"/>
-    <mergeCell ref="T17:T23"/>
-    <mergeCell ref="X21:X23"/>
-    <mergeCell ref="A10:A16"/>
-    <mergeCell ref="C10:C16"/>
-    <mergeCell ref="A17:A23"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/stat/data.xlsx
+++ b/stat/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr-PC\Documents\Workspace\LLMHalluMiti\stat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B9F5CD-9E75-4C14-94E4-B88563EDAE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B957F8D4-DD5F-4D87-9937-EC5114F60A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="43">
   <si>
     <t>gpt-4o</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -112,6 +112,87 @@
   </si>
   <si>
     <t>oa-mv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NAME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CoVe-SE</t>
+  </si>
+  <si>
+    <t>CoVe</t>
+  </si>
+  <si>
+    <t>CoT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NAME</t>
+  </si>
+  <si>
+    <t>CoVe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FreshQA</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>HotpotQA</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>TruthfulQA</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>overall</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>oc.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>hal. repair</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>rc. hal.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Method</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>run1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>run2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>run3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rc. hal.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hal. repair</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oc.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -119,7 +200,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,6 +215,26 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -143,7 +244,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -151,16 +252,274 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -443,42 +802,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X30"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2" t="s">
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2" t="s">
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2" t="s">
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
@@ -551,13 +910,13 @@
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="35">
         <v>39.81</v>
       </c>
       <c r="D3" s="1">
@@ -576,7 +935,7 @@
         <v>4.9604999999999997</v>
       </c>
       <c r="I3" s="1"/>
-      <c r="J3" s="2">
+      <c r="J3" s="35">
         <v>45.78</v>
       </c>
       <c r="K3" s="1">
@@ -589,7 +948,7 @@
         <v>9.0299999999999994</v>
       </c>
       <c r="N3" s="1"/>
-      <c r="O3" s="2">
+      <c r="O3" s="35">
         <v>38.03</v>
       </c>
       <c r="P3" s="1">
@@ -602,7 +961,7 @@
         <v>1.32</v>
       </c>
       <c r="S3" s="1"/>
-      <c r="T3" s="2">
+      <c r="T3" s="35">
         <v>30.33</v>
       </c>
       <c r="U3" s="1">
@@ -617,11 +976,11 @@
       <c r="X3" s="1"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A4" s="2"/>
+      <c r="A4" s="35"/>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="1">
         <v>25.03</v>
       </c>
@@ -638,7 +997,7 @@
         <v>22.125900000000001</v>
       </c>
       <c r="I4" s="1"/>
-      <c r="J4" s="2"/>
+      <c r="J4" s="35"/>
       <c r="K4" s="1">
         <v>23.38</v>
       </c>
@@ -649,7 +1008,7 @@
         <v>15.35</v>
       </c>
       <c r="N4" s="1"/>
-      <c r="O4" s="2"/>
+      <c r="O4" s="35"/>
       <c r="P4" s="1">
         <v>35.9</v>
       </c>
@@ -660,7 +1019,7 @@
         <v>12.17</v>
       </c>
       <c r="S4" s="1"/>
-      <c r="T4" s="2"/>
+      <c r="T4" s="35"/>
       <c r="U4" s="1">
         <v>11.78</v>
       </c>
@@ -673,11 +1032,11 @@
       <c r="X4" s="1"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
+      <c r="A5" s="35"/>
       <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2"/>
+      <c r="C5" s="35"/>
       <c r="D5" s="1">
         <v>25.58</v>
       </c>
@@ -694,7 +1053,7 @@
         <v>33.609499999999997</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="2"/>
+      <c r="J5" s="35"/>
       <c r="K5" s="1">
         <v>22.4</v>
       </c>
@@ -705,7 +1064,7 @@
         <v>9.48</v>
       </c>
       <c r="N5" s="1"/>
-      <c r="O5" s="2"/>
+      <c r="O5" s="35"/>
       <c r="P5" s="1">
         <v>38.03</v>
       </c>
@@ -716,7 +1075,7 @@
         <v>19.309999999999999</v>
       </c>
       <c r="S5" s="1"/>
-      <c r="T5" s="2"/>
+      <c r="T5" s="35"/>
       <c r="U5" s="1">
         <v>13.03</v>
       </c>
@@ -729,11 +1088,11 @@
       <c r="X5" s="1"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A6" s="2"/>
+      <c r="A6" s="35"/>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="2"/>
+      <c r="C6" s="35"/>
       <c r="D6" s="1">
         <v>17.579999999999998</v>
       </c>
@@ -750,7 +1109,7 @@
         <v>6.4598000000000004</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="2"/>
+      <c r="J6" s="35"/>
       <c r="K6" s="1">
         <v>10.4</v>
       </c>
@@ -761,7 +1120,7 @@
         <v>7</v>
       </c>
       <c r="N6" s="1"/>
-      <c r="O6" s="2"/>
+      <c r="O6" s="35"/>
       <c r="P6" s="1">
         <v>31.97</v>
       </c>
@@ -772,7 +1131,7 @@
         <v>6.88</v>
       </c>
       <c r="S6" s="1"/>
-      <c r="T6" s="2"/>
+      <c r="T6" s="35"/>
       <c r="U6" s="1">
         <v>10.28</v>
       </c>
@@ -785,11 +1144,11 @@
       <c r="X6" s="1"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
+      <c r="A7" s="35"/>
       <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="2"/>
+      <c r="C7" s="35"/>
       <c r="D7" s="1">
         <v>15.55</v>
       </c>
@@ -805,10 +1164,10 @@
       <c r="H7" s="1">
         <v>17.849</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="35">
         <v>72.760000000000005</v>
       </c>
-      <c r="J7" s="2"/>
+      <c r="J7" s="35"/>
       <c r="K7" s="1">
         <v>7.34</v>
       </c>
@@ -818,10 +1177,10 @@
       <c r="M7" s="1">
         <v>2.48</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="35">
         <v>90.37</v>
       </c>
-      <c r="O7" s="2"/>
+      <c r="O7" s="35"/>
       <c r="P7" s="1">
         <v>30.49</v>
       </c>
@@ -831,10 +1190,10 @@
       <c r="R7" s="1">
         <v>5.29</v>
       </c>
-      <c r="S7" s="2">
+      <c r="S7" s="35">
         <v>39.22</v>
       </c>
-      <c r="T7" s="2"/>
+      <c r="T7" s="35"/>
       <c r="U7" s="1">
         <v>9.52</v>
       </c>
@@ -844,16 +1203,16 @@
       <c r="W7" s="1">
         <v>4.32</v>
       </c>
-      <c r="X7" s="2">
+      <c r="X7" s="35">
         <v>82.64</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A8" s="2"/>
+      <c r="A8" s="35"/>
       <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="2"/>
+      <c r="C8" s="35"/>
       <c r="D8" s="1">
         <v>19.11</v>
       </c>
@@ -869,8 +1228,8 @@
       <c r="H8" s="1">
         <v>20.038900000000002</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
       <c r="K8" s="1">
         <v>8.69</v>
       </c>
@@ -880,8 +1239,8 @@
       <c r="M8" s="1">
         <v>3.84</v>
       </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
       <c r="P8" s="1">
         <v>31.8</v>
       </c>
@@ -891,8 +1250,8 @@
       <c r="R8" s="1">
         <v>8.1999999999999993</v>
       </c>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
+      <c r="S8" s="35"/>
+      <c r="T8" s="35"/>
       <c r="U8" s="1">
         <v>21.05</v>
       </c>
@@ -902,14 +1261,14 @@
       <c r="W8" s="1">
         <v>14.75</v>
       </c>
-      <c r="X8" s="2"/>
+      <c r="X8" s="35"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
+      <c r="A9" s="35"/>
       <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="2"/>
+      <c r="C9" s="35"/>
       <c r="D9" s="1">
         <v>14.07</v>
       </c>
@@ -925,8 +1284,8 @@
       <c r="H9" s="1">
         <v>22.114799999999999</v>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
       <c r="K9" s="1">
         <v>6.61</v>
       </c>
@@ -936,8 +1295,8 @@
       <c r="M9" s="1">
         <v>2.0299999999999998</v>
       </c>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
+      <c r="N9" s="35"/>
+      <c r="O9" s="35"/>
       <c r="P9" s="1">
         <v>26.39</v>
       </c>
@@ -947,8 +1306,8 @@
       <c r="R9" s="1">
         <v>3.17</v>
       </c>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
+      <c r="S9" s="35"/>
+      <c r="T9" s="35"/>
       <c r="U9" s="1">
         <v>10.53</v>
       </c>
@@ -958,16 +1317,16 @@
       <c r="W9" s="1">
         <v>3.96</v>
       </c>
-      <c r="X9" s="2"/>
+      <c r="X9" s="35"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="35" t="s">
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="35">
         <v>19.93</v>
       </c>
       <c r="D10" s="1">
@@ -985,7 +1344,7 @@
       <c r="H10">
         <v>12.401999999999999</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="35">
         <v>25.95</v>
       </c>
       <c r="K10" s="1">
@@ -997,7 +1356,7 @@
       <c r="M10" s="1">
         <v>2.98</v>
       </c>
-      <c r="O10" s="2">
+      <c r="O10" s="35">
         <v>19.18</v>
       </c>
       <c r="P10">
@@ -1009,7 +1368,7 @@
       <c r="R10" s="1">
         <v>1.01</v>
       </c>
-      <c r="T10" s="2">
+      <c r="T10" s="35">
         <v>8.77</v>
       </c>
       <c r="U10">
@@ -1023,11 +1382,11 @@
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="35"/>
       <c r="D11">
         <v>17.03</v>
       </c>
@@ -1043,7 +1402,7 @@
       <c r="H11">
         <v>114.9687</v>
       </c>
-      <c r="J11" s="2"/>
+      <c r="J11" s="35"/>
       <c r="K11">
         <v>16.77</v>
       </c>
@@ -1053,7 +1412,7 @@
       <c r="M11">
         <v>7.6</v>
       </c>
-      <c r="O11" s="2"/>
+      <c r="O11" s="35"/>
       <c r="P11" s="1">
         <v>22.3</v>
       </c>
@@ -1063,7 +1422,7 @@
       <c r="R11" s="1">
         <v>8.11</v>
       </c>
-      <c r="T11" s="2"/>
+      <c r="T11" s="35"/>
       <c r="U11" s="1">
         <v>9.52</v>
       </c>
@@ -1075,11 +1434,11 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
+      <c r="A12" s="35"/>
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="2"/>
+      <c r="C12" s="35"/>
       <c r="D12">
         <v>15.5</v>
       </c>
@@ -1095,7 +1454,7 @@
       <c r="H12">
         <v>113.2599</v>
       </c>
-      <c r="J12" s="2"/>
+      <c r="J12" s="35"/>
       <c r="K12" s="1">
         <v>13.83</v>
       </c>
@@ -1105,7 +1464,7 @@
       <c r="M12">
         <v>3.8</v>
       </c>
-      <c r="O12" s="2"/>
+      <c r="O12" s="35"/>
       <c r="P12">
         <v>22.62</v>
       </c>
@@ -1115,7 +1474,7 @@
       <c r="R12" s="1">
         <v>7.91</v>
       </c>
-      <c r="T12" s="2"/>
+      <c r="T12" s="35"/>
       <c r="U12">
         <v>8.02</v>
       </c>
@@ -1127,11 +1486,11 @@
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
+      <c r="A13" s="35"/>
       <c r="B13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="2"/>
+      <c r="C13" s="35"/>
       <c r="D13">
         <v>11.66</v>
       </c>
@@ -1147,7 +1506,7 @@
       <c r="H13">
         <v>17.3841</v>
       </c>
-      <c r="J13" s="2"/>
+      <c r="J13" s="35"/>
       <c r="K13">
         <v>8.1999999999999993</v>
       </c>
@@ -1157,7 +1516,7 @@
       <c r="M13">
         <v>1.49</v>
       </c>
-      <c r="O13" s="2"/>
+      <c r="O13" s="35"/>
       <c r="P13">
         <v>20.16</v>
       </c>
@@ -1167,7 +1526,7 @@
       <c r="R13">
         <v>3.65</v>
       </c>
-      <c r="T13" s="2"/>
+      <c r="T13" s="35"/>
       <c r="U13" s="1">
         <v>5.76</v>
       </c>
@@ -1179,11 +1538,11 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
+      <c r="A14" s="35"/>
       <c r="B14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="2"/>
+      <c r="C14" s="35"/>
       <c r="D14">
         <v>10.08</v>
       </c>
@@ -1199,10 +1558,10 @@
       <c r="H14">
         <v>147.7028</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="35">
         <v>65.11</v>
       </c>
-      <c r="J14" s="2"/>
+      <c r="J14" s="35"/>
       <c r="K14">
         <v>7.47</v>
       </c>
@@ -1212,10 +1571,10 @@
       <c r="M14">
         <v>0</v>
       </c>
-      <c r="N14" s="2">
+      <c r="N14" s="35">
         <v>80.66</v>
       </c>
-      <c r="O14" s="2"/>
+      <c r="O14" s="35"/>
       <c r="P14">
         <v>17.05</v>
       </c>
@@ -1225,10 +1584,10 @@
       <c r="R14" s="1">
         <v>1.22</v>
       </c>
-      <c r="S14" s="2">
+      <c r="S14" s="35">
         <v>34.19</v>
       </c>
-      <c r="T14" s="2"/>
+      <c r="T14" s="35"/>
       <c r="U14">
         <v>4.76</v>
       </c>
@@ -1238,16 +1597,16 @@
       <c r="W14" s="1">
         <v>0.27</v>
       </c>
-      <c r="X14" s="2">
+      <c r="X14" s="35">
         <v>74.290000000000006</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
+      <c r="A15" s="35"/>
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="35"/>
       <c r="D15">
         <v>9.15</v>
       </c>
@@ -1263,8 +1622,8 @@
       <c r="H15">
         <v>159.09700000000001</v>
       </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
       <c r="K15">
         <v>5.88</v>
       </c>
@@ -1274,8 +1633,8 @@
       <c r="M15">
         <v>0</v>
       </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="35"/>
       <c r="P15">
         <v>16.07</v>
       </c>
@@ -1285,8 +1644,8 @@
       <c r="R15" s="1">
         <v>1.42</v>
       </c>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
+      <c r="S15" s="35"/>
+      <c r="T15" s="35"/>
       <c r="U15" s="1">
         <v>5.26</v>
       </c>
@@ -1296,14 +1655,14 @@
       <c r="W15" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="X15" s="2"/>
+      <c r="X15" s="35"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A16" s="2"/>
+      <c r="A16" s="35"/>
       <c r="B16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="2"/>
+      <c r="C16" s="35"/>
       <c r="D16">
         <v>7.89</v>
       </c>
@@ -1319,8 +1678,8 @@
       <c r="H16">
         <v>168.54599999999999</v>
       </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
       <c r="K16">
         <v>5.14</v>
       </c>
@@ -1330,8 +1689,8 @@
       <c r="M16">
         <v>0</v>
       </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="35"/>
       <c r="P16">
         <v>14.1</v>
       </c>
@@ -1341,8 +1700,8 @@
       <c r="R16" s="1">
         <v>0.81</v>
       </c>
-      <c r="S16" s="2"/>
-      <c r="T16" s="2"/>
+      <c r="S16" s="35"/>
+      <c r="T16" s="35"/>
       <c r="U16">
         <v>4.01</v>
       </c>
@@ -1352,16 +1711,16 @@
       <c r="W16" s="1">
         <v>0</v>
       </c>
-      <c r="X16" s="2"/>
+      <c r="X16" s="35"/>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="35" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="35">
         <v>29.96</v>
       </c>
       <c r="D17">
@@ -1379,7 +1738,7 @@
       <c r="H17">
         <v>3.6791999999999998</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="35">
         <v>28.64</v>
       </c>
       <c r="K17">
@@ -1391,7 +1750,7 @@
       <c r="M17">
         <v>1.2</v>
       </c>
-      <c r="O17" s="2">
+      <c r="O17" s="35">
         <v>40.82</v>
       </c>
       <c r="P17">
@@ -1403,7 +1762,7 @@
       <c r="R17" s="1">
         <v>1.66</v>
       </c>
-      <c r="T17" s="2">
+      <c r="T17" s="35">
         <v>16.04</v>
       </c>
       <c r="U17">
@@ -1417,11 +1776,11 @@
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
+      <c r="A18" s="35"/>
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="2"/>
+      <c r="C18" s="35"/>
       <c r="D18">
         <v>36.31</v>
       </c>
@@ -1437,7 +1796,7 @@
       <c r="H18">
         <v>26.883299999999998</v>
       </c>
-      <c r="J18" s="2"/>
+      <c r="J18" s="35"/>
       <c r="K18">
         <v>31.46</v>
       </c>
@@ -1447,7 +1806,7 @@
       <c r="M18">
         <v>23.16</v>
       </c>
-      <c r="O18" s="2"/>
+      <c r="O18" s="35"/>
       <c r="P18">
         <v>48.2</v>
       </c>
@@ -1457,7 +1816,7 @@
       <c r="R18" s="1">
         <v>22.16</v>
       </c>
-      <c r="T18" s="2"/>
+      <c r="T18" s="35"/>
       <c r="U18">
         <v>28.07</v>
       </c>
@@ -1469,11 +1828,11 @@
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
+      <c r="A19" s="35"/>
       <c r="B19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="2"/>
+      <c r="C19" s="35"/>
       <c r="D19">
         <v>55.31</v>
       </c>
@@ -1489,7 +1848,7 @@
       <c r="H19">
         <v>24.215399999999999</v>
       </c>
-      <c r="J19" s="2"/>
+      <c r="J19" s="35"/>
       <c r="K19">
         <v>53.12</v>
       </c>
@@ -1499,7 +1858,7 @@
       <c r="M19">
         <v>40.82</v>
       </c>
-      <c r="O19" s="2"/>
+      <c r="O19" s="35"/>
       <c r="P19">
         <v>66.89</v>
       </c>
@@ -1509,7 +1868,7 @@
       <c r="R19" s="1">
         <v>50.69</v>
       </c>
-      <c r="T19" s="2"/>
+      <c r="T19" s="35"/>
       <c r="U19">
         <v>42.11</v>
       </c>
@@ -1521,11 +1880,11 @@
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
+      <c r="A20" s="35"/>
       <c r="B20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="2"/>
+      <c r="C20" s="35"/>
       <c r="D20">
         <v>20.87</v>
       </c>
@@ -1541,7 +1900,7 @@
       <c r="H20">
         <v>2.9369000000000001</v>
       </c>
-      <c r="J20" s="2"/>
+      <c r="J20" s="35"/>
       <c r="K20">
         <v>14.93</v>
       </c>
@@ -1551,7 +1910,7 @@
       <c r="M20">
         <v>1.54</v>
       </c>
-      <c r="O20" s="2"/>
+      <c r="O20" s="35"/>
       <c r="P20">
         <v>36.72</v>
       </c>
@@ -1561,7 +1920,7 @@
       <c r="R20">
         <v>5.26</v>
       </c>
-      <c r="T20" s="2"/>
+      <c r="T20" s="35"/>
       <c r="U20">
         <v>8.77</v>
       </c>
@@ -1573,11 +1932,11 @@
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
+      <c r="A21" s="35"/>
       <c r="B21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="2"/>
+      <c r="C21" s="35"/>
       <c r="D21">
         <v>18.89</v>
       </c>
@@ -1593,10 +1952,10 @@
       <c r="H21">
         <v>22.941400000000002</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I21" s="35">
         <v>48.81</v>
       </c>
-      <c r="J21" s="2"/>
+      <c r="J21" s="35"/>
       <c r="K21">
         <v>12.48</v>
       </c>
@@ -1606,10 +1965,10 @@
       <c r="M21">
         <v>1.03</v>
       </c>
-      <c r="N21" s="2">
+      <c r="N21" s="35">
         <v>67.09</v>
       </c>
-      <c r="O21" s="2"/>
+      <c r="O21" s="35"/>
       <c r="P21">
         <v>34.590000000000003</v>
       </c>
@@ -1619,10 +1978,10 @@
       <c r="R21">
         <v>2.2200000000000002</v>
       </c>
-      <c r="S21" s="2">
+      <c r="S21" s="35">
         <v>30.12</v>
       </c>
-      <c r="T21" s="2"/>
+      <c r="T21" s="35"/>
       <c r="U21">
         <v>8.02</v>
       </c>
@@ -1632,16 +1991,16 @@
       <c r="W21">
         <v>0</v>
       </c>
-      <c r="X21" s="2">
+      <c r="X21" s="35">
         <v>54.69</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
+      <c r="A22" s="35"/>
       <c r="B22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="2"/>
+      <c r="C22" s="35"/>
       <c r="D22">
         <v>17.8</v>
       </c>
@@ -1657,8 +2016,8 @@
       <c r="H22">
         <v>23.260400000000001</v>
       </c>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
       <c r="K22">
         <v>10.89</v>
       </c>
@@ -1668,8 +2027,8 @@
       <c r="M22">
         <v>1.2</v>
       </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="35"/>
       <c r="P22">
         <v>33.61</v>
       </c>
@@ -1679,8 +2038,8 @@
       <c r="R22">
         <v>2.2200000000000002</v>
       </c>
-      <c r="S22" s="2"/>
-      <c r="T22" s="2"/>
+      <c r="S22" s="35"/>
+      <c r="T22" s="35"/>
       <c r="U22">
         <v>7.77</v>
       </c>
@@ -1690,14 +2049,14 @@
       <c r="W22">
         <v>0</v>
       </c>
-      <c r="X22" s="2"/>
+      <c r="X22" s="35"/>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
+      <c r="A23" s="35"/>
       <c r="B23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="2"/>
+      <c r="C23" s="35"/>
       <c r="D23">
         <v>16.43</v>
       </c>
@@ -1713,8 +2072,8 @@
       <c r="H23">
         <v>52.032899999999998</v>
       </c>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
       <c r="K23">
         <v>10.039999999999999</v>
       </c>
@@ -1724,8 +2083,8 @@
       <c r="M23">
         <v>0.69</v>
       </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="35"/>
       <c r="P23">
         <v>30.82</v>
       </c>
@@ -1735,8 +2094,8 @@
       <c r="R23">
         <v>1.1100000000000001</v>
       </c>
-      <c r="S23" s="2"/>
-      <c r="T23" s="2"/>
+      <c r="S23" s="35"/>
+      <c r="T23" s="35"/>
       <c r="U23">
         <v>7.52</v>
       </c>
@@ -1746,16 +2105,16 @@
       <c r="W23">
         <v>0</v>
       </c>
-      <c r="X23" s="2"/>
+      <c r="X23" s="35"/>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="35" t="s">
         <v>20</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="35">
         <v>44.74</v>
       </c>
       <c r="D24">
@@ -1773,7 +2132,7 @@
       <c r="H24">
         <v>15.446099999999999</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J24" s="35">
         <v>38.07</v>
       </c>
       <c r="K24">
@@ -1785,7 +2144,7 @@
       <c r="M24">
         <v>5.14</v>
       </c>
-      <c r="O24" s="2">
+      <c r="O24" s="35">
         <v>56.89</v>
       </c>
       <c r="P24">
@@ -1797,7 +2156,7 @@
       <c r="R24">
         <v>6.84</v>
       </c>
-      <c r="T24" s="2">
+      <c r="T24" s="35">
         <v>39.85</v>
       </c>
       <c r="U24">
@@ -1811,11 +2170,11 @@
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
+      <c r="A25" s="35"/>
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="2"/>
+      <c r="C25" s="35"/>
       <c r="D25">
         <v>40.53</v>
       </c>
@@ -1831,7 +2190,7 @@
       <c r="H25">
         <v>27.349599999999999</v>
       </c>
-      <c r="J25" s="2"/>
+      <c r="J25" s="35"/>
       <c r="K25">
         <v>26.44</v>
       </c>
@@ -1841,7 +2200,7 @@
       <c r="M25">
         <v>14.03</v>
       </c>
-      <c r="O25" s="2"/>
+      <c r="O25" s="35"/>
       <c r="P25">
         <v>61.97</v>
       </c>
@@ -1851,7 +2210,7 @@
       <c r="R25">
         <v>26.62</v>
       </c>
-      <c r="T25" s="2"/>
+      <c r="T25" s="35"/>
       <c r="U25">
         <v>36.590000000000003</v>
       </c>
@@ -1863,11 +2222,11 @@
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A26" s="2"/>
+      <c r="A26" s="35"/>
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="2"/>
+      <c r="C26" s="35"/>
       <c r="D26">
         <v>45.02</v>
       </c>
@@ -1883,7 +2242,7 @@
       <c r="H26">
         <v>35.505099999999999</v>
       </c>
-      <c r="J26" s="2"/>
+      <c r="J26" s="35"/>
       <c r="K26">
         <v>34.39</v>
       </c>
@@ -1893,7 +2252,7 @@
       <c r="M26">
         <v>19.96</v>
       </c>
-      <c r="O26" s="2"/>
+      <c r="O26" s="35"/>
       <c r="P26">
         <v>63.28</v>
       </c>
@@ -1903,7 +2262,7 @@
       <c r="R26">
         <v>30.04</v>
       </c>
-      <c r="T26" s="2"/>
+      <c r="T26" s="35"/>
       <c r="U26">
         <v>38.85</v>
       </c>
@@ -1915,11 +2274,11 @@
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A27" s="2"/>
+      <c r="A27" s="35"/>
       <c r="B27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C27" s="2"/>
+      <c r="C27" s="35"/>
       <c r="D27">
         <v>31.16</v>
       </c>
@@ -1935,7 +2294,7 @@
       <c r="H27">
         <v>1.3381000000000001</v>
       </c>
-      <c r="J27" s="2"/>
+      <c r="J27" s="35"/>
       <c r="K27">
         <v>12.97</v>
       </c>
@@ -1945,7 +2304,7 @@
       <c r="M27">
         <v>2.96</v>
       </c>
-      <c r="O27" s="2"/>
+      <c r="O27" s="35"/>
       <c r="P27">
         <v>53.28</v>
       </c>
@@ -1955,7 +2314,7 @@
       <c r="R27">
         <v>14.07</v>
       </c>
-      <c r="T27" s="2"/>
+      <c r="T27" s="35"/>
       <c r="U27">
         <v>34.590000000000003</v>
       </c>
@@ -1967,11 +2326,11 @@
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A28" s="2"/>
+      <c r="A28" s="35"/>
       <c r="B28" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="2"/>
+      <c r="C28" s="35"/>
       <c r="D28">
         <v>28.31</v>
       </c>
@@ -1987,10 +2346,10 @@
       <c r="H28">
         <v>13.305</v>
       </c>
-      <c r="I28" s="2">
+      <c r="I28" s="35">
         <v>48.1</v>
       </c>
-      <c r="J28" s="2"/>
+      <c r="J28" s="35"/>
       <c r="K28">
         <v>11.75</v>
       </c>
@@ -2000,10 +2359,10 @@
       <c r="M28">
         <v>1.58</v>
       </c>
-      <c r="N28" s="2">
+      <c r="N28" s="35">
         <v>76.209999999999994</v>
       </c>
-      <c r="O28" s="2"/>
+      <c r="O28" s="35"/>
       <c r="P28">
         <v>50.16</v>
       </c>
@@ -2013,10 +2372,10 @@
       <c r="R28">
         <v>6.08</v>
       </c>
-      <c r="S28" s="2">
+      <c r="S28" s="35">
         <v>23.05</v>
       </c>
-      <c r="T28" s="2"/>
+      <c r="T28" s="35"/>
       <c r="U28">
         <v>28.82</v>
       </c>
@@ -2026,16 +2385,16 @@
       <c r="W28">
         <v>5</v>
       </c>
-      <c r="X28" s="2">
+      <c r="X28" s="35">
         <v>47.8</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A29" s="2"/>
+      <c r="A29" s="35"/>
       <c r="B29" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="2"/>
+      <c r="C29" s="35"/>
       <c r="D29">
         <v>27.66</v>
       </c>
@@ -2051,8 +2410,8 @@
       <c r="H29">
         <v>15.7463</v>
       </c>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="35"/>
       <c r="K29">
         <v>11.75</v>
       </c>
@@ -2062,8 +2421,8 @@
       <c r="M29">
         <v>1.78</v>
       </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+      <c r="N29" s="35"/>
+      <c r="O29" s="35"/>
       <c r="P29">
         <v>49.18</v>
       </c>
@@ -2073,8 +2432,8 @@
       <c r="R29">
         <v>5.7</v>
       </c>
-      <c r="S29" s="2"/>
-      <c r="T29" s="2"/>
+      <c r="S29" s="35"/>
+      <c r="T29" s="35"/>
       <c r="U29">
         <v>27.32</v>
       </c>
@@ -2084,14 +2443,14 @@
       <c r="W29">
         <v>5.42</v>
       </c>
-      <c r="X29" s="2"/>
+      <c r="X29" s="35"/>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A30" s="2"/>
+      <c r="A30" s="35"/>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="2"/>
+      <c r="C30" s="35"/>
       <c r="D30">
         <v>25.96</v>
       </c>
@@ -2107,8 +2466,8 @@
       <c r="H30">
         <v>21.763400000000001</v>
       </c>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
       <c r="K30">
         <v>10.28</v>
       </c>
@@ -2118,8 +2477,8 @@
       <c r="M30">
         <v>1.19</v>
       </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+      <c r="N30" s="35"/>
+      <c r="O30" s="35"/>
       <c r="P30">
         <v>47.54</v>
       </c>
@@ -2129,8 +2488,8 @@
       <c r="R30">
         <v>4.18</v>
       </c>
-      <c r="S30" s="2"/>
-      <c r="T30" s="2"/>
+      <c r="S30" s="35"/>
+      <c r="T30" s="35"/>
       <c r="U30">
         <v>25.06</v>
       </c>
@@ -2140,23 +2499,827 @@
       <c r="W30">
         <v>3.75</v>
       </c>
-      <c r="X30" s="2"/>
+      <c r="X30" s="35"/>
+    </row>
+    <row r="34" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="F34" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="G34" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="H34" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="I34" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="J34" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="K34" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="L34" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="M34" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N34" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="O34" s="23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="30"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" s="26"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="H35" s="26"/>
+      <c r="I35" s="27"/>
+      <c r="J35" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="K35" s="28"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="N35" s="28"/>
+      <c r="O35" s="28"/>
+    </row>
+    <row r="36" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" s="16">
+        <v>22.95</v>
+      </c>
+      <c r="E36" s="16">
+        <v>49.45</v>
+      </c>
+      <c r="F36" s="10">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="G36" s="16">
+        <v>24.6</v>
+      </c>
+      <c r="H36" s="16">
+        <v>56.95</v>
+      </c>
+      <c r="I36" s="10">
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="J36" s="16">
+        <v>28.52</v>
+      </c>
+      <c r="K36" s="16">
+        <v>27.16</v>
+      </c>
+      <c r="L36" s="22">
+        <v>1.32</v>
+      </c>
+      <c r="M36" s="16">
+        <v>11.28</v>
+      </c>
+      <c r="N36" s="16">
+        <v>68.599999999999994</v>
+      </c>
+      <c r="O36" s="21">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" ht="15" x14ac:dyDescent="0.2">
+      <c r="B37" s="33"/>
+      <c r="C37" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" s="16">
+        <v>25.03</v>
+      </c>
+      <c r="E37" s="16">
+        <v>55.23</v>
+      </c>
+      <c r="F37" s="10">
+        <v>12</v>
+      </c>
+      <c r="G37" s="16">
+        <v>23.38</v>
+      </c>
+      <c r="H37" s="16">
+        <v>67.11</v>
+      </c>
+      <c r="I37" s="10">
+        <v>15.35</v>
+      </c>
+      <c r="J37" s="16">
+        <v>35.9</v>
+      </c>
+      <c r="K37" s="16">
+        <v>25.43</v>
+      </c>
+      <c r="L37" s="10">
+        <v>12.17</v>
+      </c>
+      <c r="M37" s="16">
+        <v>11.78</v>
+      </c>
+      <c r="N37" s="21">
+        <v>75.209999999999994</v>
+      </c>
+      <c r="O37" s="16">
+        <v>6.12</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" ht="15" x14ac:dyDescent="0.2">
+      <c r="B38" s="33"/>
+      <c r="C38" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" s="16">
+        <v>25.58</v>
+      </c>
+      <c r="E38" s="16">
+        <v>53.72</v>
+      </c>
+      <c r="F38" s="10">
+        <v>11.91</v>
+      </c>
+      <c r="G38" s="16">
+        <v>22.4</v>
+      </c>
+      <c r="H38" s="16">
+        <v>62.3</v>
+      </c>
+      <c r="I38" s="10">
+        <v>9.48</v>
+      </c>
+      <c r="J38" s="16">
+        <v>38.03</v>
+      </c>
+      <c r="K38" s="16">
+        <v>31.47</v>
+      </c>
+      <c r="L38" s="10">
+        <v>19.309999999999999</v>
+      </c>
+      <c r="M38" s="16">
+        <v>13.03</v>
+      </c>
+      <c r="N38" s="16">
+        <v>70.25</v>
+      </c>
+      <c r="O38" s="16">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" ht="15" x14ac:dyDescent="0.2">
+      <c r="B39" s="34"/>
+      <c r="C39" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39" s="18">
+        <v>14.07</v>
+      </c>
+      <c r="E39" s="18">
+        <v>69.05</v>
+      </c>
+      <c r="F39" s="19">
+        <v>2.91</v>
+      </c>
+      <c r="G39" s="18">
+        <v>6.61</v>
+      </c>
+      <c r="H39" s="18">
+        <v>87.97</v>
+      </c>
+      <c r="I39" s="19">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="J39" s="18">
+        <v>26.39</v>
+      </c>
+      <c r="K39" s="18">
+        <v>35.78</v>
+      </c>
+      <c r="L39" s="6">
+        <v>3.17</v>
+      </c>
+      <c r="M39" s="18">
+        <v>10.53</v>
+      </c>
+      <c r="N39" s="20">
+        <v>74.38</v>
+      </c>
+      <c r="O39" s="20">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="B40" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D40" s="17">
+        <v>15.44</v>
+      </c>
+      <c r="E40" s="17">
+        <v>29.4</v>
+      </c>
+      <c r="F40" s="13">
+        <v>1.71</v>
+      </c>
+      <c r="G40" s="17">
+        <v>18.12</v>
+      </c>
+      <c r="H40" s="17">
+        <v>38.68</v>
+      </c>
+      <c r="I40" s="13">
+        <v>2.98</v>
+      </c>
+      <c r="J40" s="11">
+        <v>17.05</v>
+      </c>
+      <c r="K40" s="11">
+        <v>15.38</v>
+      </c>
+      <c r="L40" s="13">
+        <v>1.01</v>
+      </c>
+      <c r="M40" s="11">
+        <v>7.52</v>
+      </c>
+      <c r="N40" s="17">
+        <v>20</v>
+      </c>
+      <c r="O40" s="11">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="B41" s="33"/>
+      <c r="C41" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41" s="7">
+        <v>17.03</v>
+      </c>
+      <c r="E41" s="7">
+        <v>41.76</v>
+      </c>
+      <c r="F41" s="10">
+        <v>6.77</v>
+      </c>
+      <c r="G41" s="7">
+        <v>16.77</v>
+      </c>
+      <c r="H41" s="16">
+        <v>57.08</v>
+      </c>
+      <c r="I41" s="8">
+        <v>7.6</v>
+      </c>
+      <c r="J41" s="16">
+        <v>22.3</v>
+      </c>
+      <c r="K41" s="16">
+        <v>17.95</v>
+      </c>
+      <c r="L41" s="10">
+        <v>8.11</v>
+      </c>
+      <c r="M41" s="16">
+        <v>9.52</v>
+      </c>
+      <c r="N41" s="16">
+        <v>28.57</v>
+      </c>
+      <c r="O41" s="16">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="B42" s="33"/>
+      <c r="C42" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="E42" s="7">
+        <v>43.68</v>
+      </c>
+      <c r="F42" s="8">
+        <v>5.34</v>
+      </c>
+      <c r="G42" s="16">
+        <v>13.83</v>
+      </c>
+      <c r="H42" s="7">
+        <v>57.55</v>
+      </c>
+      <c r="I42" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="J42" s="7">
+        <v>22.62</v>
+      </c>
+      <c r="K42" s="7">
+        <v>15.38</v>
+      </c>
+      <c r="L42" s="10">
+        <v>7.91</v>
+      </c>
+      <c r="M42" s="7">
+        <v>8.02</v>
+      </c>
+      <c r="N42" s="7">
+        <v>54.29</v>
+      </c>
+      <c r="O42" s="16">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="B43" s="34"/>
+      <c r="C43" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="3">
+        <v>7.89</v>
+      </c>
+      <c r="E43" s="3">
+        <v>61.54</v>
+      </c>
+      <c r="F43" s="4">
+        <v>0.27</v>
+      </c>
+      <c r="G43" s="3">
+        <v>5.14</v>
+      </c>
+      <c r="H43" s="3">
+        <v>80.19</v>
+      </c>
+      <c r="I43" s="4">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
+        <v>14.1</v>
+      </c>
+      <c r="K43" s="3">
+        <v>29.91</v>
+      </c>
+      <c r="L43" s="19">
+        <v>0.81</v>
+      </c>
+      <c r="M43" s="3">
+        <v>4.01</v>
+      </c>
+      <c r="N43" s="18">
+        <v>54.29</v>
+      </c>
+      <c r="O43" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="B44" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D44" s="11">
+        <v>23.38</v>
+      </c>
+      <c r="E44" s="11">
+        <v>24.5</v>
+      </c>
+      <c r="F44" s="12">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="G44" s="11">
+        <v>17.38</v>
+      </c>
+      <c r="H44" s="11">
+        <v>42.31</v>
+      </c>
+      <c r="I44" s="12">
+        <v>1.2</v>
+      </c>
+      <c r="J44" s="11">
+        <v>38.85</v>
+      </c>
+      <c r="K44" s="11">
+        <v>7.23</v>
+      </c>
+      <c r="L44" s="13">
+        <v>1.66</v>
+      </c>
+      <c r="M44" s="11">
+        <v>12.03</v>
+      </c>
+      <c r="N44" s="17">
+        <v>26.56</v>
+      </c>
+      <c r="O44" s="17">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="B45" s="33"/>
+      <c r="C45" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" s="7">
+        <v>36.31</v>
+      </c>
+      <c r="E45" s="7">
+        <v>31.08</v>
+      </c>
+      <c r="F45" s="8">
+        <v>22.36</v>
+      </c>
+      <c r="G45" s="7">
+        <v>31.46</v>
+      </c>
+      <c r="H45" s="7">
+        <v>47.86</v>
+      </c>
+      <c r="I45" s="8">
+        <v>23.16</v>
+      </c>
+      <c r="J45" s="7">
+        <v>48.2</v>
+      </c>
+      <c r="K45" s="7">
+        <v>14.06</v>
+      </c>
+      <c r="L45" s="10">
+        <v>22.16</v>
+      </c>
+      <c r="M45" s="7">
+        <v>28.07</v>
+      </c>
+      <c r="N45" s="16">
+        <v>35.94</v>
+      </c>
+      <c r="O45" s="16">
+        <v>21.19</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="B46" s="33"/>
+      <c r="C46" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" s="7">
+        <v>55.31</v>
+      </c>
+      <c r="E46" s="7">
+        <v>14.08</v>
+      </c>
+      <c r="F46" s="8">
+        <v>41.14</v>
+      </c>
+      <c r="G46" s="7">
+        <v>53.12</v>
+      </c>
+      <c r="H46" s="7">
+        <v>16.670000000000002</v>
+      </c>
+      <c r="I46" s="8">
+        <v>40.82</v>
+      </c>
+      <c r="J46" s="7">
+        <v>66.89</v>
+      </c>
+      <c r="K46" s="7">
+        <v>9.64</v>
+      </c>
+      <c r="L46" s="10">
+        <v>50.69</v>
+      </c>
+      <c r="M46" s="7">
+        <v>42.11</v>
+      </c>
+      <c r="N46" s="7">
+        <v>21.88</v>
+      </c>
+      <c r="O46" s="7">
+        <v>35.22</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="B47" s="34"/>
+      <c r="C47" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47" s="3">
+        <v>16.43</v>
+      </c>
+      <c r="E47" s="3">
+        <v>46.62</v>
+      </c>
+      <c r="F47" s="4">
+        <v>0.63</v>
+      </c>
+      <c r="G47" s="3">
+        <v>10.039999999999999</v>
+      </c>
+      <c r="H47" s="3">
+        <v>66.67</v>
+      </c>
+      <c r="I47" s="4">
+        <v>0.69</v>
+      </c>
+      <c r="J47" s="15">
+        <v>30.82</v>
+      </c>
+      <c r="K47" s="15">
+        <v>26.1</v>
+      </c>
+      <c r="L47" s="14">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="M47" s="3">
+        <v>7.52</v>
+      </c>
+      <c r="N47" s="3">
+        <v>53.12</v>
+      </c>
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="B48" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D48" s="11">
+        <v>36.14</v>
+      </c>
+      <c r="E48" s="11">
+        <v>26.19</v>
+      </c>
+      <c r="F48" s="12">
+        <v>5.65</v>
+      </c>
+      <c r="G48" s="11">
+        <v>24.24</v>
+      </c>
+      <c r="H48" s="11">
+        <v>44.69</v>
+      </c>
+      <c r="I48" s="12">
+        <v>5.14</v>
+      </c>
+      <c r="J48" s="11">
+        <v>53.44</v>
+      </c>
+      <c r="K48" s="11">
+        <v>11.24</v>
+      </c>
+      <c r="L48" s="12">
+        <v>6.84</v>
+      </c>
+      <c r="M48" s="11">
+        <v>34.090000000000003</v>
+      </c>
+      <c r="N48" s="11">
+        <v>22.64</v>
+      </c>
+      <c r="O48" s="11">
+        <v>5.42</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="B49" s="33"/>
+      <c r="C49" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" s="7">
+        <v>40.53</v>
+      </c>
+      <c r="E49" s="7">
+        <v>31.95</v>
+      </c>
+      <c r="F49" s="8">
+        <v>18.43</v>
+      </c>
+      <c r="G49" s="7">
+        <v>26.44</v>
+      </c>
+      <c r="H49" s="7">
+        <v>52.73</v>
+      </c>
+      <c r="I49" s="8">
+        <v>14.03</v>
+      </c>
+      <c r="J49" s="7">
+        <v>61.97</v>
+      </c>
+      <c r="K49" s="7">
+        <v>11.24</v>
+      </c>
+      <c r="L49" s="8">
+        <v>26.62</v>
+      </c>
+      <c r="M49" s="7">
+        <v>36.590000000000003</v>
+      </c>
+      <c r="N49" s="7">
+        <v>36.479999999999997</v>
+      </c>
+      <c r="O49" s="7">
+        <v>18.75</v>
+      </c>
+    </row>
+    <row r="50" spans="2:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="B50" s="33"/>
+      <c r="C50" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" s="7">
+        <v>45.02</v>
+      </c>
+      <c r="E50" s="7">
+        <v>27.54</v>
+      </c>
+      <c r="F50" s="8">
+        <v>22.79</v>
+      </c>
+      <c r="G50" s="7">
+        <v>34.39</v>
+      </c>
+      <c r="H50" s="7">
+        <v>42.77</v>
+      </c>
+      <c r="I50" s="8">
+        <v>19.96</v>
+      </c>
+      <c r="J50" s="7">
+        <v>63.28</v>
+      </c>
+      <c r="K50" s="7">
+        <v>11.53</v>
+      </c>
+      <c r="L50" s="8">
+        <v>30.04</v>
+      </c>
+      <c r="M50" s="7">
+        <v>38.85</v>
+      </c>
+      <c r="N50" s="7">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="O50" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="2:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="B51" s="34"/>
+      <c r="C51" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" s="3">
+        <v>25.96</v>
+      </c>
+      <c r="E51" s="3">
+        <v>45.17</v>
+      </c>
+      <c r="F51" s="4">
+        <v>2.58</v>
+      </c>
+      <c r="G51" s="3">
+        <v>10.28</v>
+      </c>
+      <c r="H51" s="3">
+        <v>74.92</v>
+      </c>
+      <c r="I51" s="4">
+        <v>1.19</v>
+      </c>
+      <c r="J51" s="3">
+        <v>47.54</v>
+      </c>
+      <c r="K51" s="3">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="L51" s="4">
+        <v>4.18</v>
+      </c>
+      <c r="M51" s="3">
+        <v>25.06</v>
+      </c>
+      <c r="N51" s="3">
+        <v>42.77</v>
+      </c>
+      <c r="O51" s="3">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="54" spans="2:15" ht="15" x14ac:dyDescent="0.2">
+      <c r="B54" s="2"/>
+      <c r="C54" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="55" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B55" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C55" s="2">
+        <v>15</v>
+      </c>
+      <c r="D55" s="2">
+        <v>68.349999999999994</v>
+      </c>
+      <c r="E55" s="2">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="56" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B56" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C56" s="2">
+        <v>17.22</v>
+      </c>
+      <c r="D56" s="2">
+        <v>67.09</v>
+      </c>
+      <c r="E56" s="2">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="57" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B57" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C57" s="2">
+        <v>17.22</v>
+      </c>
+      <c r="D57" s="2">
+        <v>64.56</v>
+      </c>
+      <c r="E57" s="2">
+        <v>2.97</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="A10:A16"/>
-    <mergeCell ref="C10:C16"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="J24:J30"/>
+  <mergeCells count="49">
+    <mergeCell ref="A24:A30"/>
+    <mergeCell ref="C24:C30"/>
     <mergeCell ref="O24:O30"/>
     <mergeCell ref="T17:T23"/>
     <mergeCell ref="X21:X23"/>
     <mergeCell ref="X14:X16"/>
     <mergeCell ref="J1:N1"/>
     <mergeCell ref="N7:N9"/>
-    <mergeCell ref="A24:A30"/>
     <mergeCell ref="S7:S9"/>
+    <mergeCell ref="S21:S23"/>
+    <mergeCell ref="T24:T30"/>
+    <mergeCell ref="N28:N30"/>
+    <mergeCell ref="S28:S30"/>
+    <mergeCell ref="X28:X30"/>
+    <mergeCell ref="J24:J30"/>
     <mergeCell ref="A3:A9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J3:J9"/>
@@ -2166,15 +3329,9 @@
     <mergeCell ref="J17:J23"/>
     <mergeCell ref="N21:N23"/>
     <mergeCell ref="O17:O23"/>
-    <mergeCell ref="S21:S23"/>
-    <mergeCell ref="C24:C30"/>
-    <mergeCell ref="T24:T30"/>
-    <mergeCell ref="N28:N30"/>
-    <mergeCell ref="S28:S30"/>
-    <mergeCell ref="X28:X30"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="C3:C9"/>
-    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="A10:A16"/>
+    <mergeCell ref="C10:C16"/>
+    <mergeCell ref="A17:A23"/>
     <mergeCell ref="J10:J16"/>
     <mergeCell ref="X7:X9"/>
     <mergeCell ref="O1:S1"/>
@@ -2184,6 +3341,19 @@
     <mergeCell ref="T10:T16"/>
     <mergeCell ref="N14:N16"/>
     <mergeCell ref="S14:S16"/>
+    <mergeCell ref="B40:B43"/>
+    <mergeCell ref="B36:B39"/>
+    <mergeCell ref="B48:B51"/>
+    <mergeCell ref="B44:B47"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/stat/data.xlsx
+++ b/stat/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr-PC\Documents\Workspace\LLMHalluMiti\stat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B957F8D4-DD5F-4D87-9937-EC5114F60A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1872A4-BDD8-47DE-B3F8-B380071AEBD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="43">
   <si>
     <t>gpt-4o</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -489,6 +489,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -507,20 +519,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -802,42 +802,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:Y87"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35" t="s">
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35" t="s">
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35" t="s">
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
@@ -910,13 +910,13 @@
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="35">
+      <c r="C3" s="26">
         <v>39.81</v>
       </c>
       <c r="D3" s="1">
@@ -935,7 +935,7 @@
         <v>4.9604999999999997</v>
       </c>
       <c r="I3" s="1"/>
-      <c r="J3" s="35">
+      <c r="J3" s="26">
         <v>45.78</v>
       </c>
       <c r="K3" s="1">
@@ -948,7 +948,7 @@
         <v>9.0299999999999994</v>
       </c>
       <c r="N3" s="1"/>
-      <c r="O3" s="35">
+      <c r="O3" s="26">
         <v>38.03</v>
       </c>
       <c r="P3" s="1">
@@ -961,7 +961,7 @@
         <v>1.32</v>
       </c>
       <c r="S3" s="1"/>
-      <c r="T3" s="35">
+      <c r="T3" s="26">
         <v>30.33</v>
       </c>
       <c r="U3" s="1">
@@ -976,11 +976,11 @@
       <c r="X3" s="1"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A4" s="35"/>
+      <c r="A4" s="26"/>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="35"/>
+      <c r="C4" s="26"/>
       <c r="D4" s="1">
         <v>25.03</v>
       </c>
@@ -997,7 +997,7 @@
         <v>22.125900000000001</v>
       </c>
       <c r="I4" s="1"/>
-      <c r="J4" s="35"/>
+      <c r="J4" s="26"/>
       <c r="K4" s="1">
         <v>23.38</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>15.35</v>
       </c>
       <c r="N4" s="1"/>
-      <c r="O4" s="35"/>
+      <c r="O4" s="26"/>
       <c r="P4" s="1">
         <v>35.9</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>12.17</v>
       </c>
       <c r="S4" s="1"/>
-      <c r="T4" s="35"/>
+      <c r="T4" s="26"/>
       <c r="U4" s="1">
         <v>11.78</v>
       </c>
@@ -1032,11 +1032,11 @@
       <c r="X4" s="1"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A5" s="35"/>
+      <c r="A5" s="26"/>
       <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="35"/>
+      <c r="C5" s="26"/>
       <c r="D5" s="1">
         <v>25.58</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>33.609499999999997</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="35"/>
+      <c r="J5" s="26"/>
       <c r="K5" s="1">
         <v>22.4</v>
       </c>
@@ -1064,7 +1064,7 @@
         <v>9.48</v>
       </c>
       <c r="N5" s="1"/>
-      <c r="O5" s="35"/>
+      <c r="O5" s="26"/>
       <c r="P5" s="1">
         <v>38.03</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>19.309999999999999</v>
       </c>
       <c r="S5" s="1"/>
-      <c r="T5" s="35"/>
+      <c r="T5" s="26"/>
       <c r="U5" s="1">
         <v>13.03</v>
       </c>
@@ -1088,11 +1088,11 @@
       <c r="X5" s="1"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A6" s="35"/>
+      <c r="A6" s="26"/>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="35"/>
+      <c r="C6" s="26"/>
       <c r="D6" s="1">
         <v>17.579999999999998</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>6.4598000000000004</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="35"/>
+      <c r="J6" s="26"/>
       <c r="K6" s="1">
         <v>10.4</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>7</v>
       </c>
       <c r="N6" s="1"/>
-      <c r="O6" s="35"/>
+      <c r="O6" s="26"/>
       <c r="P6" s="1">
         <v>31.97</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>6.88</v>
       </c>
       <c r="S6" s="1"/>
-      <c r="T6" s="35"/>
+      <c r="T6" s="26"/>
       <c r="U6" s="1">
         <v>10.28</v>
       </c>
@@ -1144,11 +1144,11 @@
       <c r="X6" s="1"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A7" s="35"/>
+      <c r="A7" s="26"/>
       <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="35"/>
+      <c r="C7" s="26"/>
       <c r="D7" s="1">
         <v>15.55</v>
       </c>
@@ -1164,10 +1164,10 @@
       <c r="H7" s="1">
         <v>17.849</v>
       </c>
-      <c r="I7" s="35">
+      <c r="I7" s="26">
         <v>72.760000000000005</v>
       </c>
-      <c r="J7" s="35"/>
+      <c r="J7" s="26"/>
       <c r="K7" s="1">
         <v>7.34</v>
       </c>
@@ -1177,10 +1177,10 @@
       <c r="M7" s="1">
         <v>2.48</v>
       </c>
-      <c r="N7" s="35">
+      <c r="N7" s="26">
         <v>90.37</v>
       </c>
-      <c r="O7" s="35"/>
+      <c r="O7" s="26"/>
       <c r="P7" s="1">
         <v>30.49</v>
       </c>
@@ -1190,10 +1190,10 @@
       <c r="R7" s="1">
         <v>5.29</v>
       </c>
-      <c r="S7" s="35">
+      <c r="S7" s="26">
         <v>39.22</v>
       </c>
-      <c r="T7" s="35"/>
+      <c r="T7" s="26"/>
       <c r="U7" s="1">
         <v>9.52</v>
       </c>
@@ -1203,16 +1203,16 @@
       <c r="W7" s="1">
         <v>4.32</v>
       </c>
-      <c r="X7" s="35">
+      <c r="X7" s="26">
         <v>82.64</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A8" s="35"/>
+      <c r="A8" s="26"/>
       <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="35"/>
+      <c r="C8" s="26"/>
       <c r="D8" s="1">
         <v>19.11</v>
       </c>
@@ -1228,8 +1228,8 @@
       <c r="H8" s="1">
         <v>20.038900000000002</v>
       </c>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
       <c r="K8" s="1">
         <v>8.69</v>
       </c>
@@ -1239,8 +1239,8 @@
       <c r="M8" s="1">
         <v>3.84</v>
       </c>
-      <c r="N8" s="35"/>
-      <c r="O8" s="35"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
       <c r="P8" s="1">
         <v>31.8</v>
       </c>
@@ -1250,8 +1250,8 @@
       <c r="R8" s="1">
         <v>8.1999999999999993</v>
       </c>
-      <c r="S8" s="35"/>
-      <c r="T8" s="35"/>
+      <c r="S8" s="26"/>
+      <c r="T8" s="26"/>
       <c r="U8" s="1">
         <v>21.05</v>
       </c>
@@ -1261,14 +1261,14 @@
       <c r="W8" s="1">
         <v>14.75</v>
       </c>
-      <c r="X8" s="35"/>
+      <c r="X8" s="26"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A9" s="35"/>
+      <c r="A9" s="26"/>
       <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="35"/>
+      <c r="C9" s="26"/>
       <c r="D9" s="1">
         <v>14.07</v>
       </c>
@@ -1284,8 +1284,8 @@
       <c r="H9" s="1">
         <v>22.114799999999999</v>
       </c>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
       <c r="K9" s="1">
         <v>6.61</v>
       </c>
@@ -1295,8 +1295,8 @@
       <c r="M9" s="1">
         <v>2.0299999999999998</v>
       </c>
-      <c r="N9" s="35"/>
-      <c r="O9" s="35"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
       <c r="P9" s="1">
         <v>26.39</v>
       </c>
@@ -1306,8 +1306,8 @@
       <c r="R9" s="1">
         <v>3.17</v>
       </c>
-      <c r="S9" s="35"/>
-      <c r="T9" s="35"/>
+      <c r="S9" s="26"/>
+      <c r="T9" s="26"/>
       <c r="U9" s="1">
         <v>10.53</v>
       </c>
@@ -1317,16 +1317,16 @@
       <c r="W9" s="1">
         <v>3.96</v>
       </c>
-      <c r="X9" s="35"/>
+      <c r="X9" s="26"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A10" s="35" t="s">
+      <c r="A10" s="26" t="s">
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="26">
         <v>19.93</v>
       </c>
       <c r="D10" s="1">
@@ -1344,7 +1344,7 @@
       <c r="H10">
         <v>12.401999999999999</v>
       </c>
-      <c r="J10" s="35">
+      <c r="J10" s="26">
         <v>25.95</v>
       </c>
       <c r="K10" s="1">
@@ -1356,7 +1356,7 @@
       <c r="M10" s="1">
         <v>2.98</v>
       </c>
-      <c r="O10" s="35">
+      <c r="O10" s="26">
         <v>19.18</v>
       </c>
       <c r="P10">
@@ -1368,7 +1368,7 @@
       <c r="R10" s="1">
         <v>1.01</v>
       </c>
-      <c r="T10" s="35">
+      <c r="T10" s="26">
         <v>8.77</v>
       </c>
       <c r="U10">
@@ -1382,11 +1382,11 @@
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A11" s="35"/>
+      <c r="A11" s="26"/>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="35"/>
+      <c r="C11" s="26"/>
       <c r="D11">
         <v>17.03</v>
       </c>
@@ -1402,7 +1402,7 @@
       <c r="H11">
         <v>114.9687</v>
       </c>
-      <c r="J11" s="35"/>
+      <c r="J11" s="26"/>
       <c r="K11">
         <v>16.77</v>
       </c>
@@ -1412,7 +1412,7 @@
       <c r="M11">
         <v>7.6</v>
       </c>
-      <c r="O11" s="35"/>
+      <c r="O11" s="26"/>
       <c r="P11" s="1">
         <v>22.3</v>
       </c>
@@ -1422,7 +1422,7 @@
       <c r="R11" s="1">
         <v>8.11</v>
       </c>
-      <c r="T11" s="35"/>
+      <c r="T11" s="26"/>
       <c r="U11" s="1">
         <v>9.52</v>
       </c>
@@ -1434,11 +1434,11 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A12" s="35"/>
+      <c r="A12" s="26"/>
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="35"/>
+      <c r="C12" s="26"/>
       <c r="D12">
         <v>15.5</v>
       </c>
@@ -1454,7 +1454,7 @@
       <c r="H12">
         <v>113.2599</v>
       </c>
-      <c r="J12" s="35"/>
+      <c r="J12" s="26"/>
       <c r="K12" s="1">
         <v>13.83</v>
       </c>
@@ -1464,7 +1464,7 @@
       <c r="M12">
         <v>3.8</v>
       </c>
-      <c r="O12" s="35"/>
+      <c r="O12" s="26"/>
       <c r="P12">
         <v>22.62</v>
       </c>
@@ -1474,7 +1474,7 @@
       <c r="R12" s="1">
         <v>7.91</v>
       </c>
-      <c r="T12" s="35"/>
+      <c r="T12" s="26"/>
       <c r="U12">
         <v>8.02</v>
       </c>
@@ -1486,11 +1486,11 @@
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A13" s="35"/>
+      <c r="A13" s="26"/>
       <c r="B13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="35"/>
+      <c r="C13" s="26"/>
       <c r="D13">
         <v>11.66</v>
       </c>
@@ -1506,7 +1506,7 @@
       <c r="H13">
         <v>17.3841</v>
       </c>
-      <c r="J13" s="35"/>
+      <c r="J13" s="26"/>
       <c r="K13">
         <v>8.1999999999999993</v>
       </c>
@@ -1516,7 +1516,7 @@
       <c r="M13">
         <v>1.49</v>
       </c>
-      <c r="O13" s="35"/>
+      <c r="O13" s="26"/>
       <c r="P13">
         <v>20.16</v>
       </c>
@@ -1526,7 +1526,7 @@
       <c r="R13">
         <v>3.65</v>
       </c>
-      <c r="T13" s="35"/>
+      <c r="T13" s="26"/>
       <c r="U13" s="1">
         <v>5.76</v>
       </c>
@@ -1538,11 +1538,11 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A14" s="35"/>
+      <c r="A14" s="26"/>
       <c r="B14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="35"/>
+      <c r="C14" s="26"/>
       <c r="D14">
         <v>10.08</v>
       </c>
@@ -1558,10 +1558,10 @@
       <c r="H14">
         <v>147.7028</v>
       </c>
-      <c r="I14" s="35">
+      <c r="I14" s="26">
         <v>65.11</v>
       </c>
-      <c r="J14" s="35"/>
+      <c r="J14" s="26"/>
       <c r="K14">
         <v>7.47</v>
       </c>
@@ -1571,10 +1571,10 @@
       <c r="M14">
         <v>0</v>
       </c>
-      <c r="N14" s="35">
+      <c r="N14" s="26">
         <v>80.66</v>
       </c>
-      <c r="O14" s="35"/>
+      <c r="O14" s="26"/>
       <c r="P14">
         <v>17.05</v>
       </c>
@@ -1584,10 +1584,10 @@
       <c r="R14" s="1">
         <v>1.22</v>
       </c>
-      <c r="S14" s="35">
+      <c r="S14" s="26">
         <v>34.19</v>
       </c>
-      <c r="T14" s="35"/>
+      <c r="T14" s="26"/>
       <c r="U14">
         <v>4.76</v>
       </c>
@@ -1597,16 +1597,16 @@
       <c r="W14" s="1">
         <v>0.27</v>
       </c>
-      <c r="X14" s="35">
+      <c r="X14" s="26">
         <v>74.290000000000006</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A15" s="35"/>
+      <c r="A15" s="26"/>
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="35"/>
+      <c r="C15" s="26"/>
       <c r="D15">
         <v>9.15</v>
       </c>
@@ -1622,8 +1622,8 @@
       <c r="H15">
         <v>159.09700000000001</v>
       </c>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
       <c r="K15">
         <v>5.88</v>
       </c>
@@ -1633,8 +1633,8 @@
       <c r="M15">
         <v>0</v>
       </c>
-      <c r="N15" s="35"/>
-      <c r="O15" s="35"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="26"/>
       <c r="P15">
         <v>16.07</v>
       </c>
@@ -1644,8 +1644,8 @@
       <c r="R15" s="1">
         <v>1.42</v>
       </c>
-      <c r="S15" s="35"/>
-      <c r="T15" s="35"/>
+      <c r="S15" s="26"/>
+      <c r="T15" s="26"/>
       <c r="U15" s="1">
         <v>5.26</v>
       </c>
@@ -1655,14 +1655,14 @@
       <c r="W15" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="X15" s="35"/>
+      <c r="X15" s="26"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A16" s="35"/>
+      <c r="A16" s="26"/>
       <c r="B16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="35"/>
+      <c r="C16" s="26"/>
       <c r="D16">
         <v>7.89</v>
       </c>
@@ -1678,8 +1678,8 @@
       <c r="H16">
         <v>168.54599999999999</v>
       </c>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
       <c r="K16">
         <v>5.14</v>
       </c>
@@ -1689,8 +1689,8 @@
       <c r="M16">
         <v>0</v>
       </c>
-      <c r="N16" s="35"/>
-      <c r="O16" s="35"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26"/>
       <c r="P16">
         <v>14.1</v>
       </c>
@@ -1700,8 +1700,8 @@
       <c r="R16" s="1">
         <v>0.81</v>
       </c>
-      <c r="S16" s="35"/>
-      <c r="T16" s="35"/>
+      <c r="S16" s="26"/>
+      <c r="T16" s="26"/>
       <c r="U16">
         <v>4.01</v>
       </c>
@@ -1711,16 +1711,16 @@
       <c r="W16" s="1">
         <v>0</v>
       </c>
-      <c r="X16" s="35"/>
+      <c r="X16" s="26"/>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A17" s="35" t="s">
+      <c r="A17" s="26" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="26">
         <v>29.96</v>
       </c>
       <c r="D17">
@@ -1738,7 +1738,7 @@
       <c r="H17">
         <v>3.6791999999999998</v>
       </c>
-      <c r="J17" s="35">
+      <c r="J17" s="26">
         <v>28.64</v>
       </c>
       <c r="K17">
@@ -1750,7 +1750,7 @@
       <c r="M17">
         <v>1.2</v>
       </c>
-      <c r="O17" s="35">
+      <c r="O17" s="26">
         <v>40.82</v>
       </c>
       <c r="P17">
@@ -1762,7 +1762,7 @@
       <c r="R17" s="1">
         <v>1.66</v>
       </c>
-      <c r="T17" s="35">
+      <c r="T17" s="26">
         <v>16.04</v>
       </c>
       <c r="U17">
@@ -1776,11 +1776,11 @@
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A18" s="35"/>
+      <c r="A18" s="26"/>
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="35"/>
+      <c r="C18" s="26"/>
       <c r="D18">
         <v>36.31</v>
       </c>
@@ -1796,7 +1796,7 @@
       <c r="H18">
         <v>26.883299999999998</v>
       </c>
-      <c r="J18" s="35"/>
+      <c r="J18" s="26"/>
       <c r="K18">
         <v>31.46</v>
       </c>
@@ -1806,7 +1806,7 @@
       <c r="M18">
         <v>23.16</v>
       </c>
-      <c r="O18" s="35"/>
+      <c r="O18" s="26"/>
       <c r="P18">
         <v>48.2</v>
       </c>
@@ -1816,7 +1816,7 @@
       <c r="R18" s="1">
         <v>22.16</v>
       </c>
-      <c r="T18" s="35"/>
+      <c r="T18" s="26"/>
       <c r="U18">
         <v>28.07</v>
       </c>
@@ -1828,11 +1828,11 @@
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A19" s="35"/>
+      <c r="A19" s="26"/>
       <c r="B19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="35"/>
+      <c r="C19" s="26"/>
       <c r="D19">
         <v>55.31</v>
       </c>
@@ -1848,7 +1848,7 @@
       <c r="H19">
         <v>24.215399999999999</v>
       </c>
-      <c r="J19" s="35"/>
+      <c r="J19" s="26"/>
       <c r="K19">
         <v>53.12</v>
       </c>
@@ -1858,7 +1858,7 @@
       <c r="M19">
         <v>40.82</v>
       </c>
-      <c r="O19" s="35"/>
+      <c r="O19" s="26"/>
       <c r="P19">
         <v>66.89</v>
       </c>
@@ -1868,7 +1868,7 @@
       <c r="R19" s="1">
         <v>50.69</v>
       </c>
-      <c r="T19" s="35"/>
+      <c r="T19" s="26"/>
       <c r="U19">
         <v>42.11</v>
       </c>
@@ -1880,11 +1880,11 @@
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A20" s="35"/>
+      <c r="A20" s="26"/>
       <c r="B20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="35"/>
+      <c r="C20" s="26"/>
       <c r="D20">
         <v>20.87</v>
       </c>
@@ -1900,7 +1900,7 @@
       <c r="H20">
         <v>2.9369000000000001</v>
       </c>
-      <c r="J20" s="35"/>
+      <c r="J20" s="26"/>
       <c r="K20">
         <v>14.93</v>
       </c>
@@ -1910,7 +1910,7 @@
       <c r="M20">
         <v>1.54</v>
       </c>
-      <c r="O20" s="35"/>
+      <c r="O20" s="26"/>
       <c r="P20">
         <v>36.72</v>
       </c>
@@ -1920,7 +1920,7 @@
       <c r="R20">
         <v>5.26</v>
       </c>
-      <c r="T20" s="35"/>
+      <c r="T20" s="26"/>
       <c r="U20">
         <v>8.77</v>
       </c>
@@ -1932,11 +1932,11 @@
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A21" s="35"/>
+      <c r="A21" s="26"/>
       <c r="B21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="35"/>
+      <c r="C21" s="26"/>
       <c r="D21">
         <v>18.89</v>
       </c>
@@ -1952,10 +1952,10 @@
       <c r="H21">
         <v>22.941400000000002</v>
       </c>
-      <c r="I21" s="35">
+      <c r="I21" s="26">
         <v>48.81</v>
       </c>
-      <c r="J21" s="35"/>
+      <c r="J21" s="26"/>
       <c r="K21">
         <v>12.48</v>
       </c>
@@ -1965,10 +1965,10 @@
       <c r="M21">
         <v>1.03</v>
       </c>
-      <c r="N21" s="35">
+      <c r="N21" s="26">
         <v>67.09</v>
       </c>
-      <c r="O21" s="35"/>
+      <c r="O21" s="26"/>
       <c r="P21">
         <v>34.590000000000003</v>
       </c>
@@ -1978,10 +1978,10 @@
       <c r="R21">
         <v>2.2200000000000002</v>
       </c>
-      <c r="S21" s="35">
+      <c r="S21" s="26">
         <v>30.12</v>
       </c>
-      <c r="T21" s="35"/>
+      <c r="T21" s="26"/>
       <c r="U21">
         <v>8.02</v>
       </c>
@@ -1991,16 +1991,16 @@
       <c r="W21">
         <v>0</v>
       </c>
-      <c r="X21" s="35">
+      <c r="X21" s="26">
         <v>54.69</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A22" s="35"/>
+      <c r="A22" s="26"/>
       <c r="B22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="35"/>
+      <c r="C22" s="26"/>
       <c r="D22">
         <v>17.8</v>
       </c>
@@ -2016,8 +2016,8 @@
       <c r="H22">
         <v>23.260400000000001</v>
       </c>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="26"/>
       <c r="K22">
         <v>10.89</v>
       </c>
@@ -2027,8 +2027,8 @@
       <c r="M22">
         <v>1.2</v>
       </c>
-      <c r="N22" s="35"/>
-      <c r="O22" s="35"/>
+      <c r="N22" s="26"/>
+      <c r="O22" s="26"/>
       <c r="P22">
         <v>33.61</v>
       </c>
@@ -2038,8 +2038,8 @@
       <c r="R22">
         <v>2.2200000000000002</v>
       </c>
-      <c r="S22" s="35"/>
-      <c r="T22" s="35"/>
+      <c r="S22" s="26"/>
+      <c r="T22" s="26"/>
       <c r="U22">
         <v>7.77</v>
       </c>
@@ -2049,14 +2049,14 @@
       <c r="W22">
         <v>0</v>
       </c>
-      <c r="X22" s="35"/>
+      <c r="X22" s="26"/>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A23" s="35"/>
+      <c r="A23" s="26"/>
       <c r="B23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="35"/>
+      <c r="C23" s="26"/>
       <c r="D23">
         <v>16.43</v>
       </c>
@@ -2072,8 +2072,8 @@
       <c r="H23">
         <v>52.032899999999998</v>
       </c>
-      <c r="I23" s="35"/>
-      <c r="J23" s="35"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
       <c r="K23">
         <v>10.039999999999999</v>
       </c>
@@ -2083,8 +2083,8 @@
       <c r="M23">
         <v>0.69</v>
       </c>
-      <c r="N23" s="35"/>
-      <c r="O23" s="35"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
       <c r="P23">
         <v>30.82</v>
       </c>
@@ -2094,8 +2094,8 @@
       <c r="R23">
         <v>1.1100000000000001</v>
       </c>
-      <c r="S23" s="35"/>
-      <c r="T23" s="35"/>
+      <c r="S23" s="26"/>
+      <c r="T23" s="26"/>
       <c r="U23">
         <v>7.52</v>
       </c>
@@ -2105,16 +2105,16 @@
       <c r="W23">
         <v>0</v>
       </c>
-      <c r="X23" s="35"/>
+      <c r="X23" s="26"/>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A24" s="35" t="s">
+      <c r="A24" s="26" t="s">
         <v>20</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="35">
+      <c r="C24" s="26">
         <v>44.74</v>
       </c>
       <c r="D24">
@@ -2132,7 +2132,7 @@
       <c r="H24">
         <v>15.446099999999999</v>
       </c>
-      <c r="J24" s="35">
+      <c r="J24" s="26">
         <v>38.07</v>
       </c>
       <c r="K24">
@@ -2144,7 +2144,7 @@
       <c r="M24">
         <v>5.14</v>
       </c>
-      <c r="O24" s="35">
+      <c r="O24" s="26">
         <v>56.89</v>
       </c>
       <c r="P24">
@@ -2156,7 +2156,7 @@
       <c r="R24">
         <v>6.84</v>
       </c>
-      <c r="T24" s="35">
+      <c r="T24" s="26">
         <v>39.85</v>
       </c>
       <c r="U24">
@@ -2170,11 +2170,11 @@
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A25" s="35"/>
+      <c r="A25" s="26"/>
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="35"/>
+      <c r="C25" s="26"/>
       <c r="D25">
         <v>40.53</v>
       </c>
@@ -2190,7 +2190,7 @@
       <c r="H25">
         <v>27.349599999999999</v>
       </c>
-      <c r="J25" s="35"/>
+      <c r="J25" s="26"/>
       <c r="K25">
         <v>26.44</v>
       </c>
@@ -2200,7 +2200,7 @@
       <c r="M25">
         <v>14.03</v>
       </c>
-      <c r="O25" s="35"/>
+      <c r="O25" s="26"/>
       <c r="P25">
         <v>61.97</v>
       </c>
@@ -2210,7 +2210,7 @@
       <c r="R25">
         <v>26.62</v>
       </c>
-      <c r="T25" s="35"/>
+      <c r="T25" s="26"/>
       <c r="U25">
         <v>36.590000000000003</v>
       </c>
@@ -2222,11 +2222,11 @@
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A26" s="35"/>
+      <c r="A26" s="26"/>
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="35"/>
+      <c r="C26" s="26"/>
       <c r="D26">
         <v>45.02</v>
       </c>
@@ -2242,7 +2242,7 @@
       <c r="H26">
         <v>35.505099999999999</v>
       </c>
-      <c r="J26" s="35"/>
+      <c r="J26" s="26"/>
       <c r="K26">
         <v>34.39</v>
       </c>
@@ -2252,7 +2252,7 @@
       <c r="M26">
         <v>19.96</v>
       </c>
-      <c r="O26" s="35"/>
+      <c r="O26" s="26"/>
       <c r="P26">
         <v>63.28</v>
       </c>
@@ -2262,7 +2262,7 @@
       <c r="R26">
         <v>30.04</v>
       </c>
-      <c r="T26" s="35"/>
+      <c r="T26" s="26"/>
       <c r="U26">
         <v>38.85</v>
       </c>
@@ -2274,11 +2274,11 @@
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A27" s="35"/>
+      <c r="A27" s="26"/>
       <c r="B27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C27" s="35"/>
+      <c r="C27" s="26"/>
       <c r="D27">
         <v>31.16</v>
       </c>
@@ -2294,7 +2294,7 @@
       <c r="H27">
         <v>1.3381000000000001</v>
       </c>
-      <c r="J27" s="35"/>
+      <c r="J27" s="26"/>
       <c r="K27">
         <v>12.97</v>
       </c>
@@ -2304,7 +2304,7 @@
       <c r="M27">
         <v>2.96</v>
       </c>
-      <c r="O27" s="35"/>
+      <c r="O27" s="26"/>
       <c r="P27">
         <v>53.28</v>
       </c>
@@ -2314,7 +2314,7 @@
       <c r="R27">
         <v>14.07</v>
       </c>
-      <c r="T27" s="35"/>
+      <c r="T27" s="26"/>
       <c r="U27">
         <v>34.590000000000003</v>
       </c>
@@ -2326,11 +2326,11 @@
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A28" s="35"/>
+      <c r="A28" s="26"/>
       <c r="B28" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="35"/>
+      <c r="C28" s="26"/>
       <c r="D28">
         <v>28.31</v>
       </c>
@@ -2346,10 +2346,10 @@
       <c r="H28">
         <v>13.305</v>
       </c>
-      <c r="I28" s="35">
+      <c r="I28" s="26">
         <v>48.1</v>
       </c>
-      <c r="J28" s="35"/>
+      <c r="J28" s="26"/>
       <c r="K28">
         <v>11.75</v>
       </c>
@@ -2359,10 +2359,10 @@
       <c r="M28">
         <v>1.58</v>
       </c>
-      <c r="N28" s="35">
+      <c r="N28" s="26">
         <v>76.209999999999994</v>
       </c>
-      <c r="O28" s="35"/>
+      <c r="O28" s="26"/>
       <c r="P28">
         <v>50.16</v>
       </c>
@@ -2372,10 +2372,10 @@
       <c r="R28">
         <v>6.08</v>
       </c>
-      <c r="S28" s="35">
+      <c r="S28" s="26">
         <v>23.05</v>
       </c>
-      <c r="T28" s="35"/>
+      <c r="T28" s="26"/>
       <c r="U28">
         <v>28.82</v>
       </c>
@@ -2385,16 +2385,16 @@
       <c r="W28">
         <v>5</v>
       </c>
-      <c r="X28" s="35">
+      <c r="X28" s="26">
         <v>47.8</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A29" s="35"/>
+      <c r="A29" s="26"/>
       <c r="B29" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="35"/>
+      <c r="C29" s="26"/>
       <c r="D29">
         <v>27.66</v>
       </c>
@@ -2410,8 +2410,8 @@
       <c r="H29">
         <v>15.7463</v>
       </c>
-      <c r="I29" s="35"/>
-      <c r="J29" s="35"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
       <c r="K29">
         <v>11.75</v>
       </c>
@@ -2421,8 +2421,8 @@
       <c r="M29">
         <v>1.78</v>
       </c>
-      <c r="N29" s="35"/>
-      <c r="O29" s="35"/>
+      <c r="N29" s="26"/>
+      <c r="O29" s="26"/>
       <c r="P29">
         <v>49.18</v>
       </c>
@@ -2432,8 +2432,8 @@
       <c r="R29">
         <v>5.7</v>
       </c>
-      <c r="S29" s="35"/>
-      <c r="T29" s="35"/>
+      <c r="S29" s="26"/>
+      <c r="T29" s="26"/>
       <c r="U29">
         <v>27.32</v>
       </c>
@@ -2443,14 +2443,14 @@
       <c r="W29">
         <v>5.42</v>
       </c>
-      <c r="X29" s="35"/>
+      <c r="X29" s="26"/>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A30" s="35"/>
+      <c r="A30" s="26"/>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="35"/>
+      <c r="C30" s="26"/>
       <c r="D30">
         <v>25.96</v>
       </c>
@@ -2466,8 +2466,8 @@
       <c r="H30">
         <v>21.763400000000001</v>
       </c>
-      <c r="I30" s="35"/>
-      <c r="J30" s="35"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
       <c r="K30">
         <v>10.28</v>
       </c>
@@ -2477,8 +2477,8 @@
       <c r="M30">
         <v>1.19</v>
       </c>
-      <c r="N30" s="35"/>
-      <c r="O30" s="35"/>
+      <c r="N30" s="26"/>
+      <c r="O30" s="26"/>
       <c r="P30">
         <v>47.54</v>
       </c>
@@ -2488,8 +2488,8 @@
       <c r="R30">
         <v>4.18</v>
       </c>
-      <c r="S30" s="35"/>
-      <c r="T30" s="35"/>
+      <c r="S30" s="26"/>
+      <c r="T30" s="26"/>
       <c r="U30">
         <v>25.06</v>
       </c>
@@ -2499,7 +2499,7 @@
       <c r="W30">
         <v>3.75</v>
       </c>
-      <c r="X30" s="35"/>
+      <c r="X30" s="26"/>
     </row>
     <row r="34" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B34" s="23" t="s">
@@ -2546,31 +2546,31 @@
       </c>
     </row>
     <row r="35" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="30"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="26" t="s">
+      <c r="B35" s="34"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="E35" s="26"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="26" t="s">
+      <c r="E35" s="30"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="H35" s="26"/>
-      <c r="I35" s="27"/>
-      <c r="J35" s="28" t="s">
+      <c r="H35" s="30"/>
+      <c r="I35" s="31"/>
+      <c r="J35" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="K35" s="28"/>
-      <c r="L35" s="29"/>
-      <c r="M35" s="28" t="s">
+      <c r="K35" s="32"/>
+      <c r="L35" s="33"/>
+      <c r="M35" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="N35" s="28"/>
-      <c r="O35" s="28"/>
+      <c r="N35" s="32"/>
+      <c r="O35" s="32"/>
     </row>
     <row r="36" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="33" t="s">
+      <c r="B36" s="28" t="s">
         <v>0</v>
       </c>
       <c r="C36" s="9" t="s">
@@ -2614,7 +2614,7 @@
       </c>
     </row>
     <row r="37" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="B37" s="33"/>
+      <c r="B37" s="28"/>
       <c r="C37" s="9" t="s">
         <v>27</v>
       </c>
@@ -2656,7 +2656,7 @@
       </c>
     </row>
     <row r="38" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="B38" s="33"/>
+      <c r="B38" s="28"/>
       <c r="C38" s="9" t="s">
         <v>23</v>
       </c>
@@ -2698,7 +2698,7 @@
       </c>
     </row>
     <row r="39" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="B39" s="34"/>
+      <c r="B39" s="29"/>
       <c r="C39" s="5" t="s">
         <v>26</v>
       </c>
@@ -2740,7 +2740,7 @@
       </c>
     </row>
     <row r="40" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B40" s="32" t="s">
+      <c r="B40" s="27" t="s">
         <v>1</v>
       </c>
       <c r="C40" s="9" t="s">
@@ -2784,7 +2784,7 @@
       </c>
     </row>
     <row r="41" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B41" s="33"/>
+      <c r="B41" s="28"/>
       <c r="C41" s="9" t="s">
         <v>24</v>
       </c>
@@ -2826,7 +2826,7 @@
       </c>
     </row>
     <row r="42" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B42" s="33"/>
+      <c r="B42" s="28"/>
       <c r="C42" s="9" t="s">
         <v>23</v>
       </c>
@@ -2868,7 +2868,7 @@
       </c>
     </row>
     <row r="43" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B43" s="34"/>
+      <c r="B43" s="29"/>
       <c r="C43" s="5" t="s">
         <v>22</v>
       </c>
@@ -2910,7 +2910,7 @@
       </c>
     </row>
     <row r="44" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B44" s="32" t="s">
+      <c r="B44" s="27" t="s">
         <v>13</v>
       </c>
       <c r="C44" s="9" t="s">
@@ -2954,7 +2954,7 @@
       </c>
     </row>
     <row r="45" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B45" s="33"/>
+      <c r="B45" s="28"/>
       <c r="C45" s="9" t="s">
         <v>24</v>
       </c>
@@ -2996,7 +2996,7 @@
       </c>
     </row>
     <row r="46" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B46" s="33"/>
+      <c r="B46" s="28"/>
       <c r="C46" s="9" t="s">
         <v>23</v>
       </c>
@@ -3038,7 +3038,7 @@
       </c>
     </row>
     <row r="47" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B47" s="34"/>
+      <c r="B47" s="29"/>
       <c r="C47" s="5" t="s">
         <v>22</v>
       </c>
@@ -3080,7 +3080,7 @@
       </c>
     </row>
     <row r="48" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B48" s="32" t="s">
+      <c r="B48" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C48" s="9" t="s">
@@ -3124,7 +3124,7 @@
       </c>
     </row>
     <row r="49" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B49" s="33"/>
+      <c r="B49" s="28"/>
       <c r="C49" s="9" t="s">
         <v>24</v>
       </c>
@@ -3166,7 +3166,7 @@
       </c>
     </row>
     <row r="50" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B50" s="33"/>
+      <c r="B50" s="28"/>
       <c r="C50" s="9" t="s">
         <v>23</v>
       </c>
@@ -3208,7 +3208,7 @@
       </c>
     </row>
     <row r="51" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B51" s="34"/>
+      <c r="B51" s="29"/>
       <c r="C51" s="5" t="s">
         <v>22</v>
       </c>
@@ -3251,7 +3251,7 @@
     </row>
     <row r="54" spans="2:15" ht="15" x14ac:dyDescent="0.2">
       <c r="B54" s="2"/>
-      <c r="C54" s="36" t="s">
+      <c r="C54" s="16" t="s">
         <v>40</v>
       </c>
       <c r="D54" s="2" t="s">
@@ -3303,23 +3303,463 @@
         <v>2.97</v>
       </c>
     </row>
+    <row r="61" spans="2:15" ht="15" x14ac:dyDescent="0.2">
+      <c r="B61" s="36"/>
+      <c r="C61" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G61" s="36"/>
+      <c r="H61" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="62" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B62" s="36">
+        <v>0</v>
+      </c>
+      <c r="C62" s="36">
+        <v>22.22</v>
+      </c>
+      <c r="D62" s="36">
+        <v>55.7</v>
+      </c>
+      <c r="E62" s="36">
+        <v>4.95</v>
+      </c>
+      <c r="G62" s="36">
+        <v>0.1</v>
+      </c>
+      <c r="H62" s="2">
+        <v>17.22</v>
+      </c>
+      <c r="I62" s="2">
+        <v>64.56</v>
+      </c>
+      <c r="J62" s="2">
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="63" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B63" s="36">
+        <v>1</v>
+      </c>
+      <c r="C63" s="36">
+        <v>19.440000000000001</v>
+      </c>
+      <c r="D63" s="36">
+        <v>60.76</v>
+      </c>
+      <c r="E63" s="36">
+        <v>3.96</v>
+      </c>
+      <c r="G63" s="36">
+        <v>0.3</v>
+      </c>
+      <c r="H63" s="36">
+        <v>17.78</v>
+      </c>
+      <c r="I63" s="36">
+        <v>64.56</v>
+      </c>
+      <c r="J63" s="36">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="64" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B64" s="36">
+        <v>3</v>
+      </c>
+      <c r="C64" s="36">
+        <v>18.329999999999998</v>
+      </c>
+      <c r="D64" s="36">
+        <v>64.56</v>
+      </c>
+      <c r="E64" s="36">
+        <v>4.95</v>
+      </c>
+      <c r="G64" s="36">
+        <v>0.6</v>
+      </c>
+      <c r="H64" s="36">
+        <v>19.440000000000001</v>
+      </c>
+      <c r="I64" s="36">
+        <v>65.819999999999993</v>
+      </c>
+      <c r="J64" s="36">
+        <v>8.91</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B65" s="36">
+        <v>5</v>
+      </c>
+      <c r="C65" s="2">
+        <v>17.22</v>
+      </c>
+      <c r="D65" s="2">
+        <v>64.56</v>
+      </c>
+      <c r="E65" s="2">
+        <v>2.97</v>
+      </c>
+      <c r="G65" s="36">
+        <v>0.9</v>
+      </c>
+      <c r="H65" s="2">
+        <v>18.89</v>
+      </c>
+      <c r="I65" s="2">
+        <v>65.819999999999993</v>
+      </c>
+      <c r="J65" s="2">
+        <v>7.92</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B66" s="36">
+        <v>7</v>
+      </c>
+      <c r="C66" s="36">
+        <v>18.329999999999998</v>
+      </c>
+      <c r="D66" s="36">
+        <v>67.09</v>
+      </c>
+      <c r="E66" s="36">
+        <v>6.93</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B67" s="36">
+        <v>9</v>
+      </c>
+      <c r="C67" s="36">
+        <v>16.670000000000002</v>
+      </c>
+      <c r="D67" s="36">
+        <v>67.09</v>
+      </c>
+      <c r="E67" s="36">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="L71" s="1"/>
+      <c r="M71" s="1"/>
+      <c r="N71" s="1"/>
+      <c r="O71" s="1"/>
+      <c r="Q71" s="1"/>
+      <c r="R71" s="1"/>
+      <c r="S71" s="1"/>
+      <c r="T71" s="1"/>
+      <c r="V71" s="1"/>
+      <c r="W71" s="1"/>
+      <c r="X71" s="1"/>
+      <c r="Y71" s="1"/>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B73" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D73" s="1">
+        <v>65.150000000000006</v>
+      </c>
+      <c r="E73" s="1">
+        <v>85.56</v>
+      </c>
+      <c r="F73" s="1">
+        <v>27.16</v>
+      </c>
+      <c r="G73" s="1">
+        <v>74.38</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B74" s="1"/>
+      <c r="C74" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D74" s="1">
+        <v>69.05</v>
+      </c>
+      <c r="E74" s="1">
+        <v>87.97</v>
+      </c>
+      <c r="F74" s="1">
+        <v>35.78</v>
+      </c>
+      <c r="G74" s="1">
+        <v>74.38</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B75" s="1"/>
+      <c r="C75" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D75" s="1">
+        <v>72.760000000000005</v>
+      </c>
+      <c r="E75" s="1">
+        <v>90.37</v>
+      </c>
+      <c r="F75" s="1">
+        <v>39.22</v>
+      </c>
+      <c r="G75" s="1">
+        <v>82.64</v>
+      </c>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1"/>
+      <c r="N75" s="1"/>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B76" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D76">
+        <v>49.45</v>
+      </c>
+      <c r="E76">
+        <v>72.17</v>
+      </c>
+      <c r="F76">
+        <v>10.26</v>
+      </c>
+      <c r="G76" s="1">
+        <v>42.86</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B77" s="1"/>
+      <c r="C77" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D77">
+        <v>61.54</v>
+      </c>
+      <c r="E77">
+        <v>80.19</v>
+      </c>
+      <c r="F77">
+        <v>29.91</v>
+      </c>
+      <c r="G77" s="1">
+        <v>54.29</v>
+      </c>
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
+      <c r="M77" s="1"/>
+      <c r="N77" s="1"/>
+    </row>
+    <row r="78" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B78" s="1"/>
+      <c r="C78" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D78" s="1">
+        <v>65.11</v>
+      </c>
+      <c r="E78" s="1">
+        <v>80.66</v>
+      </c>
+      <c r="F78" s="1">
+        <v>34.19</v>
+      </c>
+      <c r="G78" s="1">
+        <v>74.290000000000006</v>
+      </c>
+      <c r="K78" s="1"/>
+      <c r="L78" s="1"/>
+      <c r="M78" s="1"/>
+      <c r="N78" s="1"/>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B79" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D79">
+        <v>35.47</v>
+      </c>
+      <c r="E79">
+        <v>51.71</v>
+      </c>
+      <c r="F79">
+        <v>17.670000000000002</v>
+      </c>
+      <c r="G79">
+        <v>45.31</v>
+      </c>
+    </row>
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B80" s="1"/>
+      <c r="C80" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80">
+        <v>46.62</v>
+      </c>
+      <c r="E80">
+        <v>66.67</v>
+      </c>
+      <c r="F80">
+        <v>26.1</v>
+      </c>
+      <c r="G80">
+        <v>53.12</v>
+      </c>
+    </row>
+    <row r="81" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B81" s="1"/>
+      <c r="C81" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81">
+        <v>48.81</v>
+      </c>
+      <c r="E81">
+        <v>67.09</v>
+      </c>
+      <c r="F81">
+        <v>30.12</v>
+      </c>
+      <c r="G81" s="1">
+        <v>54.69</v>
+      </c>
+    </row>
+    <row r="82" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B82" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D82">
+        <v>40.020000000000003</v>
+      </c>
+      <c r="E82">
+        <v>70.739999999999995</v>
+      </c>
+      <c r="F82">
+        <v>17</v>
+      </c>
+      <c r="G82">
+        <v>30.19</v>
+      </c>
+    </row>
+    <row r="83" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B83" s="1"/>
+      <c r="C83" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D83">
+        <v>45.17</v>
+      </c>
+      <c r="E83">
+        <v>74.92</v>
+      </c>
+      <c r="F83">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="G83">
+        <v>42.77</v>
+      </c>
+    </row>
+    <row r="84" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="C84" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D84" s="1">
+        <v>48.1</v>
+      </c>
+      <c r="E84" s="1">
+        <v>76.209999999999994</v>
+      </c>
+      <c r="F84">
+        <v>23.05</v>
+      </c>
+      <c r="G84" s="1">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="86" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="1"/>
+    </row>
+    <row r="87" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="A24:A30"/>
-    <mergeCell ref="C24:C30"/>
-    <mergeCell ref="O24:O30"/>
-    <mergeCell ref="T17:T23"/>
-    <mergeCell ref="X21:X23"/>
-    <mergeCell ref="X14:X16"/>
-    <mergeCell ref="J1:N1"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="S7:S9"/>
-    <mergeCell ref="S21:S23"/>
-    <mergeCell ref="T24:T30"/>
-    <mergeCell ref="N28:N30"/>
-    <mergeCell ref="S28:S30"/>
-    <mergeCell ref="X28:X30"/>
-    <mergeCell ref="J24:J30"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B40:B43"/>
+    <mergeCell ref="B36:B39"/>
+    <mergeCell ref="B48:B51"/>
+    <mergeCell ref="B44:B47"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="G35:I35"/>
     <mergeCell ref="A3:A9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J3:J9"/>
@@ -3333,27 +3773,29 @@
     <mergeCell ref="C10:C16"/>
     <mergeCell ref="A17:A23"/>
     <mergeCell ref="J10:J16"/>
+    <mergeCell ref="O3:O9"/>
+    <mergeCell ref="N14:N16"/>
+    <mergeCell ref="X14:X16"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="S7:S9"/>
+    <mergeCell ref="S21:S23"/>
     <mergeCell ref="X7:X9"/>
     <mergeCell ref="O1:S1"/>
     <mergeCell ref="T1:X1"/>
-    <mergeCell ref="O3:O9"/>
     <mergeCell ref="T3:T9"/>
     <mergeCell ref="T10:T16"/>
-    <mergeCell ref="N14:N16"/>
     <mergeCell ref="S14:S16"/>
-    <mergeCell ref="B40:B43"/>
-    <mergeCell ref="B36:B39"/>
-    <mergeCell ref="B48:B51"/>
-    <mergeCell ref="B44:B47"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="C3:C9"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="A24:A30"/>
+    <mergeCell ref="C24:C30"/>
+    <mergeCell ref="O24:O30"/>
+    <mergeCell ref="T17:T23"/>
+    <mergeCell ref="X21:X23"/>
+    <mergeCell ref="T24:T30"/>
+    <mergeCell ref="N28:N30"/>
+    <mergeCell ref="S28:S30"/>
+    <mergeCell ref="X28:X30"/>
+    <mergeCell ref="J24:J30"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/stat/data.xlsx
+++ b/stat/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr-PC\Documents\Workspace\LLMHalluMiti\stat\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr\Documents\Workspace\LLMHalluMiti\stat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1872A4-BDD8-47DE-B3F8-B380071AEBD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E2864F-F2D7-4875-9683-7270E02141EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7200" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -490,22 +490,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -519,8 +504,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -802,44 +802,56 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y87"/>
+  <dimension ref="A1:AN87"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="27" max="28" width="7.625" customWidth="1"/>
+    <col min="29" max="29" width="6.625" customWidth="1"/>
+    <col min="30" max="30" width="8.875" customWidth="1"/>
+    <col min="31" max="32" width="6.625" customWidth="1"/>
+    <col min="33" max="33" width="8.875" customWidth="1"/>
+    <col min="34" max="35" width="6.625" customWidth="1"/>
+    <col min="36" max="36" width="8.875" customWidth="1"/>
+    <col min="37" max="38" width="6.625" customWidth="1"/>
+    <col min="39" max="39" width="8.875" customWidth="1"/>
+    <col min="40" max="40" width="6.625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26" t="s">
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26" t="s">
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26" t="s">
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+    </row>
+    <row r="2" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
@@ -908,15 +920,57 @@
       <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A3" s="26" t="s">
+      <c r="AA2" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB2" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC2" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD2" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE2" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF2" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG2" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH2" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI2" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ2" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="AK2" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL2" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM2" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="AN2" s="23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="34" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="34">
         <v>39.81</v>
       </c>
       <c r="D3" s="1">
@@ -935,7 +989,7 @@
         <v>4.9604999999999997</v>
       </c>
       <c r="I3" s="1"/>
-      <c r="J3" s="26">
+      <c r="J3" s="34">
         <v>45.78</v>
       </c>
       <c r="K3" s="1">
@@ -948,7 +1002,7 @@
         <v>9.0299999999999994</v>
       </c>
       <c r="N3" s="1"/>
-      <c r="O3" s="26">
+      <c r="O3" s="34">
         <v>38.03</v>
       </c>
       <c r="P3" s="1">
@@ -961,7 +1015,7 @@
         <v>1.32</v>
       </c>
       <c r="S3" s="1"/>
-      <c r="T3" s="26">
+      <c r="T3" s="34">
         <v>30.33</v>
       </c>
       <c r="U3" s="1">
@@ -974,13 +1028,35 @@
         <v>2.52</v>
       </c>
       <c r="X3" s="1"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A4" s="26"/>
+      <c r="AA3" s="29"/>
+      <c r="AB3" s="30"/>
+      <c r="AC3" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD3" s="35"/>
+      <c r="AE3" s="36"/>
+      <c r="AF3" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG3" s="35"/>
+      <c r="AH3" s="36"/>
+      <c r="AI3" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="AJ3" s="27"/>
+      <c r="AK3" s="28"/>
+      <c r="AL3" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="AM3" s="27"/>
+      <c r="AN3" s="27"/>
+    </row>
+    <row r="4" spans="1:40" ht="15.75" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="34"/>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="26"/>
+      <c r="C4" s="34"/>
       <c r="D4" s="1">
         <v>25.03</v>
       </c>
@@ -997,7 +1073,7 @@
         <v>22.125900000000001</v>
       </c>
       <c r="I4" s="1"/>
-      <c r="J4" s="26"/>
+      <c r="J4" s="34"/>
       <c r="K4" s="1">
         <v>23.38</v>
       </c>
@@ -1008,7 +1084,7 @@
         <v>15.35</v>
       </c>
       <c r="N4" s="1"/>
-      <c r="O4" s="26"/>
+      <c r="O4" s="34"/>
       <c r="P4" s="1">
         <v>35.9</v>
       </c>
@@ -1019,7 +1095,7 @@
         <v>12.17</v>
       </c>
       <c r="S4" s="1"/>
-      <c r="T4" s="26"/>
+      <c r="T4" s="34"/>
       <c r="U4" s="1">
         <v>11.78</v>
       </c>
@@ -1030,13 +1106,55 @@
         <v>6.12</v>
       </c>
       <c r="X4" s="1"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A5" s="26"/>
+      <c r="AA4" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC4" s="16">
+        <v>22.95</v>
+      </c>
+      <c r="AD4" s="16">
+        <v>49.45</v>
+      </c>
+      <c r="AE4" s="10">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="AF4" s="16">
+        <v>24.6</v>
+      </c>
+      <c r="AG4" s="16">
+        <v>56.95</v>
+      </c>
+      <c r="AH4" s="10">
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="AI4" s="16">
+        <v>28.52</v>
+      </c>
+      <c r="AJ4" s="16">
+        <v>27.16</v>
+      </c>
+      <c r="AK4" s="22">
+        <v>1.32</v>
+      </c>
+      <c r="AL4" s="16">
+        <v>11.28</v>
+      </c>
+      <c r="AM4" s="16">
+        <v>68.599999999999994</v>
+      </c>
+      <c r="AN4" s="21">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:40" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="34"/>
       <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="26"/>
+      <c r="C5" s="34"/>
       <c r="D5" s="1">
         <v>25.58</v>
       </c>
@@ -1053,7 +1171,7 @@
         <v>33.609499999999997</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="26"/>
+      <c r="J5" s="34"/>
       <c r="K5" s="1">
         <v>22.4</v>
       </c>
@@ -1064,7 +1182,7 @@
         <v>9.48</v>
       </c>
       <c r="N5" s="1"/>
-      <c r="O5" s="26"/>
+      <c r="O5" s="34"/>
       <c r="P5" s="1">
         <v>38.03</v>
       </c>
@@ -1075,7 +1193,7 @@
         <v>19.309999999999999</v>
       </c>
       <c r="S5" s="1"/>
-      <c r="T5" s="26"/>
+      <c r="T5" s="34"/>
       <c r="U5" s="1">
         <v>13.03</v>
       </c>
@@ -1086,13 +1204,53 @@
         <v>5.76</v>
       </c>
       <c r="X5" s="1"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A6" s="26"/>
+      <c r="AA5" s="32"/>
+      <c r="AB5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC5" s="16">
+        <v>25.03</v>
+      </c>
+      <c r="AD5" s="16">
+        <v>55.23</v>
+      </c>
+      <c r="AE5" s="10">
+        <v>12</v>
+      </c>
+      <c r="AF5" s="16">
+        <v>23.38</v>
+      </c>
+      <c r="AG5" s="16">
+        <v>67.11</v>
+      </c>
+      <c r="AH5" s="10">
+        <v>15.35</v>
+      </c>
+      <c r="AI5" s="16">
+        <v>35.9</v>
+      </c>
+      <c r="AJ5" s="16">
+        <v>25.43</v>
+      </c>
+      <c r="AK5" s="10">
+        <v>12.17</v>
+      </c>
+      <c r="AL5" s="16">
+        <v>11.78</v>
+      </c>
+      <c r="AM5" s="21">
+        <v>75.209999999999994</v>
+      </c>
+      <c r="AN5" s="16">
+        <v>6.12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:40" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="34"/>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="26"/>
+      <c r="C6" s="34"/>
       <c r="D6" s="1">
         <v>17.579999999999998</v>
       </c>
@@ -1109,7 +1267,7 @@
         <v>6.4598000000000004</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="26"/>
+      <c r="J6" s="34"/>
       <c r="K6" s="1">
         <v>10.4</v>
       </c>
@@ -1120,7 +1278,7 @@
         <v>7</v>
       </c>
       <c r="N6" s="1"/>
-      <c r="O6" s="26"/>
+      <c r="O6" s="34"/>
       <c r="P6" s="1">
         <v>31.97</v>
       </c>
@@ -1131,7 +1289,7 @@
         <v>6.88</v>
       </c>
       <c r="S6" s="1"/>
-      <c r="T6" s="26"/>
+      <c r="T6" s="34"/>
       <c r="U6" s="1">
         <v>10.28</v>
       </c>
@@ -1142,13 +1300,53 @@
         <v>3.6</v>
       </c>
       <c r="X6" s="1"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A7" s="26"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC6" s="16">
+        <v>25.58</v>
+      </c>
+      <c r="AD6" s="16">
+        <v>53.72</v>
+      </c>
+      <c r="AE6" s="10">
+        <v>11.91</v>
+      </c>
+      <c r="AF6" s="16">
+        <v>22.4</v>
+      </c>
+      <c r="AG6" s="16">
+        <v>62.3</v>
+      </c>
+      <c r="AH6" s="10">
+        <v>9.48</v>
+      </c>
+      <c r="AI6" s="16">
+        <v>38.03</v>
+      </c>
+      <c r="AJ6" s="16">
+        <v>31.47</v>
+      </c>
+      <c r="AK6" s="10">
+        <v>19.309999999999999</v>
+      </c>
+      <c r="AL6" s="16">
+        <v>13.03</v>
+      </c>
+      <c r="AM6" s="16">
+        <v>70.25</v>
+      </c>
+      <c r="AN6" s="16">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:40" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="34"/>
       <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="26"/>
+      <c r="C7" s="34"/>
       <c r="D7" s="1">
         <v>15.55</v>
       </c>
@@ -1164,10 +1362,10 @@
       <c r="H7" s="1">
         <v>17.849</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="34">
         <v>72.760000000000005</v>
       </c>
-      <c r="J7" s="26"/>
+      <c r="J7" s="34"/>
       <c r="K7" s="1">
         <v>7.34</v>
       </c>
@@ -1177,10 +1375,10 @@
       <c r="M7" s="1">
         <v>2.48</v>
       </c>
-      <c r="N7" s="26">
+      <c r="N7" s="34">
         <v>90.37</v>
       </c>
-      <c r="O7" s="26"/>
+      <c r="O7" s="34"/>
       <c r="P7" s="1">
         <v>30.49</v>
       </c>
@@ -1190,10 +1388,10 @@
       <c r="R7" s="1">
         <v>5.29</v>
       </c>
-      <c r="S7" s="26">
+      <c r="S7" s="34">
         <v>39.22</v>
       </c>
-      <c r="T7" s="26"/>
+      <c r="T7" s="34"/>
       <c r="U7" s="1">
         <v>9.52</v>
       </c>
@@ -1203,16 +1401,56 @@
       <c r="W7" s="1">
         <v>4.32</v>
       </c>
-      <c r="X7" s="26">
+      <c r="X7" s="34">
         <v>82.64</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A8" s="26"/>
+      <c r="AA7" s="33"/>
+      <c r="AB7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC7" s="18">
+        <v>14.07</v>
+      </c>
+      <c r="AD7" s="18">
+        <v>69.05</v>
+      </c>
+      <c r="AE7" s="19">
+        <v>2.91</v>
+      </c>
+      <c r="AF7" s="18">
+        <v>6.61</v>
+      </c>
+      <c r="AG7" s="18">
+        <v>87.97</v>
+      </c>
+      <c r="AH7" s="19">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AI7" s="18">
+        <v>26.39</v>
+      </c>
+      <c r="AJ7" s="18">
+        <v>35.78</v>
+      </c>
+      <c r="AK7" s="6">
+        <v>3.17</v>
+      </c>
+      <c r="AL7" s="18">
+        <v>10.53</v>
+      </c>
+      <c r="AM7" s="20">
+        <v>74.38</v>
+      </c>
+      <c r="AN7" s="20">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="34"/>
       <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="26"/>
+      <c r="C8" s="34"/>
       <c r="D8" s="1">
         <v>19.11</v>
       </c>
@@ -1228,8 +1466,8 @@
       <c r="H8" s="1">
         <v>20.038900000000002</v>
       </c>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
       <c r="K8" s="1">
         <v>8.69</v>
       </c>
@@ -1239,8 +1477,8 @@
       <c r="M8" s="1">
         <v>3.84</v>
       </c>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
       <c r="P8" s="1">
         <v>31.8</v>
       </c>
@@ -1250,8 +1488,8 @@
       <c r="R8" s="1">
         <v>8.1999999999999993</v>
       </c>
-      <c r="S8" s="26"/>
-      <c r="T8" s="26"/>
+      <c r="S8" s="34"/>
+      <c r="T8" s="34"/>
       <c r="U8" s="1">
         <v>21.05</v>
       </c>
@@ -1261,14 +1499,56 @@
       <c r="W8" s="1">
         <v>14.75</v>
       </c>
-      <c r="X8" s="26"/>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A9" s="26"/>
+      <c r="X8" s="34"/>
+      <c r="AA8" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC8" s="17">
+        <v>15.44</v>
+      </c>
+      <c r="AD8" s="17">
+        <v>29.4</v>
+      </c>
+      <c r="AE8" s="13">
+        <v>1.71</v>
+      </c>
+      <c r="AF8" s="17">
+        <v>18.12</v>
+      </c>
+      <c r="AG8" s="17">
+        <v>38.68</v>
+      </c>
+      <c r="AH8" s="13">
+        <v>2.98</v>
+      </c>
+      <c r="AI8" s="11">
+        <v>17.05</v>
+      </c>
+      <c r="AJ8" s="11">
+        <v>15.38</v>
+      </c>
+      <c r="AK8" s="13">
+        <v>1.01</v>
+      </c>
+      <c r="AL8" s="11">
+        <v>7.52</v>
+      </c>
+      <c r="AM8" s="17">
+        <v>20</v>
+      </c>
+      <c r="AN8" s="11">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="34"/>
       <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="26"/>
+      <c r="C9" s="34"/>
       <c r="D9" s="1">
         <v>14.07</v>
       </c>
@@ -1284,8 +1564,8 @@
       <c r="H9" s="1">
         <v>22.114799999999999</v>
       </c>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
       <c r="K9" s="1">
         <v>6.61</v>
       </c>
@@ -1295,8 +1575,8 @@
       <c r="M9" s="1">
         <v>2.0299999999999998</v>
       </c>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="34"/>
       <c r="P9" s="1">
         <v>26.39</v>
       </c>
@@ -1306,8 +1586,8 @@
       <c r="R9" s="1">
         <v>3.17</v>
       </c>
-      <c r="S9" s="26"/>
-      <c r="T9" s="26"/>
+      <c r="S9" s="34"/>
+      <c r="T9" s="34"/>
       <c r="U9" s="1">
         <v>10.53</v>
       </c>
@@ -1317,16 +1597,56 @@
       <c r="W9" s="1">
         <v>3.96</v>
       </c>
-      <c r="X9" s="26"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A10" s="26" t="s">
+      <c r="X9" s="34"/>
+      <c r="AA9" s="32"/>
+      <c r="AB9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC9" s="7">
+        <v>17.03</v>
+      </c>
+      <c r="AD9" s="7">
+        <v>41.76</v>
+      </c>
+      <c r="AE9" s="10">
+        <v>6.77</v>
+      </c>
+      <c r="AF9" s="7">
+        <v>16.77</v>
+      </c>
+      <c r="AG9" s="16">
+        <v>57.08</v>
+      </c>
+      <c r="AH9" s="8">
+        <v>7.6</v>
+      </c>
+      <c r="AI9" s="16">
+        <v>22.3</v>
+      </c>
+      <c r="AJ9" s="16">
+        <v>17.95</v>
+      </c>
+      <c r="AK9" s="10">
+        <v>8.11</v>
+      </c>
+      <c r="AL9" s="16">
+        <v>9.52</v>
+      </c>
+      <c r="AM9" s="16">
+        <v>28.57</v>
+      </c>
+      <c r="AN9" s="16">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="34" t="s">
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="34">
         <v>19.93</v>
       </c>
       <c r="D10" s="1">
@@ -1344,7 +1664,7 @@
       <c r="H10">
         <v>12.401999999999999</v>
       </c>
-      <c r="J10" s="26">
+      <c r="J10" s="34">
         <v>25.95</v>
       </c>
       <c r="K10" s="1">
@@ -1356,7 +1676,7 @@
       <c r="M10" s="1">
         <v>2.98</v>
       </c>
-      <c r="O10" s="26">
+      <c r="O10" s="34">
         <v>19.18</v>
       </c>
       <c r="P10">
@@ -1368,7 +1688,7 @@
       <c r="R10" s="1">
         <v>1.01</v>
       </c>
-      <c r="T10" s="26">
+      <c r="T10" s="34">
         <v>8.77</v>
       </c>
       <c r="U10">
@@ -1380,13 +1700,53 @@
       <c r="W10">
         <v>0.55000000000000004</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A11" s="26"/>
+      <c r="AA10" s="32"/>
+      <c r="AB10" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC10" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="AD10" s="7">
+        <v>43.68</v>
+      </c>
+      <c r="AE10" s="8">
+        <v>5.34</v>
+      </c>
+      <c r="AF10" s="16">
+        <v>13.83</v>
+      </c>
+      <c r="AG10" s="7">
+        <v>57.55</v>
+      </c>
+      <c r="AH10" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="AI10" s="7">
+        <v>22.62</v>
+      </c>
+      <c r="AJ10" s="7">
+        <v>15.38</v>
+      </c>
+      <c r="AK10" s="10">
+        <v>7.91</v>
+      </c>
+      <c r="AL10" s="7">
+        <v>8.02</v>
+      </c>
+      <c r="AM10" s="7">
+        <v>54.29</v>
+      </c>
+      <c r="AN10" s="16">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="34"/>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="26"/>
+      <c r="C11" s="34"/>
       <c r="D11">
         <v>17.03</v>
       </c>
@@ -1402,7 +1762,7 @@
       <c r="H11">
         <v>114.9687</v>
       </c>
-      <c r="J11" s="26"/>
+      <c r="J11" s="34"/>
       <c r="K11">
         <v>16.77</v>
       </c>
@@ -1412,7 +1772,7 @@
       <c r="M11">
         <v>7.6</v>
       </c>
-      <c r="O11" s="26"/>
+      <c r="O11" s="34"/>
       <c r="P11" s="1">
         <v>22.3</v>
       </c>
@@ -1422,7 +1782,7 @@
       <c r="R11" s="1">
         <v>8.11</v>
       </c>
-      <c r="T11" s="26"/>
+      <c r="T11" s="34"/>
       <c r="U11" s="1">
         <v>9.52</v>
       </c>
@@ -1432,13 +1792,53 @@
       <c r="W11" s="1">
         <v>3.57</v>
       </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A12" s="26"/>
+      <c r="AA11" s="33"/>
+      <c r="AB11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC11" s="3">
+        <v>7.89</v>
+      </c>
+      <c r="AD11" s="3">
+        <v>61.54</v>
+      </c>
+      <c r="AE11" s="4">
+        <v>0.27</v>
+      </c>
+      <c r="AF11" s="3">
+        <v>5.14</v>
+      </c>
+      <c r="AG11" s="3">
+        <v>80.19</v>
+      </c>
+      <c r="AH11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="3">
+        <v>14.1</v>
+      </c>
+      <c r="AJ11" s="3">
+        <v>29.91</v>
+      </c>
+      <c r="AK11" s="19">
+        <v>0.81</v>
+      </c>
+      <c r="AL11" s="3">
+        <v>4.01</v>
+      </c>
+      <c r="AM11" s="18">
+        <v>54.29</v>
+      </c>
+      <c r="AN11" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="34"/>
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="26"/>
+      <c r="C12" s="34"/>
       <c r="D12">
         <v>15.5</v>
       </c>
@@ -1454,7 +1854,7 @@
       <c r="H12">
         <v>113.2599</v>
       </c>
-      <c r="J12" s="26"/>
+      <c r="J12" s="34"/>
       <c r="K12" s="1">
         <v>13.83</v>
       </c>
@@ -1464,7 +1864,7 @@
       <c r="M12">
         <v>3.8</v>
       </c>
-      <c r="O12" s="26"/>
+      <c r="O12" s="34"/>
       <c r="P12">
         <v>22.62</v>
       </c>
@@ -1474,7 +1874,7 @@
       <c r="R12" s="1">
         <v>7.91</v>
       </c>
-      <c r="T12" s="26"/>
+      <c r="T12" s="34"/>
       <c r="U12">
         <v>8.02</v>
       </c>
@@ -1484,13 +1884,55 @@
       <c r="W12" s="1">
         <v>4.4000000000000004</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A13" s="26"/>
+      <c r="AA12" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB12" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC12" s="11">
+        <v>23.38</v>
+      </c>
+      <c r="AD12" s="11">
+        <v>24.5</v>
+      </c>
+      <c r="AE12" s="12">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="AF12" s="11">
+        <v>17.38</v>
+      </c>
+      <c r="AG12" s="11">
+        <v>42.31</v>
+      </c>
+      <c r="AH12" s="12">
+        <v>1.2</v>
+      </c>
+      <c r="AI12" s="11">
+        <v>38.85</v>
+      </c>
+      <c r="AJ12" s="11">
+        <v>7.23</v>
+      </c>
+      <c r="AK12" s="13">
+        <v>1.66</v>
+      </c>
+      <c r="AL12" s="11">
+        <v>12.03</v>
+      </c>
+      <c r="AM12" s="17">
+        <v>26.56</v>
+      </c>
+      <c r="AN12" s="17">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="34"/>
       <c r="B13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="26"/>
+      <c r="C13" s="34"/>
       <c r="D13">
         <v>11.66</v>
       </c>
@@ -1506,7 +1948,7 @@
       <c r="H13">
         <v>17.3841</v>
       </c>
-      <c r="J13" s="26"/>
+      <c r="J13" s="34"/>
       <c r="K13">
         <v>8.1999999999999993</v>
       </c>
@@ -1516,7 +1958,7 @@
       <c r="M13">
         <v>1.49</v>
       </c>
-      <c r="O13" s="26"/>
+      <c r="O13" s="34"/>
       <c r="P13">
         <v>20.16</v>
       </c>
@@ -1526,7 +1968,7 @@
       <c r="R13">
         <v>3.65</v>
       </c>
-      <c r="T13" s="26"/>
+      <c r="T13" s="34"/>
       <c r="U13" s="1">
         <v>5.76</v>
       </c>
@@ -1536,13 +1978,53 @@
       <c r="W13" s="1">
         <v>0.82</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A14" s="26"/>
+      <c r="AA13" s="32"/>
+      <c r="AB13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC13" s="7">
+        <v>36.31</v>
+      </c>
+      <c r="AD13" s="7">
+        <v>31.08</v>
+      </c>
+      <c r="AE13" s="8">
+        <v>22.36</v>
+      </c>
+      <c r="AF13" s="7">
+        <v>31.46</v>
+      </c>
+      <c r="AG13" s="7">
+        <v>47.86</v>
+      </c>
+      <c r="AH13" s="8">
+        <v>23.16</v>
+      </c>
+      <c r="AI13" s="7">
+        <v>48.2</v>
+      </c>
+      <c r="AJ13" s="7">
+        <v>14.06</v>
+      </c>
+      <c r="AK13" s="10">
+        <v>22.16</v>
+      </c>
+      <c r="AL13" s="7">
+        <v>28.07</v>
+      </c>
+      <c r="AM13" s="16">
+        <v>35.94</v>
+      </c>
+      <c r="AN13" s="16">
+        <v>21.19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="34"/>
       <c r="B14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="26"/>
+      <c r="C14" s="34"/>
       <c r="D14">
         <v>10.08</v>
       </c>
@@ -1558,10 +2040,10 @@
       <c r="H14">
         <v>147.7028</v>
       </c>
-      <c r="I14" s="26">
+      <c r="I14" s="34">
         <v>65.11</v>
       </c>
-      <c r="J14" s="26"/>
+      <c r="J14" s="34"/>
       <c r="K14">
         <v>7.47</v>
       </c>
@@ -1571,10 +2053,10 @@
       <c r="M14">
         <v>0</v>
       </c>
-      <c r="N14" s="26">
+      <c r="N14" s="34">
         <v>80.66</v>
       </c>
-      <c r="O14" s="26"/>
+      <c r="O14" s="34"/>
       <c r="P14">
         <v>17.05</v>
       </c>
@@ -1584,10 +2066,10 @@
       <c r="R14" s="1">
         <v>1.22</v>
       </c>
-      <c r="S14" s="26">
+      <c r="S14" s="34">
         <v>34.19</v>
       </c>
-      <c r="T14" s="26"/>
+      <c r="T14" s="34"/>
       <c r="U14">
         <v>4.76</v>
       </c>
@@ -1597,16 +2079,56 @@
       <c r="W14" s="1">
         <v>0.27</v>
       </c>
-      <c r="X14" s="26">
+      <c r="X14" s="34">
         <v>74.290000000000006</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A15" s="26"/>
+      <c r="AA14" s="32"/>
+      <c r="AB14" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC14" s="7">
+        <v>55.31</v>
+      </c>
+      <c r="AD14" s="7">
+        <v>14.08</v>
+      </c>
+      <c r="AE14" s="8">
+        <v>41.14</v>
+      </c>
+      <c r="AF14" s="7">
+        <v>53.12</v>
+      </c>
+      <c r="AG14" s="7">
+        <v>16.670000000000002</v>
+      </c>
+      <c r="AH14" s="8">
+        <v>40.82</v>
+      </c>
+      <c r="AI14" s="7">
+        <v>66.89</v>
+      </c>
+      <c r="AJ14" s="7">
+        <v>9.64</v>
+      </c>
+      <c r="AK14" s="10">
+        <v>50.69</v>
+      </c>
+      <c r="AL14" s="7">
+        <v>42.11</v>
+      </c>
+      <c r="AM14" s="7">
+        <v>21.88</v>
+      </c>
+      <c r="AN14" s="7">
+        <v>35.22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A15" s="34"/>
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="26"/>
+      <c r="C15" s="34"/>
       <c r="D15">
         <v>9.15</v>
       </c>
@@ -1622,8 +2144,8 @@
       <c r="H15">
         <v>159.09700000000001</v>
       </c>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
       <c r="K15">
         <v>5.88</v>
       </c>
@@ -1633,8 +2155,8 @@
       <c r="M15">
         <v>0</v>
       </c>
-      <c r="N15" s="26"/>
-      <c r="O15" s="26"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
       <c r="P15">
         <v>16.07</v>
       </c>
@@ -1644,8 +2166,8 @@
       <c r="R15" s="1">
         <v>1.42</v>
       </c>
-      <c r="S15" s="26"/>
-      <c r="T15" s="26"/>
+      <c r="S15" s="34"/>
+      <c r="T15" s="34"/>
       <c r="U15" s="1">
         <v>5.26</v>
       </c>
@@ -1655,14 +2177,54 @@
       <c r="W15" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="X15" s="26"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A16" s="26"/>
+      <c r="X15" s="34"/>
+      <c r="AA15" s="33"/>
+      <c r="AB15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>16.43</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>46.62</v>
+      </c>
+      <c r="AE15" s="4">
+        <v>0.63</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>10.039999999999999</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>66.67</v>
+      </c>
+      <c r="AH15" s="4">
+        <v>0.69</v>
+      </c>
+      <c r="AI15" s="15">
+        <v>30.82</v>
+      </c>
+      <c r="AJ15" s="15">
+        <v>26.1</v>
+      </c>
+      <c r="AK15" s="14">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>7.52</v>
+      </c>
+      <c r="AM15" s="3">
+        <v>53.12</v>
+      </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A16" s="34"/>
       <c r="B16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="26"/>
+      <c r="C16" s="34"/>
       <c r="D16">
         <v>7.89</v>
       </c>
@@ -1678,8 +2240,8 @@
       <c r="H16">
         <v>168.54599999999999</v>
       </c>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
       <c r="K16">
         <v>5.14</v>
       </c>
@@ -1689,8 +2251,8 @@
       <c r="M16">
         <v>0</v>
       </c>
-      <c r="N16" s="26"/>
-      <c r="O16" s="26"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
       <c r="P16">
         <v>14.1</v>
       </c>
@@ -1700,8 +2262,8 @@
       <c r="R16" s="1">
         <v>0.81</v>
       </c>
-      <c r="S16" s="26"/>
-      <c r="T16" s="26"/>
+      <c r="S16" s="34"/>
+      <c r="T16" s="34"/>
       <c r="U16">
         <v>4.01</v>
       </c>
@@ -1711,16 +2273,58 @@
       <c r="W16" s="1">
         <v>0</v>
       </c>
-      <c r="X16" s="26"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A17" s="26" t="s">
+      <c r="X16" s="34"/>
+      <c r="AA16" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB16" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC16" s="11">
+        <v>36.14</v>
+      </c>
+      <c r="AD16" s="11">
+        <v>26.19</v>
+      </c>
+      <c r="AE16" s="12">
+        <v>5.65</v>
+      </c>
+      <c r="AF16" s="11">
+        <v>24.24</v>
+      </c>
+      <c r="AG16" s="11">
+        <v>44.69</v>
+      </c>
+      <c r="AH16" s="12">
+        <v>5.14</v>
+      </c>
+      <c r="AI16" s="11">
+        <v>53.44</v>
+      </c>
+      <c r="AJ16" s="11">
+        <v>11.24</v>
+      </c>
+      <c r="AK16" s="12">
+        <v>6.84</v>
+      </c>
+      <c r="AL16" s="11">
+        <v>34.090000000000003</v>
+      </c>
+      <c r="AM16" s="11">
+        <v>22.64</v>
+      </c>
+      <c r="AN16" s="11">
+        <v>5.42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="34" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="34">
         <v>29.96</v>
       </c>
       <c r="D17">
@@ -1738,7 +2342,7 @@
       <c r="H17">
         <v>3.6791999999999998</v>
       </c>
-      <c r="J17" s="26">
+      <c r="J17" s="34">
         <v>28.64</v>
       </c>
       <c r="K17">
@@ -1750,7 +2354,7 @@
       <c r="M17">
         <v>1.2</v>
       </c>
-      <c r="O17" s="26">
+      <c r="O17" s="34">
         <v>40.82</v>
       </c>
       <c r="P17">
@@ -1762,7 +2366,7 @@
       <c r="R17" s="1">
         <v>1.66</v>
       </c>
-      <c r="T17" s="26">
+      <c r="T17" s="34">
         <v>16.04</v>
       </c>
       <c r="U17">
@@ -1774,13 +2378,53 @@
       <c r="W17" s="1">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A18" s="26"/>
+      <c r="AA17" s="32"/>
+      <c r="AB17" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC17" s="7">
+        <v>40.53</v>
+      </c>
+      <c r="AD17" s="7">
+        <v>31.95</v>
+      </c>
+      <c r="AE17" s="8">
+        <v>18.43</v>
+      </c>
+      <c r="AF17" s="7">
+        <v>26.44</v>
+      </c>
+      <c r="AG17" s="7">
+        <v>52.73</v>
+      </c>
+      <c r="AH17" s="8">
+        <v>14.03</v>
+      </c>
+      <c r="AI17" s="7">
+        <v>61.97</v>
+      </c>
+      <c r="AJ17" s="7">
+        <v>11.24</v>
+      </c>
+      <c r="AK17" s="8">
+        <v>26.62</v>
+      </c>
+      <c r="AL17" s="7">
+        <v>36.590000000000003</v>
+      </c>
+      <c r="AM17" s="7">
+        <v>36.479999999999997</v>
+      </c>
+      <c r="AN17" s="7">
+        <v>18.75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A18" s="34"/>
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="26"/>
+      <c r="C18" s="34"/>
       <c r="D18">
         <v>36.31</v>
       </c>
@@ -1796,7 +2440,7 @@
       <c r="H18">
         <v>26.883299999999998</v>
       </c>
-      <c r="J18" s="26"/>
+      <c r="J18" s="34"/>
       <c r="K18">
         <v>31.46</v>
       </c>
@@ -1806,7 +2450,7 @@
       <c r="M18">
         <v>23.16</v>
       </c>
-      <c r="O18" s="26"/>
+      <c r="O18" s="34"/>
       <c r="P18">
         <v>48.2</v>
       </c>
@@ -1816,7 +2460,7 @@
       <c r="R18" s="1">
         <v>22.16</v>
       </c>
-      <c r="T18" s="26"/>
+      <c r="T18" s="34"/>
       <c r="U18">
         <v>28.07</v>
       </c>
@@ -1826,13 +2470,53 @@
       <c r="W18" s="1">
         <v>21.19</v>
       </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A19" s="26"/>
+      <c r="AA18" s="32"/>
+      <c r="AB18" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC18" s="7">
+        <v>45.02</v>
+      </c>
+      <c r="AD18" s="7">
+        <v>27.54</v>
+      </c>
+      <c r="AE18" s="8">
+        <v>22.79</v>
+      </c>
+      <c r="AF18" s="7">
+        <v>34.39</v>
+      </c>
+      <c r="AG18" s="7">
+        <v>42.77</v>
+      </c>
+      <c r="AH18" s="8">
+        <v>19.96</v>
+      </c>
+      <c r="AI18" s="7">
+        <v>63.28</v>
+      </c>
+      <c r="AJ18" s="7">
+        <v>11.53</v>
+      </c>
+      <c r="AK18" s="8">
+        <v>30.04</v>
+      </c>
+      <c r="AL18" s="7">
+        <v>38.85</v>
+      </c>
+      <c r="AM18" s="7">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="AN18" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:40" ht="15" x14ac:dyDescent="0.25">
+      <c r="A19" s="34"/>
       <c r="B19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="26"/>
+      <c r="C19" s="34"/>
       <c r="D19">
         <v>55.31</v>
       </c>
@@ -1848,7 +2532,7 @@
       <c r="H19">
         <v>24.215399999999999</v>
       </c>
-      <c r="J19" s="26"/>
+      <c r="J19" s="34"/>
       <c r="K19">
         <v>53.12</v>
       </c>
@@ -1858,7 +2542,7 @@
       <c r="M19">
         <v>40.82</v>
       </c>
-      <c r="O19" s="26"/>
+      <c r="O19" s="34"/>
       <c r="P19">
         <v>66.89</v>
       </c>
@@ -1868,7 +2552,7 @@
       <c r="R19" s="1">
         <v>50.69</v>
       </c>
-      <c r="T19" s="26"/>
+      <c r="T19" s="34"/>
       <c r="U19">
         <v>42.11</v>
       </c>
@@ -1878,13 +2562,53 @@
       <c r="W19">
         <v>35.22</v>
       </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A20" s="26"/>
+      <c r="AA19" s="33"/>
+      <c r="AB19" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC19" s="3">
+        <v>25.96</v>
+      </c>
+      <c r="AD19" s="3">
+        <v>45.17</v>
+      </c>
+      <c r="AE19" s="4">
+        <v>2.58</v>
+      </c>
+      <c r="AF19" s="3">
+        <v>10.28</v>
+      </c>
+      <c r="AG19" s="3">
+        <v>74.92</v>
+      </c>
+      <c r="AH19" s="4">
+        <v>1.19</v>
+      </c>
+      <c r="AI19" s="3">
+        <v>47.54</v>
+      </c>
+      <c r="AJ19" s="3">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="AK19" s="4">
+        <v>4.18</v>
+      </c>
+      <c r="AL19" s="3">
+        <v>25.06</v>
+      </c>
+      <c r="AM19" s="3">
+        <v>42.77</v>
+      </c>
+      <c r="AN19" s="3">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A20" s="34"/>
       <c r="B20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="26"/>
+      <c r="C20" s="34"/>
       <c r="D20">
         <v>20.87</v>
       </c>
@@ -1900,7 +2624,7 @@
       <c r="H20">
         <v>2.9369000000000001</v>
       </c>
-      <c r="J20" s="26"/>
+      <c r="J20" s="34"/>
       <c r="K20">
         <v>14.93</v>
       </c>
@@ -1910,7 +2634,7 @@
       <c r="M20">
         <v>1.54</v>
       </c>
-      <c r="O20" s="26"/>
+      <c r="O20" s="34"/>
       <c r="P20">
         <v>36.72</v>
       </c>
@@ -1920,7 +2644,7 @@
       <c r="R20">
         <v>5.26</v>
       </c>
-      <c r="T20" s="26"/>
+      <c r="T20" s="34"/>
       <c r="U20">
         <v>8.77</v>
       </c>
@@ -1931,12 +2655,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A21" s="26"/>
+    <row r="21" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A21" s="34"/>
       <c r="B21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="26"/>
+      <c r="C21" s="34"/>
       <c r="D21">
         <v>18.89</v>
       </c>
@@ -1952,10 +2676,10 @@
       <c r="H21">
         <v>22.941400000000002</v>
       </c>
-      <c r="I21" s="26">
+      <c r="I21" s="34">
         <v>48.81</v>
       </c>
-      <c r="J21" s="26"/>
+      <c r="J21" s="34"/>
       <c r="K21">
         <v>12.48</v>
       </c>
@@ -1965,10 +2689,10 @@
       <c r="M21">
         <v>1.03</v>
       </c>
-      <c r="N21" s="26">
+      <c r="N21" s="34">
         <v>67.09</v>
       </c>
-      <c r="O21" s="26"/>
+      <c r="O21" s="34"/>
       <c r="P21">
         <v>34.590000000000003</v>
       </c>
@@ -1978,10 +2702,10 @@
       <c r="R21">
         <v>2.2200000000000002</v>
       </c>
-      <c r="S21" s="26">
+      <c r="S21" s="34">
         <v>30.12</v>
       </c>
-      <c r="T21" s="26"/>
+      <c r="T21" s="34"/>
       <c r="U21">
         <v>8.02</v>
       </c>
@@ -1991,16 +2715,16 @@
       <c r="W21">
         <v>0</v>
       </c>
-      <c r="X21" s="26">
+      <c r="X21" s="34">
         <v>54.69</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A22" s="26"/>
+    <row r="22" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A22" s="34"/>
       <c r="B22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="26"/>
+      <c r="C22" s="34"/>
       <c r="D22">
         <v>17.8</v>
       </c>
@@ -2016,8 +2740,8 @@
       <c r="H22">
         <v>23.260400000000001</v>
       </c>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
       <c r="K22">
         <v>10.89</v>
       </c>
@@ -2027,8 +2751,8 @@
       <c r="M22">
         <v>1.2</v>
       </c>
-      <c r="N22" s="26"/>
-      <c r="O22" s="26"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
       <c r="P22">
         <v>33.61</v>
       </c>
@@ -2038,8 +2762,8 @@
       <c r="R22">
         <v>2.2200000000000002</v>
       </c>
-      <c r="S22" s="26"/>
-      <c r="T22" s="26"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
       <c r="U22">
         <v>7.77</v>
       </c>
@@ -2049,14 +2773,14 @@
       <c r="W22">
         <v>0</v>
       </c>
-      <c r="X22" s="26"/>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A23" s="26"/>
+      <c r="X22" s="34"/>
+    </row>
+    <row r="23" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A23" s="34"/>
       <c r="B23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="26"/>
+      <c r="C23" s="34"/>
       <c r="D23">
         <v>16.43</v>
       </c>
@@ -2072,8 +2796,8 @@
       <c r="H23">
         <v>52.032899999999998</v>
       </c>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="34"/>
       <c r="K23">
         <v>10.039999999999999</v>
       </c>
@@ -2083,8 +2807,8 @@
       <c r="M23">
         <v>0.69</v>
       </c>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
+      <c r="N23" s="34"/>
+      <c r="O23" s="34"/>
       <c r="P23">
         <v>30.82</v>
       </c>
@@ -2094,8 +2818,8 @@
       <c r="R23">
         <v>1.1100000000000001</v>
       </c>
-      <c r="S23" s="26"/>
-      <c r="T23" s="26"/>
+      <c r="S23" s="34"/>
+      <c r="T23" s="34"/>
       <c r="U23">
         <v>7.52</v>
       </c>
@@ -2105,16 +2829,16 @@
       <c r="W23">
         <v>0</v>
       </c>
-      <c r="X23" s="26"/>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A24" s="26" t="s">
+      <c r="X23" s="34"/>
+    </row>
+    <row r="24" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A24" s="34" t="s">
         <v>20</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="34">
         <v>44.74</v>
       </c>
       <c r="D24">
@@ -2132,7 +2856,7 @@
       <c r="H24">
         <v>15.446099999999999</v>
       </c>
-      <c r="J24" s="26">
+      <c r="J24" s="34">
         <v>38.07</v>
       </c>
       <c r="K24">
@@ -2144,7 +2868,7 @@
       <c r="M24">
         <v>5.14</v>
       </c>
-      <c r="O24" s="26">
+      <c r="O24" s="34">
         <v>56.89</v>
       </c>
       <c r="P24">
@@ -2156,7 +2880,7 @@
       <c r="R24">
         <v>6.84</v>
       </c>
-      <c r="T24" s="26">
+      <c r="T24" s="34">
         <v>39.85</v>
       </c>
       <c r="U24">
@@ -2169,12 +2893,12 @@
         <v>5.42</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A25" s="26"/>
+    <row r="25" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A25" s="34"/>
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="26"/>
+      <c r="C25" s="34"/>
       <c r="D25">
         <v>40.53</v>
       </c>
@@ -2190,7 +2914,7 @@
       <c r="H25">
         <v>27.349599999999999</v>
       </c>
-      <c r="J25" s="26"/>
+      <c r="J25" s="34"/>
       <c r="K25">
         <v>26.44</v>
       </c>
@@ -2200,7 +2924,7 @@
       <c r="M25">
         <v>14.03</v>
       </c>
-      <c r="O25" s="26"/>
+      <c r="O25" s="34"/>
       <c r="P25">
         <v>61.97</v>
       </c>
@@ -2210,7 +2934,7 @@
       <c r="R25">
         <v>26.62</v>
       </c>
-      <c r="T25" s="26"/>
+      <c r="T25" s="34"/>
       <c r="U25">
         <v>36.590000000000003</v>
       </c>
@@ -2221,12 +2945,12 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A26" s="26"/>
+    <row r="26" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A26" s="34"/>
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="26"/>
+      <c r="C26" s="34"/>
       <c r="D26">
         <v>45.02</v>
       </c>
@@ -2242,7 +2966,7 @@
       <c r="H26">
         <v>35.505099999999999</v>
       </c>
-      <c r="J26" s="26"/>
+      <c r="J26" s="34"/>
       <c r="K26">
         <v>34.39</v>
       </c>
@@ -2252,7 +2976,7 @@
       <c r="M26">
         <v>19.96</v>
       </c>
-      <c r="O26" s="26"/>
+      <c r="O26" s="34"/>
       <c r="P26">
         <v>63.28</v>
       </c>
@@ -2262,7 +2986,7 @@
       <c r="R26">
         <v>30.04</v>
       </c>
-      <c r="T26" s="26"/>
+      <c r="T26" s="34"/>
       <c r="U26">
         <v>38.85</v>
       </c>
@@ -2273,12 +2997,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A27" s="26"/>
+    <row r="27" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A27" s="34"/>
       <c r="B27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C27" s="26"/>
+      <c r="C27" s="34"/>
       <c r="D27">
         <v>31.16</v>
       </c>
@@ -2294,7 +3018,7 @@
       <c r="H27">
         <v>1.3381000000000001</v>
       </c>
-      <c r="J27" s="26"/>
+      <c r="J27" s="34"/>
       <c r="K27">
         <v>12.97</v>
       </c>
@@ -2304,7 +3028,7 @@
       <c r="M27">
         <v>2.96</v>
       </c>
-      <c r="O27" s="26"/>
+      <c r="O27" s="34"/>
       <c r="P27">
         <v>53.28</v>
       </c>
@@ -2314,7 +3038,7 @@
       <c r="R27">
         <v>14.07</v>
       </c>
-      <c r="T27" s="26"/>
+      <c r="T27" s="34"/>
       <c r="U27">
         <v>34.590000000000003</v>
       </c>
@@ -2325,12 +3049,12 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A28" s="26"/>
+    <row r="28" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A28" s="34"/>
       <c r="B28" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="26"/>
+      <c r="C28" s="34"/>
       <c r="D28">
         <v>28.31</v>
       </c>
@@ -2346,10 +3070,10 @@
       <c r="H28">
         <v>13.305</v>
       </c>
-      <c r="I28" s="26">
+      <c r="I28" s="34">
         <v>48.1</v>
       </c>
-      <c r="J28" s="26"/>
+      <c r="J28" s="34"/>
       <c r="K28">
         <v>11.75</v>
       </c>
@@ -2359,10 +3083,10 @@
       <c r="M28">
         <v>1.58</v>
       </c>
-      <c r="N28" s="26">
+      <c r="N28" s="34">
         <v>76.209999999999994</v>
       </c>
-      <c r="O28" s="26"/>
+      <c r="O28" s="34"/>
       <c r="P28">
         <v>50.16</v>
       </c>
@@ -2372,10 +3096,10 @@
       <c r="R28">
         <v>6.08</v>
       </c>
-      <c r="S28" s="26">
+      <c r="S28" s="34">
         <v>23.05</v>
       </c>
-      <c r="T28" s="26"/>
+      <c r="T28" s="34"/>
       <c r="U28">
         <v>28.82</v>
       </c>
@@ -2385,16 +3109,16 @@
       <c r="W28">
         <v>5</v>
       </c>
-      <c r="X28" s="26">
+      <c r="X28" s="34">
         <v>47.8</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A29" s="26"/>
+    <row r="29" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A29" s="34"/>
       <c r="B29" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="26"/>
+      <c r="C29" s="34"/>
       <c r="D29">
         <v>27.66</v>
       </c>
@@ -2410,8 +3134,8 @@
       <c r="H29">
         <v>15.7463</v>
       </c>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="34"/>
       <c r="K29">
         <v>11.75</v>
       </c>
@@ -2421,8 +3145,8 @@
       <c r="M29">
         <v>1.78</v>
       </c>
-      <c r="N29" s="26"/>
-      <c r="O29" s="26"/>
+      <c r="N29" s="34"/>
+      <c r="O29" s="34"/>
       <c r="P29">
         <v>49.18</v>
       </c>
@@ -2432,8 +3156,8 @@
       <c r="R29">
         <v>5.7</v>
       </c>
-      <c r="S29" s="26"/>
-      <c r="T29" s="26"/>
+      <c r="S29" s="34"/>
+      <c r="T29" s="34"/>
       <c r="U29">
         <v>27.32</v>
       </c>
@@ -2443,14 +3167,14 @@
       <c r="W29">
         <v>5.42</v>
       </c>
-      <c r="X29" s="26"/>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A30" s="26"/>
+      <c r="X29" s="34"/>
+    </row>
+    <row r="30" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A30" s="34"/>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="26"/>
+      <c r="C30" s="34"/>
       <c r="D30">
         <v>25.96</v>
       </c>
@@ -2466,8 +3190,8 @@
       <c r="H30">
         <v>21.763400000000001</v>
       </c>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="34"/>
       <c r="K30">
         <v>10.28</v>
       </c>
@@ -2477,8 +3201,8 @@
       <c r="M30">
         <v>1.19</v>
       </c>
-      <c r="N30" s="26"/>
-      <c r="O30" s="26"/>
+      <c r="N30" s="34"/>
+      <c r="O30" s="34"/>
       <c r="P30">
         <v>47.54</v>
       </c>
@@ -2488,8 +3212,8 @@
       <c r="R30">
         <v>4.18</v>
       </c>
-      <c r="S30" s="26"/>
-      <c r="T30" s="26"/>
+      <c r="S30" s="34"/>
+      <c r="T30" s="34"/>
       <c r="U30">
         <v>25.06</v>
       </c>
@@ -2499,982 +3223,478 @@
       <c r="W30">
         <v>3.75</v>
       </c>
-      <c r="X30" s="26"/>
-    </row>
-    <row r="34" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="E34" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="F34" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="G34" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="H34" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="I34" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="J34" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="K34" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="L34" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="M34" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="N34" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="O34" s="23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="34"/>
-      <c r="C35" s="35"/>
-      <c r="D35" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="E35" s="30"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="H35" s="30"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="K35" s="32"/>
-      <c r="L35" s="33"/>
-      <c r="M35" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="N35" s="32"/>
-      <c r="O35" s="32"/>
-    </row>
-    <row r="36" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="28" t="s">
+      <c r="X30" s="34"/>
+    </row>
+    <row r="34" spans="2:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="B34" s="2"/>
+      <c r="C34" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="2">
+        <v>15</v>
+      </c>
+      <c r="D35" s="2">
+        <v>68.349999999999994</v>
+      </c>
+      <c r="E35" s="2">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" s="2">
+        <v>17.22</v>
+      </c>
+      <c r="D36" s="2">
+        <v>67.09</v>
+      </c>
+      <c r="E36" s="2">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B37" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="2">
+        <v>17.22</v>
+      </c>
+      <c r="D37" s="2">
+        <v>64.56</v>
+      </c>
+      <c r="E37" s="2">
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="B41" s="26"/>
+      <c r="C41" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G41" s="26"/>
+      <c r="H41" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B42" s="26">
         <v>0</v>
       </c>
-      <c r="C36" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D36" s="16">
-        <v>22.95</v>
-      </c>
-      <c r="E36" s="16">
+      <c r="C42" s="26">
+        <v>22.22</v>
+      </c>
+      <c r="D42" s="26">
+        <v>55.7</v>
+      </c>
+      <c r="E42" s="26">
+        <v>4.95</v>
+      </c>
+      <c r="G42" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="H42" s="2">
+        <v>17.22</v>
+      </c>
+      <c r="I42" s="2">
+        <v>64.56</v>
+      </c>
+      <c r="J42" s="2">
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B43" s="26">
+        <v>1</v>
+      </c>
+      <c r="C43" s="26">
+        <v>19.440000000000001</v>
+      </c>
+      <c r="D43" s="26">
+        <v>60.76</v>
+      </c>
+      <c r="E43" s="26">
+        <v>3.96</v>
+      </c>
+      <c r="G43" s="26">
+        <v>0.3</v>
+      </c>
+      <c r="H43" s="26">
+        <v>17.78</v>
+      </c>
+      <c r="I43" s="26">
+        <v>64.56</v>
+      </c>
+      <c r="J43" s="26">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B44" s="26">
+        <v>3</v>
+      </c>
+      <c r="C44" s="26">
+        <v>18.329999999999998</v>
+      </c>
+      <c r="D44" s="26">
+        <v>64.56</v>
+      </c>
+      <c r="E44" s="26">
+        <v>4.95</v>
+      </c>
+      <c r="G44" s="26">
+        <v>0.6</v>
+      </c>
+      <c r="H44" s="26">
+        <v>19.440000000000001</v>
+      </c>
+      <c r="I44" s="26">
+        <v>65.819999999999993</v>
+      </c>
+      <c r="J44" s="26">
+        <v>8.91</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B45" s="26">
+        <v>5</v>
+      </c>
+      <c r="C45" s="2">
+        <v>17.22</v>
+      </c>
+      <c r="D45" s="2">
+        <v>64.56</v>
+      </c>
+      <c r="E45" s="2">
+        <v>2.97</v>
+      </c>
+      <c r="G45" s="26">
+        <v>0.9</v>
+      </c>
+      <c r="H45" s="2">
+        <v>18.89</v>
+      </c>
+      <c r="I45" s="2">
+        <v>65.819999999999993</v>
+      </c>
+      <c r="J45" s="2">
+        <v>7.92</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B46" s="26">
+        <v>7</v>
+      </c>
+      <c r="C46" s="26">
+        <v>18.329999999999998</v>
+      </c>
+      <c r="D46" s="26">
+        <v>67.09</v>
+      </c>
+      <c r="E46" s="26">
+        <v>6.93</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B47" s="26">
+        <v>9</v>
+      </c>
+      <c r="C47" s="26">
+        <v>16.670000000000002</v>
+      </c>
+      <c r="D47" s="26">
+        <v>67.09</v>
+      </c>
+      <c r="E47" s="26">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" s="1">
+        <v>65.150000000000006</v>
+      </c>
+      <c r="E53" s="1">
+        <v>85.56</v>
+      </c>
+      <c r="F53" s="1">
+        <v>27.16</v>
+      </c>
+      <c r="G53" s="1">
+        <v>74.38</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B54" s="1"/>
+      <c r="C54" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" s="1">
+        <v>69.05</v>
+      </c>
+      <c r="E54" s="1">
+        <v>87.97</v>
+      </c>
+      <c r="F54" s="1">
+        <v>35.78</v>
+      </c>
+      <c r="G54" s="1">
+        <v>74.38</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B55" s="1"/>
+      <c r="C55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="1">
+        <v>72.760000000000005</v>
+      </c>
+      <c r="E55" s="1">
+        <v>90.37</v>
+      </c>
+      <c r="F55" s="1">
+        <v>39.22</v>
+      </c>
+      <c r="G55" s="1">
+        <v>82.64</v>
+      </c>
+      <c r="K55" s="1"/>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B56" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56">
         <v>49.45</v>
       </c>
-      <c r="F36" s="10">
-        <v>4.7300000000000004</v>
-      </c>
-      <c r="G36" s="16">
-        <v>24.6</v>
-      </c>
-      <c r="H36" s="16">
-        <v>56.95</v>
-      </c>
-      <c r="I36" s="10">
-        <v>9.0299999999999994</v>
-      </c>
-      <c r="J36" s="16">
-        <v>28.52</v>
-      </c>
-      <c r="K36" s="16">
-        <v>27.16</v>
-      </c>
-      <c r="L36" s="22">
-        <v>1.32</v>
-      </c>
-      <c r="M36" s="16">
-        <v>11.28</v>
-      </c>
-      <c r="N36" s="16">
-        <v>68.599999999999994</v>
-      </c>
-      <c r="O36" s="21">
-        <v>2.52</v>
-      </c>
-    </row>
-    <row r="37" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="B37" s="28"/>
-      <c r="C37" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D37" s="16">
-        <v>25.03</v>
-      </c>
-      <c r="E37" s="16">
-        <v>55.23</v>
-      </c>
-      <c r="F37" s="10">
+      <c r="E56">
+        <v>72.17</v>
+      </c>
+      <c r="F56">
+        <v>10.26</v>
+      </c>
+      <c r="G56" s="1">
+        <v>42.86</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B57" s="1"/>
+      <c r="C57" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G37" s="16">
-        <v>23.38</v>
-      </c>
-      <c r="H37" s="16">
-        <v>67.11</v>
-      </c>
-      <c r="I37" s="10">
-        <v>15.35</v>
-      </c>
-      <c r="J37" s="16">
-        <v>35.9</v>
-      </c>
-      <c r="K37" s="16">
-        <v>25.43</v>
-      </c>
-      <c r="L37" s="10">
-        <v>12.17</v>
-      </c>
-      <c r="M37" s="16">
-        <v>11.78</v>
-      </c>
-      <c r="N37" s="21">
-        <v>75.209999999999994</v>
-      </c>
-      <c r="O37" s="16">
-        <v>6.12</v>
-      </c>
-    </row>
-    <row r="38" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="B38" s="28"/>
-      <c r="C38" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D38" s="16">
-        <v>25.58</v>
-      </c>
-      <c r="E38" s="16">
-        <v>53.72</v>
-      </c>
-      <c r="F38" s="10">
-        <v>11.91</v>
-      </c>
-      <c r="G38" s="16">
-        <v>22.4</v>
-      </c>
-      <c r="H38" s="16">
-        <v>62.3</v>
-      </c>
-      <c r="I38" s="10">
-        <v>9.48</v>
-      </c>
-      <c r="J38" s="16">
-        <v>38.03</v>
-      </c>
-      <c r="K38" s="16">
-        <v>31.47</v>
-      </c>
-      <c r="L38" s="10">
-        <v>19.309999999999999</v>
-      </c>
-      <c r="M38" s="16">
-        <v>13.03</v>
-      </c>
-      <c r="N38" s="16">
-        <v>70.25</v>
-      </c>
-      <c r="O38" s="16">
-        <v>5.76</v>
-      </c>
-    </row>
-    <row r="39" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="B39" s="29"/>
-      <c r="C39" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D39" s="18">
-        <v>14.07</v>
-      </c>
-      <c r="E39" s="18">
-        <v>69.05</v>
-      </c>
-      <c r="F39" s="19">
-        <v>2.91</v>
-      </c>
-      <c r="G39" s="18">
-        <v>6.61</v>
-      </c>
-      <c r="H39" s="18">
-        <v>87.97</v>
-      </c>
-      <c r="I39" s="19">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="J39" s="18">
-        <v>26.39</v>
-      </c>
-      <c r="K39" s="18">
-        <v>35.78</v>
-      </c>
-      <c r="L39" s="6">
-        <v>3.17</v>
-      </c>
-      <c r="M39" s="18">
-        <v>10.53</v>
-      </c>
-      <c r="N39" s="20">
-        <v>74.38</v>
-      </c>
-      <c r="O39" s="20">
-        <v>3.96</v>
-      </c>
-    </row>
-    <row r="40" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B40" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D40" s="17">
-        <v>15.44</v>
-      </c>
-      <c r="E40" s="17">
-        <v>29.4</v>
-      </c>
-      <c r="F40" s="13">
-        <v>1.71</v>
-      </c>
-      <c r="G40" s="17">
-        <v>18.12</v>
-      </c>
-      <c r="H40" s="17">
-        <v>38.68</v>
-      </c>
-      <c r="I40" s="13">
-        <v>2.98</v>
-      </c>
-      <c r="J40" s="11">
-        <v>17.05</v>
-      </c>
-      <c r="K40" s="11">
-        <v>15.38</v>
-      </c>
-      <c r="L40" s="13">
-        <v>1.01</v>
-      </c>
-      <c r="M40" s="11">
-        <v>7.52</v>
-      </c>
-      <c r="N40" s="17">
+      <c r="D57">
+        <v>61.54</v>
+      </c>
+      <c r="E57">
+        <v>80.19</v>
+      </c>
+      <c r="F57">
+        <v>29.91</v>
+      </c>
+      <c r="G57" s="1">
+        <v>54.29</v>
+      </c>
+      <c r="K57" s="1"/>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B58" s="1"/>
+      <c r="C58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" s="1">
+        <v>65.11</v>
+      </c>
+      <c r="E58" s="1">
+        <v>80.66</v>
+      </c>
+      <c r="F58" s="1">
+        <v>34.19</v>
+      </c>
+      <c r="G58" s="1">
+        <v>74.290000000000006</v>
+      </c>
+      <c r="K58" s="1"/>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D59">
+        <v>35.47</v>
+      </c>
+      <c r="E59">
+        <v>51.71</v>
+      </c>
+      <c r="F59">
+        <v>17.670000000000002</v>
+      </c>
+      <c r="G59">
+        <v>45.31</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B60" s="1"/>
+      <c r="C60" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60">
+        <v>46.62</v>
+      </c>
+      <c r="E60">
+        <v>66.67</v>
+      </c>
+      <c r="F60">
+        <v>26.1</v>
+      </c>
+      <c r="G60">
+        <v>53.12</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B61" s="1"/>
+      <c r="C61" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61">
+        <v>48.81</v>
+      </c>
+      <c r="E61">
+        <v>67.09</v>
+      </c>
+      <c r="F61">
+        <v>30.12</v>
+      </c>
+      <c r="G61" s="1">
+        <v>54.69</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="O40" s="11">
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="41" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B41" s="28"/>
-      <c r="C41" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D41" s="7">
-        <v>17.03</v>
-      </c>
-      <c r="E41" s="7">
-        <v>41.76</v>
-      </c>
-      <c r="F41" s="10">
-        <v>6.77</v>
-      </c>
-      <c r="G41" s="7">
-        <v>16.77</v>
-      </c>
-      <c r="H41" s="16">
-        <v>57.08</v>
-      </c>
-      <c r="I41" s="8">
-        <v>7.6</v>
-      </c>
-      <c r="J41" s="16">
-        <v>22.3</v>
-      </c>
-      <c r="K41" s="16">
-        <v>17.95</v>
-      </c>
-      <c r="L41" s="10">
-        <v>8.11</v>
-      </c>
-      <c r="M41" s="16">
-        <v>9.52</v>
-      </c>
-      <c r="N41" s="16">
-        <v>28.57</v>
-      </c>
-      <c r="O41" s="16">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B42" s="28"/>
-      <c r="C42" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D42" s="7">
-        <v>15.5</v>
-      </c>
-      <c r="E42" s="7">
-        <v>43.68</v>
-      </c>
-      <c r="F42" s="8">
-        <v>5.34</v>
-      </c>
-      <c r="G42" s="16">
-        <v>13.83</v>
-      </c>
-      <c r="H42" s="7">
-        <v>57.55</v>
-      </c>
-      <c r="I42" s="8">
-        <v>3.8</v>
-      </c>
-      <c r="J42" s="7">
-        <v>22.62</v>
-      </c>
-      <c r="K42" s="7">
-        <v>15.38</v>
-      </c>
-      <c r="L42" s="10">
-        <v>7.91</v>
-      </c>
-      <c r="M42" s="7">
-        <v>8.02</v>
-      </c>
-      <c r="N42" s="7">
-        <v>54.29</v>
-      </c>
-      <c r="O42" s="16">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="43" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B43" s="29"/>
-      <c r="C43" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" s="3">
-        <v>7.89</v>
-      </c>
-      <c r="E43" s="3">
-        <v>61.54</v>
-      </c>
-      <c r="F43" s="4">
-        <v>0.27</v>
-      </c>
-      <c r="G43" s="3">
-        <v>5.14</v>
-      </c>
-      <c r="H43" s="3">
-        <v>80.19</v>
-      </c>
-      <c r="I43" s="4">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>14.1</v>
-      </c>
-      <c r="K43" s="3">
-        <v>29.91</v>
-      </c>
-      <c r="L43" s="19">
-        <v>0.81</v>
-      </c>
-      <c r="M43" s="3">
-        <v>4.01</v>
-      </c>
-      <c r="N43" s="18">
-        <v>54.29</v>
-      </c>
-      <c r="O43" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B44" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D44" s="11">
-        <v>23.38</v>
-      </c>
-      <c r="E44" s="11">
-        <v>24.5</v>
-      </c>
-      <c r="F44" s="12">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="G44" s="11">
-        <v>17.38</v>
-      </c>
-      <c r="H44" s="11">
-        <v>42.31</v>
-      </c>
-      <c r="I44" s="12">
-        <v>1.2</v>
-      </c>
-      <c r="J44" s="11">
-        <v>38.85</v>
-      </c>
-      <c r="K44" s="11">
-        <v>7.23</v>
-      </c>
-      <c r="L44" s="13">
-        <v>1.66</v>
-      </c>
-      <c r="M44" s="11">
-        <v>12.03</v>
-      </c>
-      <c r="N44" s="17">
-        <v>26.56</v>
-      </c>
-      <c r="O44" s="17">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="45" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B45" s="28"/>
-      <c r="C45" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="7">
-        <v>36.31</v>
-      </c>
-      <c r="E45" s="7">
-        <v>31.08</v>
-      </c>
-      <c r="F45" s="8">
-        <v>22.36</v>
-      </c>
-      <c r="G45" s="7">
-        <v>31.46</v>
-      </c>
-      <c r="H45" s="7">
-        <v>47.86</v>
-      </c>
-      <c r="I45" s="8">
-        <v>23.16</v>
-      </c>
-      <c r="J45" s="7">
-        <v>48.2</v>
-      </c>
-      <c r="K45" s="7">
-        <v>14.06</v>
-      </c>
-      <c r="L45" s="10">
-        <v>22.16</v>
-      </c>
-      <c r="M45" s="7">
-        <v>28.07</v>
-      </c>
-      <c r="N45" s="16">
-        <v>35.94</v>
-      </c>
-      <c r="O45" s="16">
-        <v>21.19</v>
-      </c>
-    </row>
-    <row r="46" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B46" s="28"/>
-      <c r="C46" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D46" s="7">
-        <v>55.31</v>
-      </c>
-      <c r="E46" s="7">
-        <v>14.08</v>
-      </c>
-      <c r="F46" s="8">
-        <v>41.14</v>
-      </c>
-      <c r="G46" s="7">
-        <v>53.12</v>
-      </c>
-      <c r="H46" s="7">
-        <v>16.670000000000002</v>
-      </c>
-      <c r="I46" s="8">
-        <v>40.82</v>
-      </c>
-      <c r="J46" s="7">
-        <v>66.89</v>
-      </c>
-      <c r="K46" s="7">
-        <v>9.64</v>
-      </c>
-      <c r="L46" s="10">
-        <v>50.69</v>
-      </c>
-      <c r="M46" s="7">
-        <v>42.11</v>
-      </c>
-      <c r="N46" s="7">
-        <v>21.88</v>
-      </c>
-      <c r="O46" s="7">
-        <v>35.22</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B47" s="29"/>
-      <c r="C47" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D47" s="3">
-        <v>16.43</v>
-      </c>
-      <c r="E47" s="3">
-        <v>46.62</v>
-      </c>
-      <c r="F47" s="4">
-        <v>0.63</v>
-      </c>
-      <c r="G47" s="3">
-        <v>10.039999999999999</v>
-      </c>
-      <c r="H47" s="3">
-        <v>66.67</v>
-      </c>
-      <c r="I47" s="4">
-        <v>0.69</v>
-      </c>
-      <c r="J47" s="15">
-        <v>30.82</v>
-      </c>
-      <c r="K47" s="15">
-        <v>26.1</v>
-      </c>
-      <c r="L47" s="14">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="M47" s="3">
-        <v>7.52</v>
-      </c>
-      <c r="N47" s="3">
-        <v>53.12</v>
-      </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B48" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D48" s="11">
-        <v>36.14</v>
-      </c>
-      <c r="E48" s="11">
-        <v>26.19</v>
-      </c>
-      <c r="F48" s="12">
-        <v>5.65</v>
-      </c>
-      <c r="G48" s="11">
-        <v>24.24</v>
-      </c>
-      <c r="H48" s="11">
-        <v>44.69</v>
-      </c>
-      <c r="I48" s="12">
-        <v>5.14</v>
-      </c>
-      <c r="J48" s="11">
-        <v>53.44</v>
-      </c>
-      <c r="K48" s="11">
-        <v>11.24</v>
-      </c>
-      <c r="L48" s="12">
-        <v>6.84</v>
-      </c>
-      <c r="M48" s="11">
-        <v>34.090000000000003</v>
-      </c>
-      <c r="N48" s="11">
-        <v>22.64</v>
-      </c>
-      <c r="O48" s="11">
-        <v>5.42</v>
-      </c>
-    </row>
-    <row r="49" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B49" s="28"/>
-      <c r="C49" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D49" s="7">
-        <v>40.53</v>
-      </c>
-      <c r="E49" s="7">
-        <v>31.95</v>
-      </c>
-      <c r="F49" s="8">
-        <v>18.43</v>
-      </c>
-      <c r="G49" s="7">
-        <v>26.44</v>
-      </c>
-      <c r="H49" s="7">
-        <v>52.73</v>
-      </c>
-      <c r="I49" s="8">
-        <v>14.03</v>
-      </c>
-      <c r="J49" s="7">
-        <v>61.97</v>
-      </c>
-      <c r="K49" s="7">
-        <v>11.24</v>
-      </c>
-      <c r="L49" s="8">
-        <v>26.62</v>
-      </c>
-      <c r="M49" s="7">
-        <v>36.590000000000003</v>
-      </c>
-      <c r="N49" s="7">
-        <v>36.479999999999997</v>
-      </c>
-      <c r="O49" s="7">
-        <v>18.75</v>
-      </c>
-    </row>
-    <row r="50" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B50" s="28"/>
-      <c r="C50" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D50" s="7">
-        <v>45.02</v>
-      </c>
-      <c r="E50" s="7">
-        <v>27.54</v>
-      </c>
-      <c r="F50" s="8">
-        <v>22.79</v>
-      </c>
-      <c r="G50" s="7">
-        <v>34.39</v>
-      </c>
-      <c r="H50" s="7">
+      <c r="C62" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D62">
+        <v>40.020000000000003</v>
+      </c>
+      <c r="E62">
+        <v>70.739999999999995</v>
+      </c>
+      <c r="F62">
+        <v>17</v>
+      </c>
+      <c r="G62">
+        <v>30.19</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B63" s="1"/>
+      <c r="C63" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D63">
+        <v>45.17</v>
+      </c>
+      <c r="E63">
+        <v>74.92</v>
+      </c>
+      <c r="F63">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="G63">
         <v>42.77</v>
       </c>
-      <c r="I50" s="8">
-        <v>19.96</v>
-      </c>
-      <c r="J50" s="7">
-        <v>63.28</v>
-      </c>
-      <c r="K50" s="7">
-        <v>11.53</v>
-      </c>
-      <c r="L50" s="8">
-        <v>30.04</v>
-      </c>
-      <c r="M50" s="7">
-        <v>38.85</v>
-      </c>
-      <c r="N50" s="7">
-        <v>32.700000000000003</v>
-      </c>
-      <c r="O50" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51" spans="2:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="B51" s="29"/>
-      <c r="C51" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D51" s="3">
-        <v>25.96</v>
-      </c>
-      <c r="E51" s="3">
-        <v>45.17</v>
-      </c>
-      <c r="F51" s="4">
-        <v>2.58</v>
-      </c>
-      <c r="G51" s="3">
-        <v>10.28</v>
-      </c>
-      <c r="H51" s="3">
-        <v>74.92</v>
-      </c>
-      <c r="I51" s="4">
-        <v>1.19</v>
-      </c>
-      <c r="J51" s="3">
-        <v>47.54</v>
-      </c>
-      <c r="K51" s="3">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="L51" s="4">
-        <v>4.18</v>
-      </c>
-      <c r="M51" s="3">
-        <v>25.06</v>
-      </c>
-      <c r="N51" s="3">
-        <v>42.77</v>
-      </c>
-      <c r="O51" s="3">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="54" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="B54" s="2"/>
-      <c r="C54" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="55" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B55" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C55" s="2">
-        <v>15</v>
-      </c>
-      <c r="D55" s="2">
-        <v>68.349999999999994</v>
-      </c>
-      <c r="E55" s="2">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="56" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B56" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C56" s="2">
-        <v>17.22</v>
-      </c>
-      <c r="D56" s="2">
-        <v>67.09</v>
-      </c>
-      <c r="E56" s="2">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="57" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B57" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C57" s="2">
-        <v>17.22</v>
-      </c>
-      <c r="D57" s="2">
-        <v>64.56</v>
-      </c>
-      <c r="E57" s="2">
-        <v>2.97</v>
-      </c>
-    </row>
-    <row r="61" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="B61" s="36"/>
-      <c r="C61" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G61" s="36"/>
-      <c r="H61" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J61" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="62" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B62" s="36">
-        <v>0</v>
-      </c>
-      <c r="C62" s="36">
-        <v>22.22</v>
-      </c>
-      <c r="D62" s="36">
-        <v>55.7</v>
-      </c>
-      <c r="E62" s="36">
-        <v>4.95</v>
-      </c>
-      <c r="G62" s="36">
-        <v>0.1</v>
-      </c>
-      <c r="H62" s="2">
-        <v>17.22</v>
-      </c>
-      <c r="I62" s="2">
-        <v>64.56</v>
-      </c>
-      <c r="J62" s="2">
-        <v>2.97</v>
-      </c>
-    </row>
-    <row r="63" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B63" s="36">
-        <v>1</v>
-      </c>
-      <c r="C63" s="36">
-        <v>19.440000000000001</v>
-      </c>
-      <c r="D63" s="36">
-        <v>60.76</v>
-      </c>
-      <c r="E63" s="36">
-        <v>3.96</v>
-      </c>
-      <c r="G63" s="36">
-        <v>0.3</v>
-      </c>
-      <c r="H63" s="36">
-        <v>17.78</v>
-      </c>
-      <c r="I63" s="36">
-        <v>64.56</v>
-      </c>
-      <c r="J63" s="36">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="64" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B64" s="36">
-        <v>3</v>
-      </c>
-      <c r="C64" s="36">
-        <v>18.329999999999998</v>
-      </c>
-      <c r="D64" s="36">
-        <v>64.56</v>
-      </c>
-      <c r="E64" s="36">
-        <v>4.95</v>
-      </c>
-      <c r="G64" s="36">
-        <v>0.6</v>
-      </c>
-      <c r="H64" s="36">
-        <v>19.440000000000001</v>
-      </c>
-      <c r="I64" s="36">
-        <v>65.819999999999993</v>
-      </c>
-      <c r="J64" s="36">
-        <v>8.91</v>
-      </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B65" s="36">
-        <v>5</v>
-      </c>
-      <c r="C65" s="2">
-        <v>17.22</v>
-      </c>
-      <c r="D65" s="2">
-        <v>64.56</v>
-      </c>
-      <c r="E65" s="2">
-        <v>2.97</v>
-      </c>
-      <c r="G65" s="36">
-        <v>0.9</v>
-      </c>
-      <c r="H65" s="2">
-        <v>18.89</v>
-      </c>
-      <c r="I65" s="2">
-        <v>65.819999999999993</v>
-      </c>
-      <c r="J65" s="2">
-        <v>7.92</v>
-      </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B66" s="36">
-        <v>7</v>
-      </c>
-      <c r="C66" s="36">
-        <v>18.329999999999998</v>
-      </c>
-      <c r="D66" s="36">
-        <v>67.09</v>
-      </c>
-      <c r="E66" s="36">
-        <v>6.93</v>
-      </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B67" s="36">
-        <v>9</v>
-      </c>
-      <c r="C67" s="36">
-        <v>16.670000000000002</v>
-      </c>
-      <c r="D67" s="36">
-        <v>67.09</v>
-      </c>
-      <c r="E67" s="36">
-        <v>3.96</v>
-      </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" s="1">
+        <v>48.1</v>
+      </c>
+      <c r="E64" s="1">
+        <v>76.209999999999994</v>
+      </c>
+      <c r="F64">
+        <v>23.05</v>
+      </c>
+      <c r="G64" s="1">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="71" spans="12:25" x14ac:dyDescent="0.2">
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
@@ -3488,278 +3708,50 @@
       <c r="X71" s="1"/>
       <c r="Y71" s="1"/>
     </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B73" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D73" s="1">
-        <v>65.150000000000006</v>
-      </c>
-      <c r="E73" s="1">
-        <v>85.56</v>
-      </c>
-      <c r="F73" s="1">
-        <v>27.16</v>
-      </c>
-      <c r="G73" s="1">
-        <v>74.38</v>
-      </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B74" s="1"/>
-      <c r="C74" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D74" s="1">
-        <v>69.05</v>
-      </c>
-      <c r="E74" s="1">
-        <v>87.97</v>
-      </c>
-      <c r="F74" s="1">
-        <v>35.78</v>
-      </c>
-      <c r="G74" s="1">
-        <v>74.38</v>
-      </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B75" s="1"/>
-      <c r="C75" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D75" s="1">
-        <v>72.760000000000005</v>
-      </c>
-      <c r="E75" s="1">
-        <v>90.37</v>
-      </c>
-      <c r="F75" s="1">
-        <v>39.22</v>
-      </c>
-      <c r="G75" s="1">
-        <v>82.64</v>
-      </c>
-      <c r="K75" s="1"/>
+    <row r="75" spans="12:25" x14ac:dyDescent="0.2">
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
       <c r="N75" s="1"/>
     </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B76" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D76">
-        <v>49.45</v>
-      </c>
-      <c r="E76">
-        <v>72.17</v>
-      </c>
-      <c r="F76">
-        <v>10.26</v>
-      </c>
-      <c r="G76" s="1">
-        <v>42.86</v>
-      </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B77" s="1"/>
-      <c r="C77" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D77">
-        <v>61.54</v>
-      </c>
-      <c r="E77">
-        <v>80.19</v>
-      </c>
-      <c r="F77">
-        <v>29.91</v>
-      </c>
-      <c r="G77" s="1">
-        <v>54.29</v>
-      </c>
-      <c r="K77" s="1"/>
+    <row r="77" spans="12:25" x14ac:dyDescent="0.2">
       <c r="L77" s="1"/>
       <c r="M77" s="1"/>
       <c r="N77" s="1"/>
     </row>
-    <row r="78" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B78" s="1"/>
-      <c r="C78" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D78" s="1">
-        <v>65.11</v>
-      </c>
-      <c r="E78" s="1">
-        <v>80.66</v>
-      </c>
-      <c r="F78" s="1">
-        <v>34.19</v>
-      </c>
-      <c r="G78" s="1">
-        <v>74.290000000000006</v>
-      </c>
-      <c r="K78" s="1"/>
+    <row r="78" spans="12:25" x14ac:dyDescent="0.2">
       <c r="L78" s="1"/>
       <c r="M78" s="1"/>
       <c r="N78" s="1"/>
     </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B79" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D79">
-        <v>35.47</v>
-      </c>
-      <c r="E79">
-        <v>51.71</v>
-      </c>
-      <c r="F79">
-        <v>17.670000000000002</v>
-      </c>
-      <c r="G79">
-        <v>45.31</v>
-      </c>
-    </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B80" s="1"/>
-      <c r="C80" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D80">
-        <v>46.62</v>
-      </c>
-      <c r="E80">
-        <v>66.67</v>
-      </c>
-      <c r="F80">
-        <v>26.1</v>
-      </c>
-      <c r="G80">
-        <v>53.12</v>
-      </c>
-    </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B81" s="1"/>
-      <c r="C81" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D81">
-        <v>48.81</v>
-      </c>
-      <c r="E81">
-        <v>67.09</v>
-      </c>
-      <c r="F81">
-        <v>30.12</v>
-      </c>
-      <c r="G81" s="1">
-        <v>54.69</v>
-      </c>
-    </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B82" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D82">
-        <v>40.020000000000003</v>
-      </c>
-      <c r="E82">
-        <v>70.739999999999995</v>
-      </c>
-      <c r="F82">
-        <v>17</v>
-      </c>
-      <c r="G82">
-        <v>30.19</v>
-      </c>
-    </row>
-    <row r="83" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B83" s="1"/>
-      <c r="C83" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D83">
-        <v>45.17</v>
-      </c>
-      <c r="E83">
-        <v>74.92</v>
-      </c>
-      <c r="F83">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="G83">
-        <v>42.77</v>
-      </c>
-    </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="C84" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D84" s="1">
-        <v>48.1</v>
-      </c>
-      <c r="E84" s="1">
-        <v>76.209999999999994</v>
-      </c>
-      <c r="F84">
-        <v>23.05</v>
-      </c>
-      <c r="G84" s="1">
-        <v>47.8</v>
-      </c>
-    </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="86" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M86" s="1"/>
     </row>
-    <row r="87" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="87" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M87" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B40:B43"/>
-    <mergeCell ref="B36:B39"/>
-    <mergeCell ref="B48:B51"/>
-    <mergeCell ref="B44:B47"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="C3:C9"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="A24:A30"/>
+    <mergeCell ref="C24:C30"/>
+    <mergeCell ref="O24:O30"/>
+    <mergeCell ref="T17:T23"/>
+    <mergeCell ref="X21:X23"/>
+    <mergeCell ref="T24:T30"/>
+    <mergeCell ref="N28:N30"/>
+    <mergeCell ref="S28:S30"/>
+    <mergeCell ref="X28:X30"/>
+    <mergeCell ref="J24:J30"/>
+    <mergeCell ref="X14:X16"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="S7:S9"/>
+    <mergeCell ref="S21:S23"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="T1:X1"/>
+    <mergeCell ref="T3:T9"/>
+    <mergeCell ref="T10:T16"/>
+    <mergeCell ref="S14:S16"/>
     <mergeCell ref="A3:A9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J3:J9"/>
@@ -3775,27 +3767,19 @@
     <mergeCell ref="J10:J16"/>
     <mergeCell ref="O3:O9"/>
     <mergeCell ref="N14:N16"/>
-    <mergeCell ref="X14:X16"/>
-    <mergeCell ref="J1:N1"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="S7:S9"/>
-    <mergeCell ref="S21:S23"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="T1:X1"/>
-    <mergeCell ref="T3:T9"/>
-    <mergeCell ref="T10:T16"/>
-    <mergeCell ref="S14:S16"/>
-    <mergeCell ref="A24:A30"/>
-    <mergeCell ref="C24:C30"/>
-    <mergeCell ref="O24:O30"/>
-    <mergeCell ref="T17:T23"/>
-    <mergeCell ref="X21:X23"/>
-    <mergeCell ref="T24:T30"/>
-    <mergeCell ref="N28:N30"/>
-    <mergeCell ref="S28:S30"/>
-    <mergeCell ref="X28:X30"/>
-    <mergeCell ref="J24:J30"/>
+    <mergeCell ref="AA16:AA19"/>
+    <mergeCell ref="AA12:AA15"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="AC3:AE3"/>
+    <mergeCell ref="AF3:AH3"/>
+    <mergeCell ref="AI3:AK3"/>
+    <mergeCell ref="AL3:AN3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AA8:AA11"/>
+    <mergeCell ref="AA4:AA7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/stat/data.xlsx
+++ b/stat/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr\Documents\Workspace\LLMHalluMiti\stat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E2864F-F2D7-4875-9683-7270E02141EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA84B2A-59D7-488D-9B34-ECAEB15A0B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="52">
   <si>
     <t>gpt-4o</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -193,6 +193,42 @@
   </si>
   <si>
     <t>oc.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recheck hallucination rate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temperature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hallucination repair rate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>over-correction rate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>token cost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>time cost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>model</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>method</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CoVe-SE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -200,6 +236,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -412,7 +451,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -492,6 +531,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -504,23 +561,53 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -802,7 +889,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN87"/>
+  <dimension ref="A1:AZ87"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="27" max="28" width="7.625" customWidth="1"/>
@@ -815,43 +902,47 @@
     <col min="37" max="38" width="6.625" customWidth="1"/>
     <col min="39" max="39" width="8.875" customWidth="1"/>
     <col min="40" max="40" width="6.625" customWidth="1"/>
+    <col min="43" max="43" width="10.625" customWidth="1"/>
+    <col min="44" max="45" width="25.625" customWidth="1"/>
+    <col min="46" max="46" width="20.625" customWidth="1"/>
+    <col min="49" max="52" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34" t="s">
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34" t="s">
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34" t="s">
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-    </row>
-    <row r="2" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+    </row>
+    <row r="2" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
@@ -962,15 +1053,39 @@
       <c r="AN2" s="23" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:40" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="34" t="s">
+      <c r="AQ2" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="AR2" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS2" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT2" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="AW2" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="AX2" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="AY2" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="AZ2" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="27" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="34">
+      <c r="C3" s="27">
         <v>39.81</v>
       </c>
       <c r="D3" s="1">
@@ -989,7 +1104,7 @@
         <v>4.9604999999999997</v>
       </c>
       <c r="I3" s="1"/>
-      <c r="J3" s="34">
+      <c r="J3" s="27">
         <v>45.78</v>
       </c>
       <c r="K3" s="1">
@@ -1002,7 +1117,7 @@
         <v>9.0299999999999994</v>
       </c>
       <c r="N3" s="1"/>
-      <c r="O3" s="34">
+      <c r="O3" s="27">
         <v>38.03</v>
       </c>
       <c r="P3" s="1">
@@ -1015,7 +1130,7 @@
         <v>1.32</v>
       </c>
       <c r="S3" s="1"/>
-      <c r="T3" s="34">
+      <c r="T3" s="27">
         <v>30.33</v>
       </c>
       <c r="U3" s="1">
@@ -1028,35 +1143,59 @@
         <v>2.52</v>
       </c>
       <c r="X3" s="1"/>
-      <c r="AA3" s="29"/>
-      <c r="AB3" s="30"/>
-      <c r="AC3" s="35" t="s">
+      <c r="AA3" s="35"/>
+      <c r="AB3" s="36"/>
+      <c r="AC3" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="AD3" s="35"/>
-      <c r="AE3" s="36"/>
-      <c r="AF3" s="35" t="s">
+      <c r="AD3" s="31"/>
+      <c r="AE3" s="32"/>
+      <c r="AF3" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="AG3" s="35"/>
-      <c r="AH3" s="36"/>
-      <c r="AI3" s="27" t="s">
+      <c r="AG3" s="31"/>
+      <c r="AH3" s="32"/>
+      <c r="AI3" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="AJ3" s="27"/>
-      <c r="AK3" s="28"/>
-      <c r="AL3" s="27" t="s">
+      <c r="AJ3" s="33"/>
+      <c r="AK3" s="34"/>
+      <c r="AL3" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="AM3" s="27"/>
-      <c r="AN3" s="27"/>
-    </row>
-    <row r="4" spans="1:40" ht="15.75" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34"/>
+      <c r="AM3" s="33"/>
+      <c r="AN3" s="33"/>
+      <c r="AQ3" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="AR3" s="38">
+        <v>17.22</v>
+      </c>
+      <c r="AS3" s="38">
+        <v>64.56</v>
+      </c>
+      <c r="AT3" s="16">
+        <v>2.97</v>
+      </c>
+      <c r="AW3" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="AX3" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="AY3" s="45">
+        <v>100.61</v>
+      </c>
+      <c r="AZ3" s="46">
+        <v>4.9604999999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="27"/>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="34"/>
+      <c r="C4" s="27"/>
       <c r="D4" s="1">
         <v>25.03</v>
       </c>
@@ -1073,7 +1212,7 @@
         <v>22.125900000000001</v>
       </c>
       <c r="I4" s="1"/>
-      <c r="J4" s="34"/>
+      <c r="J4" s="27"/>
       <c r="K4" s="1">
         <v>23.38</v>
       </c>
@@ -1084,7 +1223,7 @@
         <v>15.35</v>
       </c>
       <c r="N4" s="1"/>
-      <c r="O4" s="34"/>
+      <c r="O4" s="27"/>
       <c r="P4" s="1">
         <v>35.9</v>
       </c>
@@ -1095,7 +1234,7 @@
         <v>12.17</v>
       </c>
       <c r="S4" s="1"/>
-      <c r="T4" s="34"/>
+      <c r="T4" s="27"/>
       <c r="U4" s="1">
         <v>11.78</v>
       </c>
@@ -1106,7 +1245,7 @@
         <v>6.12</v>
       </c>
       <c r="X4" s="1"/>
-      <c r="AA4" s="32" t="s">
+      <c r="AA4" s="29" t="s">
         <v>0</v>
       </c>
       <c r="AB4" s="9" t="s">
@@ -1148,13 +1287,35 @@
       <c r="AN4" s="21">
         <v>2.52</v>
       </c>
-    </row>
-    <row r="5" spans="1:40" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="34"/>
+      <c r="AQ4" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="AR4" s="39">
+        <v>17.78</v>
+      </c>
+      <c r="AS4" s="39">
+        <v>64.56</v>
+      </c>
+      <c r="AT4" s="7">
+        <v>4.95</v>
+      </c>
+      <c r="AW4" s="40"/>
+      <c r="AX4" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY4" s="45">
+        <v>2253.6799999999998</v>
+      </c>
+      <c r="AZ4" s="46">
+        <v>22.125900000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="27"/>
       <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="34"/>
+      <c r="C5" s="27"/>
       <c r="D5" s="1">
         <v>25.58</v>
       </c>
@@ -1171,7 +1332,7 @@
         <v>33.609499999999997</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="34"/>
+      <c r="J5" s="27"/>
       <c r="K5" s="1">
         <v>22.4</v>
       </c>
@@ -1182,7 +1343,7 @@
         <v>9.48</v>
       </c>
       <c r="N5" s="1"/>
-      <c r="O5" s="34"/>
+      <c r="O5" s="27"/>
       <c r="P5" s="1">
         <v>38.03</v>
       </c>
@@ -1193,7 +1354,7 @@
         <v>19.309999999999999</v>
       </c>
       <c r="S5" s="1"/>
-      <c r="T5" s="34"/>
+      <c r="T5" s="27"/>
       <c r="U5" s="1">
         <v>13.03</v>
       </c>
@@ -1204,7 +1365,7 @@
         <v>5.76</v>
       </c>
       <c r="X5" s="1"/>
-      <c r="AA5" s="32"/>
+      <c r="AA5" s="29"/>
       <c r="AB5" s="9" t="s">
         <v>27</v>
       </c>
@@ -1244,13 +1405,35 @@
       <c r="AN5" s="16">
         <v>6.12</v>
       </c>
-    </row>
-    <row r="6" spans="1:40" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="34"/>
+      <c r="AQ5" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="AR5" s="39">
+        <v>19.440000000000001</v>
+      </c>
+      <c r="AS5" s="39">
+        <v>65.819999999999993</v>
+      </c>
+      <c r="AT5" s="7">
+        <v>8.91</v>
+      </c>
+      <c r="AW5" s="40"/>
+      <c r="AX5" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="AY5" s="45">
+        <v>3623.59</v>
+      </c>
+      <c r="AZ5" s="46">
+        <v>33.609499999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="27"/>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="34"/>
+      <c r="C6" s="27"/>
       <c r="D6" s="1">
         <v>17.579999999999998</v>
       </c>
@@ -1267,7 +1450,7 @@
         <v>6.4598000000000004</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="34"/>
+      <c r="J6" s="27"/>
       <c r="K6" s="1">
         <v>10.4</v>
       </c>
@@ -1278,7 +1461,7 @@
         <v>7</v>
       </c>
       <c r="N6" s="1"/>
-      <c r="O6" s="34"/>
+      <c r="O6" s="27"/>
       <c r="P6" s="1">
         <v>31.97</v>
       </c>
@@ -1289,7 +1472,7 @@
         <v>6.88</v>
       </c>
       <c r="S6" s="1"/>
-      <c r="T6" s="34"/>
+      <c r="T6" s="27"/>
       <c r="U6" s="1">
         <v>10.28</v>
       </c>
@@ -1300,7 +1483,7 @@
         <v>3.6</v>
       </c>
       <c r="X6" s="1"/>
-      <c r="AA6" s="32"/>
+      <c r="AA6" s="29"/>
       <c r="AB6" s="9" t="s">
         <v>23</v>
       </c>
@@ -1340,13 +1523,35 @@
       <c r="AN6" s="16">
         <v>5.76</v>
       </c>
-    </row>
-    <row r="7" spans="1:40" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="34"/>
+      <c r="AQ6" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="AR6" s="38">
+        <v>18.89</v>
+      </c>
+      <c r="AS6" s="38">
+        <v>65.819999999999993</v>
+      </c>
+      <c r="AT6" s="16">
+        <v>7.92</v>
+      </c>
+      <c r="AW6" s="43"/>
+      <c r="AX6" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="AY6" s="47">
+        <v>4191.1000000000004</v>
+      </c>
+      <c r="AZ6" s="48">
+        <v>22.114799999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="27"/>
       <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="34"/>
+      <c r="C7" s="27"/>
       <c r="D7" s="1">
         <v>15.55</v>
       </c>
@@ -1362,10 +1567,10 @@
       <c r="H7" s="1">
         <v>17.849</v>
       </c>
-      <c r="I7" s="34">
+      <c r="I7" s="27">
         <v>72.760000000000005</v>
       </c>
-      <c r="J7" s="34"/>
+      <c r="J7" s="27"/>
       <c r="K7" s="1">
         <v>7.34</v>
       </c>
@@ -1375,10 +1580,10 @@
       <c r="M7" s="1">
         <v>2.48</v>
       </c>
-      <c r="N7" s="34">
+      <c r="N7" s="27">
         <v>90.37</v>
       </c>
-      <c r="O7" s="34"/>
+      <c r="O7" s="27"/>
       <c r="P7" s="1">
         <v>30.49</v>
       </c>
@@ -1388,10 +1593,10 @@
       <c r="R7" s="1">
         <v>5.29</v>
       </c>
-      <c r="S7" s="34">
+      <c r="S7" s="27">
         <v>39.22</v>
       </c>
-      <c r="T7" s="34"/>
+      <c r="T7" s="27"/>
       <c r="U7" s="1">
         <v>9.52</v>
       </c>
@@ -1401,10 +1606,10 @@
       <c r="W7" s="1">
         <v>4.32</v>
       </c>
-      <c r="X7" s="34">
+      <c r="X7" s="27">
         <v>82.64</v>
       </c>
-      <c r="AA7" s="33"/>
+      <c r="AA7" s="30"/>
       <c r="AB7" s="5" t="s">
         <v>26</v>
       </c>
@@ -1444,13 +1649,25 @@
       <c r="AN7" s="20">
         <v>3.96</v>
       </c>
-    </row>
-    <row r="8" spans="1:40" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" s="34"/>
+      <c r="AW7" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX7" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="AY7" s="45">
+        <v>94.58</v>
+      </c>
+      <c r="AZ7" s="49">
+        <v>12.401999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="27"/>
       <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="34"/>
+      <c r="C8" s="27"/>
       <c r="D8" s="1">
         <v>19.11</v>
       </c>
@@ -1466,8 +1683,8 @@
       <c r="H8" s="1">
         <v>20.038900000000002</v>
       </c>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
       <c r="K8" s="1">
         <v>8.69</v>
       </c>
@@ -1477,8 +1694,8 @@
       <c r="M8" s="1">
         <v>3.84</v>
       </c>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
       <c r="P8" s="1">
         <v>31.8</v>
       </c>
@@ -1488,8 +1705,8 @@
       <c r="R8" s="1">
         <v>8.1999999999999993</v>
       </c>
-      <c r="S8" s="34"/>
-      <c r="T8" s="34"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="27"/>
       <c r="U8" s="1">
         <v>21.05</v>
       </c>
@@ -1499,8 +1716,8 @@
       <c r="W8" s="1">
         <v>14.75</v>
       </c>
-      <c r="X8" s="34"/>
-      <c r="AA8" s="31" t="s">
+      <c r="X8" s="27"/>
+      <c r="AA8" s="28" t="s">
         <v>1</v>
       </c>
       <c r="AB8" s="9" t="s">
@@ -1542,13 +1759,23 @@
       <c r="AN8" s="11">
         <v>0.55000000000000004</v>
       </c>
-    </row>
-    <row r="9" spans="1:40" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="34"/>
+      <c r="AW8" s="40"/>
+      <c r="AX8" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY8" s="50">
+        <v>6743.49</v>
+      </c>
+      <c r="AZ8" s="49">
+        <v>114.9687</v>
+      </c>
+    </row>
+    <row r="9" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="27"/>
       <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="34"/>
+      <c r="C9" s="27"/>
       <c r="D9" s="1">
         <v>14.07</v>
       </c>
@@ -1564,8 +1791,8 @@
       <c r="H9" s="1">
         <v>22.114799999999999</v>
       </c>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
       <c r="K9" s="1">
         <v>6.61</v>
       </c>
@@ -1575,8 +1802,8 @@
       <c r="M9" s="1">
         <v>2.0299999999999998</v>
       </c>
-      <c r="N9" s="34"/>
-      <c r="O9" s="34"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="27"/>
       <c r="P9" s="1">
         <v>26.39</v>
       </c>
@@ -1586,8 +1813,8 @@
       <c r="R9" s="1">
         <v>3.17</v>
       </c>
-      <c r="S9" s="34"/>
-      <c r="T9" s="34"/>
+      <c r="S9" s="27"/>
+      <c r="T9" s="27"/>
       <c r="U9" s="1">
         <v>10.53</v>
       </c>
@@ -1597,8 +1824,8 @@
       <c r="W9" s="1">
         <v>3.96</v>
       </c>
-      <c r="X9" s="34"/>
-      <c r="AA9" s="32"/>
+      <c r="X9" s="27"/>
+      <c r="AA9" s="29"/>
       <c r="AB9" s="9" t="s">
         <v>24</v>
       </c>
@@ -1638,15 +1865,25 @@
       <c r="AN9" s="16">
         <v>3.57</v>
       </c>
-    </row>
-    <row r="10" spans="1:40" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
+      <c r="AW9" s="40"/>
+      <c r="AX9" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="AY9" s="50">
+        <v>7320.52</v>
+      </c>
+      <c r="AZ9" s="49">
+        <v>113.2599</v>
+      </c>
+    </row>
+    <row r="10" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="27" t="s">
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="27">
         <v>19.93</v>
       </c>
       <c r="D10" s="1">
@@ -1664,7 +1901,7 @@
       <c r="H10">
         <v>12.401999999999999</v>
       </c>
-      <c r="J10" s="34">
+      <c r="J10" s="27">
         <v>25.95</v>
       </c>
       <c r="K10" s="1">
@@ -1676,7 +1913,7 @@
       <c r="M10" s="1">
         <v>2.98</v>
       </c>
-      <c r="O10" s="34">
+      <c r="O10" s="27">
         <v>19.18</v>
       </c>
       <c r="P10">
@@ -1688,7 +1925,7 @@
       <c r="R10" s="1">
         <v>1.01</v>
       </c>
-      <c r="T10" s="34">
+      <c r="T10" s="27">
         <v>8.77</v>
       </c>
       <c r="U10">
@@ -1700,7 +1937,7 @@
       <c r="W10">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AA10" s="32"/>
+      <c r="AA10" s="29"/>
       <c r="AB10" s="9" t="s">
         <v>23</v>
       </c>
@@ -1740,13 +1977,23 @@
       <c r="AN10" s="16">
         <v>4.4000000000000004</v>
       </c>
-    </row>
-    <row r="11" spans="1:40" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="34"/>
+      <c r="AW10" s="43"/>
+      <c r="AX10" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="AY10" s="51">
+        <v>3609.91</v>
+      </c>
+      <c r="AZ10" s="52">
+        <v>168.54599999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="27"/>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="34"/>
+      <c r="C11" s="27"/>
       <c r="D11">
         <v>17.03</v>
       </c>
@@ -1762,7 +2009,7 @@
       <c r="H11">
         <v>114.9687</v>
       </c>
-      <c r="J11" s="34"/>
+      <c r="J11" s="27"/>
       <c r="K11">
         <v>16.77</v>
       </c>
@@ -1772,7 +2019,7 @@
       <c r="M11">
         <v>7.6</v>
       </c>
-      <c r="O11" s="34"/>
+      <c r="O11" s="27"/>
       <c r="P11" s="1">
         <v>22.3</v>
       </c>
@@ -1782,7 +2029,7 @@
       <c r="R11" s="1">
         <v>8.11</v>
       </c>
-      <c r="T11" s="34"/>
+      <c r="T11" s="27"/>
       <c r="U11" s="1">
         <v>9.52</v>
       </c>
@@ -1792,7 +2039,7 @@
       <c r="W11" s="1">
         <v>3.57</v>
       </c>
-      <c r="AA11" s="33"/>
+      <c r="AA11" s="30"/>
       <c r="AB11" s="5" t="s">
         <v>22</v>
       </c>
@@ -1832,13 +2079,25 @@
       <c r="AN11" s="18">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:40" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="34"/>
+      <c r="AW11" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX11" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="AY11" s="50">
+        <v>95.45</v>
+      </c>
+      <c r="AZ11" s="49">
+        <v>3.6791999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="27"/>
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="34"/>
+      <c r="C12" s="27"/>
       <c r="D12">
         <v>15.5</v>
       </c>
@@ -1854,7 +2113,7 @@
       <c r="H12">
         <v>113.2599</v>
       </c>
-      <c r="J12" s="34"/>
+      <c r="J12" s="27"/>
       <c r="K12" s="1">
         <v>13.83</v>
       </c>
@@ -1864,7 +2123,7 @@
       <c r="M12">
         <v>3.8</v>
       </c>
-      <c r="O12" s="34"/>
+      <c r="O12" s="27"/>
       <c r="P12">
         <v>22.62</v>
       </c>
@@ -1874,7 +2133,7 @@
       <c r="R12" s="1">
         <v>7.91</v>
       </c>
-      <c r="T12" s="34"/>
+      <c r="T12" s="27"/>
       <c r="U12">
         <v>8.02</v>
       </c>
@@ -1884,7 +2143,7 @@
       <c r="W12" s="1">
         <v>4.4000000000000004</v>
       </c>
-      <c r="AA12" s="31" t="s">
+      <c r="AA12" s="28" t="s">
         <v>13</v>
       </c>
       <c r="AB12" s="9" t="s">
@@ -1926,13 +2185,23 @@
       <c r="AN12" s="17">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="13" spans="1:40" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="34"/>
+      <c r="AW12" s="40"/>
+      <c r="AX12" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY12" s="50">
+        <v>3620.41</v>
+      </c>
+      <c r="AZ12" s="49">
+        <v>26.883299999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="27"/>
       <c r="B13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="34"/>
+      <c r="C13" s="27"/>
       <c r="D13">
         <v>11.66</v>
       </c>
@@ -1948,7 +2217,7 @@
       <c r="H13">
         <v>17.3841</v>
       </c>
-      <c r="J13" s="34"/>
+      <c r="J13" s="27"/>
       <c r="K13">
         <v>8.1999999999999993</v>
       </c>
@@ -1958,7 +2227,7 @@
       <c r="M13">
         <v>1.49</v>
       </c>
-      <c r="O13" s="34"/>
+      <c r="O13" s="27"/>
       <c r="P13">
         <v>20.16</v>
       </c>
@@ -1968,7 +2237,7 @@
       <c r="R13">
         <v>3.65</v>
       </c>
-      <c r="T13" s="34"/>
+      <c r="T13" s="27"/>
       <c r="U13" s="1">
         <v>5.76</v>
       </c>
@@ -1978,7 +2247,7 @@
       <c r="W13" s="1">
         <v>0.82</v>
       </c>
-      <c r="AA13" s="32"/>
+      <c r="AA13" s="29"/>
       <c r="AB13" s="9" t="s">
         <v>24</v>
       </c>
@@ -2018,13 +2287,23 @@
       <c r="AN13" s="16">
         <v>21.19</v>
       </c>
-    </row>
-    <row r="14" spans="1:40" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="34"/>
+      <c r="AW13" s="40"/>
+      <c r="AX13" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="AY13" s="50">
+        <v>3227.44</v>
+      </c>
+      <c r="AZ13" s="49">
+        <v>24.215399999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="27"/>
       <c r="B14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="34"/>
+      <c r="C14" s="27"/>
       <c r="D14">
         <v>10.08</v>
       </c>
@@ -2040,10 +2319,10 @@
       <c r="H14">
         <v>147.7028</v>
       </c>
-      <c r="I14" s="34">
+      <c r="I14" s="27">
         <v>65.11</v>
       </c>
-      <c r="J14" s="34"/>
+      <c r="J14" s="27"/>
       <c r="K14">
         <v>7.47</v>
       </c>
@@ -2053,10 +2332,10 @@
       <c r="M14">
         <v>0</v>
       </c>
-      <c r="N14" s="34">
+      <c r="N14" s="27">
         <v>80.66</v>
       </c>
-      <c r="O14" s="34"/>
+      <c r="O14" s="27"/>
       <c r="P14">
         <v>17.05</v>
       </c>
@@ -2066,10 +2345,10 @@
       <c r="R14" s="1">
         <v>1.22</v>
       </c>
-      <c r="S14" s="34">
+      <c r="S14" s="27">
         <v>34.19</v>
       </c>
-      <c r="T14" s="34"/>
+      <c r="T14" s="27"/>
       <c r="U14">
         <v>4.76</v>
       </c>
@@ -2079,10 +2358,10 @@
       <c r="W14" s="1">
         <v>0.27</v>
       </c>
-      <c r="X14" s="34">
+      <c r="X14" s="27">
         <v>74.290000000000006</v>
       </c>
-      <c r="AA14" s="32"/>
+      <c r="AA14" s="29"/>
       <c r="AB14" s="9" t="s">
         <v>23</v>
       </c>
@@ -2122,13 +2401,23 @@
       <c r="AN14" s="7">
         <v>35.22</v>
       </c>
-    </row>
-    <row r="15" spans="1:40" ht="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="34"/>
+      <c r="AW14" s="43"/>
+      <c r="AX14" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="AY14" s="51">
+        <v>4536.21</v>
+      </c>
+      <c r="AZ14" s="52">
+        <v>52.032899999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+      <c r="A15" s="27"/>
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="34"/>
+      <c r="C15" s="27"/>
       <c r="D15">
         <v>9.15</v>
       </c>
@@ -2144,8 +2433,8 @@
       <c r="H15">
         <v>159.09700000000001</v>
       </c>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
       <c r="K15">
         <v>5.88</v>
       </c>
@@ -2155,8 +2444,8 @@
       <c r="M15">
         <v>0</v>
       </c>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="27"/>
       <c r="P15">
         <v>16.07</v>
       </c>
@@ -2166,8 +2455,8 @@
       <c r="R15" s="1">
         <v>1.42</v>
       </c>
-      <c r="S15" s="34"/>
-      <c r="T15" s="34"/>
+      <c r="S15" s="27"/>
+      <c r="T15" s="27"/>
       <c r="U15" s="1">
         <v>5.26</v>
       </c>
@@ -2177,8 +2466,8 @@
       <c r="W15" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="X15" s="34"/>
-      <c r="AA15" s="33"/>
+      <c r="X15" s="27"/>
+      <c r="AA15" s="30"/>
       <c r="AB15" s="5" t="s">
         <v>22</v>
       </c>
@@ -2218,13 +2507,25 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:40" ht="15" x14ac:dyDescent="0.25">
-      <c r="A16" s="34"/>
+      <c r="AW15" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="AX15" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="AY15" s="50">
+        <v>514.66999999999996</v>
+      </c>
+      <c r="AZ15" s="49">
+        <v>15.446099999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+      <c r="A16" s="27"/>
       <c r="B16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="34"/>
+      <c r="C16" s="27"/>
       <c r="D16">
         <v>7.89</v>
       </c>
@@ -2240,8 +2541,8 @@
       <c r="H16">
         <v>168.54599999999999</v>
       </c>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
       <c r="K16">
         <v>5.14</v>
       </c>
@@ -2251,8 +2552,8 @@
       <c r="M16">
         <v>0</v>
       </c>
-      <c r="N16" s="34"/>
-      <c r="O16" s="34"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="27"/>
       <c r="P16">
         <v>14.1</v>
       </c>
@@ -2262,8 +2563,8 @@
       <c r="R16" s="1">
         <v>0.81</v>
       </c>
-      <c r="S16" s="34"/>
-      <c r="T16" s="34"/>
+      <c r="S16" s="27"/>
+      <c r="T16" s="27"/>
       <c r="U16">
         <v>4.01</v>
       </c>
@@ -2273,8 +2574,8 @@
       <c r="W16" s="1">
         <v>0</v>
       </c>
-      <c r="X16" s="34"/>
-      <c r="AA16" s="31" t="s">
+      <c r="X16" s="27"/>
+      <c r="AA16" s="28" t="s">
         <v>20</v>
       </c>
       <c r="AB16" s="9" t="s">
@@ -2316,15 +2617,25 @@
       <c r="AN16" s="11">
         <v>5.42</v>
       </c>
-    </row>
-    <row r="17" spans="1:40" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="34" t="s">
+      <c r="AW16" s="40"/>
+      <c r="AX16" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY16" s="50">
+        <v>2260.0300000000002</v>
+      </c>
+      <c r="AZ16" s="49">
+        <v>27.349599999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="27" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="27">
         <v>29.96</v>
       </c>
       <c r="D17">
@@ -2342,7 +2653,7 @@
       <c r="H17">
         <v>3.6791999999999998</v>
       </c>
-      <c r="J17" s="34">
+      <c r="J17" s="27">
         <v>28.64</v>
       </c>
       <c r="K17">
@@ -2354,7 +2665,7 @@
       <c r="M17">
         <v>1.2</v>
       </c>
-      <c r="O17" s="34">
+      <c r="O17" s="27">
         <v>40.82</v>
       </c>
       <c r="P17">
@@ -2366,7 +2677,7 @@
       <c r="R17" s="1">
         <v>1.66</v>
       </c>
-      <c r="T17" s="34">
+      <c r="T17" s="27">
         <v>16.04</v>
       </c>
       <c r="U17">
@@ -2378,7 +2689,7 @@
       <c r="W17" s="1">
         <v>0.3</v>
       </c>
-      <c r="AA17" s="32"/>
+      <c r="AA17" s="29"/>
       <c r="AB17" s="9" t="s">
         <v>24</v>
       </c>
@@ -2418,13 +2729,23 @@
       <c r="AN17" s="7">
         <v>18.75</v>
       </c>
-    </row>
-    <row r="18" spans="1:40" ht="15" x14ac:dyDescent="0.25">
-      <c r="A18" s="34"/>
+      <c r="AW17" s="40"/>
+      <c r="AX17" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="AY17" s="50">
+        <v>3219.47</v>
+      </c>
+      <c r="AZ17" s="49">
+        <v>35.505099999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+      <c r="A18" s="27"/>
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="34"/>
+      <c r="C18" s="27"/>
       <c r="D18">
         <v>36.31</v>
       </c>
@@ -2440,7 +2761,7 @@
       <c r="H18">
         <v>26.883299999999998</v>
       </c>
-      <c r="J18" s="34"/>
+      <c r="J18" s="27"/>
       <c r="K18">
         <v>31.46</v>
       </c>
@@ -2450,7 +2771,7 @@
       <c r="M18">
         <v>23.16</v>
       </c>
-      <c r="O18" s="34"/>
+      <c r="O18" s="27"/>
       <c r="P18">
         <v>48.2</v>
       </c>
@@ -2460,7 +2781,7 @@
       <c r="R18" s="1">
         <v>22.16</v>
       </c>
-      <c r="T18" s="34"/>
+      <c r="T18" s="27"/>
       <c r="U18">
         <v>28.07</v>
       </c>
@@ -2470,7 +2791,7 @@
       <c r="W18" s="1">
         <v>21.19</v>
       </c>
-      <c r="AA18" s="32"/>
+      <c r="AA18" s="29"/>
       <c r="AB18" s="9" t="s">
         <v>23</v>
       </c>
@@ -2510,13 +2831,23 @@
       <c r="AN18" s="7">
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:40" ht="15" x14ac:dyDescent="0.25">
-      <c r="A19" s="34"/>
+      <c r="AW18" s="40"/>
+      <c r="AX18" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="AY18" s="50">
+        <v>4521.08</v>
+      </c>
+      <c r="AZ18" s="49">
+        <v>21.763400000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+      <c r="A19" s="27"/>
       <c r="B19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="34"/>
+      <c r="C19" s="27"/>
       <c r="D19">
         <v>55.31</v>
       </c>
@@ -2532,7 +2863,7 @@
       <c r="H19">
         <v>24.215399999999999</v>
       </c>
-      <c r="J19" s="34"/>
+      <c r="J19" s="27"/>
       <c r="K19">
         <v>53.12</v>
       </c>
@@ -2542,7 +2873,7 @@
       <c r="M19">
         <v>40.82</v>
       </c>
-      <c r="O19" s="34"/>
+      <c r="O19" s="27"/>
       <c r="P19">
         <v>66.89</v>
       </c>
@@ -2552,7 +2883,7 @@
       <c r="R19" s="1">
         <v>50.69</v>
       </c>
-      <c r="T19" s="34"/>
+      <c r="T19" s="27"/>
       <c r="U19">
         <v>42.11</v>
       </c>
@@ -2562,7 +2893,7 @@
       <c r="W19">
         <v>35.22</v>
       </c>
-      <c r="AA19" s="33"/>
+      <c r="AA19" s="30"/>
       <c r="AB19" s="5" t="s">
         <v>22</v>
       </c>
@@ -2603,12 +2934,12 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="20" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A20" s="34"/>
+    <row r="20" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A20" s="27"/>
       <c r="B20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="34"/>
+      <c r="C20" s="27"/>
       <c r="D20">
         <v>20.87</v>
       </c>
@@ -2624,7 +2955,7 @@
       <c r="H20">
         <v>2.9369000000000001</v>
       </c>
-      <c r="J20" s="34"/>
+      <c r="J20" s="27"/>
       <c r="K20">
         <v>14.93</v>
       </c>
@@ -2634,7 +2965,7 @@
       <c r="M20">
         <v>1.54</v>
       </c>
-      <c r="O20" s="34"/>
+      <c r="O20" s="27"/>
       <c r="P20">
         <v>36.72</v>
       </c>
@@ -2644,7 +2975,7 @@
       <c r="R20">
         <v>5.26</v>
       </c>
-      <c r="T20" s="34"/>
+      <c r="T20" s="27"/>
       <c r="U20">
         <v>8.77</v>
       </c>
@@ -2655,12 +2986,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A21" s="34"/>
+    <row r="21" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A21" s="27"/>
       <c r="B21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="34"/>
+      <c r="C21" s="27"/>
       <c r="D21">
         <v>18.89</v>
       </c>
@@ -2676,10 +3007,10 @@
       <c r="H21">
         <v>22.941400000000002</v>
       </c>
-      <c r="I21" s="34">
+      <c r="I21" s="27">
         <v>48.81</v>
       </c>
-      <c r="J21" s="34"/>
+      <c r="J21" s="27"/>
       <c r="K21">
         <v>12.48</v>
       </c>
@@ -2689,10 +3020,10 @@
       <c r="M21">
         <v>1.03</v>
       </c>
-      <c r="N21" s="34">
+      <c r="N21" s="27">
         <v>67.09</v>
       </c>
-      <c r="O21" s="34"/>
+      <c r="O21" s="27"/>
       <c r="P21">
         <v>34.590000000000003</v>
       </c>
@@ -2702,10 +3033,10 @@
       <c r="R21">
         <v>2.2200000000000002</v>
       </c>
-      <c r="S21" s="34">
+      <c r="S21" s="27">
         <v>30.12</v>
       </c>
-      <c r="T21" s="34"/>
+      <c r="T21" s="27"/>
       <c r="U21">
         <v>8.02</v>
       </c>
@@ -2715,16 +3046,16 @@
       <c r="W21">
         <v>0</v>
       </c>
-      <c r="X21" s="34">
+      <c r="X21" s="27">
         <v>54.69</v>
       </c>
     </row>
-    <row r="22" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A22" s="34"/>
+    <row r="22" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A22" s="27"/>
       <c r="B22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="34"/>
+      <c r="C22" s="27"/>
       <c r="D22">
         <v>17.8</v>
       </c>
@@ -2740,8 +3071,8 @@
       <c r="H22">
         <v>23.260400000000001</v>
       </c>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="27"/>
       <c r="K22">
         <v>10.89</v>
       </c>
@@ -2751,8 +3082,8 @@
       <c r="M22">
         <v>1.2</v>
       </c>
-      <c r="N22" s="34"/>
-      <c r="O22" s="34"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="27"/>
       <c r="P22">
         <v>33.61</v>
       </c>
@@ -2762,8 +3093,8 @@
       <c r="R22">
         <v>2.2200000000000002</v>
       </c>
-      <c r="S22" s="34"/>
-      <c r="T22" s="34"/>
+      <c r="S22" s="27"/>
+      <c r="T22" s="27"/>
       <c r="U22">
         <v>7.77</v>
       </c>
@@ -2773,14 +3104,14 @@
       <c r="W22">
         <v>0</v>
       </c>
-      <c r="X22" s="34"/>
-    </row>
-    <row r="23" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A23" s="34"/>
+      <c r="X22" s="27"/>
+    </row>
+    <row r="23" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A23" s="27"/>
       <c r="B23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="34"/>
+      <c r="C23" s="27"/>
       <c r="D23">
         <v>16.43</v>
       </c>
@@ -2796,8 +3127,8 @@
       <c r="H23">
         <v>52.032899999999998</v>
       </c>
-      <c r="I23" s="34"/>
-      <c r="J23" s="34"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
       <c r="K23">
         <v>10.039999999999999</v>
       </c>
@@ -2807,8 +3138,8 @@
       <c r="M23">
         <v>0.69</v>
       </c>
-      <c r="N23" s="34"/>
-      <c r="O23" s="34"/>
+      <c r="N23" s="27"/>
+      <c r="O23" s="27"/>
       <c r="P23">
         <v>30.82</v>
       </c>
@@ -2818,8 +3149,8 @@
       <c r="R23">
         <v>1.1100000000000001</v>
       </c>
-      <c r="S23" s="34"/>
-      <c r="T23" s="34"/>
+      <c r="S23" s="27"/>
+      <c r="T23" s="27"/>
       <c r="U23">
         <v>7.52</v>
       </c>
@@ -2829,16 +3160,16 @@
       <c r="W23">
         <v>0</v>
       </c>
-      <c r="X23" s="34"/>
-    </row>
-    <row r="24" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A24" s="34" t="s">
+      <c r="X23" s="27"/>
+    </row>
+    <row r="24" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A24" s="27" t="s">
         <v>20</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="27">
         <v>44.74</v>
       </c>
       <c r="D24">
@@ -2856,7 +3187,7 @@
       <c r="H24">
         <v>15.446099999999999</v>
       </c>
-      <c r="J24" s="34">
+      <c r="J24" s="27">
         <v>38.07</v>
       </c>
       <c r="K24">
@@ -2868,7 +3199,7 @@
       <c r="M24">
         <v>5.14</v>
       </c>
-      <c r="O24" s="34">
+      <c r="O24" s="27">
         <v>56.89</v>
       </c>
       <c r="P24">
@@ -2880,7 +3211,7 @@
       <c r="R24">
         <v>6.84</v>
       </c>
-      <c r="T24" s="34">
+      <c r="T24" s="27">
         <v>39.85</v>
       </c>
       <c r="U24">
@@ -2893,12 +3224,12 @@
         <v>5.42</v>
       </c>
     </row>
-    <row r="25" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A25" s="34"/>
+    <row r="25" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A25" s="27"/>
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="34"/>
+      <c r="C25" s="27"/>
       <c r="D25">
         <v>40.53</v>
       </c>
@@ -2914,7 +3245,7 @@
       <c r="H25">
         <v>27.349599999999999</v>
       </c>
-      <c r="J25" s="34"/>
+      <c r="J25" s="27"/>
       <c r="K25">
         <v>26.44</v>
       </c>
@@ -2924,7 +3255,7 @@
       <c r="M25">
         <v>14.03</v>
       </c>
-      <c r="O25" s="34"/>
+      <c r="O25" s="27"/>
       <c r="P25">
         <v>61.97</v>
       </c>
@@ -2934,7 +3265,7 @@
       <c r="R25">
         <v>26.62</v>
       </c>
-      <c r="T25" s="34"/>
+      <c r="T25" s="27"/>
       <c r="U25">
         <v>36.590000000000003</v>
       </c>
@@ -2945,12 +3276,12 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="26" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A26" s="34"/>
+    <row r="26" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A26" s="27"/>
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="34"/>
+      <c r="C26" s="27"/>
       <c r="D26">
         <v>45.02</v>
       </c>
@@ -2966,7 +3297,7 @@
       <c r="H26">
         <v>35.505099999999999</v>
       </c>
-      <c r="J26" s="34"/>
+      <c r="J26" s="27"/>
       <c r="K26">
         <v>34.39</v>
       </c>
@@ -2976,7 +3307,7 @@
       <c r="M26">
         <v>19.96</v>
       </c>
-      <c r="O26" s="34"/>
+      <c r="O26" s="27"/>
       <c r="P26">
         <v>63.28</v>
       </c>
@@ -2986,7 +3317,7 @@
       <c r="R26">
         <v>30.04</v>
       </c>
-      <c r="T26" s="34"/>
+      <c r="T26" s="27"/>
       <c r="U26">
         <v>38.85</v>
       </c>
@@ -2997,12 +3328,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A27" s="34"/>
+    <row r="27" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A27" s="27"/>
       <c r="B27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C27" s="34"/>
+      <c r="C27" s="27"/>
       <c r="D27">
         <v>31.16</v>
       </c>
@@ -3018,7 +3349,7 @@
       <c r="H27">
         <v>1.3381000000000001</v>
       </c>
-      <c r="J27" s="34"/>
+      <c r="J27" s="27"/>
       <c r="K27">
         <v>12.97</v>
       </c>
@@ -3028,7 +3359,7 @@
       <c r="M27">
         <v>2.96</v>
       </c>
-      <c r="O27" s="34"/>
+      <c r="O27" s="27"/>
       <c r="P27">
         <v>53.28</v>
       </c>
@@ -3038,7 +3369,7 @@
       <c r="R27">
         <v>14.07</v>
       </c>
-      <c r="T27" s="34"/>
+      <c r="T27" s="27"/>
       <c r="U27">
         <v>34.590000000000003</v>
       </c>
@@ -3049,12 +3380,12 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="28" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A28" s="34"/>
+    <row r="28" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A28" s="27"/>
       <c r="B28" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="34"/>
+      <c r="C28" s="27"/>
       <c r="D28">
         <v>28.31</v>
       </c>
@@ -3070,10 +3401,10 @@
       <c r="H28">
         <v>13.305</v>
       </c>
-      <c r="I28" s="34">
+      <c r="I28" s="27">
         <v>48.1</v>
       </c>
-      <c r="J28" s="34"/>
+      <c r="J28" s="27"/>
       <c r="K28">
         <v>11.75</v>
       </c>
@@ -3083,10 +3414,10 @@
       <c r="M28">
         <v>1.58</v>
       </c>
-      <c r="N28" s="34">
+      <c r="N28" s="27">
         <v>76.209999999999994</v>
       </c>
-      <c r="O28" s="34"/>
+      <c r="O28" s="27"/>
       <c r="P28">
         <v>50.16</v>
       </c>
@@ -3096,10 +3427,10 @@
       <c r="R28">
         <v>6.08</v>
       </c>
-      <c r="S28" s="34">
+      <c r="S28" s="27">
         <v>23.05</v>
       </c>
-      <c r="T28" s="34"/>
+      <c r="T28" s="27"/>
       <c r="U28">
         <v>28.82</v>
       </c>
@@ -3109,16 +3440,16 @@
       <c r="W28">
         <v>5</v>
       </c>
-      <c r="X28" s="34">
+      <c r="X28" s="27">
         <v>47.8</v>
       </c>
     </row>
-    <row r="29" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A29" s="34"/>
+    <row r="29" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A29" s="27"/>
       <c r="B29" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="34"/>
+      <c r="C29" s="27"/>
       <c r="D29">
         <v>27.66</v>
       </c>
@@ -3134,8 +3465,8 @@
       <c r="H29">
         <v>15.7463</v>
       </c>
-      <c r="I29" s="34"/>
-      <c r="J29" s="34"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="27"/>
       <c r="K29">
         <v>11.75</v>
       </c>
@@ -3145,8 +3476,8 @@
       <c r="M29">
         <v>1.78</v>
       </c>
-      <c r="N29" s="34"/>
-      <c r="O29" s="34"/>
+      <c r="N29" s="27"/>
+      <c r="O29" s="27"/>
       <c r="P29">
         <v>49.18</v>
       </c>
@@ -3156,8 +3487,8 @@
       <c r="R29">
         <v>5.7</v>
       </c>
-      <c r="S29" s="34"/>
-      <c r="T29" s="34"/>
+      <c r="S29" s="27"/>
+      <c r="T29" s="27"/>
       <c r="U29">
         <v>27.32</v>
       </c>
@@ -3167,14 +3498,14 @@
       <c r="W29">
         <v>5.42</v>
       </c>
-      <c r="X29" s="34"/>
-    </row>
-    <row r="30" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A30" s="34"/>
+      <c r="X29" s="27"/>
+    </row>
+    <row r="30" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A30" s="27"/>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="34"/>
+      <c r="C30" s="27"/>
       <c r="D30">
         <v>25.96</v>
       </c>
@@ -3190,8 +3521,8 @@
       <c r="H30">
         <v>21.763400000000001</v>
       </c>
-      <c r="I30" s="34"/>
-      <c r="J30" s="34"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="27"/>
       <c r="K30">
         <v>10.28</v>
       </c>
@@ -3201,8 +3532,8 @@
       <c r="M30">
         <v>1.19</v>
       </c>
-      <c r="N30" s="34"/>
-      <c r="O30" s="34"/>
+      <c r="N30" s="27"/>
+      <c r="O30" s="27"/>
       <c r="P30">
         <v>47.54</v>
       </c>
@@ -3212,8 +3543,8 @@
       <c r="R30">
         <v>4.18</v>
       </c>
-      <c r="S30" s="34"/>
-      <c r="T30" s="34"/>
+      <c r="S30" s="27"/>
+      <c r="T30" s="27"/>
       <c r="U30">
         <v>25.06</v>
       </c>
@@ -3223,9 +3554,9 @@
       <c r="W30">
         <v>3.75</v>
       </c>
-      <c r="X30" s="34"/>
-    </row>
-    <row r="34" spans="2:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="X30" s="27"/>
+    </row>
+    <row r="34" spans="2:5" ht="15" x14ac:dyDescent="0.2">
       <c r="B34" s="2"/>
       <c r="C34" s="16" t="s">
         <v>40</v>
@@ -3237,7 +3568,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
         <v>37</v>
       </c>
@@ -3251,7 +3582,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
         <v>38</v>
       </c>
@@ -3265,7 +3596,7 @@
         <v>4.95</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
         <v>39</v>
       </c>
@@ -3279,7 +3610,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="41" spans="2:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:5" ht="15" x14ac:dyDescent="0.2">
       <c r="B41" s="26"/>
       <c r="C41" s="16" t="s">
         <v>40</v>
@@ -3290,18 +3621,8 @@
       <c r="E41" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G41" s="26"/>
-      <c r="H41" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B42" s="26">
         <v>0</v>
       </c>
@@ -3314,20 +3635,8 @@
       <c r="E42" s="26">
         <v>4.95</v>
       </c>
-      <c r="G42" s="26">
-        <v>0.1</v>
-      </c>
-      <c r="H42" s="2">
-        <v>17.22</v>
-      </c>
-      <c r="I42" s="2">
-        <v>64.56</v>
-      </c>
-      <c r="J42" s="2">
-        <v>2.97</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B43" s="26">
         <v>1</v>
       </c>
@@ -3340,20 +3649,8 @@
       <c r="E43" s="26">
         <v>3.96</v>
       </c>
-      <c r="G43" s="26">
-        <v>0.3</v>
-      </c>
-      <c r="H43" s="26">
-        <v>17.78</v>
-      </c>
-      <c r="I43" s="26">
-        <v>64.56</v>
-      </c>
-      <c r="J43" s="26">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B44" s="26">
         <v>3</v>
       </c>
@@ -3366,20 +3663,8 @@
       <c r="E44" s="26">
         <v>4.95</v>
       </c>
-      <c r="G44" s="26">
-        <v>0.6</v>
-      </c>
-      <c r="H44" s="26">
-        <v>19.440000000000001</v>
-      </c>
-      <c r="I44" s="26">
-        <v>65.819999999999993</v>
-      </c>
-      <c r="J44" s="26">
-        <v>8.91</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B45" s="26">
         <v>5</v>
       </c>
@@ -3392,20 +3677,8 @@
       <c r="E45" s="2">
         <v>2.97</v>
       </c>
-      <c r="G45" s="26">
-        <v>0.9</v>
-      </c>
-      <c r="H45" s="2">
-        <v>18.89</v>
-      </c>
-      <c r="I45" s="2">
-        <v>65.819999999999993</v>
-      </c>
-      <c r="J45" s="2">
-        <v>7.92</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B46" s="26">
         <v>7</v>
       </c>
@@ -3419,7 +3692,7 @@
         <v>6.93</v>
       </c>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B47" s="26">
         <v>9</v>
       </c>
@@ -3730,28 +4003,23 @@
       <c r="M87" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="A24:A30"/>
-    <mergeCell ref="C24:C30"/>
-    <mergeCell ref="O24:O30"/>
-    <mergeCell ref="T17:T23"/>
-    <mergeCell ref="X21:X23"/>
-    <mergeCell ref="T24:T30"/>
-    <mergeCell ref="N28:N30"/>
-    <mergeCell ref="S28:S30"/>
-    <mergeCell ref="X28:X30"/>
-    <mergeCell ref="J24:J30"/>
-    <mergeCell ref="X14:X16"/>
-    <mergeCell ref="J1:N1"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="S7:S9"/>
-    <mergeCell ref="S21:S23"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="T1:X1"/>
-    <mergeCell ref="T3:T9"/>
-    <mergeCell ref="T10:T16"/>
-    <mergeCell ref="S14:S16"/>
+  <mergeCells count="53">
+    <mergeCell ref="AW3:AW6"/>
+    <mergeCell ref="AW7:AW10"/>
+    <mergeCell ref="AW11:AW14"/>
+    <mergeCell ref="AW15:AW18"/>
+    <mergeCell ref="AC3:AE3"/>
+    <mergeCell ref="AF3:AH3"/>
+    <mergeCell ref="AI3:AK3"/>
+    <mergeCell ref="AL3:AN3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AA16:AA19"/>
+    <mergeCell ref="AA12:AA15"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="AA8:AA11"/>
+    <mergeCell ref="AA4:AA7"/>
     <mergeCell ref="A3:A9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J3:J9"/>
@@ -3767,19 +4035,28 @@
     <mergeCell ref="J10:J16"/>
     <mergeCell ref="O3:O9"/>
     <mergeCell ref="N14:N16"/>
-    <mergeCell ref="AA16:AA19"/>
-    <mergeCell ref="AA12:AA15"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="C3:C9"/>
-    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="X14:X16"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="S7:S9"/>
+    <mergeCell ref="S21:S23"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="T1:X1"/>
+    <mergeCell ref="T3:T9"/>
+    <mergeCell ref="T10:T16"/>
+    <mergeCell ref="S14:S16"/>
+    <mergeCell ref="A24:A30"/>
+    <mergeCell ref="C24:C30"/>
+    <mergeCell ref="O24:O30"/>
+    <mergeCell ref="T17:T23"/>
+    <mergeCell ref="X21:X23"/>
+    <mergeCell ref="T24:T30"/>
+    <mergeCell ref="N28:N30"/>
+    <mergeCell ref="S28:S30"/>
+    <mergeCell ref="X28:X30"/>
+    <mergeCell ref="J24:J30"/>
     <mergeCell ref="I28:I30"/>
-    <mergeCell ref="AC3:AE3"/>
-    <mergeCell ref="AF3:AH3"/>
-    <mergeCell ref="AI3:AK3"/>
-    <mergeCell ref="AL3:AN3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AA8:AA11"/>
-    <mergeCell ref="AA4:AA7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/stat/data.xlsx
+++ b/stat/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr\Documents\Workspace\LLMHalluMiti\stat\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr-PC\Documents\Workspace\LLMHalluMiti\stat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA84B2A-59D7-488D-9B34-ECAEB15A0B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038B63BD-6E1D-422B-8B5B-F223F4ACE76E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="59">
   <si>
     <t>gpt-4o</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -152,18 +152,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>oc.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>hal. repair</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>rc. hal.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Method</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -229,6 +217,45 @@
   </si>
   <si>
     <t>CoVe-SE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RHR</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>HRR</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>OCR</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>HR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RHR p-value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HRR p-value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OCR p-value</t>
+  </si>
+  <si>
+    <t>&lt; 0.001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;0.001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt; 0.05</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -283,7 +310,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -413,11 +440,98 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
       <bottom style="double">
         <color indexed="64"/>
       </bottom>
@@ -426,8 +540,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -436,13 +552,11 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -451,7 +565,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -465,9 +579,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -477,9 +588,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -492,12 +600,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -525,88 +627,92 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -889,60 +995,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ87"/>
+  <dimension ref="A1:BG87"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="27" max="28" width="7.625" customWidth="1"/>
-    <col min="29" max="29" width="6.625" customWidth="1"/>
-    <col min="30" max="30" width="8.875" customWidth="1"/>
-    <col min="31" max="32" width="6.625" customWidth="1"/>
-    <col min="33" max="33" width="8.875" customWidth="1"/>
-    <col min="34" max="35" width="6.625" customWidth="1"/>
-    <col min="36" max="36" width="8.875" customWidth="1"/>
-    <col min="37" max="38" width="6.625" customWidth="1"/>
+    <col min="29" max="30" width="6.625" customWidth="1"/>
+    <col min="31" max="31" width="8.875" customWidth="1"/>
+    <col min="32" max="34" width="6.625" customWidth="1"/>
+    <col min="35" max="35" width="8.875" customWidth="1"/>
+    <col min="36" max="38" width="6.625" customWidth="1"/>
     <col min="39" max="39" width="8.875" customWidth="1"/>
     <col min="40" max="40" width="6.625" customWidth="1"/>
     <col min="43" max="43" width="10.625" customWidth="1"/>
     <col min="44" max="45" width="25.625" customWidth="1"/>
     <col min="46" max="46" width="20.625" customWidth="1"/>
     <col min="49" max="52" width="8.875" customWidth="1"/>
+    <col min="57" max="59" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27" t="s">
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27" t="s">
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27" t="s">
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="27"/>
-    </row>
-    <row r="2" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U1" s="44"/>
+      <c r="V1" s="44"/>
+      <c r="W1" s="44"/>
+      <c r="X1" s="44"/>
+      <c r="AS1" s="31"/>
+      <c r="AT1" s="31"/>
+      <c r="AW1" s="31"/>
+      <c r="AX1" s="31"/>
+      <c r="AY1" s="31"/>
+      <c r="AZ1" s="31"/>
+    </row>
+    <row r="2" spans="1:59" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
@@ -1011,81 +1122,96 @@
       <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="AA2" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB2" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC2" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AD2" s="23" t="s">
+      <c r="AA2" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="AE2" s="24" t="s">
+      <c r="AB2" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="AF2" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG2" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="AH2" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI2" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ2" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="AK2" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="AL2" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AM2" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="AN2" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="AQ2" s="14" t="s">
+      <c r="AC2" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD2" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE2" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF2" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG2" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH2" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI2" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ2" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="AK2" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="AL2" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM2" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN2" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="AQ2" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR2" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="AS2" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AT2" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="AW2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AX2" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="AY2" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="AR2" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS2" s="37" t="s">
+      <c r="AZ2" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="AT2" s="20" t="s">
+      <c r="BC2" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="AW2" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="AX2" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="AY2" s="41" t="s">
+      <c r="BD2" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="AZ2" s="15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:52" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="27" t="s">
+      <c r="BE2" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="BF2" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="BG2" s="49" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:59" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="44" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="44">
         <v>39.81</v>
       </c>
       <c r="D3" s="1">
@@ -1104,7 +1230,7 @@
         <v>4.9604999999999997</v>
       </c>
       <c r="I3" s="1"/>
-      <c r="J3" s="27">
+      <c r="J3" s="44">
         <v>45.78</v>
       </c>
       <c r="K3" s="1">
@@ -1117,7 +1243,7 @@
         <v>9.0299999999999994</v>
       </c>
       <c r="N3" s="1"/>
-      <c r="O3" s="27">
+      <c r="O3" s="44">
         <v>38.03</v>
       </c>
       <c r="P3" s="1">
@@ -1130,7 +1256,7 @@
         <v>1.32</v>
       </c>
       <c r="S3" s="1"/>
-      <c r="T3" s="27">
+      <c r="T3" s="44">
         <v>30.33</v>
       </c>
       <c r="U3" s="1">
@@ -1143,59 +1269,72 @@
         <v>2.52</v>
       </c>
       <c r="X3" s="1"/>
-      <c r="AA3" s="35"/>
-      <c r="AB3" s="36"/>
-      <c r="AC3" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD3" s="31"/>
-      <c r="AE3" s="32"/>
-      <c r="AF3" s="31" t="s">
+      <c r="AA3" s="38"/>
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="AG3" s="31"/>
-      <c r="AH3" s="32"/>
-      <c r="AI3" s="33" t="s">
+      <c r="AD3" s="38"/>
+      <c r="AE3" s="38"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="AJ3" s="33"/>
-      <c r="AK3" s="34"/>
-      <c r="AL3" s="33" t="s">
+      <c r="AH3" s="38"/>
+      <c r="AI3" s="38"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="AM3" s="33"/>
-      <c r="AN3" s="33"/>
+      <c r="AL3" s="38"/>
+      <c r="AM3" s="38"/>
+      <c r="AN3" s="38"/>
       <c r="AQ3" s="8">
         <v>0.1</v>
       </c>
-      <c r="AR3" s="38">
+      <c r="AR3" s="24">
         <v>17.22</v>
       </c>
-      <c r="AS3" s="38">
+      <c r="AS3" s="24">
         <v>64.56</v>
       </c>
-      <c r="AT3" s="16">
+      <c r="AT3" s="12">
         <v>2.97</v>
       </c>
-      <c r="AW3" s="44" t="s">
+      <c r="AW3" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="AX3" s="42" t="s">
+      <c r="AX3" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="AY3" s="45">
+      <c r="AY3" s="25">
         <v>100.61</v>
       </c>
-      <c r="AZ3" s="46">
+      <c r="AZ3" s="26">
         <v>4.9604999999999997</v>
       </c>
-    </row>
-    <row r="4" spans="1:52" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="27"/>
+      <c r="BC3" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD3" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="BE3" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF3" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="BG3" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:59" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="44"/>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="27"/>
+      <c r="C4" s="44"/>
       <c r="D4" s="1">
         <v>25.03</v>
       </c>
@@ -1212,7 +1351,7 @@
         <v>22.125900000000001</v>
       </c>
       <c r="I4" s="1"/>
-      <c r="J4" s="27"/>
+      <c r="J4" s="44"/>
       <c r="K4" s="1">
         <v>23.38</v>
       </c>
@@ -1223,7 +1362,7 @@
         <v>15.35</v>
       </c>
       <c r="N4" s="1"/>
-      <c r="O4" s="27"/>
+      <c r="O4" s="44"/>
       <c r="P4" s="1">
         <v>35.9</v>
       </c>
@@ -1234,7 +1373,7 @@
         <v>12.17</v>
       </c>
       <c r="S4" s="1"/>
-      <c r="T4" s="27"/>
+      <c r="T4" s="44"/>
       <c r="U4" s="1">
         <v>11.78</v>
       </c>
@@ -1245,77 +1384,90 @@
         <v>6.12</v>
       </c>
       <c r="X4" s="1"/>
-      <c r="AA4" s="29" t="s">
+      <c r="AA4" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="AB4" s="9" t="s">
+      <c r="AB4" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="AC4" s="16">
-        <v>22.95</v>
-      </c>
-      <c r="AD4" s="16">
-        <v>49.45</v>
-      </c>
-      <c r="AE4" s="10">
-        <v>4.7300000000000004</v>
-      </c>
-      <c r="AF4" s="16">
+      <c r="AC4" s="43">
+        <v>45.78</v>
+      </c>
+      <c r="AD4" s="12">
         <v>24.6</v>
       </c>
-      <c r="AG4" s="16">
+      <c r="AE4" s="12">
         <v>56.95</v>
       </c>
-      <c r="AH4" s="10">
+      <c r="AF4" s="8">
         <v>9.0299999999999994</v>
       </c>
-      <c r="AI4" s="16">
+      <c r="AG4" s="34">
+        <v>38.03</v>
+      </c>
+      <c r="AH4" s="12">
         <v>28.52</v>
       </c>
-      <c r="AJ4" s="16">
+      <c r="AI4" s="12">
         <v>27.16</v>
       </c>
-      <c r="AK4" s="22">
+      <c r="AJ4" s="18">
         <v>1.32</v>
       </c>
-      <c r="AL4" s="16">
+      <c r="AK4" s="34">
+        <v>30.33</v>
+      </c>
+      <c r="AL4" s="12">
         <v>11.28</v>
       </c>
-      <c r="AM4" s="16">
+      <c r="AM4" s="12">
         <v>68.599999999999994</v>
       </c>
-      <c r="AN4" s="21">
+      <c r="AN4" s="17">
         <v>2.52</v>
       </c>
       <c r="AQ4" s="8">
         <v>0.3</v>
       </c>
-      <c r="AR4" s="39">
+      <c r="AR4" s="24">
         <v>17.78</v>
       </c>
-      <c r="AS4" s="39">
+      <c r="AS4" s="24">
         <v>64.56</v>
       </c>
-      <c r="AT4" s="7">
+      <c r="AT4" s="12">
         <v>4.95</v>
       </c>
-      <c r="AW4" s="40"/>
-      <c r="AX4" s="39" t="s">
+      <c r="AW4" s="41"/>
+      <c r="AX4" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="AY4" s="45">
+      <c r="AY4" s="25">
         <v>2253.6799999999998</v>
       </c>
-      <c r="AZ4" s="46">
+      <c r="AZ4" s="26">
         <v>22.125900000000001</v>
       </c>
-    </row>
-    <row r="5" spans="1:52" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="27"/>
+      <c r="BC4" s="41"/>
+      <c r="BD4" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE4" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF4" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="BG4" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:59" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="44"/>
       <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="27"/>
+      <c r="C5" s="44"/>
       <c r="D5" s="1">
         <v>25.58</v>
       </c>
@@ -1332,7 +1484,7 @@
         <v>33.609499999999997</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="27"/>
+      <c r="J5" s="44"/>
       <c r="K5" s="1">
         <v>22.4</v>
       </c>
@@ -1343,7 +1495,7 @@
         <v>9.48</v>
       </c>
       <c r="N5" s="1"/>
-      <c r="O5" s="27"/>
+      <c r="O5" s="44"/>
       <c r="P5" s="1">
         <v>38.03</v>
       </c>
@@ -1354,7 +1506,7 @@
         <v>19.309999999999999</v>
       </c>
       <c r="S5" s="1"/>
-      <c r="T5" s="27"/>
+      <c r="T5" s="44"/>
       <c r="U5" s="1">
         <v>13.03</v>
       </c>
@@ -1365,75 +1517,82 @@
         <v>5.76</v>
       </c>
       <c r="X5" s="1"/>
-      <c r="AA5" s="29"/>
-      <c r="AB5" s="9" t="s">
+      <c r="AA5" s="41"/>
+      <c r="AB5" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="AC5" s="16">
-        <v>25.03</v>
-      </c>
-      <c r="AD5" s="16">
-        <v>55.23</v>
-      </c>
-      <c r="AE5" s="10">
-        <v>12</v>
-      </c>
-      <c r="AF5" s="16">
+      <c r="AC5" s="34"/>
+      <c r="AD5" s="12">
         <v>23.38</v>
       </c>
-      <c r="AG5" s="16">
+      <c r="AE5" s="12">
         <v>67.11</v>
       </c>
-      <c r="AH5" s="10">
+      <c r="AF5" s="8">
         <v>15.35</v>
       </c>
-      <c r="AI5" s="16">
+      <c r="AG5" s="34"/>
+      <c r="AH5" s="12">
         <v>35.9</v>
       </c>
-      <c r="AJ5" s="16">
+      <c r="AI5" s="12">
         <v>25.43</v>
       </c>
-      <c r="AK5" s="10">
+      <c r="AJ5" s="8">
         <v>12.17</v>
       </c>
-      <c r="AL5" s="16">
+      <c r="AK5" s="34"/>
+      <c r="AL5" s="12">
         <v>11.78</v>
       </c>
-      <c r="AM5" s="21">
+      <c r="AM5" s="17">
         <v>75.209999999999994</v>
       </c>
-      <c r="AN5" s="16">
+      <c r="AN5" s="12">
         <v>6.12</v>
       </c>
       <c r="AQ5" s="8">
         <v>0.6</v>
       </c>
-      <c r="AR5" s="39">
+      <c r="AR5" s="24">
         <v>19.440000000000001</v>
       </c>
-      <c r="AS5" s="39">
+      <c r="AS5" s="24">
         <v>65.819999999999993</v>
       </c>
-      <c r="AT5" s="7">
+      <c r="AT5" s="12">
         <v>8.91</v>
       </c>
-      <c r="AW5" s="40"/>
-      <c r="AX5" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="AY5" s="45">
+      <c r="AW5" s="41"/>
+      <c r="AX5" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY5" s="25">
         <v>3623.59</v>
       </c>
-      <c r="AZ5" s="46">
+      <c r="AZ5" s="26">
         <v>33.609499999999997</v>
       </c>
-    </row>
-    <row r="6" spans="1:52" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="27"/>
+      <c r="BC5" s="42"/>
+      <c r="BD5" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="BE5" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF5" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="BG5" s="50" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:59" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="44"/>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="27"/>
+      <c r="C6" s="44"/>
       <c r="D6" s="1">
         <v>17.579999999999998</v>
       </c>
@@ -1450,7 +1609,7 @@
         <v>6.4598000000000004</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="27"/>
+      <c r="J6" s="44"/>
       <c r="K6" s="1">
         <v>10.4</v>
       </c>
@@ -1461,7 +1620,7 @@
         <v>7</v>
       </c>
       <c r="N6" s="1"/>
-      <c r="O6" s="27"/>
+      <c r="O6" s="44"/>
       <c r="P6" s="1">
         <v>31.97</v>
       </c>
@@ -1472,7 +1631,7 @@
         <v>6.88</v>
       </c>
       <c r="S6" s="1"/>
-      <c r="T6" s="27"/>
+      <c r="T6" s="44"/>
       <c r="U6" s="1">
         <v>10.28</v>
       </c>
@@ -1483,75 +1642,84 @@
         <v>3.6</v>
       </c>
       <c r="X6" s="1"/>
-      <c r="AA6" s="29"/>
-      <c r="AB6" s="9" t="s">
+      <c r="AA6" s="41"/>
+      <c r="AB6" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="AC6" s="16">
-        <v>25.58</v>
-      </c>
-      <c r="AD6" s="16">
-        <v>53.72</v>
-      </c>
-      <c r="AE6" s="10">
-        <v>11.91</v>
-      </c>
-      <c r="AF6" s="16">
+      <c r="AC6" s="34"/>
+      <c r="AD6" s="12">
         <v>22.4</v>
       </c>
-      <c r="AG6" s="16">
+      <c r="AE6" s="12">
         <v>62.3</v>
       </c>
-      <c r="AH6" s="10">
+      <c r="AF6" s="8">
         <v>9.48</v>
       </c>
-      <c r="AI6" s="16">
+      <c r="AG6" s="34"/>
+      <c r="AH6" s="12">
         <v>38.03</v>
       </c>
-      <c r="AJ6" s="16">
+      <c r="AI6" s="12">
         <v>31.47</v>
       </c>
-      <c r="AK6" s="10">
+      <c r="AJ6" s="8">
         <v>19.309999999999999</v>
       </c>
-      <c r="AL6" s="16">
+      <c r="AK6" s="34"/>
+      <c r="AL6" s="12">
         <v>13.03</v>
       </c>
-      <c r="AM6" s="16">
+      <c r="AM6" s="12">
         <v>70.25</v>
       </c>
-      <c r="AN6" s="16">
+      <c r="AN6" s="12">
         <v>5.76</v>
       </c>
-      <c r="AQ6" s="8">
+      <c r="AQ6" s="5">
         <v>0.9</v>
       </c>
-      <c r="AR6" s="38">
+      <c r="AR6" s="23">
         <v>18.89</v>
       </c>
-      <c r="AS6" s="38">
+      <c r="AS6" s="23">
         <v>65.819999999999993</v>
       </c>
       <c r="AT6" s="16">
         <v>7.92</v>
       </c>
-      <c r="AW6" s="43"/>
-      <c r="AX6" s="41" t="s">
+      <c r="AW6" s="42"/>
+      <c r="AX6" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="AY6" s="47">
+      <c r="AY6" s="27">
         <v>4191.1000000000004</v>
       </c>
-      <c r="AZ6" s="48">
+      <c r="AZ6" s="28">
         <v>22.114799999999999</v>
       </c>
-    </row>
-    <row r="7" spans="1:52" ht="15" x14ac:dyDescent="0.25">
-      <c r="A7" s="27"/>
+      <c r="BC6" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD6" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="BE6" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF6" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="BG6" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:59" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="44"/>
       <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="27"/>
+      <c r="C7" s="44"/>
       <c r="D7" s="1">
         <v>15.55</v>
       </c>
@@ -1567,10 +1735,10 @@
       <c r="H7" s="1">
         <v>17.849</v>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="44">
         <v>72.760000000000005</v>
       </c>
-      <c r="J7" s="27"/>
+      <c r="J7" s="44"/>
       <c r="K7" s="1">
         <v>7.34</v>
       </c>
@@ -1580,10 +1748,10 @@
       <c r="M7" s="1">
         <v>2.48</v>
       </c>
-      <c r="N7" s="27">
+      <c r="N7" s="44">
         <v>90.37</v>
       </c>
-      <c r="O7" s="27"/>
+      <c r="O7" s="44"/>
       <c r="P7" s="1">
         <v>30.49</v>
       </c>
@@ -1593,10 +1761,10 @@
       <c r="R7" s="1">
         <v>5.29</v>
       </c>
-      <c r="S7" s="27">
+      <c r="S7" s="44">
         <v>39.22</v>
       </c>
-      <c r="T7" s="27"/>
+      <c r="T7" s="44"/>
       <c r="U7" s="1">
         <v>9.52</v>
       </c>
@@ -1606,68 +1774,75 @@
       <c r="W7" s="1">
         <v>4.32</v>
       </c>
-      <c r="X7" s="27">
+      <c r="X7" s="44">
         <v>82.64</v>
       </c>
-      <c r="AA7" s="30"/>
-      <c r="AB7" s="5" t="s">
+      <c r="AA7" s="42"/>
+      <c r="AB7" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="AC7" s="18">
-        <v>14.07</v>
-      </c>
-      <c r="AD7" s="18">
-        <v>69.05</v>
-      </c>
-      <c r="AE7" s="19">
-        <v>2.91</v>
-      </c>
-      <c r="AF7" s="18">
+      <c r="AC7" s="35"/>
+      <c r="AD7" s="14">
         <v>6.61</v>
       </c>
-      <c r="AG7" s="18">
+      <c r="AE7" s="14">
         <v>87.97</v>
       </c>
-      <c r="AH7" s="19">
+      <c r="AF7" s="15">
         <v>2.0299999999999998</v>
       </c>
-      <c r="AI7" s="18">
+      <c r="AG7" s="35"/>
+      <c r="AH7" s="14">
         <v>26.39</v>
       </c>
-      <c r="AJ7" s="18">
+      <c r="AI7" s="14">
         <v>35.78</v>
       </c>
-      <c r="AK7" s="6">
+      <c r="AJ7" s="5">
         <v>3.17</v>
       </c>
-      <c r="AL7" s="18">
+      <c r="AK7" s="35"/>
+      <c r="AL7" s="14">
         <v>10.53</v>
       </c>
-      <c r="AM7" s="20">
+      <c r="AM7" s="16">
         <v>74.38</v>
       </c>
-      <c r="AN7" s="20">
+      <c r="AN7" s="16">
         <v>3.96</v>
       </c>
-      <c r="AW7" s="44" t="s">
+      <c r="AW7" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="AX7" s="42" t="s">
+      <c r="AX7" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="AY7" s="45">
+      <c r="AY7" s="25">
         <v>94.58</v>
       </c>
-      <c r="AZ7" s="49">
+      <c r="AZ7" s="26">
         <v>12.401999999999999</v>
       </c>
-    </row>
-    <row r="8" spans="1:52" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" s="27"/>
+      <c r="BC7" s="41"/>
+      <c r="BD7" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE7" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF7" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="BG7" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:59" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="44"/>
       <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="27"/>
+      <c r="C8" s="44"/>
       <c r="D8" s="1">
         <v>19.11</v>
       </c>
@@ -1683,8 +1858,8 @@
       <c r="H8" s="1">
         <v>20.038900000000002</v>
       </c>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
       <c r="K8" s="1">
         <v>8.69</v>
       </c>
@@ -1694,8 +1869,8 @@
       <c r="M8" s="1">
         <v>3.84</v>
       </c>
-      <c r="N8" s="27"/>
-      <c r="O8" s="27"/>
+      <c r="N8" s="44"/>
+      <c r="O8" s="44"/>
       <c r="P8" s="1">
         <v>31.8</v>
       </c>
@@ -1705,8 +1880,8 @@
       <c r="R8" s="1">
         <v>8.1999999999999993</v>
       </c>
-      <c r="S8" s="27"/>
-      <c r="T8" s="27"/>
+      <c r="S8" s="44"/>
+      <c r="T8" s="44"/>
       <c r="U8" s="1">
         <v>21.05</v>
       </c>
@@ -1716,66 +1891,79 @@
       <c r="W8" s="1">
         <v>14.75</v>
       </c>
-      <c r="X8" s="27"/>
-      <c r="AA8" s="28" t="s">
+      <c r="X8" s="44"/>
+      <c r="AA8" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="AB8" s="9" t="s">
+      <c r="AB8" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="AC8" s="17">
-        <v>15.44</v>
-      </c>
-      <c r="AD8" s="17">
-        <v>29.4</v>
+      <c r="AC8" s="36">
+        <v>26.95</v>
+      </c>
+      <c r="AD8" s="13">
+        <v>18.12</v>
       </c>
       <c r="AE8" s="13">
-        <v>1.71</v>
-      </c>
-      <c r="AF8" s="17">
-        <v>18.12</v>
-      </c>
-      <c r="AG8" s="17">
         <v>38.68</v>
       </c>
+      <c r="AF8" s="11">
+        <v>2.98</v>
+      </c>
+      <c r="AG8" s="36">
+        <v>19.18</v>
+      </c>
       <c r="AH8" s="13">
-        <v>2.98</v>
-      </c>
-      <c r="AI8" s="11">
         <v>17.05</v>
       </c>
+      <c r="AI8" s="13">
+        <v>15.38</v>
+      </c>
       <c r="AJ8" s="11">
-        <v>15.38</v>
-      </c>
-      <c r="AK8" s="13">
         <v>1.01</v>
       </c>
-      <c r="AL8" s="11">
+      <c r="AK8" s="36">
+        <v>8.77</v>
+      </c>
+      <c r="AL8" s="13">
         <v>7.52</v>
       </c>
-      <c r="AM8" s="17">
+      <c r="AM8" s="13">
         <v>20</v>
       </c>
-      <c r="AN8" s="11">
+      <c r="AN8" s="13">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AW8" s="40"/>
-      <c r="AX8" s="39" t="s">
+      <c r="AW8" s="41"/>
+      <c r="AX8" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="AY8" s="50">
+      <c r="AY8" s="25">
         <v>6743.49</v>
       </c>
-      <c r="AZ8" s="49">
+      <c r="AZ8" s="26">
         <v>114.9687</v>
       </c>
-    </row>
-    <row r="9" spans="1:52" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="27"/>
+      <c r="BC8" s="42"/>
+      <c r="BD8" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="BE8" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF8" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="BG8" s="50" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:59" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="44"/>
       <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="27"/>
+      <c r="C9" s="44"/>
       <c r="D9" s="1">
         <v>14.07</v>
       </c>
@@ -1791,8 +1979,8 @@
       <c r="H9" s="1">
         <v>22.114799999999999</v>
       </c>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
       <c r="K9" s="1">
         <v>6.61</v>
       </c>
@@ -1802,8 +1990,8 @@
       <c r="M9" s="1">
         <v>2.0299999999999998</v>
       </c>
-      <c r="N9" s="27"/>
-      <c r="O9" s="27"/>
+      <c r="N9" s="44"/>
+      <c r="O9" s="44"/>
       <c r="P9" s="1">
         <v>26.39</v>
       </c>
@@ -1813,8 +2001,8 @@
       <c r="R9" s="1">
         <v>3.17</v>
       </c>
-      <c r="S9" s="27"/>
-      <c r="T9" s="27"/>
+      <c r="S9" s="44"/>
+      <c r="T9" s="44"/>
       <c r="U9" s="1">
         <v>10.53</v>
       </c>
@@ -1824,66 +2012,75 @@
       <c r="W9" s="1">
         <v>3.96</v>
       </c>
-      <c r="X9" s="27"/>
-      <c r="AA9" s="29"/>
-      <c r="AB9" s="9" t="s">
+      <c r="X9" s="44"/>
+      <c r="AA9" s="41"/>
+      <c r="AB9" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="AC9" s="7">
-        <v>17.03</v>
-      </c>
-      <c r="AD9" s="7">
-        <v>41.76</v>
-      </c>
-      <c r="AE9" s="10">
-        <v>6.77</v>
-      </c>
-      <c r="AF9" s="7">
+      <c r="AC9" s="34"/>
+      <c r="AD9" s="12">
         <v>16.77</v>
       </c>
-      <c r="AG9" s="16">
+      <c r="AE9" s="12">
         <v>57.08</v>
       </c>
-      <c r="AH9" s="8">
+      <c r="AF9" s="8">
         <v>7.6</v>
       </c>
-      <c r="AI9" s="16">
+      <c r="AG9" s="34"/>
+      <c r="AH9" s="12">
         <v>22.3</v>
       </c>
-      <c r="AJ9" s="16">
+      <c r="AI9" s="12">
         <v>17.95</v>
       </c>
-      <c r="AK9" s="10">
+      <c r="AJ9" s="8">
         <v>8.11</v>
       </c>
-      <c r="AL9" s="16">
+      <c r="AK9" s="34"/>
+      <c r="AL9" s="12">
         <v>9.52</v>
       </c>
-      <c r="AM9" s="16">
+      <c r="AM9" s="12">
         <v>28.57</v>
       </c>
-      <c r="AN9" s="16">
+      <c r="AN9" s="12">
         <v>3.57</v>
       </c>
-      <c r="AW9" s="40"/>
-      <c r="AX9" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="AY9" s="50">
+      <c r="AW9" s="41"/>
+      <c r="AX9" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY9" s="25">
         <v>7320.52</v>
       </c>
-      <c r="AZ9" s="49">
+      <c r="AZ9" s="26">
         <v>113.2599</v>
       </c>
-    </row>
-    <row r="10" spans="1:52" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="27" t="s">
+      <c r="BC9" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="BD9" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="BE9" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF9" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="BG9" s="6">
+        <v>0.157</v>
+      </c>
+    </row>
+    <row r="10" spans="1:59" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="44" t="s">
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="44">
         <v>19.93</v>
       </c>
       <c r="D10" s="1">
@@ -1901,7 +2098,7 @@
       <c r="H10">
         <v>12.401999999999999</v>
       </c>
-      <c r="J10" s="27">
+      <c r="J10" s="44">
         <v>25.95</v>
       </c>
       <c r="K10" s="1">
@@ -1913,7 +2110,7 @@
       <c r="M10" s="1">
         <v>2.98</v>
       </c>
-      <c r="O10" s="27">
+      <c r="O10" s="44">
         <v>19.18</v>
       </c>
       <c r="P10">
@@ -1925,7 +2122,7 @@
       <c r="R10" s="1">
         <v>1.01</v>
       </c>
-      <c r="T10" s="27">
+      <c r="T10" s="44">
         <v>8.77</v>
       </c>
       <c r="U10">
@@ -1937,63 +2134,70 @@
       <c r="W10">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AA10" s="29"/>
-      <c r="AB10" s="9" t="s">
+      <c r="AA10" s="41"/>
+      <c r="AB10" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="AC10" s="7">
-        <v>15.5</v>
-      </c>
-      <c r="AD10" s="7">
-        <v>43.68</v>
-      </c>
-      <c r="AE10" s="8">
-        <v>5.34</v>
-      </c>
-      <c r="AF10" s="16">
+      <c r="AC10" s="34"/>
+      <c r="AD10" s="12">
         <v>13.83</v>
       </c>
-      <c r="AG10" s="7">
+      <c r="AE10" s="12">
         <v>57.55</v>
       </c>
-      <c r="AH10" s="8">
+      <c r="AF10" s="8">
         <v>3.8</v>
       </c>
-      <c r="AI10" s="7">
+      <c r="AG10" s="34"/>
+      <c r="AH10" s="12">
         <v>22.62</v>
       </c>
-      <c r="AJ10" s="7">
+      <c r="AI10" s="12">
         <v>15.38</v>
       </c>
-      <c r="AK10" s="10">
+      <c r="AJ10" s="8">
         <v>7.91</v>
       </c>
-      <c r="AL10" s="7">
+      <c r="AK10" s="34"/>
+      <c r="AL10" s="12">
         <v>8.02</v>
       </c>
-      <c r="AM10" s="7">
+      <c r="AM10" s="12">
         <v>54.29</v>
       </c>
-      <c r="AN10" s="16">
+      <c r="AN10" s="12">
         <v>4.4000000000000004</v>
       </c>
-      <c r="AW10" s="43"/>
-      <c r="AX10" s="41" t="s">
+      <c r="AW10" s="42"/>
+      <c r="AX10" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="AY10" s="51">
+      <c r="AY10" s="27">
         <v>3609.91</v>
       </c>
-      <c r="AZ10" s="52">
+      <c r="AZ10" s="28">
         <v>168.54599999999999</v>
       </c>
-    </row>
-    <row r="11" spans="1:52" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="27"/>
+      <c r="BC10" s="41"/>
+      <c r="BD10" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE10" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF10" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="BG10" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:59" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="44"/>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="27"/>
+      <c r="C11" s="44"/>
       <c r="D11">
         <v>17.03</v>
       </c>
@@ -2009,7 +2213,7 @@
       <c r="H11">
         <v>114.9687</v>
       </c>
-      <c r="J11" s="27"/>
+      <c r="J11" s="44"/>
       <c r="K11">
         <v>16.77</v>
       </c>
@@ -2019,7 +2223,7 @@
       <c r="M11">
         <v>7.6</v>
       </c>
-      <c r="O11" s="27"/>
+      <c r="O11" s="44"/>
       <c r="P11" s="1">
         <v>22.3</v>
       </c>
@@ -2029,7 +2233,7 @@
       <c r="R11" s="1">
         <v>8.11</v>
       </c>
-      <c r="T11" s="27"/>
+      <c r="T11" s="44"/>
       <c r="U11" s="1">
         <v>9.52</v>
       </c>
@@ -2039,65 +2243,72 @@
       <c r="W11" s="1">
         <v>3.57</v>
       </c>
-      <c r="AA11" s="30"/>
-      <c r="AB11" s="5" t="s">
+      <c r="AA11" s="42"/>
+      <c r="AB11" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="AC11" s="3">
-        <v>7.89</v>
-      </c>
-      <c r="AD11" s="3">
-        <v>61.54</v>
-      </c>
-      <c r="AE11" s="4">
-        <v>0.27</v>
-      </c>
-      <c r="AF11" s="3">
+      <c r="AC11" s="35"/>
+      <c r="AD11" s="14">
         <v>5.14</v>
       </c>
-      <c r="AG11" s="3">
+      <c r="AE11" s="14">
         <v>80.19</v>
       </c>
-      <c r="AH11" s="4">
+      <c r="AF11" s="15">
         <v>0</v>
       </c>
-      <c r="AI11" s="3">
+      <c r="AG11" s="35"/>
+      <c r="AH11" s="14">
         <v>14.1</v>
       </c>
-      <c r="AJ11" s="3">
+      <c r="AI11" s="14">
         <v>29.91</v>
       </c>
-      <c r="AK11" s="19">
+      <c r="AJ11" s="15">
         <v>0.81</v>
       </c>
-      <c r="AL11" s="3">
+      <c r="AK11" s="35"/>
+      <c r="AL11" s="14">
         <v>4.01</v>
       </c>
-      <c r="AM11" s="18">
+      <c r="AM11" s="14">
         <v>54.29</v>
       </c>
-      <c r="AN11" s="18">
+      <c r="AN11" s="14">
         <v>0</v>
       </c>
-      <c r="AW11" s="44" t="s">
+      <c r="AW11" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="AX11" s="42" t="s">
+      <c r="AX11" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="AY11" s="50">
+      <c r="AY11" s="25">
         <v>95.45</v>
       </c>
-      <c r="AZ11" s="49">
+      <c r="AZ11" s="26">
         <v>3.6791999999999998</v>
       </c>
-    </row>
-    <row r="12" spans="1:52" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="27"/>
+      <c r="BC11" s="42"/>
+      <c r="BD11" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="BE11" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF11" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="BG11" s="50" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:59" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="44"/>
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="27"/>
+      <c r="C12" s="44"/>
       <c r="D12">
         <v>15.5</v>
       </c>
@@ -2113,7 +2324,7 @@
       <c r="H12">
         <v>113.2599</v>
       </c>
-      <c r="J12" s="27"/>
+      <c r="J12" s="44"/>
       <c r="K12" s="1">
         <v>13.83</v>
       </c>
@@ -2123,7 +2334,7 @@
       <c r="M12">
         <v>3.8</v>
       </c>
-      <c r="O12" s="27"/>
+      <c r="O12" s="44"/>
       <c r="P12">
         <v>22.62</v>
       </c>
@@ -2133,7 +2344,7 @@
       <c r="R12" s="1">
         <v>7.91</v>
       </c>
-      <c r="T12" s="27"/>
+      <c r="T12" s="44"/>
       <c r="U12">
         <v>8.02</v>
       </c>
@@ -2143,65 +2354,80 @@
       <c r="W12" s="1">
         <v>4.4000000000000004</v>
       </c>
-      <c r="AA12" s="28" t="s">
+      <c r="AA12" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="AB12" s="9" t="s">
+      <c r="AB12" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="AC12" s="11">
-        <v>23.38</v>
-      </c>
-      <c r="AD12" s="11">
-        <v>24.5</v>
-      </c>
-      <c r="AE12" s="12">
-        <v>1.0900000000000001</v>
+      <c r="AC12" s="36">
+        <v>28.64</v>
+      </c>
+      <c r="AD12" s="13">
+        <v>17.38</v>
+      </c>
+      <c r="AE12" s="13">
+        <v>42.31</v>
       </c>
       <c r="AF12" s="11">
-        <v>17.38</v>
-      </c>
-      <c r="AG12" s="11">
-        <v>42.31</v>
-      </c>
-      <c r="AH12" s="12">
         <v>1.2</v>
       </c>
-      <c r="AI12" s="11">
+      <c r="AG12" s="36">
+        <v>40.82</v>
+      </c>
+      <c r="AH12" s="13">
         <v>38.85</v>
       </c>
+      <c r="AI12" s="13">
+        <v>7.23</v>
+      </c>
       <c r="AJ12" s="11">
-        <v>7.23</v>
-      </c>
-      <c r="AK12" s="13">
         <v>1.66</v>
       </c>
-      <c r="AL12" s="11">
+      <c r="AK12" s="36">
+        <v>16.04</v>
+      </c>
+      <c r="AL12" s="13">
         <v>12.03</v>
       </c>
-      <c r="AM12" s="17">
+      <c r="AM12" s="13">
         <v>26.56</v>
       </c>
-      <c r="AN12" s="17">
+      <c r="AN12" s="13">
         <v>0.3</v>
       </c>
-      <c r="AW12" s="40"/>
-      <c r="AX12" s="39" t="s">
+      <c r="AW12" s="41"/>
+      <c r="AX12" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="AY12" s="50">
+      <c r="AY12" s="25">
         <v>3620.41</v>
       </c>
-      <c r="AZ12" s="49">
+      <c r="AZ12" s="26">
         <v>26.883299999999998</v>
       </c>
-    </row>
-    <row r="13" spans="1:52" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="27"/>
+      <c r="BC12" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="BD12" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="BE12" s="48" t="s">
+        <v>57</v>
+      </c>
+      <c r="BF12" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG12" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:59" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="44"/>
       <c r="B13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="27"/>
+      <c r="C13" s="44"/>
       <c r="D13">
         <v>11.66</v>
       </c>
@@ -2217,7 +2443,7 @@
       <c r="H13">
         <v>17.3841</v>
       </c>
-      <c r="J13" s="27"/>
+      <c r="J13" s="44"/>
       <c r="K13">
         <v>8.1999999999999993</v>
       </c>
@@ -2227,7 +2453,7 @@
       <c r="M13">
         <v>1.49</v>
       </c>
-      <c r="O13" s="27"/>
+      <c r="O13" s="44"/>
       <c r="P13">
         <v>20.16</v>
       </c>
@@ -2237,7 +2463,7 @@
       <c r="R13">
         <v>3.65</v>
       </c>
-      <c r="T13" s="27"/>
+      <c r="T13" s="44"/>
       <c r="U13" s="1">
         <v>5.76</v>
       </c>
@@ -2247,63 +2473,64 @@
       <c r="W13" s="1">
         <v>0.82</v>
       </c>
-      <c r="AA13" s="29"/>
-      <c r="AB13" s="9" t="s">
+      <c r="AA13" s="41"/>
+      <c r="AB13" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="AC13" s="7">
-        <v>36.31</v>
-      </c>
-      <c r="AD13" s="7">
-        <v>31.08</v>
-      </c>
-      <c r="AE13" s="8">
-        <v>22.36</v>
-      </c>
-      <c r="AF13" s="7">
+      <c r="AC13" s="34"/>
+      <c r="AD13" s="12">
         <v>31.46</v>
       </c>
-      <c r="AG13" s="7">
+      <c r="AE13" s="12">
         <v>47.86</v>
       </c>
-      <c r="AH13" s="8">
+      <c r="AF13" s="8">
         <v>23.16</v>
       </c>
-      <c r="AI13" s="7">
+      <c r="AG13" s="34"/>
+      <c r="AH13" s="12">
         <v>48.2</v>
       </c>
-      <c r="AJ13" s="7">
+      <c r="AI13" s="12">
         <v>14.06</v>
       </c>
-      <c r="AK13" s="10">
+      <c r="AJ13" s="8">
         <v>22.16</v>
       </c>
-      <c r="AL13" s="7">
+      <c r="AK13" s="34"/>
+      <c r="AL13" s="12">
         <v>28.07</v>
       </c>
-      <c r="AM13" s="16">
+      <c r="AM13" s="12">
         <v>35.94</v>
       </c>
-      <c r="AN13" s="16">
+      <c r="AN13" s="12">
         <v>21.19</v>
       </c>
-      <c r="AW13" s="40"/>
-      <c r="AX13" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="AY13" s="50">
+      <c r="AW13" s="41"/>
+      <c r="AX13" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY13" s="25">
         <v>3227.44</v>
       </c>
-      <c r="AZ13" s="49">
+      <c r="AZ13" s="26">
         <v>24.215399999999999</v>
       </c>
-    </row>
-    <row r="14" spans="1:52" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="27"/>
+      <c r="BC13" s="41"/>
+      <c r="BD13" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE13" s="48"/>
+      <c r="BF13" s="6"/>
+      <c r="BG13" s="6"/>
+    </row>
+    <row r="14" spans="1:59" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="44"/>
       <c r="B14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="27"/>
+      <c r="C14" s="44"/>
       <c r="D14">
         <v>10.08</v>
       </c>
@@ -2319,10 +2546,10 @@
       <c r="H14">
         <v>147.7028</v>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="44">
         <v>65.11</v>
       </c>
-      <c r="J14" s="27"/>
+      <c r="J14" s="44"/>
       <c r="K14">
         <v>7.47</v>
       </c>
@@ -2332,10 +2559,10 @@
       <c r="M14">
         <v>0</v>
       </c>
-      <c r="N14" s="27">
+      <c r="N14" s="44">
         <v>80.66</v>
       </c>
-      <c r="O14" s="27"/>
+      <c r="O14" s="44"/>
       <c r="P14">
         <v>17.05</v>
       </c>
@@ -2345,10 +2572,10 @@
       <c r="R14" s="1">
         <v>1.22</v>
       </c>
-      <c r="S14" s="27">
+      <c r="S14" s="44">
         <v>34.19</v>
       </c>
-      <c r="T14" s="27"/>
+      <c r="T14" s="44"/>
       <c r="U14">
         <v>4.76</v>
       </c>
@@ -2358,66 +2585,67 @@
       <c r="W14" s="1">
         <v>0.27</v>
       </c>
-      <c r="X14" s="27">
+      <c r="X14" s="44">
         <v>74.290000000000006</v>
       </c>
-      <c r="AA14" s="29"/>
-      <c r="AB14" s="9" t="s">
+      <c r="AA14" s="41"/>
+      <c r="AB14" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="AC14" s="7">
-        <v>55.31</v>
-      </c>
-      <c r="AD14" s="7">
-        <v>14.08</v>
-      </c>
-      <c r="AE14" s="8">
-        <v>41.14</v>
-      </c>
-      <c r="AF14" s="7">
+      <c r="AC14" s="34"/>
+      <c r="AD14" s="12">
         <v>53.12</v>
       </c>
-      <c r="AG14" s="7">
+      <c r="AE14" s="12">
         <v>16.670000000000002</v>
       </c>
-      <c r="AH14" s="8">
+      <c r="AF14" s="8">
         <v>40.82</v>
       </c>
-      <c r="AI14" s="7">
+      <c r="AG14" s="34"/>
+      <c r="AH14" s="12">
         <v>66.89</v>
       </c>
-      <c r="AJ14" s="7">
+      <c r="AI14" s="12">
         <v>9.64</v>
       </c>
-      <c r="AK14" s="10">
+      <c r="AJ14" s="8">
         <v>50.69</v>
       </c>
-      <c r="AL14" s="7">
+      <c r="AK14" s="34"/>
+      <c r="AL14" s="12">
         <v>42.11</v>
       </c>
-      <c r="AM14" s="7">
+      <c r="AM14" s="12">
         <v>21.88</v>
       </c>
-      <c r="AN14" s="7">
+      <c r="AN14" s="12">
         <v>35.22</v>
       </c>
-      <c r="AW14" s="43"/>
-      <c r="AX14" s="41" t="s">
+      <c r="AW14" s="42"/>
+      <c r="AX14" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="AY14" s="51">
+      <c r="AY14" s="27">
         <v>4536.21</v>
       </c>
-      <c r="AZ14" s="52">
+      <c r="AZ14" s="28">
         <v>52.032899999999998</v>
       </c>
-    </row>
-    <row r="15" spans="1:52" ht="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="27"/>
+      <c r="BC14" s="42"/>
+      <c r="BD14" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="BE14" s="16"/>
+      <c r="BF14" s="50"/>
+      <c r="BG14" s="50"/>
+    </row>
+    <row r="15" spans="1:59" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15" s="44"/>
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="27"/>
+      <c r="C15" s="44"/>
       <c r="D15">
         <v>9.15</v>
       </c>
@@ -2433,8 +2661,8 @@
       <c r="H15">
         <v>159.09700000000001</v>
       </c>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
       <c r="K15">
         <v>5.88</v>
       </c>
@@ -2444,8 +2672,8 @@
       <c r="M15">
         <v>0</v>
       </c>
-      <c r="N15" s="27"/>
-      <c r="O15" s="27"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="44"/>
       <c r="P15">
         <v>16.07</v>
       </c>
@@ -2455,8 +2683,8 @@
       <c r="R15" s="1">
         <v>1.42</v>
       </c>
-      <c r="S15" s="27"/>
-      <c r="T15" s="27"/>
+      <c r="S15" s="44"/>
+      <c r="T15" s="44"/>
       <c r="U15" s="1">
         <v>5.26</v>
       </c>
@@ -2466,66 +2694,60 @@
       <c r="W15" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="X15" s="27"/>
-      <c r="AA15" s="30"/>
-      <c r="AB15" s="5" t="s">
+      <c r="X15" s="44"/>
+      <c r="AA15" s="42"/>
+      <c r="AB15" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="AC15" s="3">
-        <v>16.43</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>46.62</v>
-      </c>
-      <c r="AE15" s="4">
-        <v>0.63</v>
-      </c>
-      <c r="AF15" s="3">
+      <c r="AC15" s="35"/>
+      <c r="AD15" s="14">
         <v>10.039999999999999</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AE15" s="14">
         <v>66.67</v>
       </c>
-      <c r="AH15" s="4">
+      <c r="AF15" s="15">
         <v>0.69</v>
       </c>
-      <c r="AI15" s="15">
+      <c r="AG15" s="35"/>
+      <c r="AH15" s="16">
         <v>30.82</v>
       </c>
-      <c r="AJ15" s="15">
+      <c r="AI15" s="16">
         <v>26.1</v>
       </c>
-      <c r="AK15" s="14">
+      <c r="AJ15" s="5">
         <v>1.1100000000000001</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AK15" s="35"/>
+      <c r="AL15" s="14">
         <v>7.52</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AM15" s="14">
         <v>53.12</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AN15" s="14">
         <v>0</v>
       </c>
-      <c r="AW15" s="44" t="s">
+      <c r="AW15" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="AX15" s="42" t="s">
+      <c r="AX15" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="AY15" s="50">
+      <c r="AY15" s="25">
         <v>514.66999999999996</v>
       </c>
-      <c r="AZ15" s="49">
+      <c r="AZ15" s="26">
         <v>15.446099999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:52" ht="15" x14ac:dyDescent="0.25">
-      <c r="A16" s="27"/>
+    <row r="16" spans="1:59" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16" s="44"/>
       <c r="B16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="27"/>
+      <c r="C16" s="44"/>
       <c r="D16">
         <v>7.89</v>
       </c>
@@ -2541,8 +2763,8 @@
       <c r="H16">
         <v>168.54599999999999</v>
       </c>
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
       <c r="K16">
         <v>5.14</v>
       </c>
@@ -2552,8 +2774,8 @@
       <c r="M16">
         <v>0</v>
       </c>
-      <c r="N16" s="27"/>
-      <c r="O16" s="27"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="44"/>
       <c r="P16">
         <v>14.1</v>
       </c>
@@ -2563,8 +2785,8 @@
       <c r="R16" s="1">
         <v>0.81</v>
       </c>
-      <c r="S16" s="27"/>
-      <c r="T16" s="27"/>
+      <c r="S16" s="44"/>
+      <c r="T16" s="44"/>
       <c r="U16">
         <v>4.01</v>
       </c>
@@ -2574,68 +2796,68 @@
       <c r="W16" s="1">
         <v>0</v>
       </c>
-      <c r="X16" s="27"/>
-      <c r="AA16" s="28" t="s">
+      <c r="X16" s="44"/>
+      <c r="AA16" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="AB16" s="9" t="s">
+      <c r="AB16" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="AC16" s="11">
-        <v>36.14</v>
-      </c>
-      <c r="AD16" s="11">
-        <v>26.19</v>
-      </c>
-      <c r="AE16" s="12">
-        <v>5.65</v>
+      <c r="AC16" s="36">
+        <v>38.07</v>
+      </c>
+      <c r="AD16" s="13">
+        <v>24.24</v>
+      </c>
+      <c r="AE16" s="13">
+        <v>44.69</v>
       </c>
       <c r="AF16" s="11">
-        <v>24.24</v>
-      </c>
-      <c r="AG16" s="11">
-        <v>44.69</v>
-      </c>
-      <c r="AH16" s="12">
         <v>5.14</v>
       </c>
-      <c r="AI16" s="11">
+      <c r="AG16" s="36">
+        <v>56.89</v>
+      </c>
+      <c r="AH16" s="13">
         <v>53.44</v>
       </c>
+      <c r="AI16" s="13">
+        <v>11.24</v>
+      </c>
       <c r="AJ16" s="11">
-        <v>11.24</v>
-      </c>
-      <c r="AK16" s="12">
         <v>6.84</v>
       </c>
-      <c r="AL16" s="11">
+      <c r="AK16" s="36">
+        <v>39.85</v>
+      </c>
+      <c r="AL16" s="13">
         <v>34.090000000000003</v>
       </c>
-      <c r="AM16" s="11">
+      <c r="AM16" s="13">
         <v>22.64</v>
       </c>
-      <c r="AN16" s="11">
+      <c r="AN16" s="13">
         <v>5.42</v>
       </c>
-      <c r="AW16" s="40"/>
-      <c r="AX16" s="39" t="s">
+      <c r="AW16" s="41"/>
+      <c r="AX16" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="AY16" s="50">
+      <c r="AY16" s="25">
         <v>2260.0300000000002</v>
       </c>
-      <c r="AZ16" s="49">
+      <c r="AZ16" s="26">
         <v>27.349599999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:52" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="27" t="s">
+    <row r="17" spans="1:52" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17" s="44" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="44">
         <v>29.96</v>
       </c>
       <c r="D17">
@@ -2653,7 +2875,7 @@
       <c r="H17">
         <v>3.6791999999999998</v>
       </c>
-      <c r="J17" s="27">
+      <c r="J17" s="44">
         <v>28.64</v>
       </c>
       <c r="K17">
@@ -2665,7 +2887,7 @@
       <c r="M17">
         <v>1.2</v>
       </c>
-      <c r="O17" s="27">
+      <c r="O17" s="44">
         <v>40.82</v>
       </c>
       <c r="P17">
@@ -2677,7 +2899,7 @@
       <c r="R17" s="1">
         <v>1.66</v>
       </c>
-      <c r="T17" s="27">
+      <c r="T17" s="44">
         <v>16.04</v>
       </c>
       <c r="U17">
@@ -2689,63 +2911,57 @@
       <c r="W17" s="1">
         <v>0.3</v>
       </c>
-      <c r="AA17" s="29"/>
-      <c r="AB17" s="9" t="s">
+      <c r="AA17" s="41"/>
+      <c r="AB17" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="AC17" s="7">
-        <v>40.53</v>
-      </c>
-      <c r="AD17" s="7">
-        <v>31.95</v>
-      </c>
-      <c r="AE17" s="8">
-        <v>18.43</v>
-      </c>
-      <c r="AF17" s="7">
+      <c r="AC17" s="34"/>
+      <c r="AD17" s="12">
         <v>26.44</v>
       </c>
-      <c r="AG17" s="7">
+      <c r="AE17" s="12">
         <v>52.73</v>
       </c>
-      <c r="AH17" s="8">
+      <c r="AF17" s="8">
         <v>14.03</v>
       </c>
-      <c r="AI17" s="7">
+      <c r="AG17" s="34"/>
+      <c r="AH17" s="12">
         <v>61.97</v>
       </c>
-      <c r="AJ17" s="7">
+      <c r="AI17" s="12">
         <v>11.24</v>
       </c>
-      <c r="AK17" s="8">
+      <c r="AJ17" s="8">
         <v>26.62</v>
       </c>
-      <c r="AL17" s="7">
+      <c r="AK17" s="34"/>
+      <c r="AL17" s="12">
         <v>36.590000000000003</v>
       </c>
-      <c r="AM17" s="7">
+      <c r="AM17" s="12">
         <v>36.479999999999997</v>
       </c>
-      <c r="AN17" s="7">
+      <c r="AN17" s="12">
         <v>18.75</v>
       </c>
-      <c r="AW17" s="40"/>
-      <c r="AX17" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="AY17" s="50">
+      <c r="AW17" s="41"/>
+      <c r="AX17" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY17" s="25">
         <v>3219.47</v>
       </c>
-      <c r="AZ17" s="49">
+      <c r="AZ17" s="26">
         <v>35.505099999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:52" ht="15" x14ac:dyDescent="0.25">
-      <c r="A18" s="27"/>
+    <row r="18" spans="1:52" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18" s="44"/>
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="27"/>
+      <c r="C18" s="44"/>
       <c r="D18">
         <v>36.31</v>
       </c>
@@ -2761,7 +2977,7 @@
       <c r="H18">
         <v>26.883299999999998</v>
       </c>
-      <c r="J18" s="27"/>
+      <c r="J18" s="44"/>
       <c r="K18">
         <v>31.46</v>
       </c>
@@ -2771,7 +2987,7 @@
       <c r="M18">
         <v>23.16</v>
       </c>
-      <c r="O18" s="27"/>
+      <c r="O18" s="44"/>
       <c r="P18">
         <v>48.2</v>
       </c>
@@ -2781,7 +2997,7 @@
       <c r="R18" s="1">
         <v>22.16</v>
       </c>
-      <c r="T18" s="27"/>
+      <c r="T18" s="44"/>
       <c r="U18">
         <v>28.07</v>
       </c>
@@ -2791,63 +3007,57 @@
       <c r="W18" s="1">
         <v>21.19</v>
       </c>
-      <c r="AA18" s="29"/>
-      <c r="AB18" s="9" t="s">
+      <c r="AA18" s="41"/>
+      <c r="AB18" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="AC18" s="7">
-        <v>45.02</v>
-      </c>
-      <c r="AD18" s="7">
-        <v>27.54</v>
-      </c>
-      <c r="AE18" s="8">
-        <v>22.79</v>
-      </c>
-      <c r="AF18" s="7">
+      <c r="AC18" s="34"/>
+      <c r="AD18" s="12">
         <v>34.39</v>
       </c>
-      <c r="AG18" s="7">
+      <c r="AE18" s="12">
         <v>42.77</v>
       </c>
-      <c r="AH18" s="8">
+      <c r="AF18" s="8">
         <v>19.96</v>
       </c>
-      <c r="AI18" s="7">
+      <c r="AG18" s="34"/>
+      <c r="AH18" s="12">
         <v>63.28</v>
       </c>
-      <c r="AJ18" s="7">
+      <c r="AI18" s="12">
         <v>11.53</v>
       </c>
-      <c r="AK18" s="8">
+      <c r="AJ18" s="8">
         <v>30.04</v>
       </c>
-      <c r="AL18" s="7">
+      <c r="AK18" s="34"/>
+      <c r="AL18" s="12">
         <v>38.85</v>
       </c>
-      <c r="AM18" s="7">
+      <c r="AM18" s="12">
         <v>32.700000000000003</v>
       </c>
-      <c r="AN18" s="7">
+      <c r="AN18" s="12">
         <v>20</v>
       </c>
-      <c r="AW18" s="40"/>
-      <c r="AX18" s="39" t="s">
+      <c r="AW18" s="42"/>
+      <c r="AX18" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="AY18" s="50">
+      <c r="AY18" s="27">
         <v>4521.08</v>
       </c>
-      <c r="AZ18" s="49">
+      <c r="AZ18" s="28">
         <v>21.763400000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:52" ht="15" x14ac:dyDescent="0.25">
-      <c r="A19" s="27"/>
+    <row r="19" spans="1:52" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19" s="44"/>
       <c r="B19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="27"/>
+      <c r="C19" s="44"/>
       <c r="D19">
         <v>55.31</v>
       </c>
@@ -2863,7 +3073,7 @@
       <c r="H19">
         <v>24.215399999999999</v>
       </c>
-      <c r="J19" s="27"/>
+      <c r="J19" s="44"/>
       <c r="K19">
         <v>53.12</v>
       </c>
@@ -2873,7 +3083,7 @@
       <c r="M19">
         <v>40.82</v>
       </c>
-      <c r="O19" s="27"/>
+      <c r="O19" s="44"/>
       <c r="P19">
         <v>66.89</v>
       </c>
@@ -2883,7 +3093,7 @@
       <c r="R19" s="1">
         <v>50.69</v>
       </c>
-      <c r="T19" s="27"/>
+      <c r="T19" s="44"/>
       <c r="U19">
         <v>42.11</v>
       </c>
@@ -2893,53 +3103,47 @@
       <c r="W19">
         <v>35.22</v>
       </c>
-      <c r="AA19" s="30"/>
-      <c r="AB19" s="5" t="s">
+      <c r="AA19" s="42"/>
+      <c r="AB19" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="AC19" s="3">
-        <v>25.96</v>
-      </c>
-      <c r="AD19" s="3">
-        <v>45.17</v>
-      </c>
-      <c r="AE19" s="4">
-        <v>2.58</v>
-      </c>
-      <c r="AF19" s="3">
+      <c r="AC19" s="35"/>
+      <c r="AD19" s="14">
         <v>10.28</v>
       </c>
-      <c r="AG19" s="3">
+      <c r="AE19" s="14">
         <v>74.92</v>
       </c>
-      <c r="AH19" s="4">
+      <c r="AF19" s="15">
         <v>1.19</v>
       </c>
-      <c r="AI19" s="3">
+      <c r="AG19" s="35"/>
+      <c r="AH19" s="14">
         <v>47.54</v>
       </c>
-      <c r="AJ19" s="3">
+      <c r="AI19" s="14">
         <v>19.600000000000001</v>
       </c>
-      <c r="AK19" s="4">
+      <c r="AJ19" s="15">
         <v>4.18</v>
       </c>
-      <c r="AL19" s="3">
+      <c r="AK19" s="35"/>
+      <c r="AL19" s="14">
         <v>25.06</v>
       </c>
-      <c r="AM19" s="3">
+      <c r="AM19" s="14">
         <v>42.77</v>
       </c>
-      <c r="AN19" s="3">
+      <c r="AN19" s="14">
         <v>3.75</v>
       </c>
     </row>
     <row r="20" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A20" s="27"/>
+      <c r="A20" s="44"/>
       <c r="B20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="27"/>
+      <c r="C20" s="44"/>
       <c r="D20">
         <v>20.87</v>
       </c>
@@ -2955,7 +3159,7 @@
       <c r="H20">
         <v>2.9369000000000001</v>
       </c>
-      <c r="J20" s="27"/>
+      <c r="J20" s="44"/>
       <c r="K20">
         <v>14.93</v>
       </c>
@@ -2965,7 +3169,7 @@
       <c r="M20">
         <v>1.54</v>
       </c>
-      <c r="O20" s="27"/>
+      <c r="O20" s="44"/>
       <c r="P20">
         <v>36.72</v>
       </c>
@@ -2975,7 +3179,7 @@
       <c r="R20">
         <v>5.26</v>
       </c>
-      <c r="T20" s="27"/>
+      <c r="T20" s="44"/>
       <c r="U20">
         <v>8.77</v>
       </c>
@@ -2987,11 +3191,11 @@
       </c>
     </row>
     <row r="21" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A21" s="27"/>
+      <c r="A21" s="44"/>
       <c r="B21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="27"/>
+      <c r="C21" s="44"/>
       <c r="D21">
         <v>18.89</v>
       </c>
@@ -3007,10 +3211,10 @@
       <c r="H21">
         <v>22.941400000000002</v>
       </c>
-      <c r="I21" s="27">
+      <c r="I21" s="44">
         <v>48.81</v>
       </c>
-      <c r="J21" s="27"/>
+      <c r="J21" s="44"/>
       <c r="K21">
         <v>12.48</v>
       </c>
@@ -3020,10 +3224,10 @@
       <c r="M21">
         <v>1.03</v>
       </c>
-      <c r="N21" s="27">
+      <c r="N21" s="44">
         <v>67.09</v>
       </c>
-      <c r="O21" s="27"/>
+      <c r="O21" s="44"/>
       <c r="P21">
         <v>34.590000000000003</v>
       </c>
@@ -3033,10 +3237,10 @@
       <c r="R21">
         <v>2.2200000000000002</v>
       </c>
-      <c r="S21" s="27">
+      <c r="S21" s="44">
         <v>30.12</v>
       </c>
-      <c r="T21" s="27"/>
+      <c r="T21" s="44"/>
       <c r="U21">
         <v>8.02</v>
       </c>
@@ -3046,16 +3250,16 @@
       <c r="W21">
         <v>0</v>
       </c>
-      <c r="X21" s="27">
+      <c r="X21" s="44">
         <v>54.69</v>
       </c>
     </row>
     <row r="22" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A22" s="27"/>
+      <c r="A22" s="44"/>
       <c r="B22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="27"/>
+      <c r="C22" s="44"/>
       <c r="D22">
         <v>17.8</v>
       </c>
@@ -3071,8 +3275,8 @@
       <c r="H22">
         <v>23.260400000000001</v>
       </c>
-      <c r="I22" s="27"/>
-      <c r="J22" s="27"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
       <c r="K22">
         <v>10.89</v>
       </c>
@@ -3082,8 +3286,8 @@
       <c r="M22">
         <v>1.2</v>
       </c>
-      <c r="N22" s="27"/>
-      <c r="O22" s="27"/>
+      <c r="N22" s="44"/>
+      <c r="O22" s="44"/>
       <c r="P22">
         <v>33.61</v>
       </c>
@@ -3093,8 +3297,8 @@
       <c r="R22">
         <v>2.2200000000000002</v>
       </c>
-      <c r="S22" s="27"/>
-      <c r="T22" s="27"/>
+      <c r="S22" s="44"/>
+      <c r="T22" s="44"/>
       <c r="U22">
         <v>7.77</v>
       </c>
@@ -3104,14 +3308,14 @@
       <c r="W22">
         <v>0</v>
       </c>
-      <c r="X22" s="27"/>
+      <c r="X22" s="44"/>
     </row>
     <row r="23" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A23" s="27"/>
+      <c r="A23" s="44"/>
       <c r="B23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="27"/>
+      <c r="C23" s="44"/>
       <c r="D23">
         <v>16.43</v>
       </c>
@@ -3127,8 +3331,8 @@
       <c r="H23">
         <v>52.032899999999998</v>
       </c>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
       <c r="K23">
         <v>10.039999999999999</v>
       </c>
@@ -3138,8 +3342,8 @@
       <c r="M23">
         <v>0.69</v>
       </c>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="44"/>
       <c r="P23">
         <v>30.82</v>
       </c>
@@ -3149,8 +3353,8 @@
       <c r="R23">
         <v>1.1100000000000001</v>
       </c>
-      <c r="S23" s="27"/>
-      <c r="T23" s="27"/>
+      <c r="S23" s="44"/>
+      <c r="T23" s="44"/>
       <c r="U23">
         <v>7.52</v>
       </c>
@@ -3160,16 +3364,16 @@
       <c r="W23">
         <v>0</v>
       </c>
-      <c r="X23" s="27"/>
+      <c r="X23" s="44"/>
     </row>
     <row r="24" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="44" t="s">
         <v>20</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="44">
         <v>44.74</v>
       </c>
       <c r="D24">
@@ -3187,7 +3391,7 @@
       <c r="H24">
         <v>15.446099999999999</v>
       </c>
-      <c r="J24" s="27">
+      <c r="J24" s="44">
         <v>38.07</v>
       </c>
       <c r="K24">
@@ -3199,7 +3403,7 @@
       <c r="M24">
         <v>5.14</v>
       </c>
-      <c r="O24" s="27">
+      <c r="O24" s="44">
         <v>56.89</v>
       </c>
       <c r="P24">
@@ -3211,7 +3415,7 @@
       <c r="R24">
         <v>6.84</v>
       </c>
-      <c r="T24" s="27">
+      <c r="T24" s="44">
         <v>39.85</v>
       </c>
       <c r="U24">
@@ -3225,11 +3429,11 @@
       </c>
     </row>
     <row r="25" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A25" s="27"/>
+      <c r="A25" s="44"/>
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="27"/>
+      <c r="C25" s="44"/>
       <c r="D25">
         <v>40.53</v>
       </c>
@@ -3245,7 +3449,7 @@
       <c r="H25">
         <v>27.349599999999999</v>
       </c>
-      <c r="J25" s="27"/>
+      <c r="J25" s="44"/>
       <c r="K25">
         <v>26.44</v>
       </c>
@@ -3255,7 +3459,7 @@
       <c r="M25">
         <v>14.03</v>
       </c>
-      <c r="O25" s="27"/>
+      <c r="O25" s="44"/>
       <c r="P25">
         <v>61.97</v>
       </c>
@@ -3265,7 +3469,7 @@
       <c r="R25">
         <v>26.62</v>
       </c>
-      <c r="T25" s="27"/>
+      <c r="T25" s="44"/>
       <c r="U25">
         <v>36.590000000000003</v>
       </c>
@@ -3277,11 +3481,11 @@
       </c>
     </row>
     <row r="26" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A26" s="27"/>
+      <c r="A26" s="44"/>
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="27"/>
+      <c r="C26" s="44"/>
       <c r="D26">
         <v>45.02</v>
       </c>
@@ -3297,7 +3501,7 @@
       <c r="H26">
         <v>35.505099999999999</v>
       </c>
-      <c r="J26" s="27"/>
+      <c r="J26" s="44"/>
       <c r="K26">
         <v>34.39</v>
       </c>
@@ -3307,7 +3511,7 @@
       <c r="M26">
         <v>19.96</v>
       </c>
-      <c r="O26" s="27"/>
+      <c r="O26" s="44"/>
       <c r="P26">
         <v>63.28</v>
       </c>
@@ -3317,7 +3521,7 @@
       <c r="R26">
         <v>30.04</v>
       </c>
-      <c r="T26" s="27"/>
+      <c r="T26" s="44"/>
       <c r="U26">
         <v>38.85</v>
       </c>
@@ -3329,11 +3533,11 @@
       </c>
     </row>
     <row r="27" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A27" s="27"/>
+      <c r="A27" s="44"/>
       <c r="B27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C27" s="27"/>
+      <c r="C27" s="44"/>
       <c r="D27">
         <v>31.16</v>
       </c>
@@ -3349,7 +3553,7 @@
       <c r="H27">
         <v>1.3381000000000001</v>
       </c>
-      <c r="J27" s="27"/>
+      <c r="J27" s="44"/>
       <c r="K27">
         <v>12.97</v>
       </c>
@@ -3359,7 +3563,7 @@
       <c r="M27">
         <v>2.96</v>
       </c>
-      <c r="O27" s="27"/>
+      <c r="O27" s="44"/>
       <c r="P27">
         <v>53.28</v>
       </c>
@@ -3369,7 +3573,7 @@
       <c r="R27">
         <v>14.07</v>
       </c>
-      <c r="T27" s="27"/>
+      <c r="T27" s="44"/>
       <c r="U27">
         <v>34.590000000000003</v>
       </c>
@@ -3381,11 +3585,11 @@
       </c>
     </row>
     <row r="28" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A28" s="27"/>
+      <c r="A28" s="44"/>
       <c r="B28" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="27"/>
+      <c r="C28" s="44"/>
       <c r="D28">
         <v>28.31</v>
       </c>
@@ -3401,10 +3605,10 @@
       <c r="H28">
         <v>13.305</v>
       </c>
-      <c r="I28" s="27">
+      <c r="I28" s="44">
         <v>48.1</v>
       </c>
-      <c r="J28" s="27"/>
+      <c r="J28" s="44"/>
       <c r="K28">
         <v>11.75</v>
       </c>
@@ -3414,10 +3618,10 @@
       <c r="M28">
         <v>1.58</v>
       </c>
-      <c r="N28" s="27">
+      <c r="N28" s="44">
         <v>76.209999999999994</v>
       </c>
-      <c r="O28" s="27"/>
+      <c r="O28" s="44"/>
       <c r="P28">
         <v>50.16</v>
       </c>
@@ -3427,10 +3631,10 @@
       <c r="R28">
         <v>6.08</v>
       </c>
-      <c r="S28" s="27">
+      <c r="S28" s="44">
         <v>23.05</v>
       </c>
-      <c r="T28" s="27"/>
+      <c r="T28" s="44"/>
       <c r="U28">
         <v>28.82</v>
       </c>
@@ -3440,16 +3644,16 @@
       <c r="W28">
         <v>5</v>
       </c>
-      <c r="X28" s="27">
+      <c r="X28" s="44">
         <v>47.8</v>
       </c>
     </row>
     <row r="29" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A29" s="27"/>
+      <c r="A29" s="44"/>
       <c r="B29" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="27"/>
+      <c r="C29" s="44"/>
       <c r="D29">
         <v>27.66</v>
       </c>
@@ -3465,8 +3669,8 @@
       <c r="H29">
         <v>15.7463</v>
       </c>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="44"/>
       <c r="K29">
         <v>11.75</v>
       </c>
@@ -3476,8 +3680,8 @@
       <c r="M29">
         <v>1.78</v>
       </c>
-      <c r="N29" s="27"/>
-      <c r="O29" s="27"/>
+      <c r="N29" s="44"/>
+      <c r="O29" s="44"/>
       <c r="P29">
         <v>49.18</v>
       </c>
@@ -3487,8 +3691,8 @@
       <c r="R29">
         <v>5.7</v>
       </c>
-      <c r="S29" s="27"/>
-      <c r="T29" s="27"/>
+      <c r="S29" s="44"/>
+      <c r="T29" s="44"/>
       <c r="U29">
         <v>27.32</v>
       </c>
@@ -3498,14 +3702,14 @@
       <c r="W29">
         <v>5.42</v>
       </c>
-      <c r="X29" s="27"/>
+      <c r="X29" s="44"/>
     </row>
     <row r="30" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A30" s="27"/>
+      <c r="A30" s="44"/>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="27"/>
+      <c r="C30" s="44"/>
       <c r="D30">
         <v>25.96</v>
       </c>
@@ -3521,8 +3725,8 @@
       <c r="H30">
         <v>21.763400000000001</v>
       </c>
-      <c r="I30" s="27"/>
-      <c r="J30" s="27"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="44"/>
       <c r="K30">
         <v>10.28</v>
       </c>
@@ -3532,8 +3736,8 @@
       <c r="M30">
         <v>1.19</v>
       </c>
-      <c r="N30" s="27"/>
-      <c r="O30" s="27"/>
+      <c r="N30" s="44"/>
+      <c r="O30" s="44"/>
       <c r="P30">
         <v>47.54</v>
       </c>
@@ -3543,8 +3747,8 @@
       <c r="R30">
         <v>4.18</v>
       </c>
-      <c r="S30" s="27"/>
-      <c r="T30" s="27"/>
+      <c r="S30" s="44"/>
+      <c r="T30" s="44"/>
       <c r="U30">
         <v>25.06</v>
       </c>
@@ -3554,23 +3758,23 @@
       <c r="W30">
         <v>3.75</v>
       </c>
-      <c r="X30" s="27"/>
-    </row>
-    <row r="34" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="X30" s="44"/>
+    </row>
+    <row r="34" spans="2:23" ht="15" x14ac:dyDescent="0.2">
       <c r="B34" s="2"/>
-      <c r="C34" s="16" t="s">
-        <v>40</v>
+      <c r="C34" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C35" s="2">
         <v>15</v>
@@ -3582,9 +3786,9 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C36" s="2">
         <v>17.22</v>
@@ -3595,10 +3799,19 @@
       <c r="E36" s="2">
         <v>4.95</v>
       </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="U36" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="V36" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="W36" s="20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C37" s="2">
         <v>17.22</v>
@@ -3609,63 +3822,137 @@
       <c r="E37" s="2">
         <v>2.97</v>
       </c>
-    </row>
-    <row r="41" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B41" s="26"/>
-      <c r="C41" s="16" t="s">
-        <v>40</v>
+      <c r="U37" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="V37" s="38"/>
+      <c r="W37" s="39"/>
+    </row>
+    <row r="38" spans="2:23" ht="15.75" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="U38" s="12">
+        <v>22.95</v>
+      </c>
+      <c r="V38" s="12">
+        <v>49.45</v>
+      </c>
+      <c r="W38" s="8">
+        <v>4.7300000000000004</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="U39" s="12">
+        <v>25.03</v>
+      </c>
+      <c r="V39" s="12">
+        <v>55.23</v>
+      </c>
+      <c r="W39" s="8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="U40" s="12">
+        <v>25.58</v>
+      </c>
+      <c r="V40" s="12">
+        <v>53.72</v>
+      </c>
+      <c r="W40" s="8">
+        <v>11.91</v>
+      </c>
+    </row>
+    <row r="41" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="B41" s="22"/>
+      <c r="C41" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B42" s="26">
+        <v>39</v>
+      </c>
+      <c r="U41" s="14">
+        <v>14.07</v>
+      </c>
+      <c r="V41" s="14">
+        <v>69.05</v>
+      </c>
+      <c r="W41" s="15">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="B42" s="22">
         <v>0</v>
       </c>
-      <c r="C42" s="26">
+      <c r="C42" s="22">
         <v>22.22</v>
       </c>
-      <c r="D42" s="26">
+      <c r="D42" s="22">
         <v>55.7</v>
       </c>
-      <c r="E42" s="26">
+      <c r="E42" s="22">
         <v>4.95</v>
       </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B43" s="26">
+      <c r="U42" s="13">
+        <v>15.44</v>
+      </c>
+      <c r="V42" s="13">
+        <v>29.4</v>
+      </c>
+      <c r="W42" s="11">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" ht="15" x14ac:dyDescent="0.25">
+      <c r="B43" s="22">
         <v>1</v>
       </c>
-      <c r="C43" s="26">
+      <c r="C43" s="22">
         <v>19.440000000000001</v>
       </c>
-      <c r="D43" s="26">
+      <c r="D43" s="22">
         <v>60.76</v>
       </c>
-      <c r="E43" s="26">
+      <c r="E43" s="22">
         <v>3.96</v>
       </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B44" s="26">
+      <c r="U43" s="6">
+        <v>17.03</v>
+      </c>
+      <c r="V43" s="6">
+        <v>41.76</v>
+      </c>
+      <c r="W43" s="8">
+        <v>6.77</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" ht="15" x14ac:dyDescent="0.25">
+      <c r="B44" s="22">
         <v>3</v>
       </c>
-      <c r="C44" s="26">
+      <c r="C44" s="22">
         <v>18.329999999999998</v>
       </c>
-      <c r="D44" s="26">
+      <c r="D44" s="22">
         <v>64.56</v>
       </c>
-      <c r="E44" s="26">
+      <c r="E44" s="22">
         <v>4.95</v>
       </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B45" s="26">
+      <c r="U44" s="6">
+        <v>15.5</v>
+      </c>
+      <c r="V44" s="6">
+        <v>43.68</v>
+      </c>
+      <c r="W44" s="7">
+        <v>5.34</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" ht="15" x14ac:dyDescent="0.25">
+      <c r="B45" s="22">
         <v>5</v>
       </c>
       <c r="C45" s="2">
@@ -3677,36 +3964,96 @@
       <c r="E45" s="2">
         <v>2.97</v>
       </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B46" s="26">
+      <c r="U45" s="3">
+        <v>7.89</v>
+      </c>
+      <c r="V45" s="3">
+        <v>61.54</v>
+      </c>
+      <c r="W45" s="4">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" ht="15" x14ac:dyDescent="0.25">
+      <c r="B46" s="22">
         <v>7</v>
       </c>
-      <c r="C46" s="26">
+      <c r="C46" s="22">
         <v>18.329999999999998</v>
       </c>
-      <c r="D46" s="26">
+      <c r="D46" s="22">
         <v>67.09</v>
       </c>
-      <c r="E46" s="26">
+      <c r="E46" s="22">
         <v>6.93</v>
       </c>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B47" s="26">
+      <c r="U46" s="9">
+        <v>23.38</v>
+      </c>
+      <c r="V46" s="9">
+        <v>24.5</v>
+      </c>
+      <c r="W46" s="10">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" ht="15" x14ac:dyDescent="0.25">
+      <c r="B47" s="22">
         <v>9</v>
       </c>
-      <c r="C47" s="26">
+      <c r="C47" s="22">
         <v>16.670000000000002</v>
       </c>
-      <c r="D47" s="26">
+      <c r="D47" s="22">
         <v>67.09</v>
       </c>
-      <c r="E47" s="26">
+      <c r="E47" s="22">
         <v>3.96</v>
       </c>
-    </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="U47" s="6">
+        <v>36.31</v>
+      </c>
+      <c r="V47" s="6">
+        <v>31.08</v>
+      </c>
+      <c r="W47" s="7">
+        <v>22.36</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" ht="15" x14ac:dyDescent="0.25">
+      <c r="U48" s="6">
+        <v>55.31</v>
+      </c>
+      <c r="V48" s="6">
+        <v>14.08</v>
+      </c>
+      <c r="W48" s="7">
+        <v>41.14</v>
+      </c>
+    </row>
+    <row r="49" spans="2:23" ht="15" x14ac:dyDescent="0.25">
+      <c r="U49" s="3">
+        <v>16.43</v>
+      </c>
+      <c r="V49" s="3">
+        <v>46.62</v>
+      </c>
+      <c r="W49" s="4">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="50" spans="2:23" ht="15" x14ac:dyDescent="0.25">
+      <c r="U50" s="9">
+        <v>36.14</v>
+      </c>
+      <c r="V50" s="9">
+        <v>26.19</v>
+      </c>
+      <c r="W50" s="10">
+        <v>5.65</v>
+      </c>
+    </row>
+    <row r="51" spans="2:23" ht="15" x14ac:dyDescent="0.25">
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1" t="s">
@@ -3724,8 +4071,17 @@
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
-    </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="U51" s="6">
+        <v>40.53</v>
+      </c>
+      <c r="V51" s="6">
+        <v>31.95</v>
+      </c>
+      <c r="W51" s="7">
+        <v>18.43</v>
+      </c>
+    </row>
+    <row r="52" spans="2:23" ht="15" x14ac:dyDescent="0.25">
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1" t="s">
@@ -3740,8 +4096,17 @@
       <c r="G52" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="U52" s="6">
+        <v>45.02</v>
+      </c>
+      <c r="V52" s="6">
+        <v>27.54</v>
+      </c>
+      <c r="W52" s="7">
+        <v>22.79</v>
+      </c>
+    </row>
+    <row r="53" spans="2:23" ht="15" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
         <v>0</v>
       </c>
@@ -3760,8 +4125,17 @@
       <c r="G53" s="1">
         <v>74.38</v>
       </c>
-    </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>25.96</v>
+      </c>
+      <c r="V53" s="3">
+        <v>45.17</v>
+      </c>
+      <c r="W53" s="4">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="54" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B54" s="1"/>
       <c r="C54" s="1" t="s">
         <v>12</v>
@@ -3779,7 +4153,7 @@
         <v>74.38</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B55" s="1"/>
       <c r="C55" s="1" t="s">
         <v>11</v>
@@ -3798,7 +4172,7 @@
       </c>
       <c r="K55" s="1"/>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
         <v>1</v>
       </c>
@@ -3818,7 +4192,7 @@
         <v>42.86</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B57" s="1"/>
       <c r="C57" s="1" t="s">
         <v>12</v>
@@ -3837,7 +4211,7 @@
       </c>
       <c r="K57" s="1"/>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B58" s="1"/>
       <c r="C58" s="1" t="s">
         <v>11</v>
@@ -3856,7 +4230,7 @@
       </c>
       <c r="K58" s="1"/>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
         <v>13</v>
       </c>
@@ -3876,7 +4250,7 @@
         <v>45.31</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B60" s="1"/>
       <c r="C60" s="1" t="s">
         <v>12</v>
@@ -3894,7 +4268,7 @@
         <v>53.12</v>
       </c>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B61" s="1"/>
       <c r="C61" s="1" t="s">
         <v>11</v>
@@ -3912,7 +4286,7 @@
         <v>54.69</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B62" s="1" t="s">
         <v>20</v>
       </c>
@@ -3932,7 +4306,7 @@
         <v>30.19</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B63" s="1"/>
       <c r="C63" s="1" t="s">
         <v>12</v>
@@ -3950,7 +4324,7 @@
         <v>42.77</v>
       </c>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>11</v>
       </c>
@@ -4003,23 +4377,23 @@
       <c r="M87" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="53">
-    <mergeCell ref="AW3:AW6"/>
-    <mergeCell ref="AW7:AW10"/>
-    <mergeCell ref="AW11:AW14"/>
-    <mergeCell ref="AW15:AW18"/>
-    <mergeCell ref="AC3:AE3"/>
-    <mergeCell ref="AF3:AH3"/>
-    <mergeCell ref="AI3:AK3"/>
-    <mergeCell ref="AL3:AN3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AA16:AA19"/>
-    <mergeCell ref="AA12:AA15"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="C3:C9"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="AA8:AA11"/>
-    <mergeCell ref="AA4:AA7"/>
+  <mergeCells count="69">
+    <mergeCell ref="BC3:BC5"/>
+    <mergeCell ref="BC6:BC8"/>
+    <mergeCell ref="BC9:BC11"/>
+    <mergeCell ref="BC12:BC14"/>
+    <mergeCell ref="A24:A30"/>
+    <mergeCell ref="C24:C30"/>
+    <mergeCell ref="O24:O30"/>
+    <mergeCell ref="T17:T23"/>
+    <mergeCell ref="X21:X23"/>
+    <mergeCell ref="T24:T30"/>
+    <mergeCell ref="N28:N30"/>
+    <mergeCell ref="S28:S30"/>
+    <mergeCell ref="X28:X30"/>
+    <mergeCell ref="J24:J30"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="S21:S23"/>
     <mergeCell ref="A3:A9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J3:J9"/>
@@ -4035,28 +4409,44 @@
     <mergeCell ref="J10:J16"/>
     <mergeCell ref="O3:O9"/>
     <mergeCell ref="N14:N16"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="AA8:AA11"/>
+    <mergeCell ref="AA4:AA7"/>
     <mergeCell ref="X14:X16"/>
     <mergeCell ref="J1:N1"/>
-    <mergeCell ref="N7:N9"/>
     <mergeCell ref="S7:S9"/>
-    <mergeCell ref="S21:S23"/>
     <mergeCell ref="X7:X9"/>
     <mergeCell ref="O1:S1"/>
     <mergeCell ref="T1:X1"/>
     <mergeCell ref="T3:T9"/>
     <mergeCell ref="T10:T16"/>
     <mergeCell ref="S14:S16"/>
-    <mergeCell ref="A24:A30"/>
-    <mergeCell ref="C24:C30"/>
-    <mergeCell ref="O24:O30"/>
-    <mergeCell ref="T17:T23"/>
-    <mergeCell ref="X21:X23"/>
-    <mergeCell ref="T24:T30"/>
-    <mergeCell ref="N28:N30"/>
-    <mergeCell ref="S28:S30"/>
-    <mergeCell ref="X28:X30"/>
-    <mergeCell ref="J24:J30"/>
-    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="AW3:AW6"/>
+    <mergeCell ref="AW7:AW10"/>
+    <mergeCell ref="AW11:AW14"/>
+    <mergeCell ref="AW15:AW18"/>
+    <mergeCell ref="U37:W37"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AC4:AC7"/>
+    <mergeCell ref="AC8:AC11"/>
+    <mergeCell ref="AC12:AC15"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AA16:AA19"/>
+    <mergeCell ref="AA12:AA15"/>
+    <mergeCell ref="AC16:AC19"/>
+    <mergeCell ref="AG4:AG7"/>
+    <mergeCell ref="AG8:AG11"/>
+    <mergeCell ref="AG12:AG15"/>
+    <mergeCell ref="AG16:AG19"/>
+    <mergeCell ref="AK4:AK7"/>
+    <mergeCell ref="AK8:AK11"/>
+    <mergeCell ref="AK12:AK15"/>
+    <mergeCell ref="AK16:AK19"/>
+    <mergeCell ref="AG3:AJ3"/>
+    <mergeCell ref="AK3:AN3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/stat/data.xlsx
+++ b/stat/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr-PC\Documents\Workspace\LLMHalluMiti\stat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038B63BD-6E1D-422B-8B5B-F223F4ACE76E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7AFDBB-F138-4416-BA6D-D1F72AC25CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="59">
   <si>
     <t>gpt-4o</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -565,7 +565,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -697,6 +697,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1188,19 +1189,20 @@
       <c r="AZ2" s="16" t="s">
         <v>45</v>
       </c>
+      <c r="BB2" s="45"/>
       <c r="BC2" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="BD2" s="47" t="s">
+      <c r="BD2" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="BE2" s="46" t="s">
+      <c r="BE2" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="BF2" s="45" t="s">
+      <c r="BF2" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="BG2" s="49" t="s">
+      <c r="BG2" s="50" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1319,7 +1321,7 @@
       <c r="BD3" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="BE3" s="48" t="s">
+      <c r="BE3" s="49" t="s">
         <v>56</v>
       </c>
       <c r="BF3" s="6" t="s">
@@ -1452,7 +1454,7 @@
       <c r="BD4" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="BE4" s="48" t="s">
+      <c r="BE4" s="49" t="s">
         <v>56</v>
       </c>
       <c r="BF4" s="6" t="s">
@@ -1580,10 +1582,10 @@
       <c r="BE5" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="BF5" s="50" t="s">
+      <c r="BF5" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="BG5" s="50" t="s">
+      <c r="BG5" s="51" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1704,7 +1706,7 @@
       <c r="BD6" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="BE6" s="48" t="s">
+      <c r="BE6" s="49" t="s">
         <v>56</v>
       </c>
       <c r="BF6" s="6" t="s">
@@ -1827,7 +1829,7 @@
       <c r="BD7" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="BE7" s="48" t="s">
+      <c r="BE7" s="49" t="s">
         <v>56</v>
       </c>
       <c r="BF7" s="6" t="s">
@@ -1951,10 +1953,10 @@
       <c r="BE8" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="BF8" s="50" t="s">
+      <c r="BF8" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="BG8" s="50" t="s">
+      <c r="BG8" s="51" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2063,7 +2065,7 @@
       <c r="BD9" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="BE9" s="48" t="s">
+      <c r="BE9" s="49" t="s">
         <v>56</v>
       </c>
       <c r="BF9" s="6" t="s">
@@ -2182,7 +2184,7 @@
       <c r="BD10" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="BE10" s="48" t="s">
+      <c r="BE10" s="49" t="s">
         <v>56</v>
       </c>
       <c r="BF10" s="6" t="s">
@@ -2296,10 +2298,10 @@
       <c r="BE11" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="BF11" s="50" t="s">
+      <c r="BF11" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="BG11" s="50" t="s">
+      <c r="BG11" s="51" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2412,7 +2414,7 @@
       <c r="BD12" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="BE12" s="48" t="s">
+      <c r="BE12" s="49" t="s">
         <v>57</v>
       </c>
       <c r="BF12" s="6" t="s">
@@ -2521,9 +2523,15 @@
       <c r="BD13" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="BE13" s="48"/>
-      <c r="BF13" s="6"/>
-      <c r="BG13" s="6"/>
+      <c r="BE13" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="BF13" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG13" s="6" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="14" spans="1:59" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="44"/>
@@ -2636,9 +2644,15 @@
       <c r="BD14" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="BE14" s="16"/>
-      <c r="BF14" s="50"/>
-      <c r="BG14" s="50"/>
+      <c r="BE14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="BF14" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG14" s="51" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="15" spans="1:59" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="44"/>

--- a/stat/data.xlsx
+++ b/stat/data.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr-PC\Documents\Workspace\LLMHalluMiti\stat\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr\Documents\Workspace\LLMHalluMiti\stat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7AFDBB-F138-4416-BA6D-D1F72AC25CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3706A258-3FCA-40B6-8E83-F68E97B4EACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="60">
   <si>
     <t>gpt-4o</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -256,6 +256,10 @@
   </si>
   <si>
     <t>&lt; 0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>average</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -664,15 +668,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -680,6 +690,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -696,25 +715,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -996,7 +996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BG87"/>
+  <dimension ref="A1:BN87"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="27" max="28" width="7.625" customWidth="1"/>
@@ -1014,39 +1014,39 @@
     <col min="57" max="59" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:59" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:66" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44" t="s">
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44" t="s">
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44" t="s">
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
-      <c r="W1" s="44"/>
-      <c r="X1" s="44"/>
+      <c r="U1" s="51"/>
+      <c r="V1" s="51"/>
+      <c r="W1" s="51"/>
+      <c r="X1" s="51"/>
       <c r="AS1" s="31"/>
       <c r="AT1" s="31"/>
       <c r="AW1" s="31"/>
@@ -1054,7 +1054,7 @@
       <c r="AY1" s="31"/>
       <c r="AZ1" s="31"/>
     </row>
-    <row r="2" spans="1:59" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:66" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
@@ -1189,31 +1189,42 @@
       <c r="AZ2" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="BB2" s="45"/>
-      <c r="BC2" s="46" t="s">
+      <c r="BC2" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="BD2" s="48" t="s">
+      <c r="BD2" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="BE2" s="47" t="s">
+      <c r="BE2" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="BF2" s="46" t="s">
+      <c r="BF2" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="BG2" s="50" t="s">
+      <c r="BG2" s="36" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="3" spans="1:59" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="44" t="s">
+      <c r="BK2" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="BL2" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="BM2" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="BN2" s="39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:66" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="51" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="44">
+      <c r="C3" s="51">
         <v>39.81</v>
       </c>
       <c r="D3" s="1">
@@ -1232,7 +1243,7 @@
         <v>4.9604999999999997</v>
       </c>
       <c r="I3" s="1"/>
-      <c r="J3" s="44">
+      <c r="J3" s="51">
         <v>45.78</v>
       </c>
       <c r="K3" s="1">
@@ -1245,7 +1256,7 @@
         <v>9.0299999999999994</v>
       </c>
       <c r="N3" s="1"/>
-      <c r="O3" s="44">
+      <c r="O3" s="51">
         <v>38.03</v>
       </c>
       <c r="P3" s="1">
@@ -1258,7 +1269,7 @@
         <v>1.32</v>
       </c>
       <c r="S3" s="1"/>
-      <c r="T3" s="44">
+      <c r="T3" s="51">
         <v>30.33</v>
       </c>
       <c r="U3" s="1">
@@ -1271,26 +1282,26 @@
         <v>2.52</v>
       </c>
       <c r="X3" s="1"/>
-      <c r="AA3" s="38"/>
-      <c r="AB3" s="39"/>
-      <c r="AC3" s="37" t="s">
+      <c r="AA3" s="42"/>
+      <c r="AB3" s="43"/>
+      <c r="AC3" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="AD3" s="38"/>
-      <c r="AE3" s="38"/>
-      <c r="AF3" s="39"/>
-      <c r="AG3" s="37" t="s">
+      <c r="AD3" s="42"/>
+      <c r="AE3" s="42"/>
+      <c r="AF3" s="43"/>
+      <c r="AG3" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="AH3" s="38"/>
-      <c r="AI3" s="38"/>
-      <c r="AJ3" s="39"/>
-      <c r="AK3" s="37" t="s">
+      <c r="AH3" s="42"/>
+      <c r="AI3" s="42"/>
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="AL3" s="38"/>
-      <c r="AM3" s="38"/>
-      <c r="AN3" s="38"/>
+      <c r="AL3" s="42"/>
+      <c r="AM3" s="42"/>
+      <c r="AN3" s="42"/>
       <c r="AQ3" s="8">
         <v>0.1</v>
       </c>
@@ -1303,7 +1314,7 @@
       <c r="AT3" s="12">
         <v>2.97</v>
       </c>
-      <c r="AW3" s="40" t="s">
+      <c r="AW3" s="47" t="s">
         <v>0</v>
       </c>
       <c r="AX3" s="24" t="s">
@@ -1315,13 +1326,13 @@
       <c r="AZ3" s="26">
         <v>4.9604999999999997</v>
       </c>
-      <c r="BC3" s="41" t="s">
+      <c r="BC3" s="48" t="s">
         <v>0</v>
       </c>
       <c r="BD3" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="BE3" s="49" t="s">
+      <c r="BE3" s="12" t="s">
         <v>56</v>
       </c>
       <c r="BF3" s="6" t="s">
@@ -1330,13 +1341,28 @@
       <c r="BG3" s="12" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="4" spans="1:59" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="44"/>
+      <c r="BJ3" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="BK3" s="40">
+        <v>55.03</v>
+      </c>
+      <c r="BL3" s="40">
+        <v>61.48</v>
+      </c>
+      <c r="BM3" s="40">
+        <v>25.43</v>
+      </c>
+      <c r="BN3" s="40">
+        <v>72.03</v>
+      </c>
+    </row>
+    <row r="4" spans="1:66" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="51"/>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="44"/>
+      <c r="C4" s="51"/>
       <c r="D4" s="1">
         <v>25.03</v>
       </c>
@@ -1353,7 +1379,7 @@
         <v>22.125900000000001</v>
       </c>
       <c r="I4" s="1"/>
-      <c r="J4" s="44"/>
+      <c r="J4" s="51"/>
       <c r="K4" s="1">
         <v>23.38</v>
       </c>
@@ -1364,7 +1390,7 @@
         <v>15.35</v>
       </c>
       <c r="N4" s="1"/>
-      <c r="O4" s="44"/>
+      <c r="O4" s="51"/>
       <c r="P4" s="1">
         <v>35.9</v>
       </c>
@@ -1375,7 +1401,7 @@
         <v>12.17</v>
       </c>
       <c r="S4" s="1"/>
-      <c r="T4" s="44"/>
+      <c r="T4" s="51"/>
       <c r="U4" s="1">
         <v>11.78</v>
       </c>
@@ -1386,13 +1412,13 @@
         <v>6.12</v>
       </c>
       <c r="X4" s="1"/>
-      <c r="AA4" s="41" t="s">
+      <c r="AA4" s="48" t="s">
         <v>0</v>
       </c>
       <c r="AB4" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="AC4" s="43">
+      <c r="AC4" s="50">
         <v>45.78</v>
       </c>
       <c r="AD4" s="12">
@@ -1404,7 +1430,7 @@
       <c r="AF4" s="8">
         <v>9.0299999999999994</v>
       </c>
-      <c r="AG4" s="34">
+      <c r="AG4" s="45">
         <v>38.03</v>
       </c>
       <c r="AH4" s="12">
@@ -1416,7 +1442,7 @@
       <c r="AJ4" s="18">
         <v>1.32</v>
       </c>
-      <c r="AK4" s="34">
+      <c r="AK4" s="45">
         <v>30.33</v>
       </c>
       <c r="AL4" s="12">
@@ -1440,7 +1466,7 @@
       <c r="AT4" s="12">
         <v>4.95</v>
       </c>
-      <c r="AW4" s="41"/>
+      <c r="AW4" s="48"/>
       <c r="AX4" s="24" t="s">
         <v>27</v>
       </c>
@@ -1450,11 +1476,11 @@
       <c r="AZ4" s="26">
         <v>22.125900000000001</v>
       </c>
-      <c r="BC4" s="41"/>
+      <c r="BC4" s="48"/>
       <c r="BD4" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="BE4" s="49" t="s">
+      <c r="BE4" s="12" t="s">
         <v>56</v>
       </c>
       <c r="BF4" s="6" t="s">
@@ -1463,13 +1489,25 @@
       <c r="BG4" s="6" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="5" spans="1:59" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="44"/>
+      <c r="BK4" s="40">
+        <v>69.05</v>
+      </c>
+      <c r="BL4" s="40">
+        <v>87.97</v>
+      </c>
+      <c r="BM4" s="40">
+        <v>35.78</v>
+      </c>
+      <c r="BN4" s="40">
+        <v>74.38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:66" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="51"/>
       <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="44"/>
+      <c r="C5" s="51"/>
       <c r="D5" s="1">
         <v>25.58</v>
       </c>
@@ -1486,7 +1524,7 @@
         <v>33.609499999999997</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="44"/>
+      <c r="J5" s="51"/>
       <c r="K5" s="1">
         <v>22.4</v>
       </c>
@@ -1497,7 +1535,7 @@
         <v>9.48</v>
       </c>
       <c r="N5" s="1"/>
-      <c r="O5" s="44"/>
+      <c r="O5" s="51"/>
       <c r="P5" s="1">
         <v>38.03</v>
       </c>
@@ -1508,7 +1546,7 @@
         <v>19.309999999999999</v>
       </c>
       <c r="S5" s="1"/>
-      <c r="T5" s="44"/>
+      <c r="T5" s="51"/>
       <c r="U5" s="1">
         <v>13.03</v>
       </c>
@@ -1519,11 +1557,11 @@
         <v>5.76</v>
       </c>
       <c r="X5" s="1"/>
-      <c r="AA5" s="41"/>
+      <c r="AA5" s="48"/>
       <c r="AB5" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="AC5" s="34"/>
+      <c r="AC5" s="45"/>
       <c r="AD5" s="12">
         <v>23.38</v>
       </c>
@@ -1533,7 +1571,7 @@
       <c r="AF5" s="8">
         <v>15.35</v>
       </c>
-      <c r="AG5" s="34"/>
+      <c r="AG5" s="45"/>
       <c r="AH5" s="12">
         <v>35.9</v>
       </c>
@@ -1543,7 +1581,7 @@
       <c r="AJ5" s="8">
         <v>12.17</v>
       </c>
-      <c r="AK5" s="34"/>
+      <c r="AK5" s="45"/>
       <c r="AL5" s="12">
         <v>11.78</v>
       </c>
@@ -1565,7 +1603,7 @@
       <c r="AT5" s="12">
         <v>8.91</v>
       </c>
-      <c r="AW5" s="41"/>
+      <c r="AW5" s="48"/>
       <c r="AX5" s="24" t="s">
         <v>48</v>
       </c>
@@ -1575,26 +1613,42 @@
       <c r="AZ5" s="26">
         <v>33.609499999999997</v>
       </c>
-      <c r="BC5" s="42"/>
+      <c r="BC5" s="49"/>
       <c r="BD5" s="23" t="s">
         <v>48</v>
       </c>
       <c r="BE5" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="BF5" s="51" t="s">
+      <c r="BF5" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="BG5" s="51" t="s">
+      <c r="BG5" s="37" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="6" spans="1:59" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="44"/>
+      <c r="BK5" s="40">
+        <f>BK4-BK3</f>
+        <v>14.019999999999996</v>
+      </c>
+      <c r="BL5" s="40">
+        <f t="shared" ref="BL5:BN5" si="0">BL4-BL3</f>
+        <v>26.490000000000002</v>
+      </c>
+      <c r="BM5" s="40">
+        <f t="shared" si="0"/>
+        <v>10.350000000000001</v>
+      </c>
+      <c r="BN5" s="40">
+        <f t="shared" si="0"/>
+        <v>2.3499999999999943</v>
+      </c>
+    </row>
+    <row r="6" spans="1:66" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="51"/>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="44"/>
+      <c r="C6" s="51"/>
       <c r="D6" s="1">
         <v>17.579999999999998</v>
       </c>
@@ -1611,7 +1665,7 @@
         <v>6.4598000000000004</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="44"/>
+      <c r="J6" s="51"/>
       <c r="K6" s="1">
         <v>10.4</v>
       </c>
@@ -1622,7 +1676,7 @@
         <v>7</v>
       </c>
       <c r="N6" s="1"/>
-      <c r="O6" s="44"/>
+      <c r="O6" s="51"/>
       <c r="P6" s="1">
         <v>31.97</v>
       </c>
@@ -1633,7 +1687,7 @@
         <v>6.88</v>
       </c>
       <c r="S6" s="1"/>
-      <c r="T6" s="44"/>
+      <c r="T6" s="51"/>
       <c r="U6" s="1">
         <v>10.28</v>
       </c>
@@ -1644,11 +1698,11 @@
         <v>3.6</v>
       </c>
       <c r="X6" s="1"/>
-      <c r="AA6" s="41"/>
+      <c r="AA6" s="48"/>
       <c r="AB6" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="AC6" s="34"/>
+      <c r="AC6" s="45"/>
       <c r="AD6" s="12">
         <v>22.4</v>
       </c>
@@ -1658,7 +1712,7 @@
       <c r="AF6" s="8">
         <v>9.48</v>
       </c>
-      <c r="AG6" s="34"/>
+      <c r="AG6" s="45"/>
       <c r="AH6" s="12">
         <v>38.03</v>
       </c>
@@ -1668,7 +1722,7 @@
       <c r="AJ6" s="8">
         <v>19.309999999999999</v>
       </c>
-      <c r="AK6" s="34"/>
+      <c r="AK6" s="45"/>
       <c r="AL6" s="12">
         <v>13.03</v>
       </c>
@@ -1690,7 +1744,7 @@
       <c r="AT6" s="16">
         <v>7.92</v>
       </c>
-      <c r="AW6" s="42"/>
+      <c r="AW6" s="49"/>
       <c r="AX6" s="23" t="s">
         <v>22</v>
       </c>
@@ -1700,13 +1754,13 @@
       <c r="AZ6" s="28">
         <v>22.114799999999999</v>
       </c>
-      <c r="BC6" s="40" t="s">
+      <c r="BC6" s="47" t="s">
         <v>1</v>
       </c>
       <c r="BD6" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="BE6" s="49" t="s">
+      <c r="BE6" s="12" t="s">
         <v>56</v>
       </c>
       <c r="BF6" s="6" t="s">
@@ -1715,13 +1769,29 @@
       <c r="BG6" s="6" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="7" spans="1:59" ht="15" x14ac:dyDescent="0.25">
-      <c r="A7" s="44"/>
+      <c r="BK6" s="40">
+        <f>BK5/BK3*100</f>
+        <v>25.477012538615295</v>
+      </c>
+      <c r="BL6" s="40">
+        <f t="shared" ref="BL6:BN6" si="1">BL5/BL3*100</f>
+        <v>43.087182823682504</v>
+      </c>
+      <c r="BM6" s="40">
+        <f t="shared" si="1"/>
+        <v>40.699960676366501</v>
+      </c>
+      <c r="BN6" s="40">
+        <f t="shared" si="1"/>
+        <v>3.262529501596549</v>
+      </c>
+    </row>
+    <row r="7" spans="1:66" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="51"/>
       <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="44"/>
+      <c r="C7" s="51"/>
       <c r="D7" s="1">
         <v>15.55</v>
       </c>
@@ -1737,10 +1807,10 @@
       <c r="H7" s="1">
         <v>17.849</v>
       </c>
-      <c r="I7" s="44">
+      <c r="I7" s="51">
         <v>72.760000000000005</v>
       </c>
-      <c r="J7" s="44"/>
+      <c r="J7" s="51"/>
       <c r="K7" s="1">
         <v>7.34</v>
       </c>
@@ -1750,10 +1820,10 @@
       <c r="M7" s="1">
         <v>2.48</v>
       </c>
-      <c r="N7" s="44">
+      <c r="N7" s="51">
         <v>90.37</v>
       </c>
-      <c r="O7" s="44"/>
+      <c r="O7" s="51"/>
       <c r="P7" s="1">
         <v>30.49</v>
       </c>
@@ -1763,10 +1833,10 @@
       <c r="R7" s="1">
         <v>5.29</v>
       </c>
-      <c r="S7" s="44">
+      <c r="S7" s="51">
         <v>39.22</v>
       </c>
-      <c r="T7" s="44"/>
+      <c r="T7" s="51"/>
       <c r="U7" s="1">
         <v>9.52</v>
       </c>
@@ -1776,14 +1846,14 @@
       <c r="W7" s="1">
         <v>4.32</v>
       </c>
-      <c r="X7" s="44">
+      <c r="X7" s="51">
         <v>82.64</v>
       </c>
-      <c r="AA7" s="42"/>
+      <c r="AA7" s="49"/>
       <c r="AB7" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="AC7" s="35"/>
+      <c r="AC7" s="46"/>
       <c r="AD7" s="14">
         <v>6.61</v>
       </c>
@@ -1793,7 +1863,7 @@
       <c r="AF7" s="15">
         <v>2.0299999999999998</v>
       </c>
-      <c r="AG7" s="35"/>
+      <c r="AG7" s="46"/>
       <c r="AH7" s="14">
         <v>26.39</v>
       </c>
@@ -1803,7 +1873,7 @@
       <c r="AJ7" s="5">
         <v>3.17</v>
       </c>
-      <c r="AK7" s="35"/>
+      <c r="AK7" s="46"/>
       <c r="AL7" s="14">
         <v>10.53</v>
       </c>
@@ -1813,7 +1883,7 @@
       <c r="AN7" s="16">
         <v>3.96</v>
       </c>
-      <c r="AW7" s="40" t="s">
+      <c r="AW7" s="47" t="s">
         <v>1</v>
       </c>
       <c r="AX7" s="24" t="s">
@@ -1825,11 +1895,11 @@
       <c r="AZ7" s="26">
         <v>12.401999999999999</v>
       </c>
-      <c r="BC7" s="41"/>
+      <c r="BC7" s="48"/>
       <c r="BD7" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="BE7" s="49" t="s">
+      <c r="BE7" s="12" t="s">
         <v>56</v>
       </c>
       <c r="BF7" s="6" t="s">
@@ -1838,13 +1908,28 @@
       <c r="BG7" s="6" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="8" spans="1:59" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" s="44"/>
+      <c r="BJ7" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK7" s="40">
+        <v>38.42</v>
+      </c>
+      <c r="BL7" s="40">
+        <v>45.13</v>
+      </c>
+      <c r="BM7" s="40">
+        <v>10.26</v>
+      </c>
+      <c r="BN7" s="40">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:66" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="51"/>
       <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="44"/>
+      <c r="C8" s="51"/>
       <c r="D8" s="1">
         <v>19.11</v>
       </c>
@@ -1860,8 +1945,8 @@
       <c r="H8" s="1">
         <v>20.038900000000002</v>
       </c>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
       <c r="K8" s="1">
         <v>8.69</v>
       </c>
@@ -1871,8 +1956,8 @@
       <c r="M8" s="1">
         <v>3.84</v>
       </c>
-      <c r="N8" s="44"/>
-      <c r="O8" s="44"/>
+      <c r="N8" s="51"/>
+      <c r="O8" s="51"/>
       <c r="P8" s="1">
         <v>31.8</v>
       </c>
@@ -1882,8 +1967,8 @@
       <c r="R8" s="1">
         <v>8.1999999999999993</v>
       </c>
-      <c r="S8" s="44"/>
-      <c r="T8" s="44"/>
+      <c r="S8" s="51"/>
+      <c r="T8" s="51"/>
       <c r="U8" s="1">
         <v>21.05</v>
       </c>
@@ -1893,14 +1978,14 @@
       <c r="W8" s="1">
         <v>14.75</v>
       </c>
-      <c r="X8" s="44"/>
-      <c r="AA8" s="40" t="s">
+      <c r="X8" s="51"/>
+      <c r="AA8" s="47" t="s">
         <v>1</v>
       </c>
       <c r="AB8" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="AC8" s="36">
+      <c r="AC8" s="44">
         <v>26.95</v>
       </c>
       <c r="AD8" s="13">
@@ -1912,7 +1997,7 @@
       <c r="AF8" s="11">
         <v>2.98</v>
       </c>
-      <c r="AG8" s="36">
+      <c r="AG8" s="44">
         <v>19.18</v>
       </c>
       <c r="AH8" s="13">
@@ -1924,7 +2009,7 @@
       <c r="AJ8" s="11">
         <v>1.01</v>
       </c>
-      <c r="AK8" s="36">
+      <c r="AK8" s="44">
         <v>8.77</v>
       </c>
       <c r="AL8" s="13">
@@ -1936,7 +2021,7 @@
       <c r="AN8" s="13">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AW8" s="41"/>
+      <c r="AW8" s="48"/>
       <c r="AX8" s="24" t="s">
         <v>27</v>
       </c>
@@ -1946,26 +2031,38 @@
       <c r="AZ8" s="26">
         <v>114.9687</v>
       </c>
-      <c r="BC8" s="42"/>
+      <c r="BC8" s="49"/>
       <c r="BD8" s="23" t="s">
         <v>48</v>
       </c>
       <c r="BE8" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="BF8" s="51" t="s">
+      <c r="BF8" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="BG8" s="51" t="s">
+      <c r="BG8" s="37" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="9" spans="1:59" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="44"/>
+      <c r="BK8" s="40">
+        <v>61.54</v>
+      </c>
+      <c r="BL8" s="40">
+        <v>80.19</v>
+      </c>
+      <c r="BM8" s="40">
+        <v>29.91</v>
+      </c>
+      <c r="BN8" s="40">
+        <v>54.29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:66" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="51"/>
       <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="44"/>
+      <c r="C9" s="51"/>
       <c r="D9" s="1">
         <v>14.07</v>
       </c>
@@ -1981,8 +2078,8 @@
       <c r="H9" s="1">
         <v>22.114799999999999</v>
       </c>
-      <c r="I9" s="44"/>
-      <c r="J9" s="44"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
       <c r="K9" s="1">
         <v>6.61</v>
       </c>
@@ -1992,8 +2089,8 @@
       <c r="M9" s="1">
         <v>2.0299999999999998</v>
       </c>
-      <c r="N9" s="44"/>
-      <c r="O9" s="44"/>
+      <c r="N9" s="51"/>
+      <c r="O9" s="51"/>
       <c r="P9" s="1">
         <v>26.39</v>
       </c>
@@ -2003,8 +2100,8 @@
       <c r="R9" s="1">
         <v>3.17</v>
       </c>
-      <c r="S9" s="44"/>
-      <c r="T9" s="44"/>
+      <c r="S9" s="51"/>
+      <c r="T9" s="51"/>
       <c r="U9" s="1">
         <v>10.53</v>
       </c>
@@ -2014,12 +2111,12 @@
       <c r="W9" s="1">
         <v>3.96</v>
       </c>
-      <c r="X9" s="44"/>
-      <c r="AA9" s="41"/>
+      <c r="X9" s="51"/>
+      <c r="AA9" s="48"/>
       <c r="AB9" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="AC9" s="34"/>
+      <c r="AC9" s="45"/>
       <c r="AD9" s="12">
         <v>16.77</v>
       </c>
@@ -2029,7 +2126,7 @@
       <c r="AF9" s="8">
         <v>7.6</v>
       </c>
-      <c r="AG9" s="34"/>
+      <c r="AG9" s="45"/>
       <c r="AH9" s="12">
         <v>22.3</v>
       </c>
@@ -2039,7 +2136,7 @@
       <c r="AJ9" s="8">
         <v>8.11</v>
       </c>
-      <c r="AK9" s="34"/>
+      <c r="AK9" s="45"/>
       <c r="AL9" s="12">
         <v>9.52</v>
       </c>
@@ -2049,7 +2146,7 @@
       <c r="AN9" s="12">
         <v>3.57</v>
       </c>
-      <c r="AW9" s="41"/>
+      <c r="AW9" s="48"/>
       <c r="AX9" s="24" t="s">
         <v>48</v>
       </c>
@@ -2059,13 +2156,13 @@
       <c r="AZ9" s="26">
         <v>113.2599</v>
       </c>
-      <c r="BC9" s="41" t="s">
+      <c r="BC9" s="48" t="s">
         <v>13</v>
       </c>
       <c r="BD9" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="BE9" s="49" t="s">
+      <c r="BE9" s="12" t="s">
         <v>56</v>
       </c>
       <c r="BF9" s="6" t="s">
@@ -2074,15 +2171,31 @@
       <c r="BG9" s="6">
         <v>0.157</v>
       </c>
-    </row>
-    <row r="10" spans="1:59" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="44" t="s">
+      <c r="BK9" s="40">
+        <f>BK8-BK7</f>
+        <v>23.119999999999997</v>
+      </c>
+      <c r="BL9" s="40">
+        <f t="shared" ref="BL9:BN9" si="2">BL8-BL7</f>
+        <v>35.059999999999995</v>
+      </c>
+      <c r="BM9" s="40">
+        <f t="shared" si="2"/>
+        <v>19.649999999999999</v>
+      </c>
+      <c r="BN9" s="40">
+        <f t="shared" si="2"/>
+        <v>27.689999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:66" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="51" t="s">
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="44">
+      <c r="C10" s="51">
         <v>19.93</v>
       </c>
       <c r="D10" s="1">
@@ -2100,7 +2213,7 @@
       <c r="H10">
         <v>12.401999999999999</v>
       </c>
-      <c r="J10" s="44">
+      <c r="J10" s="51">
         <v>25.95</v>
       </c>
       <c r="K10" s="1">
@@ -2112,7 +2225,7 @@
       <c r="M10" s="1">
         <v>2.98</v>
       </c>
-      <c r="O10" s="44">
+      <c r="O10" s="51">
         <v>19.18</v>
       </c>
       <c r="P10">
@@ -2124,7 +2237,7 @@
       <c r="R10" s="1">
         <v>1.01</v>
       </c>
-      <c r="T10" s="44">
+      <c r="T10" s="51">
         <v>8.77</v>
       </c>
       <c r="U10">
@@ -2136,11 +2249,11 @@
       <c r="W10">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AA10" s="41"/>
+      <c r="AA10" s="48"/>
       <c r="AB10" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="AC10" s="34"/>
+      <c r="AC10" s="45"/>
       <c r="AD10" s="12">
         <v>13.83</v>
       </c>
@@ -2150,7 +2263,7 @@
       <c r="AF10" s="8">
         <v>3.8</v>
       </c>
-      <c r="AG10" s="34"/>
+      <c r="AG10" s="45"/>
       <c r="AH10" s="12">
         <v>22.62</v>
       </c>
@@ -2160,7 +2273,7 @@
       <c r="AJ10" s="8">
         <v>7.91</v>
       </c>
-      <c r="AK10" s="34"/>
+      <c r="AK10" s="45"/>
       <c r="AL10" s="12">
         <v>8.02</v>
       </c>
@@ -2170,7 +2283,7 @@
       <c r="AN10" s="12">
         <v>4.4000000000000004</v>
       </c>
-      <c r="AW10" s="42"/>
+      <c r="AW10" s="49"/>
       <c r="AX10" s="23" t="s">
         <v>22</v>
       </c>
@@ -2180,11 +2293,11 @@
       <c r="AZ10" s="28">
         <v>168.54599999999999</v>
       </c>
-      <c r="BC10" s="41"/>
+      <c r="BC10" s="48"/>
       <c r="BD10" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="BE10" s="49" t="s">
+      <c r="BE10" s="12" t="s">
         <v>56</v>
       </c>
       <c r="BF10" s="6" t="s">
@@ -2193,13 +2306,29 @@
       <c r="BG10" s="6" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="11" spans="1:59" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="44"/>
+      <c r="BK10" s="40">
+        <f>BK9/BK7*100</f>
+        <v>60.176991150442468</v>
+      </c>
+      <c r="BL10" s="40">
+        <f t="shared" ref="BL10:BN10" si="3">BL9/BL7*100</f>
+        <v>77.686682916020374</v>
+      </c>
+      <c r="BM10" s="40">
+        <f t="shared" si="3"/>
+        <v>191.5204678362573</v>
+      </c>
+      <c r="BN10" s="40">
+        <f t="shared" si="3"/>
+        <v>104.09774436090224</v>
+      </c>
+    </row>
+    <row r="11" spans="1:66" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="51"/>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="44"/>
+      <c r="C11" s="51"/>
       <c r="D11">
         <v>17.03</v>
       </c>
@@ -2215,7 +2344,7 @@
       <c r="H11">
         <v>114.9687</v>
       </c>
-      <c r="J11" s="44"/>
+      <c r="J11" s="51"/>
       <c r="K11">
         <v>16.77</v>
       </c>
@@ -2225,7 +2354,7 @@
       <c r="M11">
         <v>7.6</v>
       </c>
-      <c r="O11" s="44"/>
+      <c r="O11" s="51"/>
       <c r="P11" s="1">
         <v>22.3</v>
       </c>
@@ -2235,7 +2364,7 @@
       <c r="R11" s="1">
         <v>8.11</v>
       </c>
-      <c r="T11" s="44"/>
+      <c r="T11" s="51"/>
       <c r="U11" s="1">
         <v>9.52</v>
       </c>
@@ -2245,11 +2374,11 @@
       <c r="W11" s="1">
         <v>3.57</v>
       </c>
-      <c r="AA11" s="42"/>
+      <c r="AA11" s="49"/>
       <c r="AB11" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="AC11" s="35"/>
+      <c r="AC11" s="46"/>
       <c r="AD11" s="14">
         <v>5.14</v>
       </c>
@@ -2259,7 +2388,7 @@
       <c r="AF11" s="15">
         <v>0</v>
       </c>
-      <c r="AG11" s="35"/>
+      <c r="AG11" s="46"/>
       <c r="AH11" s="14">
         <v>14.1</v>
       </c>
@@ -2269,7 +2398,7 @@
       <c r="AJ11" s="15">
         <v>0.81</v>
       </c>
-      <c r="AK11" s="35"/>
+      <c r="AK11" s="46"/>
       <c r="AL11" s="14">
         <v>4.01</v>
       </c>
@@ -2279,7 +2408,7 @@
       <c r="AN11" s="14">
         <v>0</v>
       </c>
-      <c r="AW11" s="40" t="s">
+      <c r="AW11" s="47" t="s">
         <v>13</v>
       </c>
       <c r="AX11" s="24" t="s">
@@ -2291,26 +2420,41 @@
       <c r="AZ11" s="26">
         <v>3.6791999999999998</v>
       </c>
-      <c r="BC11" s="42"/>
+      <c r="BC11" s="49"/>
       <c r="BD11" s="23" t="s">
         <v>48</v>
       </c>
       <c r="BE11" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="BF11" s="51" t="s">
+      <c r="BF11" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="BG11" s="51" t="s">
+      <c r="BG11" s="37" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="12" spans="1:59" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="44"/>
+      <c r="BJ11" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="BK11" s="40">
+        <v>33.81</v>
+      </c>
+      <c r="BL11" s="40">
+        <v>57.28</v>
+      </c>
+      <c r="BM11" s="40">
+        <v>11.21</v>
+      </c>
+      <c r="BN11" s="40">
+        <v>32.700000000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:66" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="51"/>
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="44"/>
+      <c r="C12" s="51"/>
       <c r="D12">
         <v>15.5</v>
       </c>
@@ -2326,7 +2470,7 @@
       <c r="H12">
         <v>113.2599</v>
       </c>
-      <c r="J12" s="44"/>
+      <c r="J12" s="51"/>
       <c r="K12" s="1">
         <v>13.83</v>
       </c>
@@ -2336,7 +2480,7 @@
       <c r="M12">
         <v>3.8</v>
       </c>
-      <c r="O12" s="44"/>
+      <c r="O12" s="51"/>
       <c r="P12">
         <v>22.62</v>
       </c>
@@ -2346,7 +2490,7 @@
       <c r="R12" s="1">
         <v>7.91</v>
       </c>
-      <c r="T12" s="44"/>
+      <c r="T12" s="51"/>
       <c r="U12">
         <v>8.02</v>
       </c>
@@ -2356,13 +2500,13 @@
       <c r="W12" s="1">
         <v>4.4000000000000004</v>
       </c>
-      <c r="AA12" s="40" t="s">
+      <c r="AA12" s="47" t="s">
         <v>13</v>
       </c>
       <c r="AB12" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="AC12" s="36">
+      <c r="AC12" s="44">
         <v>28.64</v>
       </c>
       <c r="AD12" s="13">
@@ -2374,7 +2518,7 @@
       <c r="AF12" s="11">
         <v>1.2</v>
       </c>
-      <c r="AG12" s="36">
+      <c r="AG12" s="44">
         <v>40.82</v>
       </c>
       <c r="AH12" s="13">
@@ -2386,7 +2530,7 @@
       <c r="AJ12" s="11">
         <v>1.66</v>
       </c>
-      <c r="AK12" s="36">
+      <c r="AK12" s="44">
         <v>16.04</v>
       </c>
       <c r="AL12" s="13">
@@ -2398,7 +2542,7 @@
       <c r="AN12" s="13">
         <v>0.3</v>
       </c>
-      <c r="AW12" s="41"/>
+      <c r="AW12" s="48"/>
       <c r="AX12" s="24" t="s">
         <v>27</v>
       </c>
@@ -2408,13 +2552,13 @@
       <c r="AZ12" s="26">
         <v>26.883299999999998</v>
       </c>
-      <c r="BC12" s="41" t="s">
+      <c r="BC12" s="48" t="s">
         <v>20</v>
       </c>
       <c r="BD12" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="BE12" s="49" t="s">
+      <c r="BE12" s="12" t="s">
         <v>57</v>
       </c>
       <c r="BF12" s="6" t="s">
@@ -2423,13 +2567,25 @@
       <c r="BG12" s="6" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="13" spans="1:59" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="44"/>
+      <c r="BK12" s="40">
+        <v>46.62</v>
+      </c>
+      <c r="BL12" s="40">
+        <v>66.67</v>
+      </c>
+      <c r="BM12" s="40">
+        <v>26.1</v>
+      </c>
+      <c r="BN12" s="40">
+        <v>53.12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:66" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="51"/>
       <c r="B13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="44"/>
+      <c r="C13" s="51"/>
       <c r="D13">
         <v>11.66</v>
       </c>
@@ -2445,7 +2601,7 @@
       <c r="H13">
         <v>17.3841</v>
       </c>
-      <c r="J13" s="44"/>
+      <c r="J13" s="51"/>
       <c r="K13">
         <v>8.1999999999999993</v>
       </c>
@@ -2455,7 +2611,7 @@
       <c r="M13">
         <v>1.49</v>
       </c>
-      <c r="O13" s="44"/>
+      <c r="O13" s="51"/>
       <c r="P13">
         <v>20.16</v>
       </c>
@@ -2465,7 +2621,7 @@
       <c r="R13">
         <v>3.65</v>
       </c>
-      <c r="T13" s="44"/>
+      <c r="T13" s="51"/>
       <c r="U13" s="1">
         <v>5.76</v>
       </c>
@@ -2475,11 +2631,11 @@
       <c r="W13" s="1">
         <v>0.82</v>
       </c>
-      <c r="AA13" s="41"/>
+      <c r="AA13" s="48"/>
       <c r="AB13" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="AC13" s="34"/>
+      <c r="AC13" s="45"/>
       <c r="AD13" s="12">
         <v>31.46</v>
       </c>
@@ -2489,7 +2645,7 @@
       <c r="AF13" s="8">
         <v>23.16</v>
       </c>
-      <c r="AG13" s="34"/>
+      <c r="AG13" s="45"/>
       <c r="AH13" s="12">
         <v>48.2</v>
       </c>
@@ -2499,7 +2655,7 @@
       <c r="AJ13" s="8">
         <v>22.16</v>
       </c>
-      <c r="AK13" s="34"/>
+      <c r="AK13" s="45"/>
       <c r="AL13" s="12">
         <v>28.07</v>
       </c>
@@ -2509,7 +2665,7 @@
       <c r="AN13" s="12">
         <v>21.19</v>
       </c>
-      <c r="AW13" s="41"/>
+      <c r="AW13" s="48"/>
       <c r="AX13" s="24" t="s">
         <v>48</v>
       </c>
@@ -2519,11 +2675,11 @@
       <c r="AZ13" s="26">
         <v>24.215399999999999</v>
       </c>
-      <c r="BC13" s="41"/>
+      <c r="BC13" s="48"/>
       <c r="BD13" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="BE13" s="49" t="s">
+      <c r="BE13" s="12" t="s">
         <v>57</v>
       </c>
       <c r="BF13" s="6" t="s">
@@ -2532,13 +2688,29 @@
       <c r="BG13" s="6" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="14" spans="1:59" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="44"/>
+      <c r="BK13" s="40">
+        <f>BK12-BK11</f>
+        <v>12.809999999999995</v>
+      </c>
+      <c r="BL13" s="40">
+        <f t="shared" ref="BL13:BN13" si="4">BL12-BL11</f>
+        <v>9.39</v>
+      </c>
+      <c r="BM13" s="40">
+        <f t="shared" si="4"/>
+        <v>14.89</v>
+      </c>
+      <c r="BN13" s="40">
+        <f t="shared" si="4"/>
+        <v>20.419999999999995</v>
+      </c>
+    </row>
+    <row r="14" spans="1:66" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="51"/>
       <c r="B14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="44"/>
+      <c r="C14" s="51"/>
       <c r="D14">
         <v>10.08</v>
       </c>
@@ -2554,10 +2726,10 @@
       <c r="H14">
         <v>147.7028</v>
       </c>
-      <c r="I14" s="44">
+      <c r="I14" s="51">
         <v>65.11</v>
       </c>
-      <c r="J14" s="44"/>
+      <c r="J14" s="51"/>
       <c r="K14">
         <v>7.47</v>
       </c>
@@ -2567,10 +2739,10 @@
       <c r="M14">
         <v>0</v>
       </c>
-      <c r="N14" s="44">
+      <c r="N14" s="51">
         <v>80.66</v>
       </c>
-      <c r="O14" s="44"/>
+      <c r="O14" s="51"/>
       <c r="P14">
         <v>17.05</v>
       </c>
@@ -2580,10 +2752,10 @@
       <c r="R14" s="1">
         <v>1.22</v>
       </c>
-      <c r="S14" s="44">
+      <c r="S14" s="51">
         <v>34.19</v>
       </c>
-      <c r="T14" s="44"/>
+      <c r="T14" s="51"/>
       <c r="U14">
         <v>4.76</v>
       </c>
@@ -2593,14 +2765,14 @@
       <c r="W14" s="1">
         <v>0.27</v>
       </c>
-      <c r="X14" s="44">
+      <c r="X14" s="51">
         <v>74.290000000000006</v>
       </c>
-      <c r="AA14" s="41"/>
+      <c r="AA14" s="48"/>
       <c r="AB14" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="AC14" s="34"/>
+      <c r="AC14" s="45"/>
       <c r="AD14" s="12">
         <v>53.12</v>
       </c>
@@ -2610,7 +2782,7 @@
       <c r="AF14" s="8">
         <v>40.82</v>
       </c>
-      <c r="AG14" s="34"/>
+      <c r="AG14" s="45"/>
       <c r="AH14" s="12">
         <v>66.89</v>
       </c>
@@ -2620,7 +2792,7 @@
       <c r="AJ14" s="8">
         <v>50.69</v>
       </c>
-      <c r="AK14" s="34"/>
+      <c r="AK14" s="45"/>
       <c r="AL14" s="12">
         <v>42.11</v>
       </c>
@@ -2630,7 +2802,7 @@
       <c r="AN14" s="12">
         <v>35.22</v>
       </c>
-      <c r="AW14" s="42"/>
+      <c r="AW14" s="49"/>
       <c r="AX14" s="23" t="s">
         <v>22</v>
       </c>
@@ -2640,26 +2812,42 @@
       <c r="AZ14" s="28">
         <v>52.032899999999998</v>
       </c>
-      <c r="BC14" s="42"/>
+      <c r="BC14" s="49"/>
       <c r="BD14" s="23" t="s">
         <v>48</v>
       </c>
       <c r="BE14" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="BF14" s="51" t="s">
+      <c r="BF14" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="BG14" s="51" t="s">
+      <c r="BG14" s="37" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="15" spans="1:59" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="44"/>
+      <c r="BK14" s="40">
+        <f>BK13/BK11*100</f>
+        <v>37.888198757763959</v>
+      </c>
+      <c r="BL14" s="40">
+        <f t="shared" ref="BL14:BN14" si="5">BL13/BL11*100</f>
+        <v>16.393156424581008</v>
+      </c>
+      <c r="BM14" s="40">
+        <f t="shared" si="5"/>
+        <v>132.8278322925959</v>
+      </c>
+      <c r="BN14" s="40">
+        <f t="shared" si="5"/>
+        <v>62.446483180428118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:66" ht="15" x14ac:dyDescent="0.25">
+      <c r="A15" s="51"/>
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="44"/>
+      <c r="C15" s="51"/>
       <c r="D15">
         <v>9.15</v>
       </c>
@@ -2675,8 +2863,8 @@
       <c r="H15">
         <v>159.09700000000001</v>
       </c>
-      <c r="I15" s="44"/>
-      <c r="J15" s="44"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
       <c r="K15">
         <v>5.88</v>
       </c>
@@ -2686,8 +2874,8 @@
       <c r="M15">
         <v>0</v>
       </c>
-      <c r="N15" s="44"/>
-      <c r="O15" s="44"/>
+      <c r="N15" s="51"/>
+      <c r="O15" s="51"/>
       <c r="P15">
         <v>16.07</v>
       </c>
@@ -2697,8 +2885,8 @@
       <c r="R15" s="1">
         <v>1.42</v>
       </c>
-      <c r="S15" s="44"/>
-      <c r="T15" s="44"/>
+      <c r="S15" s="51"/>
+      <c r="T15" s="51"/>
       <c r="U15" s="1">
         <v>5.26</v>
       </c>
@@ -2708,12 +2896,12 @@
       <c r="W15" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="X15" s="44"/>
-      <c r="AA15" s="42"/>
+      <c r="X15" s="51"/>
+      <c r="AA15" s="49"/>
       <c r="AB15" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="AC15" s="35"/>
+      <c r="AC15" s="46"/>
       <c r="AD15" s="14">
         <v>10.039999999999999</v>
       </c>
@@ -2723,7 +2911,7 @@
       <c r="AF15" s="15">
         <v>0.69</v>
       </c>
-      <c r="AG15" s="35"/>
+      <c r="AG15" s="46"/>
       <c r="AH15" s="16">
         <v>30.82</v>
       </c>
@@ -2733,7 +2921,7 @@
       <c r="AJ15" s="5">
         <v>1.1100000000000001</v>
       </c>
-      <c r="AK15" s="35"/>
+      <c r="AK15" s="46"/>
       <c r="AL15" s="14">
         <v>7.52</v>
       </c>
@@ -2743,7 +2931,7 @@
       <c r="AN15" s="14">
         <v>0</v>
       </c>
-      <c r="AW15" s="40" t="s">
+      <c r="AW15" s="47" t="s">
         <v>20</v>
       </c>
       <c r="AX15" s="24" t="s">
@@ -2755,13 +2943,28 @@
       <c r="AZ15" s="26">
         <v>15.446099999999999</v>
       </c>
-    </row>
-    <row r="16" spans="1:59" ht="15" x14ac:dyDescent="0.2">
-      <c r="A16" s="44"/>
+      <c r="BJ15" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK15" s="40">
+        <v>31.04</v>
+      </c>
+      <c r="BL15" s="40">
+        <v>49.7</v>
+      </c>
+      <c r="BM15" s="40">
+        <v>13.61</v>
+      </c>
+      <c r="BN15" s="40">
+        <v>33.68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:66" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16" s="51"/>
       <c r="B16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="44"/>
+      <c r="C16" s="51"/>
       <c r="D16">
         <v>7.89</v>
       </c>
@@ -2777,8 +2980,8 @@
       <c r="H16">
         <v>168.54599999999999</v>
       </c>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
       <c r="K16">
         <v>5.14</v>
       </c>
@@ -2788,8 +2991,8 @@
       <c r="M16">
         <v>0</v>
       </c>
-      <c r="N16" s="44"/>
-      <c r="O16" s="44"/>
+      <c r="N16" s="51"/>
+      <c r="O16" s="51"/>
       <c r="P16">
         <v>14.1</v>
       </c>
@@ -2799,8 +3002,8 @@
       <c r="R16" s="1">
         <v>0.81</v>
       </c>
-      <c r="S16" s="44"/>
-      <c r="T16" s="44"/>
+      <c r="S16" s="51"/>
+      <c r="T16" s="51"/>
       <c r="U16">
         <v>4.01</v>
       </c>
@@ -2810,14 +3013,14 @@
       <c r="W16" s="1">
         <v>0</v>
       </c>
-      <c r="X16" s="44"/>
-      <c r="AA16" s="40" t="s">
+      <c r="X16" s="51"/>
+      <c r="AA16" s="47" t="s">
         <v>20</v>
       </c>
       <c r="AB16" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="AC16" s="36">
+      <c r="AC16" s="44">
         <v>38.07</v>
       </c>
       <c r="AD16" s="13">
@@ -2829,7 +3032,7 @@
       <c r="AF16" s="11">
         <v>5.14</v>
       </c>
-      <c r="AG16" s="36">
+      <c r="AG16" s="44">
         <v>56.89</v>
       </c>
       <c r="AH16" s="13">
@@ -2841,7 +3044,7 @@
       <c r="AJ16" s="11">
         <v>6.84</v>
       </c>
-      <c r="AK16" s="36">
+      <c r="AK16" s="44">
         <v>39.85</v>
       </c>
       <c r="AL16" s="13">
@@ -2853,7 +3056,7 @@
       <c r="AN16" s="13">
         <v>5.42</v>
       </c>
-      <c r="AW16" s="41"/>
+      <c r="AW16" s="48"/>
       <c r="AX16" s="24" t="s">
         <v>27</v>
       </c>
@@ -2863,15 +3066,27 @@
       <c r="AZ16" s="26">
         <v>27.349599999999999</v>
       </c>
-    </row>
-    <row r="17" spans="1:52" ht="15" x14ac:dyDescent="0.2">
-      <c r="A17" s="44" t="s">
+      <c r="BK16" s="40">
+        <v>45.17</v>
+      </c>
+      <c r="BL16" s="40">
+        <v>74.92</v>
+      </c>
+      <c r="BM16" s="40">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="BN16" s="40">
+        <v>42.77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:66" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17" s="51" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="44">
+      <c r="C17" s="51">
         <v>29.96</v>
       </c>
       <c r="D17">
@@ -2889,7 +3104,7 @@
       <c r="H17">
         <v>3.6791999999999998</v>
       </c>
-      <c r="J17" s="44">
+      <c r="J17" s="51">
         <v>28.64</v>
       </c>
       <c r="K17">
@@ -2901,7 +3116,7 @@
       <c r="M17">
         <v>1.2</v>
       </c>
-      <c r="O17" s="44">
+      <c r="O17" s="51">
         <v>40.82</v>
       </c>
       <c r="P17">
@@ -2913,7 +3128,7 @@
       <c r="R17" s="1">
         <v>1.66</v>
       </c>
-      <c r="T17" s="44">
+      <c r="T17" s="51">
         <v>16.04</v>
       </c>
       <c r="U17">
@@ -2925,11 +3140,11 @@
       <c r="W17" s="1">
         <v>0.3</v>
       </c>
-      <c r="AA17" s="41"/>
+      <c r="AA17" s="48"/>
       <c r="AB17" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="AC17" s="34"/>
+      <c r="AC17" s="45"/>
       <c r="AD17" s="12">
         <v>26.44</v>
       </c>
@@ -2939,7 +3154,7 @@
       <c r="AF17" s="8">
         <v>14.03</v>
       </c>
-      <c r="AG17" s="34"/>
+      <c r="AG17" s="45"/>
       <c r="AH17" s="12">
         <v>61.97</v>
       </c>
@@ -2949,7 +3164,7 @@
       <c r="AJ17" s="8">
         <v>26.62</v>
       </c>
-      <c r="AK17" s="34"/>
+      <c r="AK17" s="45"/>
       <c r="AL17" s="12">
         <v>36.590000000000003</v>
       </c>
@@ -2959,7 +3174,7 @@
       <c r="AN17" s="12">
         <v>18.75</v>
       </c>
-      <c r="AW17" s="41"/>
+      <c r="AW17" s="48"/>
       <c r="AX17" s="24" t="s">
         <v>48</v>
       </c>
@@ -2969,13 +3184,29 @@
       <c r="AZ17" s="26">
         <v>35.505099999999999</v>
       </c>
-    </row>
-    <row r="18" spans="1:52" ht="15" x14ac:dyDescent="0.2">
-      <c r="A18" s="44"/>
+      <c r="BK17" s="40">
+        <f>BK16-BK15</f>
+        <v>14.130000000000003</v>
+      </c>
+      <c r="BL17" s="40">
+        <f t="shared" ref="BL17" si="6">BL16-BL15</f>
+        <v>25.22</v>
+      </c>
+      <c r="BM17" s="40">
+        <f t="shared" ref="BM17" si="7">BM16-BM15</f>
+        <v>5.990000000000002</v>
+      </c>
+      <c r="BN17" s="40">
+        <f t="shared" ref="BN17" si="8">BN16-BN15</f>
+        <v>9.0900000000000034</v>
+      </c>
+    </row>
+    <row r="18" spans="1:66" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18" s="51"/>
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="44"/>
+      <c r="C18" s="51"/>
       <c r="D18">
         <v>36.31</v>
       </c>
@@ -2991,7 +3222,7 @@
       <c r="H18">
         <v>26.883299999999998</v>
       </c>
-      <c r="J18" s="44"/>
+      <c r="J18" s="51"/>
       <c r="K18">
         <v>31.46</v>
       </c>
@@ -3001,7 +3232,7 @@
       <c r="M18">
         <v>23.16</v>
       </c>
-      <c r="O18" s="44"/>
+      <c r="O18" s="51"/>
       <c r="P18">
         <v>48.2</v>
       </c>
@@ -3011,7 +3242,7 @@
       <c r="R18" s="1">
         <v>22.16</v>
       </c>
-      <c r="T18" s="44"/>
+      <c r="T18" s="51"/>
       <c r="U18">
         <v>28.07</v>
       </c>
@@ -3021,11 +3252,11 @@
       <c r="W18" s="1">
         <v>21.19</v>
       </c>
-      <c r="AA18" s="41"/>
+      <c r="AA18" s="48"/>
       <c r="AB18" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="AC18" s="34"/>
+      <c r="AC18" s="45"/>
       <c r="AD18" s="12">
         <v>34.39</v>
       </c>
@@ -3035,7 +3266,7 @@
       <c r="AF18" s="8">
         <v>19.96</v>
       </c>
-      <c r="AG18" s="34"/>
+      <c r="AG18" s="45"/>
       <c r="AH18" s="12">
         <v>63.28</v>
       </c>
@@ -3045,7 +3276,7 @@
       <c r="AJ18" s="8">
         <v>30.04</v>
       </c>
-      <c r="AK18" s="34"/>
+      <c r="AK18" s="45"/>
       <c r="AL18" s="12">
         <v>38.85</v>
       </c>
@@ -3055,7 +3286,7 @@
       <c r="AN18" s="12">
         <v>20</v>
       </c>
-      <c r="AW18" s="42"/>
+      <c r="AW18" s="49"/>
       <c r="AX18" s="23" t="s">
         <v>22</v>
       </c>
@@ -3065,13 +3296,29 @@
       <c r="AZ18" s="28">
         <v>21.763400000000001</v>
       </c>
-    </row>
-    <row r="19" spans="1:52" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19" s="44"/>
+      <c r="BK18" s="40">
+        <f>BK17/BK15*100</f>
+        <v>45.521907216494853</v>
+      </c>
+      <c r="BL18" s="40">
+        <f t="shared" ref="BL18" si="9">BL17/BL15*100</f>
+        <v>50.744466800804823</v>
+      </c>
+      <c r="BM18" s="40">
+        <f t="shared" ref="BM18" si="10">BM17/BM15*100</f>
+        <v>44.011756061719339</v>
+      </c>
+      <c r="BN18" s="40">
+        <f t="shared" ref="BN18" si="11">BN17/BN15*100</f>
+        <v>26.989311163895497</v>
+      </c>
+    </row>
+    <row r="19" spans="1:66" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19" s="51"/>
       <c r="B19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="44"/>
+      <c r="C19" s="51"/>
       <c r="D19">
         <v>55.31</v>
       </c>
@@ -3087,7 +3334,7 @@
       <c r="H19">
         <v>24.215399999999999</v>
       </c>
-      <c r="J19" s="44"/>
+      <c r="J19" s="51"/>
       <c r="K19">
         <v>53.12</v>
       </c>
@@ -3097,7 +3344,7 @@
       <c r="M19">
         <v>40.82</v>
       </c>
-      <c r="O19" s="44"/>
+      <c r="O19" s="51"/>
       <c r="P19">
         <v>66.89</v>
       </c>
@@ -3107,7 +3354,7 @@
       <c r="R19" s="1">
         <v>50.69</v>
       </c>
-      <c r="T19" s="44"/>
+      <c r="T19" s="51"/>
       <c r="U19">
         <v>42.11</v>
       </c>
@@ -3117,11 +3364,11 @@
       <c r="W19">
         <v>35.22</v>
       </c>
-      <c r="AA19" s="42"/>
+      <c r="AA19" s="49"/>
       <c r="AB19" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="AC19" s="35"/>
+      <c r="AC19" s="46"/>
       <c r="AD19" s="14">
         <v>10.28</v>
       </c>
@@ -3131,7 +3378,7 @@
       <c r="AF19" s="15">
         <v>1.19</v>
       </c>
-      <c r="AG19" s="35"/>
+      <c r="AG19" s="46"/>
       <c r="AH19" s="14">
         <v>47.54</v>
       </c>
@@ -3141,7 +3388,7 @@
       <c r="AJ19" s="15">
         <v>4.18</v>
       </c>
-      <c r="AK19" s="35"/>
+      <c r="AK19" s="46"/>
       <c r="AL19" s="14">
         <v>25.06</v>
       </c>
@@ -3152,12 +3399,12 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="20" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A20" s="44"/>
+    <row r="20" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="A20" s="51"/>
       <c r="B20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="44"/>
+      <c r="C20" s="51"/>
       <c r="D20">
         <v>20.87</v>
       </c>
@@ -3173,7 +3420,7 @@
       <c r="H20">
         <v>2.9369000000000001</v>
       </c>
-      <c r="J20" s="44"/>
+      <c r="J20" s="51"/>
       <c r="K20">
         <v>14.93</v>
       </c>
@@ -3183,7 +3430,7 @@
       <c r="M20">
         <v>1.54</v>
       </c>
-      <c r="O20" s="44"/>
+      <c r="O20" s="51"/>
       <c r="P20">
         <v>36.72</v>
       </c>
@@ -3193,7 +3440,7 @@
       <c r="R20">
         <v>5.26</v>
       </c>
-      <c r="T20" s="44"/>
+      <c r="T20" s="51"/>
       <c r="U20">
         <v>8.77</v>
       </c>
@@ -3204,12 +3451,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A21" s="44"/>
+    <row r="21" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="A21" s="51"/>
       <c r="B21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="44"/>
+      <c r="C21" s="51"/>
       <c r="D21">
         <v>18.89</v>
       </c>
@@ -3225,10 +3472,10 @@
       <c r="H21">
         <v>22.941400000000002</v>
       </c>
-      <c r="I21" s="44">
+      <c r="I21" s="51">
         <v>48.81</v>
       </c>
-      <c r="J21" s="44"/>
+      <c r="J21" s="51"/>
       <c r="K21">
         <v>12.48</v>
       </c>
@@ -3238,10 +3485,10 @@
       <c r="M21">
         <v>1.03</v>
       </c>
-      <c r="N21" s="44">
+      <c r="N21" s="51">
         <v>67.09</v>
       </c>
-      <c r="O21" s="44"/>
+      <c r="O21" s="51"/>
       <c r="P21">
         <v>34.590000000000003</v>
       </c>
@@ -3251,10 +3498,10 @@
       <c r="R21">
         <v>2.2200000000000002</v>
       </c>
-      <c r="S21" s="44">
+      <c r="S21" s="51">
         <v>30.12</v>
       </c>
-      <c r="T21" s="44"/>
+      <c r="T21" s="51"/>
       <c r="U21">
         <v>8.02</v>
       </c>
@@ -3264,16 +3511,16 @@
       <c r="W21">
         <v>0</v>
       </c>
-      <c r="X21" s="44">
+      <c r="X21" s="51">
         <v>54.69</v>
       </c>
     </row>
-    <row r="22" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A22" s="44"/>
+    <row r="22" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="A22" s="51"/>
       <c r="B22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="44"/>
+      <c r="C22" s="51"/>
       <c r="D22">
         <v>17.8</v>
       </c>
@@ -3289,8 +3536,8 @@
       <c r="H22">
         <v>23.260400000000001</v>
       </c>
-      <c r="I22" s="44"/>
-      <c r="J22" s="44"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
       <c r="K22">
         <v>10.89</v>
       </c>
@@ -3300,8 +3547,8 @@
       <c r="M22">
         <v>1.2</v>
       </c>
-      <c r="N22" s="44"/>
-      <c r="O22" s="44"/>
+      <c r="N22" s="51"/>
+      <c r="O22" s="51"/>
       <c r="P22">
         <v>33.61</v>
       </c>
@@ -3311,8 +3558,8 @@
       <c r="R22">
         <v>2.2200000000000002</v>
       </c>
-      <c r="S22" s="44"/>
-      <c r="T22" s="44"/>
+      <c r="S22" s="51"/>
+      <c r="T22" s="51"/>
       <c r="U22">
         <v>7.77</v>
       </c>
@@ -3322,14 +3569,14 @@
       <c r="W22">
         <v>0</v>
       </c>
-      <c r="X22" s="44"/>
-    </row>
-    <row r="23" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A23" s="44"/>
+      <c r="X22" s="51"/>
+    </row>
+    <row r="23" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="A23" s="51"/>
       <c r="B23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="44"/>
+      <c r="C23" s="51"/>
       <c r="D23">
         <v>16.43</v>
       </c>
@@ -3345,8 +3592,8 @@
       <c r="H23">
         <v>52.032899999999998</v>
       </c>
-      <c r="I23" s="44"/>
-      <c r="J23" s="44"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
       <c r="K23">
         <v>10.039999999999999</v>
       </c>
@@ -3356,8 +3603,8 @@
       <c r="M23">
         <v>0.69</v>
       </c>
-      <c r="N23" s="44"/>
-      <c r="O23" s="44"/>
+      <c r="N23" s="51"/>
+      <c r="O23" s="51"/>
       <c r="P23">
         <v>30.82</v>
       </c>
@@ -3367,8 +3614,8 @@
       <c r="R23">
         <v>1.1100000000000001</v>
       </c>
-      <c r="S23" s="44"/>
-      <c r="T23" s="44"/>
+      <c r="S23" s="51"/>
+      <c r="T23" s="51"/>
       <c r="U23">
         <v>7.52</v>
       </c>
@@ -3378,16 +3625,16 @@
       <c r="W23">
         <v>0</v>
       </c>
-      <c r="X23" s="44"/>
-    </row>
-    <row r="24" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A24" s="44" t="s">
+      <c r="X23" s="51"/>
+    </row>
+    <row r="24" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="A24" s="51" t="s">
         <v>20</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="44">
+      <c r="C24" s="51">
         <v>44.74</v>
       </c>
       <c r="D24">
@@ -3405,7 +3652,7 @@
       <c r="H24">
         <v>15.446099999999999</v>
       </c>
-      <c r="J24" s="44">
+      <c r="J24" s="51">
         <v>38.07</v>
       </c>
       <c r="K24">
@@ -3417,7 +3664,7 @@
       <c r="M24">
         <v>5.14</v>
       </c>
-      <c r="O24" s="44">
+      <c r="O24" s="51">
         <v>56.89</v>
       </c>
       <c r="P24">
@@ -3429,7 +3676,7 @@
       <c r="R24">
         <v>6.84</v>
       </c>
-      <c r="T24" s="44">
+      <c r="T24" s="51">
         <v>39.85</v>
       </c>
       <c r="U24">
@@ -3442,12 +3689,12 @@
         <v>5.42</v>
       </c>
     </row>
-    <row r="25" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A25" s="44"/>
+    <row r="25" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="A25" s="51"/>
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="44"/>
+      <c r="C25" s="51"/>
       <c r="D25">
         <v>40.53</v>
       </c>
@@ -3463,7 +3710,7 @@
       <c r="H25">
         <v>27.349599999999999</v>
       </c>
-      <c r="J25" s="44"/>
+      <c r="J25" s="51"/>
       <c r="K25">
         <v>26.44</v>
       </c>
@@ -3473,7 +3720,7 @@
       <c r="M25">
         <v>14.03</v>
       </c>
-      <c r="O25" s="44"/>
+      <c r="O25" s="51"/>
       <c r="P25">
         <v>61.97</v>
       </c>
@@ -3483,7 +3730,7 @@
       <c r="R25">
         <v>26.62</v>
       </c>
-      <c r="T25" s="44"/>
+      <c r="T25" s="51"/>
       <c r="U25">
         <v>36.590000000000003</v>
       </c>
@@ -3494,12 +3741,12 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="26" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A26" s="44"/>
+    <row r="26" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="A26" s="51"/>
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="44"/>
+      <c r="C26" s="51"/>
       <c r="D26">
         <v>45.02</v>
       </c>
@@ -3515,7 +3762,7 @@
       <c r="H26">
         <v>35.505099999999999</v>
       </c>
-      <c r="J26" s="44"/>
+      <c r="J26" s="51"/>
       <c r="K26">
         <v>34.39</v>
       </c>
@@ -3525,7 +3772,7 @@
       <c r="M26">
         <v>19.96</v>
       </c>
-      <c r="O26" s="44"/>
+      <c r="O26" s="51"/>
       <c r="P26">
         <v>63.28</v>
       </c>
@@ -3535,7 +3782,7 @@
       <c r="R26">
         <v>30.04</v>
       </c>
-      <c r="T26" s="44"/>
+      <c r="T26" s="51"/>
       <c r="U26">
         <v>38.85</v>
       </c>
@@ -3546,12 +3793,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A27" s="44"/>
+    <row r="27" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="A27" s="51"/>
       <c r="B27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C27" s="44"/>
+      <c r="C27" s="51"/>
       <c r="D27">
         <v>31.16</v>
       </c>
@@ -3567,7 +3814,7 @@
       <c r="H27">
         <v>1.3381000000000001</v>
       </c>
-      <c r="J27" s="44"/>
+      <c r="J27" s="51"/>
       <c r="K27">
         <v>12.97</v>
       </c>
@@ -3577,7 +3824,7 @@
       <c r="M27">
         <v>2.96</v>
       </c>
-      <c r="O27" s="44"/>
+      <c r="O27" s="51"/>
       <c r="P27">
         <v>53.28</v>
       </c>
@@ -3587,7 +3834,7 @@
       <c r="R27">
         <v>14.07</v>
       </c>
-      <c r="T27" s="44"/>
+      <c r="T27" s="51"/>
       <c r="U27">
         <v>34.590000000000003</v>
       </c>
@@ -3598,12 +3845,12 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="28" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A28" s="44"/>
+    <row r="28" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="A28" s="51"/>
       <c r="B28" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="44"/>
+      <c r="C28" s="51"/>
       <c r="D28">
         <v>28.31</v>
       </c>
@@ -3619,10 +3866,10 @@
       <c r="H28">
         <v>13.305</v>
       </c>
-      <c r="I28" s="44">
+      <c r="I28" s="51">
         <v>48.1</v>
       </c>
-      <c r="J28" s="44"/>
+      <c r="J28" s="51"/>
       <c r="K28">
         <v>11.75</v>
       </c>
@@ -3632,10 +3879,10 @@
       <c r="M28">
         <v>1.58</v>
       </c>
-      <c r="N28" s="44">
+      <c r="N28" s="51">
         <v>76.209999999999994</v>
       </c>
-      <c r="O28" s="44"/>
+      <c r="O28" s="51"/>
       <c r="P28">
         <v>50.16</v>
       </c>
@@ -3645,10 +3892,10 @@
       <c r="R28">
         <v>6.08</v>
       </c>
-      <c r="S28" s="44">
+      <c r="S28" s="51">
         <v>23.05</v>
       </c>
-      <c r="T28" s="44"/>
+      <c r="T28" s="51"/>
       <c r="U28">
         <v>28.82</v>
       </c>
@@ -3658,16 +3905,16 @@
       <c r="W28">
         <v>5</v>
       </c>
-      <c r="X28" s="44">
+      <c r="X28" s="51">
         <v>47.8</v>
       </c>
     </row>
-    <row r="29" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A29" s="44"/>
+    <row r="29" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="A29" s="51"/>
       <c r="B29" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="44"/>
+      <c r="C29" s="51"/>
       <c r="D29">
         <v>27.66</v>
       </c>
@@ -3683,8 +3930,8 @@
       <c r="H29">
         <v>15.7463</v>
       </c>
-      <c r="I29" s="44"/>
-      <c r="J29" s="44"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="51"/>
       <c r="K29">
         <v>11.75</v>
       </c>
@@ -3694,8 +3941,8 @@
       <c r="M29">
         <v>1.78</v>
       </c>
-      <c r="N29" s="44"/>
-      <c r="O29" s="44"/>
+      <c r="N29" s="51"/>
+      <c r="O29" s="51"/>
       <c r="P29">
         <v>49.18</v>
       </c>
@@ -3705,8 +3952,8 @@
       <c r="R29">
         <v>5.7</v>
       </c>
-      <c r="S29" s="44"/>
-      <c r="T29" s="44"/>
+      <c r="S29" s="51"/>
+      <c r="T29" s="51"/>
       <c r="U29">
         <v>27.32</v>
       </c>
@@ -3716,14 +3963,14 @@
       <c r="W29">
         <v>5.42</v>
       </c>
-      <c r="X29" s="44"/>
-    </row>
-    <row r="30" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A30" s="44"/>
+      <c r="X29" s="51"/>
+    </row>
+    <row r="30" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="A30" s="51"/>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="44"/>
+      <c r="C30" s="51"/>
       <c r="D30">
         <v>25.96</v>
       </c>
@@ -3739,8 +3986,8 @@
       <c r="H30">
         <v>21.763400000000001</v>
       </c>
-      <c r="I30" s="44"/>
-      <c r="J30" s="44"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="51"/>
       <c r="K30">
         <v>10.28</v>
       </c>
@@ -3750,8 +3997,8 @@
       <c r="M30">
         <v>1.19</v>
       </c>
-      <c r="N30" s="44"/>
-      <c r="O30" s="44"/>
+      <c r="N30" s="51"/>
+      <c r="O30" s="51"/>
       <c r="P30">
         <v>47.54</v>
       </c>
@@ -3761,8 +4008,8 @@
       <c r="R30">
         <v>4.18</v>
       </c>
-      <c r="S30" s="44"/>
-      <c r="T30" s="44"/>
+      <c r="S30" s="51"/>
+      <c r="T30" s="51"/>
       <c r="U30">
         <v>25.06</v>
       </c>
@@ -3772,7 +4019,7 @@
       <c r="W30">
         <v>3.75</v>
       </c>
-      <c r="X30" s="44"/>
+      <c r="X30" s="51"/>
     </row>
     <row r="34" spans="2:23" ht="15" x14ac:dyDescent="0.2">
       <c r="B34" s="2"/>
@@ -3836,11 +4083,11 @@
       <c r="E37" s="2">
         <v>2.97</v>
       </c>
-      <c r="U37" s="38" t="s">
+      <c r="U37" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="V37" s="38"/>
-      <c r="W37" s="39"/>
+      <c r="V37" s="42"/>
+      <c r="W37" s="43"/>
     </row>
     <row r="38" spans="2:23" ht="15.75" thickTop="1" x14ac:dyDescent="0.2">
       <c r="U38" s="12">
@@ -4454,13 +4701,13 @@
     <mergeCell ref="AG4:AG7"/>
     <mergeCell ref="AG8:AG11"/>
     <mergeCell ref="AG12:AG15"/>
+    <mergeCell ref="AG3:AJ3"/>
+    <mergeCell ref="AK3:AN3"/>
     <mergeCell ref="AG16:AG19"/>
     <mergeCell ref="AK4:AK7"/>
     <mergeCell ref="AK8:AK11"/>
     <mergeCell ref="AK12:AK15"/>
     <mergeCell ref="AK16:AK19"/>
-    <mergeCell ref="AG3:AJ3"/>
-    <mergeCell ref="AK3:AN3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/stat/data.xlsx
+++ b/stat/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr\Documents\Workspace\LLMHalluMiti\stat\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr-PC\Documents\Workspace\LLMHalluMiti\stat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3706A258-3FCA-40B6-8E83-F68E97B4EACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF5FB64F-CB79-4499-91A0-B00B58CBBBF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="59">
   <si>
     <t>gpt-4o</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -115,10 +126,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NAME</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CoVe-SE</t>
   </si>
   <si>
@@ -129,9 +136,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NAME</t>
-  </si>
-  <si>
     <t>CoVe</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -261,6 +265,9 @@
   <si>
     <t>average</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MutRepair</t>
   </si>
 </sst>
 </file>
@@ -683,7 +690,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -692,7 +708,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -701,19 +720,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1017,36 +1024,36 @@
     <row r="1" spans="1:66" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51" t="s">
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51" t="s">
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51" t="s">
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
-      <c r="X1" s="51"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="44"/>
+      <c r="W1" s="44"/>
+      <c r="X1" s="44"/>
       <c r="AS1" s="31"/>
       <c r="AT1" s="31"/>
       <c r="AW1" s="31"/>
@@ -1124,88 +1131,88 @@
         <v>11</v>
       </c>
       <c r="AA2" s="19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="AB2" s="21" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AC2" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD2" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE2" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF2" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="AG2" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH2" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI2" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="AJ2" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="AK2" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL2" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="AM2" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="AN2" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="AQ2" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="AR2" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="AS2" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="AT2" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="AW2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AX2" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="AY2" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AZ2" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="BC2" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="BD2" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="BE2" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="BF2" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="AD2" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE2" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF2" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG2" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="AH2" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI2" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="AJ2" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK2" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="AL2" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="AM2" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="AN2" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="AQ2" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="AR2" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="AS2" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="AT2" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="AW2" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="AX2" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="AY2" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="AZ2" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="BC2" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="BD2" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="BE2" s="35" t="s">
+      <c r="BG2" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="BF2" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="BG2" s="36" t="s">
-        <v>55</v>
-      </c>
       <c r="BK2" s="39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="BL2" s="39" t="s">
         <v>17</v>
@@ -1218,13 +1225,13 @@
       </c>
     </row>
     <row r="3" spans="1:66" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="44" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="51">
+      <c r="C3" s="44">
         <v>39.81</v>
       </c>
       <c r="D3" s="1">
@@ -1243,7 +1250,7 @@
         <v>4.9604999999999997</v>
       </c>
       <c r="I3" s="1"/>
-      <c r="J3" s="51">
+      <c r="J3" s="44">
         <v>45.78</v>
       </c>
       <c r="K3" s="1">
@@ -1256,7 +1263,7 @@
         <v>9.0299999999999994</v>
       </c>
       <c r="N3" s="1"/>
-      <c r="O3" s="51">
+      <c r="O3" s="44">
         <v>38.03</v>
       </c>
       <c r="P3" s="1">
@@ -1269,7 +1276,7 @@
         <v>1.32</v>
       </c>
       <c r="S3" s="1"/>
-      <c r="T3" s="51">
+      <c r="T3" s="44">
         <v>30.33</v>
       </c>
       <c r="U3" s="1">
@@ -1282,26 +1289,26 @@
         <v>2.52</v>
       </c>
       <c r="X3" s="1"/>
-      <c r="AA3" s="42"/>
-      <c r="AB3" s="43"/>
-      <c r="AC3" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD3" s="42"/>
-      <c r="AE3" s="42"/>
-      <c r="AF3" s="43"/>
-      <c r="AG3" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="AH3" s="42"/>
-      <c r="AI3" s="42"/>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="41" t="s">
+      <c r="AA3" s="45"/>
+      <c r="AB3" s="46"/>
+      <c r="AC3" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="AL3" s="42"/>
-      <c r="AM3" s="42"/>
-      <c r="AN3" s="42"/>
+      <c r="AD3" s="45"/>
+      <c r="AE3" s="45"/>
+      <c r="AF3" s="46"/>
+      <c r="AG3" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH3" s="45"/>
+      <c r="AI3" s="45"/>
+      <c r="AJ3" s="46"/>
+      <c r="AK3" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL3" s="45"/>
+      <c r="AM3" s="45"/>
+      <c r="AN3" s="45"/>
       <c r="AQ3" s="8">
         <v>0.1</v>
       </c>
@@ -1314,11 +1321,11 @@
       <c r="AT3" s="12">
         <v>2.97</v>
       </c>
-      <c r="AW3" s="47" t="s">
+      <c r="AW3" s="43" t="s">
         <v>0</v>
       </c>
       <c r="AX3" s="24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY3" s="25">
         <v>100.61</v>
@@ -1326,20 +1333,20 @@
       <c r="AZ3" s="26">
         <v>4.9604999999999997</v>
       </c>
-      <c r="BC3" s="48" t="s">
+      <c r="BC3" s="41" t="s">
         <v>0</v>
       </c>
       <c r="BD3" s="24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE3" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="BF3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="BG3" s="12" t="s">
         <v>56</v>
-      </c>
-      <c r="BF3" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="BG3" s="12" t="s">
-        <v>58</v>
       </c>
       <c r="BJ3" s="38" t="s">
         <v>0</v>
@@ -1358,11 +1365,11 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="51"/>
+      <c r="A4" s="44"/>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="51"/>
+      <c r="C4" s="44"/>
       <c r="D4" s="1">
         <v>25.03</v>
       </c>
@@ -1379,7 +1386,7 @@
         <v>22.125900000000001</v>
       </c>
       <c r="I4" s="1"/>
-      <c r="J4" s="51"/>
+      <c r="J4" s="44"/>
       <c r="K4" s="1">
         <v>23.38</v>
       </c>
@@ -1390,7 +1397,7 @@
         <v>15.35</v>
       </c>
       <c r="N4" s="1"/>
-      <c r="O4" s="51"/>
+      <c r="O4" s="44"/>
       <c r="P4" s="1">
         <v>35.9</v>
       </c>
@@ -1401,7 +1408,7 @@
         <v>12.17</v>
       </c>
       <c r="S4" s="1"/>
-      <c r="T4" s="51"/>
+      <c r="T4" s="44"/>
       <c r="U4" s="1">
         <v>11.78</v>
       </c>
@@ -1412,13 +1419,13 @@
         <v>6.12</v>
       </c>
       <c r="X4" s="1"/>
-      <c r="AA4" s="48" t="s">
+      <c r="AA4" s="41" t="s">
         <v>0</v>
       </c>
       <c r="AB4" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC4" s="50">
+        <v>24</v>
+      </c>
+      <c r="AC4" s="48">
         <v>45.78</v>
       </c>
       <c r="AD4" s="12">
@@ -1430,7 +1437,7 @@
       <c r="AF4" s="8">
         <v>9.0299999999999994</v>
       </c>
-      <c r="AG4" s="45">
+      <c r="AG4" s="49">
         <v>38.03</v>
       </c>
       <c r="AH4" s="12">
@@ -1442,7 +1449,7 @@
       <c r="AJ4" s="18">
         <v>1.32</v>
       </c>
-      <c r="AK4" s="45">
+      <c r="AK4" s="49">
         <v>30.33</v>
       </c>
       <c r="AL4" s="12">
@@ -1466,9 +1473,9 @@
       <c r="AT4" s="12">
         <v>4.95</v>
       </c>
-      <c r="AW4" s="48"/>
+      <c r="AW4" s="41"/>
       <c r="AX4" s="24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AY4" s="25">
         <v>2253.6799999999998</v>
@@ -1476,18 +1483,18 @@
       <c r="AZ4" s="26">
         <v>22.125900000000001</v>
       </c>
-      <c r="BC4" s="48"/>
+      <c r="BC4" s="41"/>
       <c r="BD4" s="24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BE4" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BF4" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BG4" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BK4" s="40">
         <v>69.05</v>
@@ -1503,11 +1510,11 @@
       </c>
     </row>
     <row r="5" spans="1:66" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="51"/>
+      <c r="A5" s="44"/>
       <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="51"/>
+      <c r="C5" s="44"/>
       <c r="D5" s="1">
         <v>25.58</v>
       </c>
@@ -1524,7 +1531,7 @@
         <v>33.609499999999997</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="51"/>
+      <c r="J5" s="44"/>
       <c r="K5" s="1">
         <v>22.4</v>
       </c>
@@ -1535,7 +1542,7 @@
         <v>9.48</v>
       </c>
       <c r="N5" s="1"/>
-      <c r="O5" s="51"/>
+      <c r="O5" s="44"/>
       <c r="P5" s="1">
         <v>38.03</v>
       </c>
@@ -1546,7 +1553,7 @@
         <v>19.309999999999999</v>
       </c>
       <c r="S5" s="1"/>
-      <c r="T5" s="51"/>
+      <c r="T5" s="44"/>
       <c r="U5" s="1">
         <v>13.03</v>
       </c>
@@ -1557,11 +1564,11 @@
         <v>5.76</v>
       </c>
       <c r="X5" s="1"/>
-      <c r="AA5" s="48"/>
+      <c r="AA5" s="41"/>
       <c r="AB5" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC5" s="45"/>
+        <v>25</v>
+      </c>
+      <c r="AC5" s="49"/>
       <c r="AD5" s="12">
         <v>23.38</v>
       </c>
@@ -1571,7 +1578,7 @@
       <c r="AF5" s="8">
         <v>15.35</v>
       </c>
-      <c r="AG5" s="45"/>
+      <c r="AG5" s="49"/>
       <c r="AH5" s="12">
         <v>35.9</v>
       </c>
@@ -1581,7 +1588,7 @@
       <c r="AJ5" s="8">
         <v>12.17</v>
       </c>
-      <c r="AK5" s="45"/>
+      <c r="AK5" s="49"/>
       <c r="AL5" s="12">
         <v>11.78</v>
       </c>
@@ -1603,9 +1610,9 @@
       <c r="AT5" s="12">
         <v>8.91</v>
       </c>
-      <c r="AW5" s="48"/>
+      <c r="AW5" s="41"/>
       <c r="AX5" s="24" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AY5" s="25">
         <v>3623.59</v>
@@ -1613,18 +1620,18 @@
       <c r="AZ5" s="26">
         <v>33.609499999999997</v>
       </c>
-      <c r="BC5" s="49"/>
+      <c r="BC5" s="42"/>
       <c r="BD5" s="23" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BE5" s="33" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BF5" s="37" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BG5" s="37" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BK5" s="40">
         <f>BK4-BK3</f>
@@ -1644,11 +1651,11 @@
       </c>
     </row>
     <row r="6" spans="1:66" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="51"/>
+      <c r="A6" s="44"/>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="51"/>
+      <c r="C6" s="44"/>
       <c r="D6" s="1">
         <v>17.579999999999998</v>
       </c>
@@ -1665,7 +1672,7 @@
         <v>6.4598000000000004</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="51"/>
+      <c r="J6" s="44"/>
       <c r="K6" s="1">
         <v>10.4</v>
       </c>
@@ -1676,7 +1683,7 @@
         <v>7</v>
       </c>
       <c r="N6" s="1"/>
-      <c r="O6" s="51"/>
+      <c r="O6" s="44"/>
       <c r="P6" s="1">
         <v>31.97</v>
       </c>
@@ -1687,7 +1694,7 @@
         <v>6.88</v>
       </c>
       <c r="S6" s="1"/>
-      <c r="T6" s="51"/>
+      <c r="T6" s="44"/>
       <c r="U6" s="1">
         <v>10.28</v>
       </c>
@@ -1698,11 +1705,11 @@
         <v>3.6</v>
       </c>
       <c r="X6" s="1"/>
-      <c r="AA6" s="48"/>
+      <c r="AA6" s="41"/>
       <c r="AB6" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC6" s="45"/>
+        <v>22</v>
+      </c>
+      <c r="AC6" s="49"/>
       <c r="AD6" s="12">
         <v>22.4</v>
       </c>
@@ -1712,7 +1719,7 @@
       <c r="AF6" s="8">
         <v>9.48</v>
       </c>
-      <c r="AG6" s="45"/>
+      <c r="AG6" s="49"/>
       <c r="AH6" s="12">
         <v>38.03</v>
       </c>
@@ -1722,7 +1729,7 @@
       <c r="AJ6" s="8">
         <v>19.309999999999999</v>
       </c>
-      <c r="AK6" s="45"/>
+      <c r="AK6" s="49"/>
       <c r="AL6" s="12">
         <v>13.03</v>
       </c>
@@ -1744,30 +1751,30 @@
       <c r="AT6" s="16">
         <v>7.92</v>
       </c>
-      <c r="AW6" s="49"/>
+      <c r="AW6" s="42"/>
       <c r="AX6" s="23" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="AY6" s="27">
-        <v>4191.1000000000004</v>
+        <v>2095.5500000000002</v>
       </c>
       <c r="AZ6" s="28">
         <v>22.114799999999999</v>
       </c>
-      <c r="BC6" s="47" t="s">
+      <c r="BC6" s="43" t="s">
         <v>1</v>
       </c>
       <c r="BD6" s="24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE6" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BF6" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BG6" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BK6" s="40">
         <f>BK5/BK3*100</f>
@@ -1787,11 +1794,11 @@
       </c>
     </row>
     <row r="7" spans="1:66" ht="15" x14ac:dyDescent="0.25">
-      <c r="A7" s="51"/>
+      <c r="A7" s="44"/>
       <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="51"/>
+      <c r="C7" s="44"/>
       <c r="D7" s="1">
         <v>15.55</v>
       </c>
@@ -1807,10 +1814,10 @@
       <c r="H7" s="1">
         <v>17.849</v>
       </c>
-      <c r="I7" s="51">
+      <c r="I7" s="44">
         <v>72.760000000000005</v>
       </c>
-      <c r="J7" s="51"/>
+      <c r="J7" s="44"/>
       <c r="K7" s="1">
         <v>7.34</v>
       </c>
@@ -1820,10 +1827,10 @@
       <c r="M7" s="1">
         <v>2.48</v>
       </c>
-      <c r="N7" s="51">
+      <c r="N7" s="44">
         <v>90.37</v>
       </c>
-      <c r="O7" s="51"/>
+      <c r="O7" s="44"/>
       <c r="P7" s="1">
         <v>30.49</v>
       </c>
@@ -1833,10 +1840,10 @@
       <c r="R7" s="1">
         <v>5.29</v>
       </c>
-      <c r="S7" s="51">
+      <c r="S7" s="44">
         <v>39.22</v>
       </c>
-      <c r="T7" s="51"/>
+      <c r="T7" s="44"/>
       <c r="U7" s="1">
         <v>9.52</v>
       </c>
@@ -1846,14 +1853,14 @@
       <c r="W7" s="1">
         <v>4.32</v>
       </c>
-      <c r="X7" s="51">
+      <c r="X7" s="44">
         <v>82.64</v>
       </c>
-      <c r="AA7" s="49"/>
+      <c r="AA7" s="42"/>
       <c r="AB7" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC7" s="46"/>
+        <v>58</v>
+      </c>
+      <c r="AC7" s="50"/>
       <c r="AD7" s="14">
         <v>6.61</v>
       </c>
@@ -1863,7 +1870,7 @@
       <c r="AF7" s="15">
         <v>2.0299999999999998</v>
       </c>
-      <c r="AG7" s="46"/>
+      <c r="AG7" s="50"/>
       <c r="AH7" s="14">
         <v>26.39</v>
       </c>
@@ -1873,7 +1880,7 @@
       <c r="AJ7" s="5">
         <v>3.17</v>
       </c>
-      <c r="AK7" s="46"/>
+      <c r="AK7" s="50"/>
       <c r="AL7" s="14">
         <v>10.53</v>
       </c>
@@ -1883,11 +1890,11 @@
       <c r="AN7" s="16">
         <v>3.96</v>
       </c>
-      <c r="AW7" s="47" t="s">
+      <c r="AW7" s="43" t="s">
         <v>1</v>
       </c>
       <c r="AX7" s="24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY7" s="25">
         <v>94.58</v>
@@ -1895,18 +1902,18 @@
       <c r="AZ7" s="26">
         <v>12.401999999999999</v>
       </c>
-      <c r="BC7" s="48"/>
+      <c r="BC7" s="41"/>
       <c r="BD7" s="24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BE7" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BF7" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BG7" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BJ7" s="38" t="s">
         <v>1</v>
@@ -1925,11 +1932,11 @@
       </c>
     </row>
     <row r="8" spans="1:66" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" s="51"/>
+      <c r="A8" s="44"/>
       <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="51"/>
+      <c r="C8" s="44"/>
       <c r="D8" s="1">
         <v>19.11</v>
       </c>
@@ -1945,8 +1952,8 @@
       <c r="H8" s="1">
         <v>20.038900000000002</v>
       </c>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
       <c r="K8" s="1">
         <v>8.69</v>
       </c>
@@ -1956,8 +1963,8 @@
       <c r="M8" s="1">
         <v>3.84</v>
       </c>
-      <c r="N8" s="51"/>
-      <c r="O8" s="51"/>
+      <c r="N8" s="44"/>
+      <c r="O8" s="44"/>
       <c r="P8" s="1">
         <v>31.8</v>
       </c>
@@ -1967,8 +1974,8 @@
       <c r="R8" s="1">
         <v>8.1999999999999993</v>
       </c>
-      <c r="S8" s="51"/>
-      <c r="T8" s="51"/>
+      <c r="S8" s="44"/>
+      <c r="T8" s="44"/>
       <c r="U8" s="1">
         <v>21.05</v>
       </c>
@@ -1978,14 +1985,14 @@
       <c r="W8" s="1">
         <v>14.75</v>
       </c>
-      <c r="X8" s="51"/>
-      <c r="AA8" s="47" t="s">
+      <c r="X8" s="44"/>
+      <c r="AA8" s="43" t="s">
         <v>1</v>
       </c>
       <c r="AB8" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC8" s="44">
+        <v>24</v>
+      </c>
+      <c r="AC8" s="51">
         <v>26.95</v>
       </c>
       <c r="AD8" s="13">
@@ -1997,7 +2004,7 @@
       <c r="AF8" s="11">
         <v>2.98</v>
       </c>
-      <c r="AG8" s="44">
+      <c r="AG8" s="51">
         <v>19.18</v>
       </c>
       <c r="AH8" s="13">
@@ -2009,7 +2016,7 @@
       <c r="AJ8" s="11">
         <v>1.01</v>
       </c>
-      <c r="AK8" s="44">
+      <c r="AK8" s="51">
         <v>8.77</v>
       </c>
       <c r="AL8" s="13">
@@ -2021,9 +2028,9 @@
       <c r="AN8" s="13">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AW8" s="48"/>
+      <c r="AW8" s="41"/>
       <c r="AX8" s="24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AY8" s="25">
         <v>6743.49</v>
@@ -2031,18 +2038,18 @@
       <c r="AZ8" s="26">
         <v>114.9687</v>
       </c>
-      <c r="BC8" s="49"/>
+      <c r="BC8" s="42"/>
       <c r="BD8" s="23" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BE8" s="33" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BF8" s="37" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BG8" s="37" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BK8" s="40">
         <v>61.54</v>
@@ -2058,11 +2065,11 @@
       </c>
     </row>
     <row r="9" spans="1:66" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="51"/>
+      <c r="A9" s="44"/>
       <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="51"/>
+      <c r="C9" s="44"/>
       <c r="D9" s="1">
         <v>14.07</v>
       </c>
@@ -2078,8 +2085,8 @@
       <c r="H9" s="1">
         <v>22.114799999999999</v>
       </c>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
       <c r="K9" s="1">
         <v>6.61</v>
       </c>
@@ -2089,8 +2096,8 @@
       <c r="M9" s="1">
         <v>2.0299999999999998</v>
       </c>
-      <c r="N9" s="51"/>
-      <c r="O9" s="51"/>
+      <c r="N9" s="44"/>
+      <c r="O9" s="44"/>
       <c r="P9" s="1">
         <v>26.39</v>
       </c>
@@ -2100,8 +2107,8 @@
       <c r="R9" s="1">
         <v>3.17</v>
       </c>
-      <c r="S9" s="51"/>
-      <c r="T9" s="51"/>
+      <c r="S9" s="44"/>
+      <c r="T9" s="44"/>
       <c r="U9" s="1">
         <v>10.53</v>
       </c>
@@ -2111,12 +2118,12 @@
       <c r="W9" s="1">
         <v>3.96</v>
       </c>
-      <c r="X9" s="51"/>
-      <c r="AA9" s="48"/>
+      <c r="X9" s="44"/>
+      <c r="AA9" s="41"/>
       <c r="AB9" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="AC9" s="45"/>
+        <v>23</v>
+      </c>
+      <c r="AC9" s="49"/>
       <c r="AD9" s="12">
         <v>16.77</v>
       </c>
@@ -2126,7 +2133,7 @@
       <c r="AF9" s="8">
         <v>7.6</v>
       </c>
-      <c r="AG9" s="45"/>
+      <c r="AG9" s="49"/>
       <c r="AH9" s="12">
         <v>22.3</v>
       </c>
@@ -2136,7 +2143,7 @@
       <c r="AJ9" s="8">
         <v>8.11</v>
       </c>
-      <c r="AK9" s="45"/>
+      <c r="AK9" s="49"/>
       <c r="AL9" s="12">
         <v>9.52</v>
       </c>
@@ -2146,9 +2153,9 @@
       <c r="AN9" s="12">
         <v>3.57</v>
       </c>
-      <c r="AW9" s="48"/>
+      <c r="AW9" s="41"/>
       <c r="AX9" s="24" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AY9" s="25">
         <v>7320.52</v>
@@ -2156,17 +2163,17 @@
       <c r="AZ9" s="26">
         <v>113.2599</v>
       </c>
-      <c r="BC9" s="48" t="s">
+      <c r="BC9" s="41" t="s">
         <v>13</v>
       </c>
       <c r="BD9" s="24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE9" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BF9" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BG9" s="6">
         <v>0.157</v>
@@ -2189,13 +2196,13 @@
       </c>
     </row>
     <row r="10" spans="1:66" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="51" t="s">
+      <c r="A10" s="44" t="s">
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="51">
+      <c r="C10" s="44">
         <v>19.93</v>
       </c>
       <c r="D10" s="1">
@@ -2213,7 +2220,7 @@
       <c r="H10">
         <v>12.401999999999999</v>
       </c>
-      <c r="J10" s="51">
+      <c r="J10" s="44">
         <v>25.95</v>
       </c>
       <c r="K10" s="1">
@@ -2225,7 +2232,7 @@
       <c r="M10" s="1">
         <v>2.98</v>
       </c>
-      <c r="O10" s="51">
+      <c r="O10" s="44">
         <v>19.18</v>
       </c>
       <c r="P10">
@@ -2237,7 +2244,7 @@
       <c r="R10" s="1">
         <v>1.01</v>
       </c>
-      <c r="T10" s="51">
+      <c r="T10" s="44">
         <v>8.77</v>
       </c>
       <c r="U10">
@@ -2249,11 +2256,11 @@
       <c r="W10">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AA10" s="48"/>
+      <c r="AA10" s="41"/>
       <c r="AB10" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC10" s="45"/>
+        <v>22</v>
+      </c>
+      <c r="AC10" s="49"/>
       <c r="AD10" s="12">
         <v>13.83</v>
       </c>
@@ -2263,7 +2270,7 @@
       <c r="AF10" s="8">
         <v>3.8</v>
       </c>
-      <c r="AG10" s="45"/>
+      <c r="AG10" s="49"/>
       <c r="AH10" s="12">
         <v>22.62</v>
       </c>
@@ -2273,7 +2280,7 @@
       <c r="AJ10" s="8">
         <v>7.91</v>
       </c>
-      <c r="AK10" s="45"/>
+      <c r="AK10" s="49"/>
       <c r="AL10" s="12">
         <v>8.02</v>
       </c>
@@ -2283,28 +2290,28 @@
       <c r="AN10" s="12">
         <v>4.4000000000000004</v>
       </c>
-      <c r="AW10" s="49"/>
+      <c r="AW10" s="42"/>
       <c r="AX10" s="23" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="AY10" s="27">
-        <v>3609.91</v>
+        <v>1804.96</v>
       </c>
       <c r="AZ10" s="28">
         <v>168.54599999999999</v>
       </c>
-      <c r="BC10" s="48"/>
+      <c r="BC10" s="41"/>
       <c r="BD10" s="24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BE10" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BF10" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BG10" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BK10" s="40">
         <f>BK9/BK7*100</f>
@@ -2324,11 +2331,11 @@
       </c>
     </row>
     <row r="11" spans="1:66" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="51"/>
+      <c r="A11" s="44"/>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="51"/>
+      <c r="C11" s="44"/>
       <c r="D11">
         <v>17.03</v>
       </c>
@@ -2344,7 +2351,7 @@
       <c r="H11">
         <v>114.9687</v>
       </c>
-      <c r="J11" s="51"/>
+      <c r="J11" s="44"/>
       <c r="K11">
         <v>16.77</v>
       </c>
@@ -2354,7 +2361,7 @@
       <c r="M11">
         <v>7.6</v>
       </c>
-      <c r="O11" s="51"/>
+      <c r="O11" s="44"/>
       <c r="P11" s="1">
         <v>22.3</v>
       </c>
@@ -2364,7 +2371,7 @@
       <c r="R11" s="1">
         <v>8.11</v>
       </c>
-      <c r="T11" s="51"/>
+      <c r="T11" s="44"/>
       <c r="U11" s="1">
         <v>9.52</v>
       </c>
@@ -2374,11 +2381,11 @@
       <c r="W11" s="1">
         <v>3.57</v>
       </c>
-      <c r="AA11" s="49"/>
+      <c r="AA11" s="42"/>
       <c r="AB11" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC11" s="46"/>
+        <v>58</v>
+      </c>
+      <c r="AC11" s="50"/>
       <c r="AD11" s="14">
         <v>5.14</v>
       </c>
@@ -2388,7 +2395,7 @@
       <c r="AF11" s="15">
         <v>0</v>
       </c>
-      <c r="AG11" s="46"/>
+      <c r="AG11" s="50"/>
       <c r="AH11" s="14">
         <v>14.1</v>
       </c>
@@ -2398,7 +2405,7 @@
       <c r="AJ11" s="15">
         <v>0.81</v>
       </c>
-      <c r="AK11" s="46"/>
+      <c r="AK11" s="50"/>
       <c r="AL11" s="14">
         <v>4.01</v>
       </c>
@@ -2408,11 +2415,11 @@
       <c r="AN11" s="14">
         <v>0</v>
       </c>
-      <c r="AW11" s="47" t="s">
+      <c r="AW11" s="43" t="s">
         <v>13</v>
       </c>
       <c r="AX11" s="24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY11" s="25">
         <v>95.45</v>
@@ -2420,18 +2427,18 @@
       <c r="AZ11" s="26">
         <v>3.6791999999999998</v>
       </c>
-      <c r="BC11" s="49"/>
+      <c r="BC11" s="42"/>
       <c r="BD11" s="23" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BE11" s="16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BF11" s="37" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BG11" s="37" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="BJ11" s="38" t="s">
         <v>13</v>
@@ -2450,11 +2457,11 @@
       </c>
     </row>
     <row r="12" spans="1:66" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="51"/>
+      <c r="A12" s="44"/>
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="51"/>
+      <c r="C12" s="44"/>
       <c r="D12">
         <v>15.5</v>
       </c>
@@ -2470,7 +2477,7 @@
       <c r="H12">
         <v>113.2599</v>
       </c>
-      <c r="J12" s="51"/>
+      <c r="J12" s="44"/>
       <c r="K12" s="1">
         <v>13.83</v>
       </c>
@@ -2480,7 +2487,7 @@
       <c r="M12">
         <v>3.8</v>
       </c>
-      <c r="O12" s="51"/>
+      <c r="O12" s="44"/>
       <c r="P12">
         <v>22.62</v>
       </c>
@@ -2490,7 +2497,7 @@
       <c r="R12" s="1">
         <v>7.91</v>
       </c>
-      <c r="T12" s="51"/>
+      <c r="T12" s="44"/>
       <c r="U12">
         <v>8.02</v>
       </c>
@@ -2500,13 +2507,13 @@
       <c r="W12" s="1">
         <v>4.4000000000000004</v>
       </c>
-      <c r="AA12" s="47" t="s">
+      <c r="AA12" s="43" t="s">
         <v>13</v>
       </c>
       <c r="AB12" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC12" s="44">
+        <v>24</v>
+      </c>
+      <c r="AC12" s="51">
         <v>28.64</v>
       </c>
       <c r="AD12" s="13">
@@ -2518,7 +2525,7 @@
       <c r="AF12" s="11">
         <v>1.2</v>
       </c>
-      <c r="AG12" s="44">
+      <c r="AG12" s="51">
         <v>40.82</v>
       </c>
       <c r="AH12" s="13">
@@ -2530,7 +2537,7 @@
       <c r="AJ12" s="11">
         <v>1.66</v>
       </c>
-      <c r="AK12" s="44">
+      <c r="AK12" s="51">
         <v>16.04</v>
       </c>
       <c r="AL12" s="13">
@@ -2542,9 +2549,9 @@
       <c r="AN12" s="13">
         <v>0.3</v>
       </c>
-      <c r="AW12" s="48"/>
+      <c r="AW12" s="41"/>
       <c r="AX12" s="24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AY12" s="25">
         <v>3620.41</v>
@@ -2552,20 +2559,20 @@
       <c r="AZ12" s="26">
         <v>26.883299999999998</v>
       </c>
-      <c r="BC12" s="48" t="s">
+      <c r="BC12" s="41" t="s">
         <v>20</v>
       </c>
       <c r="BD12" s="24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE12" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="BF12" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="BG12" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="BK12" s="40">
         <v>46.62</v>
@@ -2581,11 +2588,11 @@
       </c>
     </row>
     <row r="13" spans="1:66" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="51"/>
+      <c r="A13" s="44"/>
       <c r="B13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="51"/>
+      <c r="C13" s="44"/>
       <c r="D13">
         <v>11.66</v>
       </c>
@@ -2601,7 +2608,7 @@
       <c r="H13">
         <v>17.3841</v>
       </c>
-      <c r="J13" s="51"/>
+      <c r="J13" s="44"/>
       <c r="K13">
         <v>8.1999999999999993</v>
       </c>
@@ -2611,7 +2618,7 @@
       <c r="M13">
         <v>1.49</v>
       </c>
-      <c r="O13" s="51"/>
+      <c r="O13" s="44"/>
       <c r="P13">
         <v>20.16</v>
       </c>
@@ -2621,7 +2628,7 @@
       <c r="R13">
         <v>3.65</v>
       </c>
-      <c r="T13" s="51"/>
+      <c r="T13" s="44"/>
       <c r="U13" s="1">
         <v>5.76</v>
       </c>
@@ -2631,11 +2638,11 @@
       <c r="W13" s="1">
         <v>0.82</v>
       </c>
-      <c r="AA13" s="48"/>
+      <c r="AA13" s="41"/>
       <c r="AB13" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="AC13" s="45"/>
+        <v>23</v>
+      </c>
+      <c r="AC13" s="49"/>
       <c r="AD13" s="12">
         <v>31.46</v>
       </c>
@@ -2645,7 +2652,7 @@
       <c r="AF13" s="8">
         <v>23.16</v>
       </c>
-      <c r="AG13" s="45"/>
+      <c r="AG13" s="49"/>
       <c r="AH13" s="12">
         <v>48.2</v>
       </c>
@@ -2655,7 +2662,7 @@
       <c r="AJ13" s="8">
         <v>22.16</v>
       </c>
-      <c r="AK13" s="45"/>
+      <c r="AK13" s="49"/>
       <c r="AL13" s="12">
         <v>28.07</v>
       </c>
@@ -2665,9 +2672,9 @@
       <c r="AN13" s="12">
         <v>21.19</v>
       </c>
-      <c r="AW13" s="48"/>
+      <c r="AW13" s="41"/>
       <c r="AX13" s="24" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AY13" s="25">
         <v>3227.44</v>
@@ -2675,18 +2682,18 @@
       <c r="AZ13" s="26">
         <v>24.215399999999999</v>
       </c>
-      <c r="BC13" s="48"/>
+      <c r="BC13" s="41"/>
       <c r="BD13" s="24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BE13" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="BF13" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="BG13" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="BK13" s="40">
         <f>BK12-BK11</f>
@@ -2706,11 +2713,11 @@
       </c>
     </row>
     <row r="14" spans="1:66" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="51"/>
+      <c r="A14" s="44"/>
       <c r="B14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="51"/>
+      <c r="C14" s="44"/>
       <c r="D14">
         <v>10.08</v>
       </c>
@@ -2726,10 +2733,10 @@
       <c r="H14">
         <v>147.7028</v>
       </c>
-      <c r="I14" s="51">
+      <c r="I14" s="44">
         <v>65.11</v>
       </c>
-      <c r="J14" s="51"/>
+      <c r="J14" s="44"/>
       <c r="K14">
         <v>7.47</v>
       </c>
@@ -2739,10 +2746,10 @@
       <c r="M14">
         <v>0</v>
       </c>
-      <c r="N14" s="51">
+      <c r="N14" s="44">
         <v>80.66</v>
       </c>
-      <c r="O14" s="51"/>
+      <c r="O14" s="44"/>
       <c r="P14">
         <v>17.05</v>
       </c>
@@ -2752,10 +2759,10 @@
       <c r="R14" s="1">
         <v>1.22</v>
       </c>
-      <c r="S14" s="51">
+      <c r="S14" s="44">
         <v>34.19</v>
       </c>
-      <c r="T14" s="51"/>
+      <c r="T14" s="44"/>
       <c r="U14">
         <v>4.76</v>
       </c>
@@ -2765,14 +2772,14 @@
       <c r="W14" s="1">
         <v>0.27</v>
       </c>
-      <c r="X14" s="51">
+      <c r="X14" s="44">
         <v>74.290000000000006</v>
       </c>
-      <c r="AA14" s="48"/>
+      <c r="AA14" s="41"/>
       <c r="AB14" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC14" s="45"/>
+        <v>22</v>
+      </c>
+      <c r="AC14" s="49"/>
       <c r="AD14" s="12">
         <v>53.12</v>
       </c>
@@ -2782,7 +2789,7 @@
       <c r="AF14" s="8">
         <v>40.82</v>
       </c>
-      <c r="AG14" s="45"/>
+      <c r="AG14" s="49"/>
       <c r="AH14" s="12">
         <v>66.89</v>
       </c>
@@ -2792,7 +2799,7 @@
       <c r="AJ14" s="8">
         <v>50.69</v>
       </c>
-      <c r="AK14" s="45"/>
+      <c r="AK14" s="49"/>
       <c r="AL14" s="12">
         <v>42.11</v>
       </c>
@@ -2802,28 +2809,28 @@
       <c r="AN14" s="12">
         <v>35.22</v>
       </c>
-      <c r="AW14" s="49"/>
+      <c r="AW14" s="42"/>
       <c r="AX14" s="23" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="AY14" s="27">
-        <v>4536.21</v>
+        <v>2268.11</v>
       </c>
       <c r="AZ14" s="28">
         <v>52.032899999999998</v>
       </c>
-      <c r="BC14" s="49"/>
+      <c r="BC14" s="42"/>
       <c r="BD14" s="23" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BE14" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="BF14" s="37" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="BG14" s="37" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="BK14" s="40">
         <f>BK13/BK11*100</f>
@@ -2843,11 +2850,11 @@
       </c>
     </row>
     <row r="15" spans="1:66" ht="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="51"/>
+      <c r="A15" s="44"/>
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="51"/>
+      <c r="C15" s="44"/>
       <c r="D15">
         <v>9.15</v>
       </c>
@@ -2863,8 +2870,8 @@
       <c r="H15">
         <v>159.09700000000001</v>
       </c>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
       <c r="K15">
         <v>5.88</v>
       </c>
@@ -2874,8 +2881,8 @@
       <c r="M15">
         <v>0</v>
       </c>
-      <c r="N15" s="51"/>
-      <c r="O15" s="51"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="44"/>
       <c r="P15">
         <v>16.07</v>
       </c>
@@ -2885,8 +2892,8 @@
       <c r="R15" s="1">
         <v>1.42</v>
       </c>
-      <c r="S15" s="51"/>
-      <c r="T15" s="51"/>
+      <c r="S15" s="44"/>
+      <c r="T15" s="44"/>
       <c r="U15" s="1">
         <v>5.26</v>
       </c>
@@ -2896,12 +2903,12 @@
       <c r="W15" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="X15" s="51"/>
-      <c r="AA15" s="49"/>
+      <c r="X15" s="44"/>
+      <c r="AA15" s="42"/>
       <c r="AB15" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC15" s="46"/>
+        <v>58</v>
+      </c>
+      <c r="AC15" s="50"/>
       <c r="AD15" s="14">
         <v>10.039999999999999</v>
       </c>
@@ -2911,7 +2918,7 @@
       <c r="AF15" s="15">
         <v>0.69</v>
       </c>
-      <c r="AG15" s="46"/>
+      <c r="AG15" s="50"/>
       <c r="AH15" s="16">
         <v>30.82</v>
       </c>
@@ -2921,7 +2928,7 @@
       <c r="AJ15" s="5">
         <v>1.1100000000000001</v>
       </c>
-      <c r="AK15" s="46"/>
+      <c r="AK15" s="50"/>
       <c r="AL15" s="14">
         <v>7.52</v>
       </c>
@@ -2931,11 +2938,11 @@
       <c r="AN15" s="14">
         <v>0</v>
       </c>
-      <c r="AW15" s="47" t="s">
+      <c r="AW15" s="43" t="s">
         <v>20</v>
       </c>
       <c r="AX15" s="24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY15" s="25">
         <v>514.66999999999996</v>
@@ -2960,11 +2967,11 @@
       </c>
     </row>
     <row r="16" spans="1:66" ht="15" x14ac:dyDescent="0.2">
-      <c r="A16" s="51"/>
+      <c r="A16" s="44"/>
       <c r="B16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="51"/>
+      <c r="C16" s="44"/>
       <c r="D16">
         <v>7.89</v>
       </c>
@@ -2980,8 +2987,8 @@
       <c r="H16">
         <v>168.54599999999999</v>
       </c>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
       <c r="K16">
         <v>5.14</v>
       </c>
@@ -2991,8 +2998,8 @@
       <c r="M16">
         <v>0</v>
       </c>
-      <c r="N16" s="51"/>
-      <c r="O16" s="51"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="44"/>
       <c r="P16">
         <v>14.1</v>
       </c>
@@ -3002,8 +3009,8 @@
       <c r="R16" s="1">
         <v>0.81</v>
       </c>
-      <c r="S16" s="51"/>
-      <c r="T16" s="51"/>
+      <c r="S16" s="44"/>
+      <c r="T16" s="44"/>
       <c r="U16">
         <v>4.01</v>
       </c>
@@ -3013,14 +3020,14 @@
       <c r="W16" s="1">
         <v>0</v>
       </c>
-      <c r="X16" s="51"/>
-      <c r="AA16" s="47" t="s">
+      <c r="X16" s="44"/>
+      <c r="AA16" s="43" t="s">
         <v>20</v>
       </c>
       <c r="AB16" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC16" s="44">
+        <v>24</v>
+      </c>
+      <c r="AC16" s="51">
         <v>38.07</v>
       </c>
       <c r="AD16" s="13">
@@ -3032,7 +3039,7 @@
       <c r="AF16" s="11">
         <v>5.14</v>
       </c>
-      <c r="AG16" s="44">
+      <c r="AG16" s="51">
         <v>56.89</v>
       </c>
       <c r="AH16" s="13">
@@ -3044,7 +3051,7 @@
       <c r="AJ16" s="11">
         <v>6.84</v>
       </c>
-      <c r="AK16" s="44">
+      <c r="AK16" s="51">
         <v>39.85</v>
       </c>
       <c r="AL16" s="13">
@@ -3056,9 +3063,9 @@
       <c r="AN16" s="13">
         <v>5.42</v>
       </c>
-      <c r="AW16" s="48"/>
+      <c r="AW16" s="41"/>
       <c r="AX16" s="24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AY16" s="25">
         <v>2260.0300000000002</v>
@@ -3080,13 +3087,13 @@
       </c>
     </row>
     <row r="17" spans="1:66" ht="15" x14ac:dyDescent="0.2">
-      <c r="A17" s="51" t="s">
+      <c r="A17" s="44" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="51">
+      <c r="C17" s="44">
         <v>29.96</v>
       </c>
       <c r="D17">
@@ -3104,7 +3111,7 @@
       <c r="H17">
         <v>3.6791999999999998</v>
       </c>
-      <c r="J17" s="51">
+      <c r="J17" s="44">
         <v>28.64</v>
       </c>
       <c r="K17">
@@ -3116,7 +3123,7 @@
       <c r="M17">
         <v>1.2</v>
       </c>
-      <c r="O17" s="51">
+      <c r="O17" s="44">
         <v>40.82</v>
       </c>
       <c r="P17">
@@ -3128,7 +3135,7 @@
       <c r="R17" s="1">
         <v>1.66</v>
       </c>
-      <c r="T17" s="51">
+      <c r="T17" s="44">
         <v>16.04</v>
       </c>
       <c r="U17">
@@ -3140,11 +3147,11 @@
       <c r="W17" s="1">
         <v>0.3</v>
       </c>
-      <c r="AA17" s="48"/>
+      <c r="AA17" s="41"/>
       <c r="AB17" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="AC17" s="45"/>
+        <v>23</v>
+      </c>
+      <c r="AC17" s="49"/>
       <c r="AD17" s="12">
         <v>26.44</v>
       </c>
@@ -3154,7 +3161,7 @@
       <c r="AF17" s="8">
         <v>14.03</v>
       </c>
-      <c r="AG17" s="45"/>
+      <c r="AG17" s="49"/>
       <c r="AH17" s="12">
         <v>61.97</v>
       </c>
@@ -3164,7 +3171,7 @@
       <c r="AJ17" s="8">
         <v>26.62</v>
       </c>
-      <c r="AK17" s="45"/>
+      <c r="AK17" s="49"/>
       <c r="AL17" s="12">
         <v>36.590000000000003</v>
       </c>
@@ -3174,9 +3181,9 @@
       <c r="AN17" s="12">
         <v>18.75</v>
       </c>
-      <c r="AW17" s="48"/>
+      <c r="AW17" s="41"/>
       <c r="AX17" s="24" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AY17" s="25">
         <v>3219.47</v>
@@ -3202,11 +3209,11 @@
       </c>
     </row>
     <row r="18" spans="1:66" ht="15" x14ac:dyDescent="0.2">
-      <c r="A18" s="51"/>
+      <c r="A18" s="44"/>
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="51"/>
+      <c r="C18" s="44"/>
       <c r="D18">
         <v>36.31</v>
       </c>
@@ -3222,7 +3229,7 @@
       <c r="H18">
         <v>26.883299999999998</v>
       </c>
-      <c r="J18" s="51"/>
+      <c r="J18" s="44"/>
       <c r="K18">
         <v>31.46</v>
       </c>
@@ -3232,7 +3239,7 @@
       <c r="M18">
         <v>23.16</v>
       </c>
-      <c r="O18" s="51"/>
+      <c r="O18" s="44"/>
       <c r="P18">
         <v>48.2</v>
       </c>
@@ -3242,7 +3249,7 @@
       <c r="R18" s="1">
         <v>22.16</v>
       </c>
-      <c r="T18" s="51"/>
+      <c r="T18" s="44"/>
       <c r="U18">
         <v>28.07</v>
       </c>
@@ -3252,11 +3259,11 @@
       <c r="W18" s="1">
         <v>21.19</v>
       </c>
-      <c r="AA18" s="48"/>
+      <c r="AA18" s="41"/>
       <c r="AB18" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC18" s="45"/>
+        <v>22</v>
+      </c>
+      <c r="AC18" s="49"/>
       <c r="AD18" s="12">
         <v>34.39</v>
       </c>
@@ -3266,7 +3273,7 @@
       <c r="AF18" s="8">
         <v>19.96</v>
       </c>
-      <c r="AG18" s="45"/>
+      <c r="AG18" s="49"/>
       <c r="AH18" s="12">
         <v>63.28</v>
       </c>
@@ -3276,7 +3283,7 @@
       <c r="AJ18" s="8">
         <v>30.04</v>
       </c>
-      <c r="AK18" s="45"/>
+      <c r="AK18" s="49"/>
       <c r="AL18" s="12">
         <v>38.85</v>
       </c>
@@ -3286,12 +3293,12 @@
       <c r="AN18" s="12">
         <v>20</v>
       </c>
-      <c r="AW18" s="49"/>
+      <c r="AW18" s="42"/>
       <c r="AX18" s="23" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="AY18" s="27">
-        <v>4521.08</v>
+        <v>2260.54</v>
       </c>
       <c r="AZ18" s="28">
         <v>21.763400000000001</v>
@@ -3314,11 +3321,11 @@
       </c>
     </row>
     <row r="19" spans="1:66" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19" s="51"/>
+      <c r="A19" s="44"/>
       <c r="B19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="51"/>
+      <c r="C19" s="44"/>
       <c r="D19">
         <v>55.31</v>
       </c>
@@ -3334,7 +3341,7 @@
       <c r="H19">
         <v>24.215399999999999</v>
       </c>
-      <c r="J19" s="51"/>
+      <c r="J19" s="44"/>
       <c r="K19">
         <v>53.12</v>
       </c>
@@ -3344,7 +3351,7 @@
       <c r="M19">
         <v>40.82</v>
       </c>
-      <c r="O19" s="51"/>
+      <c r="O19" s="44"/>
       <c r="P19">
         <v>66.89</v>
       </c>
@@ -3354,7 +3361,7 @@
       <c r="R19" s="1">
         <v>50.69</v>
       </c>
-      <c r="T19" s="51"/>
+      <c r="T19" s="44"/>
       <c r="U19">
         <v>42.11</v>
       </c>
@@ -3364,11 +3371,11 @@
       <c r="W19">
         <v>35.22</v>
       </c>
-      <c r="AA19" s="49"/>
+      <c r="AA19" s="42"/>
       <c r="AB19" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC19" s="46"/>
+        <v>58</v>
+      </c>
+      <c r="AC19" s="50"/>
       <c r="AD19" s="14">
         <v>10.28</v>
       </c>
@@ -3378,7 +3385,7 @@
       <c r="AF19" s="15">
         <v>1.19</v>
       </c>
-      <c r="AG19" s="46"/>
+      <c r="AG19" s="50"/>
       <c r="AH19" s="14">
         <v>47.54</v>
       </c>
@@ -3388,7 +3395,7 @@
       <c r="AJ19" s="15">
         <v>4.18</v>
       </c>
-      <c r="AK19" s="46"/>
+      <c r="AK19" s="50"/>
       <c r="AL19" s="14">
         <v>25.06</v>
       </c>
@@ -3400,11 +3407,11 @@
       </c>
     </row>
     <row r="20" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A20" s="51"/>
+      <c r="A20" s="44"/>
       <c r="B20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="51"/>
+      <c r="C20" s="44"/>
       <c r="D20">
         <v>20.87</v>
       </c>
@@ -3420,7 +3427,7 @@
       <c r="H20">
         <v>2.9369000000000001</v>
       </c>
-      <c r="J20" s="51"/>
+      <c r="J20" s="44"/>
       <c r="K20">
         <v>14.93</v>
       </c>
@@ -3430,7 +3437,7 @@
       <c r="M20">
         <v>1.54</v>
       </c>
-      <c r="O20" s="51"/>
+      <c r="O20" s="44"/>
       <c r="P20">
         <v>36.72</v>
       </c>
@@ -3440,7 +3447,7 @@
       <c r="R20">
         <v>5.26</v>
       </c>
-      <c r="T20" s="51"/>
+      <c r="T20" s="44"/>
       <c r="U20">
         <v>8.77</v>
       </c>
@@ -3452,11 +3459,11 @@
       </c>
     </row>
     <row r="21" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A21" s="51"/>
+      <c r="A21" s="44"/>
       <c r="B21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="51"/>
+      <c r="C21" s="44"/>
       <c r="D21">
         <v>18.89</v>
       </c>
@@ -3472,10 +3479,10 @@
       <c r="H21">
         <v>22.941400000000002</v>
       </c>
-      <c r="I21" s="51">
+      <c r="I21" s="44">
         <v>48.81</v>
       </c>
-      <c r="J21" s="51"/>
+      <c r="J21" s="44"/>
       <c r="K21">
         <v>12.48</v>
       </c>
@@ -3485,10 +3492,10 @@
       <c r="M21">
         <v>1.03</v>
       </c>
-      <c r="N21" s="51">
+      <c r="N21" s="44">
         <v>67.09</v>
       </c>
-      <c r="O21" s="51"/>
+      <c r="O21" s="44"/>
       <c r="P21">
         <v>34.590000000000003</v>
       </c>
@@ -3498,10 +3505,10 @@
       <c r="R21">
         <v>2.2200000000000002</v>
       </c>
-      <c r="S21" s="51">
+      <c r="S21" s="44">
         <v>30.12</v>
       </c>
-      <c r="T21" s="51"/>
+      <c r="T21" s="44"/>
       <c r="U21">
         <v>8.02</v>
       </c>
@@ -3511,16 +3518,16 @@
       <c r="W21">
         <v>0</v>
       </c>
-      <c r="X21" s="51">
+      <c r="X21" s="44">
         <v>54.69</v>
       </c>
     </row>
     <row r="22" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A22" s="51"/>
+      <c r="A22" s="44"/>
       <c r="B22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="51"/>
+      <c r="C22" s="44"/>
       <c r="D22">
         <v>17.8</v>
       </c>
@@ -3536,8 +3543,8 @@
       <c r="H22">
         <v>23.260400000000001</v>
       </c>
-      <c r="I22" s="51"/>
-      <c r="J22" s="51"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
       <c r="K22">
         <v>10.89</v>
       </c>
@@ -3547,8 +3554,8 @@
       <c r="M22">
         <v>1.2</v>
       </c>
-      <c r="N22" s="51"/>
-      <c r="O22" s="51"/>
+      <c r="N22" s="44"/>
+      <c r="O22" s="44"/>
       <c r="P22">
         <v>33.61</v>
       </c>
@@ -3558,8 +3565,8 @@
       <c r="R22">
         <v>2.2200000000000002</v>
       </c>
-      <c r="S22" s="51"/>
-      <c r="T22" s="51"/>
+      <c r="S22" s="44"/>
+      <c r="T22" s="44"/>
       <c r="U22">
         <v>7.77</v>
       </c>
@@ -3569,14 +3576,14 @@
       <c r="W22">
         <v>0</v>
       </c>
-      <c r="X22" s="51"/>
+      <c r="X22" s="44"/>
     </row>
     <row r="23" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A23" s="51"/>
+      <c r="A23" s="44"/>
       <c r="B23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="51"/>
+      <c r="C23" s="44"/>
       <c r="D23">
         <v>16.43</v>
       </c>
@@ -3592,8 +3599,8 @@
       <c r="H23">
         <v>52.032899999999998</v>
       </c>
-      <c r="I23" s="51"/>
-      <c r="J23" s="51"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
       <c r="K23">
         <v>10.039999999999999</v>
       </c>
@@ -3603,8 +3610,8 @@
       <c r="M23">
         <v>0.69</v>
       </c>
-      <c r="N23" s="51"/>
-      <c r="O23" s="51"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="44"/>
       <c r="P23">
         <v>30.82</v>
       </c>
@@ -3614,8 +3621,8 @@
       <c r="R23">
         <v>1.1100000000000001</v>
       </c>
-      <c r="S23" s="51"/>
-      <c r="T23" s="51"/>
+      <c r="S23" s="44"/>
+      <c r="T23" s="44"/>
       <c r="U23">
         <v>7.52</v>
       </c>
@@ -3625,16 +3632,16 @@
       <c r="W23">
         <v>0</v>
       </c>
-      <c r="X23" s="51"/>
+      <c r="X23" s="44"/>
     </row>
     <row r="24" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A24" s="51" t="s">
+      <c r="A24" s="44" t="s">
         <v>20</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="51">
+      <c r="C24" s="44">
         <v>44.74</v>
       </c>
       <c r="D24">
@@ -3652,7 +3659,7 @@
       <c r="H24">
         <v>15.446099999999999</v>
       </c>
-      <c r="J24" s="51">
+      <c r="J24" s="44">
         <v>38.07</v>
       </c>
       <c r="K24">
@@ -3664,7 +3671,7 @@
       <c r="M24">
         <v>5.14</v>
       </c>
-      <c r="O24" s="51">
+      <c r="O24" s="44">
         <v>56.89</v>
       </c>
       <c r="P24">
@@ -3676,7 +3683,7 @@
       <c r="R24">
         <v>6.84</v>
       </c>
-      <c r="T24" s="51">
+      <c r="T24" s="44">
         <v>39.85</v>
       </c>
       <c r="U24">
@@ -3690,11 +3697,11 @@
       </c>
     </row>
     <row r="25" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A25" s="51"/>
+      <c r="A25" s="44"/>
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="51"/>
+      <c r="C25" s="44"/>
       <c r="D25">
         <v>40.53</v>
       </c>
@@ -3710,7 +3717,7 @@
       <c r="H25">
         <v>27.349599999999999</v>
       </c>
-      <c r="J25" s="51"/>
+      <c r="J25" s="44"/>
       <c r="K25">
         <v>26.44</v>
       </c>
@@ -3720,7 +3727,7 @@
       <c r="M25">
         <v>14.03</v>
       </c>
-      <c r="O25" s="51"/>
+      <c r="O25" s="44"/>
       <c r="P25">
         <v>61.97</v>
       </c>
@@ -3730,7 +3737,7 @@
       <c r="R25">
         <v>26.62</v>
       </c>
-      <c r="T25" s="51"/>
+      <c r="T25" s="44"/>
       <c r="U25">
         <v>36.590000000000003</v>
       </c>
@@ -3742,11 +3749,11 @@
       </c>
     </row>
     <row r="26" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A26" s="51"/>
+      <c r="A26" s="44"/>
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="51"/>
+      <c r="C26" s="44"/>
       <c r="D26">
         <v>45.02</v>
       </c>
@@ -3762,7 +3769,7 @@
       <c r="H26">
         <v>35.505099999999999</v>
       </c>
-      <c r="J26" s="51"/>
+      <c r="J26" s="44"/>
       <c r="K26">
         <v>34.39</v>
       </c>
@@ -3772,7 +3779,7 @@
       <c r="M26">
         <v>19.96</v>
       </c>
-      <c r="O26" s="51"/>
+      <c r="O26" s="44"/>
       <c r="P26">
         <v>63.28</v>
       </c>
@@ -3782,7 +3789,7 @@
       <c r="R26">
         <v>30.04</v>
       </c>
-      <c r="T26" s="51"/>
+      <c r="T26" s="44"/>
       <c r="U26">
         <v>38.85</v>
       </c>
@@ -3794,11 +3801,11 @@
       </c>
     </row>
     <row r="27" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A27" s="51"/>
+      <c r="A27" s="44"/>
       <c r="B27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C27" s="51"/>
+      <c r="C27" s="44"/>
       <c r="D27">
         <v>31.16</v>
       </c>
@@ -3814,7 +3821,7 @@
       <c r="H27">
         <v>1.3381000000000001</v>
       </c>
-      <c r="J27" s="51"/>
+      <c r="J27" s="44"/>
       <c r="K27">
         <v>12.97</v>
       </c>
@@ -3824,7 +3831,7 @@
       <c r="M27">
         <v>2.96</v>
       </c>
-      <c r="O27" s="51"/>
+      <c r="O27" s="44"/>
       <c r="P27">
         <v>53.28</v>
       </c>
@@ -3834,7 +3841,7 @@
       <c r="R27">
         <v>14.07</v>
       </c>
-      <c r="T27" s="51"/>
+      <c r="T27" s="44"/>
       <c r="U27">
         <v>34.590000000000003</v>
       </c>
@@ -3846,11 +3853,11 @@
       </c>
     </row>
     <row r="28" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A28" s="51"/>
+      <c r="A28" s="44"/>
       <c r="B28" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="51"/>
+      <c r="C28" s="44"/>
       <c r="D28">
         <v>28.31</v>
       </c>
@@ -3866,10 +3873,10 @@
       <c r="H28">
         <v>13.305</v>
       </c>
-      <c r="I28" s="51">
+      <c r="I28" s="44">
         <v>48.1</v>
       </c>
-      <c r="J28" s="51"/>
+      <c r="J28" s="44"/>
       <c r="K28">
         <v>11.75</v>
       </c>
@@ -3879,10 +3886,10 @@
       <c r="M28">
         <v>1.58</v>
       </c>
-      <c r="N28" s="51">
+      <c r="N28" s="44">
         <v>76.209999999999994</v>
       </c>
-      <c r="O28" s="51"/>
+      <c r="O28" s="44"/>
       <c r="P28">
         <v>50.16</v>
       </c>
@@ -3892,10 +3899,10 @@
       <c r="R28">
         <v>6.08</v>
       </c>
-      <c r="S28" s="51">
+      <c r="S28" s="44">
         <v>23.05</v>
       </c>
-      <c r="T28" s="51"/>
+      <c r="T28" s="44"/>
       <c r="U28">
         <v>28.82</v>
       </c>
@@ -3905,16 +3912,16 @@
       <c r="W28">
         <v>5</v>
       </c>
-      <c r="X28" s="51">
+      <c r="X28" s="44">
         <v>47.8</v>
       </c>
     </row>
     <row r="29" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A29" s="51"/>
+      <c r="A29" s="44"/>
       <c r="B29" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="51"/>
+      <c r="C29" s="44"/>
       <c r="D29">
         <v>27.66</v>
       </c>
@@ -3930,8 +3937,8 @@
       <c r="H29">
         <v>15.7463</v>
       </c>
-      <c r="I29" s="51"/>
-      <c r="J29" s="51"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="44"/>
       <c r="K29">
         <v>11.75</v>
       </c>
@@ -3941,8 +3948,8 @@
       <c r="M29">
         <v>1.78</v>
       </c>
-      <c r="N29" s="51"/>
-      <c r="O29" s="51"/>
+      <c r="N29" s="44"/>
+      <c r="O29" s="44"/>
       <c r="P29">
         <v>49.18</v>
       </c>
@@ -3952,8 +3959,8 @@
       <c r="R29">
         <v>5.7</v>
       </c>
-      <c r="S29" s="51"/>
-      <c r="T29" s="51"/>
+      <c r="S29" s="44"/>
+      <c r="T29" s="44"/>
       <c r="U29">
         <v>27.32</v>
       </c>
@@ -3963,14 +3970,14 @@
       <c r="W29">
         <v>5.42</v>
       </c>
-      <c r="X29" s="51"/>
+      <c r="X29" s="44"/>
     </row>
     <row r="30" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A30" s="51"/>
+      <c r="A30" s="44"/>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="51"/>
+      <c r="C30" s="44"/>
       <c r="D30">
         <v>25.96</v>
       </c>
@@ -3986,8 +3993,8 @@
       <c r="H30">
         <v>21.763400000000001</v>
       </c>
-      <c r="I30" s="51"/>
-      <c r="J30" s="51"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="44"/>
       <c r="K30">
         <v>10.28</v>
       </c>
@@ -3997,8 +4004,8 @@
       <c r="M30">
         <v>1.19</v>
       </c>
-      <c r="N30" s="51"/>
-      <c r="O30" s="51"/>
+      <c r="N30" s="44"/>
+      <c r="O30" s="44"/>
       <c r="P30">
         <v>47.54</v>
       </c>
@@ -4008,8 +4015,8 @@
       <c r="R30">
         <v>4.18</v>
       </c>
-      <c r="S30" s="51"/>
-      <c r="T30" s="51"/>
+      <c r="S30" s="44"/>
+      <c r="T30" s="44"/>
       <c r="U30">
         <v>25.06</v>
       </c>
@@ -4019,23 +4026,23 @@
       <c r="W30">
         <v>3.75</v>
       </c>
-      <c r="X30" s="51"/>
+      <c r="X30" s="44"/>
     </row>
     <row r="34" spans="2:23" ht="15" x14ac:dyDescent="0.2">
       <c r="B34" s="2"/>
       <c r="C34" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C35" s="2">
         <v>15</v>
@@ -4049,7 +4056,7 @@
     </row>
     <row r="36" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C36" s="2">
         <v>17.22</v>
@@ -4061,18 +4068,18 @@
         <v>4.95</v>
       </c>
       <c r="U36" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="V36" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="W36" s="20" t="s">
         <v>49</v>
-      </c>
-      <c r="V36" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="W36" s="20" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="37" spans="2:23" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C37" s="2">
         <v>17.22</v>
@@ -4083,11 +4090,11 @@
       <c r="E37" s="2">
         <v>2.97</v>
       </c>
-      <c r="U37" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="V37" s="42"/>
-      <c r="W37" s="43"/>
+      <c r="U37" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="V37" s="45"/>
+      <c r="W37" s="46"/>
     </row>
     <row r="38" spans="2:23" ht="15.75" thickTop="1" x14ac:dyDescent="0.2">
       <c r="U38" s="12">
@@ -4125,13 +4132,13 @@
     <row r="41" spans="2:23" ht="15" x14ac:dyDescent="0.2">
       <c r="B41" s="22"/>
       <c r="C41" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="U41" s="14">
         <v>14.07</v>
@@ -4639,6 +4646,59 @@
     </row>
   </sheetData>
   <mergeCells count="69">
+    <mergeCell ref="AG3:AJ3"/>
+    <mergeCell ref="AK3:AN3"/>
+    <mergeCell ref="AG16:AG19"/>
+    <mergeCell ref="AK4:AK7"/>
+    <mergeCell ref="AK8:AK11"/>
+    <mergeCell ref="AK12:AK15"/>
+    <mergeCell ref="AK16:AK19"/>
+    <mergeCell ref="AW3:AW6"/>
+    <mergeCell ref="AW7:AW10"/>
+    <mergeCell ref="AW11:AW14"/>
+    <mergeCell ref="AW15:AW18"/>
+    <mergeCell ref="U37:W37"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AC4:AC7"/>
+    <mergeCell ref="AC8:AC11"/>
+    <mergeCell ref="AC12:AC15"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AA16:AA19"/>
+    <mergeCell ref="AA12:AA15"/>
+    <mergeCell ref="AC16:AC19"/>
+    <mergeCell ref="AG4:AG7"/>
+    <mergeCell ref="AG8:AG11"/>
+    <mergeCell ref="AG12:AG15"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="AA8:AA11"/>
+    <mergeCell ref="AA4:AA7"/>
+    <mergeCell ref="X14:X16"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="S7:S9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="T1:X1"/>
+    <mergeCell ref="T3:T9"/>
+    <mergeCell ref="T10:T16"/>
+    <mergeCell ref="S14:S16"/>
+    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J3:J9"/>
+    <mergeCell ref="O10:O16"/>
+    <mergeCell ref="C17:C23"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="N21:N23"/>
+    <mergeCell ref="O17:O23"/>
+    <mergeCell ref="A10:A16"/>
+    <mergeCell ref="C10:C16"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="J10:J16"/>
+    <mergeCell ref="O3:O9"/>
+    <mergeCell ref="N14:N16"/>
+    <mergeCell ref="N7:N9"/>
     <mergeCell ref="BC3:BC5"/>
     <mergeCell ref="BC6:BC8"/>
     <mergeCell ref="BC9:BC11"/>
@@ -4655,59 +4715,6 @@
     <mergeCell ref="J24:J30"/>
     <mergeCell ref="I28:I30"/>
     <mergeCell ref="S21:S23"/>
-    <mergeCell ref="A3:A9"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J3:J9"/>
-    <mergeCell ref="O10:O16"/>
-    <mergeCell ref="C17:C23"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="N21:N23"/>
-    <mergeCell ref="O17:O23"/>
-    <mergeCell ref="A10:A16"/>
-    <mergeCell ref="C10:C16"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="J10:J16"/>
-    <mergeCell ref="O3:O9"/>
-    <mergeCell ref="N14:N16"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="C3:C9"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="AA8:AA11"/>
-    <mergeCell ref="AA4:AA7"/>
-    <mergeCell ref="X14:X16"/>
-    <mergeCell ref="J1:N1"/>
-    <mergeCell ref="S7:S9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="T1:X1"/>
-    <mergeCell ref="T3:T9"/>
-    <mergeCell ref="T10:T16"/>
-    <mergeCell ref="S14:S16"/>
-    <mergeCell ref="AW3:AW6"/>
-    <mergeCell ref="AW7:AW10"/>
-    <mergeCell ref="AW11:AW14"/>
-    <mergeCell ref="AW15:AW18"/>
-    <mergeCell ref="U37:W37"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AC4:AC7"/>
-    <mergeCell ref="AC8:AC11"/>
-    <mergeCell ref="AC12:AC15"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AA16:AA19"/>
-    <mergeCell ref="AA12:AA15"/>
-    <mergeCell ref="AC16:AC19"/>
-    <mergeCell ref="AG4:AG7"/>
-    <mergeCell ref="AG8:AG11"/>
-    <mergeCell ref="AG12:AG15"/>
-    <mergeCell ref="AG3:AJ3"/>
-    <mergeCell ref="AK3:AN3"/>
-    <mergeCell ref="AG16:AG19"/>
-    <mergeCell ref="AK4:AK7"/>
-    <mergeCell ref="AK8:AK11"/>
-    <mergeCell ref="AK12:AK15"/>
-    <mergeCell ref="AK16:AK19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/stat/data.xlsx
+++ b/stat/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr-PC\Documents\Workspace\LLMHalluMiti\stat\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbybr\Documents\Workspace\LLMHalluMiti\stat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF5FB64F-CB79-4499-91A0-B00B58CBBBF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B619EFC8-0885-4134-A1AF-67CCC18C5E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="62">
   <si>
     <t>gpt-4o</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -152,10 +141,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>overall</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Method</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -268,6 +253,22 @@
   </si>
   <si>
     <t>MutRepair</t>
+  </si>
+  <si>
+    <t>RCR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RHR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OCR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>average</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1131,88 +1132,88 @@
         <v>11</v>
       </c>
       <c r="AA2" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AB2" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AC2" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD2" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE2" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG2" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="AH2" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI2" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK2" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="AL2" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM2" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="AN2" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="AQ2" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="AR2" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="AS2" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="AT2" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="AW2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="AX2" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="AY2" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="AZ2" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="BC2" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="BD2" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="BE2" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="AD2" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="AE2" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF2" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AG2" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH2" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="AI2" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AJ2" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AK2" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="AL2" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="AM2" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AN2" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AQ2" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="AR2" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="AS2" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="AT2" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="AW2" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="AX2" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="AY2" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="AZ2" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="BC2" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="BD2" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="BE2" s="35" t="s">
+      <c r="BF2" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="BF2" s="34" t="s">
+      <c r="BG2" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="BG2" s="36" t="s">
-        <v>53</v>
-      </c>
       <c r="BK2" s="39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="BL2" s="39" t="s">
         <v>17</v>
@@ -1340,13 +1341,13 @@
         <v>24</v>
       </c>
       <c r="BE3" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BF3" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BG3" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="BJ3" s="38" t="s">
         <v>0</v>
@@ -1488,13 +1489,13 @@
         <v>25</v>
       </c>
       <c r="BE4" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BF4" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BG4" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BK4" s="40">
         <v>69.05</v>
@@ -1612,7 +1613,7 @@
       </c>
       <c r="AW5" s="41"/>
       <c r="AX5" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AY5" s="25">
         <v>3623.59</v>
@@ -1622,16 +1623,16 @@
       </c>
       <c r="BC5" s="42"/>
       <c r="BD5" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="BE5" s="33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BF5" s="37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BG5" s="37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BK5" s="40">
         <f>BK4-BK3</f>
@@ -1753,7 +1754,7 @@
       </c>
       <c r="AW6" s="42"/>
       <c r="AX6" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AY6" s="27">
         <v>2095.5500000000002</v>
@@ -1768,13 +1769,13 @@
         <v>24</v>
       </c>
       <c r="BE6" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BF6" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BG6" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BK6" s="40">
         <f>BK5/BK3*100</f>
@@ -1858,7 +1859,7 @@
       </c>
       <c r="AA7" s="42"/>
       <c r="AB7" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC7" s="50"/>
       <c r="AD7" s="14">
@@ -1907,13 +1908,13 @@
         <v>25</v>
       </c>
       <c r="BE7" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BF7" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BG7" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BJ7" s="38" t="s">
         <v>1</v>
@@ -2040,16 +2041,16 @@
       </c>
       <c r="BC8" s="42"/>
       <c r="BD8" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="BE8" s="33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BF8" s="37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BG8" s="37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BK8" s="40">
         <v>61.54</v>
@@ -2155,7 +2156,7 @@
       </c>
       <c r="AW9" s="41"/>
       <c r="AX9" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AY9" s="25">
         <v>7320.52</v>
@@ -2170,10 +2171,10 @@
         <v>24</v>
       </c>
       <c r="BE9" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BF9" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BG9" s="6">
         <v>0.157</v>
@@ -2292,7 +2293,7 @@
       </c>
       <c r="AW10" s="42"/>
       <c r="AX10" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AY10" s="27">
         <v>1804.96</v>
@@ -2305,13 +2306,13 @@
         <v>25</v>
       </c>
       <c r="BE10" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BF10" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BG10" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BK10" s="40">
         <f>BK9/BK7*100</f>
@@ -2383,7 +2384,7 @@
       </c>
       <c r="AA11" s="42"/>
       <c r="AB11" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC11" s="50"/>
       <c r="AD11" s="14">
@@ -2429,16 +2430,16 @@
       </c>
       <c r="BC11" s="42"/>
       <c r="BD11" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="BE11" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BF11" s="37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BG11" s="37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BJ11" s="38" t="s">
         <v>13</v>
@@ -2566,13 +2567,13 @@
         <v>24</v>
       </c>
       <c r="BE12" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="BF12" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="BG12" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="BK12" s="40">
         <v>46.62</v>
@@ -2674,7 +2675,7 @@
       </c>
       <c r="AW13" s="41"/>
       <c r="AX13" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AY13" s="25">
         <v>3227.44</v>
@@ -2687,13 +2688,13 @@
         <v>25</v>
       </c>
       <c r="BE13" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="BF13" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="BG13" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="BK13" s="40">
         <f>BK12-BK11</f>
@@ -2811,7 +2812,7 @@
       </c>
       <c r="AW14" s="42"/>
       <c r="AX14" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AY14" s="27">
         <v>2268.11</v>
@@ -2821,16 +2822,16 @@
       </c>
       <c r="BC14" s="42"/>
       <c r="BD14" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="BE14" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="BF14" s="37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="BG14" s="37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="BK14" s="40">
         <f>BK13/BK11*100</f>
@@ -2906,7 +2907,7 @@
       <c r="X15" s="44"/>
       <c r="AA15" s="42"/>
       <c r="AB15" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC15" s="50"/>
       <c r="AD15" s="14">
@@ -3183,7 +3184,7 @@
       </c>
       <c r="AW17" s="41"/>
       <c r="AX17" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AY17" s="25">
         <v>3219.47</v>
@@ -3295,7 +3296,7 @@
       </c>
       <c r="AW18" s="42"/>
       <c r="AX18" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AY18" s="27">
         <v>2260.54</v>
@@ -3373,7 +3374,7 @@
       </c>
       <c r="AA19" s="42"/>
       <c r="AB19" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC19" s="50"/>
       <c r="AD19" s="14">
@@ -4031,18 +4032,18 @@
     <row r="34" spans="2:23" ht="15" x14ac:dyDescent="0.2">
       <c r="B34" s="2"/>
       <c r="C34" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C35" s="2">
         <v>15</v>
@@ -4056,7 +4057,7 @@
     </row>
     <row r="36" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C36" s="2">
         <v>17.22</v>
@@ -4068,18 +4069,18 @@
         <v>4.95</v>
       </c>
       <c r="U36" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="V36" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="V36" s="19" t="s">
+      <c r="W36" s="20" t="s">
         <v>48</v>
-      </c>
-      <c r="W36" s="20" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="37" spans="2:23" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C37" s="2">
         <v>17.22</v>
@@ -4091,7 +4092,7 @@
         <v>2.97</v>
       </c>
       <c r="U37" s="45" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="V37" s="45"/>
       <c r="W37" s="46"/>
@@ -4132,13 +4133,13 @@
     <row r="41" spans="2:23" ht="15" x14ac:dyDescent="0.2">
       <c r="B41" s="22"/>
       <c r="C41" s="12" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="U41" s="14">
         <v>14.07</v>
